--- a/output/wp_figures.xlsx
+++ b/output/wp_figures.xlsx
@@ -407,629 +407,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2" t="n">
-        <v>196.177</v>
+        <v>239.403</v>
       </c>
       <c r="C2" t="n">
-        <v>219.975</v>
+        <v>251.705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3" t="n">
-        <v>236.046</v>
+        <v>242.201</v>
       </c>
       <c r="C3" t="n">
-        <v>250.795</v>
+        <v>258.065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4" t="n">
-        <v>227.98</v>
+        <v>280.569</v>
       </c>
       <c r="C4" t="n">
-        <v>249.813</v>
+        <v>258.328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>225.1</v>
+        <v>225.855</v>
       </c>
       <c r="C5" t="n">
-        <v>229.726</v>
+        <v>213.497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>239.379</v>
+        <v>216.673</v>
       </c>
       <c r="C6" t="n">
-        <v>251.705</v>
+        <v>205.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>242.191</v>
+        <v>204.066</v>
       </c>
       <c r="C7" t="n">
-        <v>258.065</v>
+        <v>227.917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>280.555</v>
+        <v>200.837</v>
       </c>
       <c r="C8" t="n">
-        <v>258.328</v>
+        <v>213.803</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>225.839</v>
+        <v>192.455</v>
       </c>
       <c r="C9" t="n">
-        <v>213.497</v>
+        <v>199.517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>216.643</v>
+        <v>192.739</v>
       </c>
       <c r="C10" t="n">
-        <v>205.55</v>
+        <v>193.441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>204.03</v>
+        <v>190.623</v>
       </c>
       <c r="C11" t="n">
-        <v>227.917</v>
+        <v>191.353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>200.845</v>
+        <v>178.682</v>
       </c>
       <c r="C12" t="n">
-        <v>213.803</v>
+        <v>175.594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>192.463</v>
+        <v>186.832</v>
       </c>
       <c r="C13" t="n">
-        <v>199.517</v>
+        <v>176.586</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>192.741</v>
+        <v>181.701</v>
       </c>
       <c r="C14" t="n">
-        <v>193.441</v>
+        <v>175.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>190.631</v>
+        <v>181.204</v>
       </c>
       <c r="C15" t="n">
-        <v>191.353</v>
+        <v>174.701</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>178.687</v>
+        <v>236.171</v>
       </c>
       <c r="C16" t="n">
-        <v>175.594</v>
+        <v>199.743</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>186.835</v>
+        <v>225.23</v>
       </c>
       <c r="C17" t="n">
-        <v>176.586</v>
+        <v>182.394</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>181.713</v>
+        <v>203.475</v>
       </c>
       <c r="C18" t="n">
-        <v>175.65</v>
+        <v>193.999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>181.21</v>
+        <v>201.443</v>
       </c>
       <c r="C19" t="n">
-        <v>174.701</v>
+        <v>199.306</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>236.179</v>
+        <v>212.741</v>
       </c>
       <c r="C20" t="n">
-        <v>199.743</v>
+        <v>214.161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>225.245</v>
+        <v>230.801</v>
       </c>
       <c r="C21" t="n">
-        <v>182.394</v>
+        <v>217.438</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>203.482</v>
+        <v>214.254</v>
       </c>
       <c r="C22" t="n">
-        <v>193.999</v>
+        <v>240.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>201.447</v>
+        <v>245.27</v>
       </c>
       <c r="C23" t="n">
-        <v>199.306</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>212.743</v>
+        <v>211.323</v>
       </c>
       <c r="C24" t="n">
-        <v>214.161</v>
+        <v>294.615</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>230.81</v>
+        <v>309.775</v>
       </c>
       <c r="C25" t="n">
-        <v>217.438</v>
+        <v>249.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>214.257</v>
+        <v>252.349</v>
       </c>
       <c r="C26" t="n">
-        <v>240.99</v>
+        <v>241.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>245.276</v>
+        <v>275.638</v>
       </c>
       <c r="C27" t="n">
-        <v>199.75</v>
+        <v>274.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>211.322</v>
+        <v>283.652</v>
       </c>
       <c r="C28" t="n">
-        <v>294.615</v>
+        <v>269.416</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>309.775</v>
+        <v>306.295</v>
       </c>
       <c r="C29" t="n">
-        <v>249.09</v>
+        <v>318.906</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>252.349</v>
+        <v>352.63</v>
       </c>
       <c r="C30" t="n">
-        <v>241.04</v>
+        <v>291.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>275.638</v>
+        <v>284.6</v>
       </c>
       <c r="C31" t="n">
-        <v>274.84</v>
+        <v>249.947</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>283.652</v>
+        <v>228.484</v>
       </c>
       <c r="C32" t="n">
-        <v>269.416</v>
+        <v>263.919</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>306.295</v>
+        <v>241.111</v>
       </c>
       <c r="C33" t="n">
-        <v>318.906</v>
+        <v>234.729</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>352.63</v>
+        <v>232.685</v>
       </c>
       <c r="C34" t="n">
-        <v>291.33</v>
+        <v>223.985</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>284.6</v>
+        <v>223.539</v>
       </c>
       <c r="C35" t="n">
-        <v>249.947</v>
+        <v>199.337</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>228.484</v>
+        <v>220.856</v>
       </c>
       <c r="C36" t="n">
-        <v>263.919</v>
+        <v>195.604</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>241.111</v>
+        <v>226.019</v>
       </c>
       <c r="C37" t="n">
-        <v>234.729</v>
+        <v>214.425</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>232.685</v>
+        <v>214.007</v>
       </c>
       <c r="C38" t="n">
-        <v>223.985</v>
+        <v>202.723</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>223.539</v>
+        <v>207.398</v>
       </c>
       <c r="C39" t="n">
-        <v>199.337</v>
+        <v>191.773</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>220.856</v>
+        <v>199.9</v>
       </c>
       <c r="C40" t="n">
-        <v>195.604</v>
+        <v>193.923</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>226.019</v>
+        <v>200.081</v>
       </c>
       <c r="C41" t="n">
-        <v>214.425</v>
+        <v>197.349</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>214.007</v>
+        <v>216.534</v>
       </c>
       <c r="C42" t="n">
-        <v>202.723</v>
+        <v>215.265</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>207.398</v>
+        <v>220.962</v>
       </c>
       <c r="C43" t="n">
-        <v>191.773</v>
+        <v>209.064</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>199.9</v>
+        <v>210.816</v>
       </c>
       <c r="C44" t="n">
-        <v>193.923</v>
+        <v>202.619</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>200.081</v>
+        <v>224.021</v>
       </c>
       <c r="C45" t="n">
-        <v>197.349</v>
+        <v>189.634</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>216.534</v>
+        <v>206.71</v>
       </c>
       <c r="C46" t="n">
-        <v>215.265</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>220.962</v>
+        <v>203.579</v>
       </c>
       <c r="C47" t="n">
-        <v>209.064</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>210.816</v>
+        <v>200.637</v>
       </c>
       <c r="C48" t="n">
-        <v>202.619</v>
+        <v>192.717</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>224.021</v>
+        <v>210.16</v>
       </c>
       <c r="C49" t="n">
-        <v>189.634</v>
+        <v>197.164</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>206.71</v>
+        <v>207.512</v>
       </c>
       <c r="C50" t="n">
-        <v>210.05</v>
+        <v>196.177</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>203.579</v>
+        <v>243.98</v>
       </c>
       <c r="C51" t="n">
-        <v>197.68</v>
+        <v>236.046</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>200.637</v>
+        <v>234.859</v>
       </c>
       <c r="C52" t="n">
-        <v>192.717</v>
+        <v>227.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>210.16</v>
+        <v>227.516</v>
       </c>
       <c r="C53" t="n">
-        <v>197.164</v>
+        <v>225.13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>207.512</v>
+        <v>230.392</v>
       </c>
       <c r="C54" t="n">
-        <v>196.177</v>
+        <v>239.403</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>243.98</v>
+        <v>241.361</v>
       </c>
       <c r="C55" t="n">
-        <v>236.046</v>
+        <v>242.201</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>234.859</v>
+        <v>261.111</v>
       </c>
       <c r="C56" t="n">
-        <v>227.98</v>
+        <v>280.569</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
+        <v>45857</v>
       </c>
       <c r="B57" t="n">
-        <v>227.516</v>
+        <v>216.023</v>
       </c>
       <c r="C57" t="n">
-        <v>225.1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58" t="n">
-        <v>230.798</v>
-      </c>
-      <c r="C58" t="n">
-        <v>239.379</v>
+        <v>225.855</v>
       </c>
     </row>
   </sheetData>
@@ -1056,629 +1045,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="C2" t="n">
-        <v>431</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3" t="n">
-        <v>419</v>
+        <v>327</v>
       </c>
       <c r="C3" t="n">
-        <v>470</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4" t="n">
-        <v>344</v>
+        <v>476</v>
       </c>
       <c r="C4" t="n">
-        <v>397</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="C5" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>407</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>474</v>
+        <v>336</v>
       </c>
       <c r="C8" t="n">
-        <v>445</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>387</v>
+        <v>285</v>
       </c>
       <c r="C9" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C10" t="n">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>332</v>
+        <v>274</v>
       </c>
       <c r="C11" t="n">
-        <v>377</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>337</v>
+        <v>266</v>
       </c>
       <c r="C12" t="n">
-        <v>348</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="C13" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="C14" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="C15" t="n">
-        <v>314</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>263</v>
+        <v>351</v>
       </c>
       <c r="C16" t="n">
-        <v>272</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>312</v>
+        <v>434</v>
       </c>
       <c r="C17" t="n">
-        <v>363</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="C18" t="n">
-        <v>363</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>311</v>
+        <v>533</v>
       </c>
       <c r="C19" t="n">
-        <v>390</v>
+        <v>628</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>345</v>
+        <v>507</v>
       </c>
       <c r="C20" t="n">
-        <v>464</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>425</v>
+        <v>622</v>
       </c>
       <c r="C21" t="n">
-        <v>439</v>
+        <v>655</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>387</v>
+        <v>529</v>
       </c>
       <c r="C22" t="n">
-        <v>460</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>528</v>
+        <v>760</v>
       </c>
       <c r="C23" t="n">
-        <v>628</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>506</v>
+        <v>399</v>
       </c>
       <c r="C24" t="n">
-        <v>519</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>615</v>
+        <v>759</v>
       </c>
       <c r="C25" t="n">
-        <v>655</v>
+        <v>747</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="C26" t="n">
-        <v>662</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>754</v>
+        <v>507</v>
       </c>
       <c r="C27" t="n">
-        <v>511</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>399</v>
+        <v>343</v>
       </c>
       <c r="C28" t="n">
-        <v>729</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>759</v>
+        <v>479</v>
       </c>
       <c r="C29" t="n">
-        <v>747</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>549</v>
+        <v>597</v>
       </c>
       <c r="C30" t="n">
-        <v>514</v>
+        <v>762</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C31" t="n">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>343</v>
+        <v>497</v>
       </c>
       <c r="C32" t="n">
-        <v>415</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>479</v>
+        <v>599</v>
       </c>
       <c r="C33" t="n">
-        <v>643</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="C34" t="n">
-        <v>762</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>495</v>
+        <v>613</v>
       </c>
       <c r="C35" t="n">
-        <v>420</v>
+        <v>337</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>497</v>
+        <v>1634</v>
       </c>
       <c r="C36" t="n">
-        <v>502</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>599</v>
+        <v>1580</v>
       </c>
       <c r="C37" t="n">
-        <v>411</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>613</v>
+        <v>1066</v>
       </c>
       <c r="C38" t="n">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>613</v>
+        <v>821</v>
       </c>
       <c r="C39" t="n">
-        <v>337</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>1634</v>
+        <v>564</v>
       </c>
       <c r="C40" t="n">
-        <v>330</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>1580</v>
+        <v>508</v>
       </c>
       <c r="C41" t="n">
-        <v>393</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>1066</v>
+        <v>542</v>
       </c>
       <c r="C42" t="n">
-        <v>365</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>821</v>
+        <v>657</v>
       </c>
       <c r="C43" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>564</v>
+        <v>466</v>
       </c>
       <c r="C44" t="n">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>508</v>
+        <v>465</v>
       </c>
       <c r="C45" t="n">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>542</v>
+        <v>434</v>
       </c>
       <c r="C46" t="n">
-        <v>327</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>657</v>
+        <v>599</v>
       </c>
       <c r="C47" t="n">
-        <v>361</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>466</v>
+        <v>592</v>
       </c>
       <c r="C48" t="n">
-        <v>365</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>465</v>
+        <v>523</v>
       </c>
       <c r="C49" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>434</v>
+        <v>553</v>
       </c>
       <c r="C50" t="n">
-        <v>385</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>599</v>
+        <v>532</v>
       </c>
       <c r="C51" t="n">
-        <v>386</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>592</v>
+        <v>472</v>
       </c>
       <c r="C52" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>523</v>
+        <v>453</v>
       </c>
       <c r="C53" t="n">
-        <v>353</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>553</v>
+        <v>438</v>
       </c>
       <c r="C54" t="n">
-        <v>400</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>532</v>
+        <v>596</v>
       </c>
       <c r="C55" t="n">
-        <v>419</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>472</v>
+        <v>789</v>
       </c>
       <c r="C56" t="n">
-        <v>344</v>
+        <v>476</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
+        <v>45857</v>
       </c>
       <c r="B57" t="n">
-        <v>453</v>
+        <v>722</v>
       </c>
       <c r="C57" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58" t="n">
-        <v>438</v>
-      </c>
-      <c r="C58" t="n">
-        <v>370</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -1705,627 +1683,616 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2" t="n">
-        <v>1708.158</v>
+        <v>1795.365</v>
       </c>
       <c r="C2" t="n">
-        <v>1647.848</v>
+        <v>1724.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3" t="n">
-        <v>1727.754</v>
+        <v>1945.731</v>
       </c>
       <c r="C3" t="n">
-        <v>1670.3</v>
+        <v>1887.928</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4" t="n">
-        <v>1747.949</v>
+        <v>1914.075</v>
       </c>
       <c r="C4" t="n">
-        <v>1674.548</v>
+        <v>1835.614</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>1820.786</v>
+        <v>1934.382</v>
       </c>
       <c r="C5" t="n">
-        <v>1737.351</v>
+        <v>1827.375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>1795.072</v>
+        <v>1907.041</v>
       </c>
       <c r="C6" t="n">
-        <v>1724.28</v>
+        <v>1809.776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>1945.762</v>
+        <v>1883.372</v>
       </c>
       <c r="C7" t="n">
-        <v>1887.928</v>
+        <v>1814.133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>1913.683</v>
+        <v>1857.167</v>
       </c>
       <c r="C8" t="n">
-        <v>1835.614</v>
+        <v>1802.463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>1934.409</v>
+        <v>1843.217</v>
       </c>
       <c r="C9" t="n">
-        <v>1827.375</v>
+        <v>1789.862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>1906.472</v>
+        <v>1800.515</v>
       </c>
       <c r="C10" t="n">
-        <v>1809.776</v>
+        <v>1747.737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>1883.316</v>
+        <v>1704.638</v>
       </c>
       <c r="C11" t="n">
-        <v>1814.133</v>
+        <v>1655.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>1857.111</v>
+        <v>1671.837</v>
       </c>
       <c r="C12" t="n">
-        <v>1802.463</v>
+        <v>1645.927</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>1843.165</v>
+        <v>1628.081</v>
       </c>
       <c r="C13" t="n">
-        <v>1789.862</v>
+        <v>1588.285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>1800.462</v>
+        <v>1613.719</v>
       </c>
       <c r="C14" t="n">
-        <v>1747.737</v>
+        <v>1585.277</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>1704.574</v>
+        <v>1614.385</v>
       </c>
       <c r="C15" t="n">
-        <v>1655.84</v>
+        <v>1555.172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>1671.782</v>
+        <v>1598.241</v>
       </c>
       <c r="C16" t="n">
-        <v>1645.927</v>
+        <v>1542.397</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>1628.013</v>
+        <v>1627.825</v>
       </c>
       <c r="C17" t="n">
-        <v>1588.285</v>
+        <v>1572.658</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>1613.67</v>
+        <v>1616.144</v>
       </c>
       <c r="C18" t="n">
-        <v>1585.277</v>
+        <v>1574.471</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>1614.324</v>
+        <v>1646.982</v>
       </c>
       <c r="C19" t="n">
-        <v>1555.172</v>
+        <v>1607.693</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>1598.184</v>
+        <v>1647.301</v>
       </c>
       <c r="C20" t="n">
-        <v>1542.397</v>
+        <v>1578.946</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>1627.757</v>
+        <v>1660.894</v>
       </c>
       <c r="C21" t="n">
-        <v>1572.658</v>
+        <v>1654.732</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>1616.081</v>
+        <v>1721.154</v>
       </c>
       <c r="C22" t="n">
-        <v>1574.471</v>
+        <v>1555.596</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>1646.92</v>
+        <v>1661.071</v>
       </c>
       <c r="C23" t="n">
-        <v>1607.693</v>
+        <v>1845.084</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>1647.23</v>
+        <v>1933.23</v>
       </c>
       <c r="C24" t="n">
-        <v>1578.946</v>
+        <v>1767.267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>1660.806</v>
+        <v>1864.863</v>
       </c>
       <c r="C25" t="n">
-        <v>1654.732</v>
+        <v>1835.427</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>1721.069</v>
+        <v>1946.787</v>
       </c>
       <c r="C26" t="n">
-        <v>1555.596</v>
+        <v>1836.539</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>1661.071</v>
+        <v>1860.888</v>
       </c>
       <c r="C27" t="n">
-        <v>1845.084</v>
+        <v>1902.054</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>1933.23</v>
+        <v>2187.475</v>
       </c>
       <c r="C28" t="n">
-        <v>1767.267</v>
+        <v>2104.257</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>1864.863</v>
+        <v>2273.651</v>
       </c>
       <c r="C29" t="n">
-        <v>1835.427</v>
+        <v>2122.561</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>1946.787</v>
+        <v>2246.551</v>
       </c>
       <c r="C30" t="n">
-        <v>1836.539</v>
+        <v>2053.289</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>1860.888</v>
+        <v>2170.633</v>
       </c>
       <c r="C31" t="n">
-        <v>1902.054</v>
+        <v>2181.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>2187.475</v>
+        <v>2250.894</v>
       </c>
       <c r="C32" t="n">
-        <v>2104.257</v>
+        <v>2130.018</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>2273.651</v>
+        <v>2185.828</v>
       </c>
       <c r="C33" t="n">
-        <v>2122.561</v>
+        <v>2139.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>2246.551</v>
+        <v>2191.042</v>
       </c>
       <c r="C34" t="n">
-        <v>2053.289</v>
+        <v>2092.787</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>2170.633</v>
+        <v>2160.103</v>
       </c>
       <c r="C35" t="n">
-        <v>2181.43</v>
+        <v>2092.108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2250.894</v>
+        <v>2229.07</v>
       </c>
       <c r="C36" t="n">
-        <v>2130.018</v>
+        <v>2113.581</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>2185.828</v>
+        <v>2149.919</v>
       </c>
       <c r="C37" t="n">
-        <v>2139.97</v>
+        <v>2078.603</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>2191.042</v>
+        <v>2116.538</v>
       </c>
       <c r="C38" t="n">
-        <v>2092.787</v>
+        <v>2008.79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>2160.103</v>
+        <v>2072.402</v>
       </c>
       <c r="C39" t="n">
-        <v>2092.108</v>
+        <v>2012.613</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>2229.07</v>
+        <v>2058.751</v>
       </c>
       <c r="C40" t="n">
-        <v>2113.581</v>
+        <v>1937.982</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>2149.919</v>
+        <v>1985.73</v>
       </c>
       <c r="C41" t="n">
-        <v>2078.603</v>
+        <v>1928.017</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>2116.538</v>
+        <v>1943.418</v>
       </c>
       <c r="C42" t="n">
-        <v>2008.79</v>
+        <v>1848.827</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>2072.402</v>
+        <v>1880.372</v>
       </c>
       <c r="C43" t="n">
-        <v>2012.613</v>
+        <v>1812.811</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>2058.751</v>
+        <v>1898.153</v>
       </c>
       <c r="C44" t="n">
-        <v>1937.982</v>
+        <v>1753.465</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>1985.73</v>
+        <v>1838.279</v>
       </c>
       <c r="C45" t="n">
-        <v>1928.017</v>
+        <v>1743.445</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>1943.418</v>
+        <v>1782.724</v>
       </c>
       <c r="C46" t="n">
-        <v>1848.827</v>
+        <v>1686.177</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>1880.372</v>
+        <v>1779.686</v>
       </c>
       <c r="C47" t="n">
-        <v>1812.811</v>
+        <v>1686.782</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>1898.153</v>
+        <v>1775.51</v>
       </c>
       <c r="C48" t="n">
-        <v>1753.465</v>
+        <v>1666.648</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>1838.279</v>
+        <v>1755.336</v>
       </c>
       <c r="C49" t="n">
-        <v>1743.445</v>
+        <v>1670.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>1779.624</v>
+        <v>1826.063</v>
       </c>
       <c r="C50" t="n">
-        <v>1686.177</v>
+        <v>1708.158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>1779.686</v>
+        <v>1813.454</v>
       </c>
       <c r="C51" t="n">
-        <v>1686.782</v>
+        <v>1727.754</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>1775.51</v>
+        <v>1862.043</v>
       </c>
       <c r="C52" t="n">
-        <v>1666.648</v>
+        <v>1748.567</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>1755.336</v>
+        <v>1900.787</v>
       </c>
       <c r="C53" t="n">
-        <v>1670.55</v>
+        <v>1821.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>1826.063</v>
+        <v>1895.589</v>
       </c>
       <c r="C54" t="n">
-        <v>1708.158</v>
+        <v>1795.365</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>1813.454</v>
+        <v>2011.503</v>
       </c>
       <c r="C55" t="n">
-        <v>1727.754</v>
+        <v>1945.731</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>1862.036</v>
+        <v>2006.599</v>
       </c>
       <c r="C56" t="n">
-        <v>1747.949</v>
+        <v>1914.075</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
-      </c>
-      <c r="B57" t="n">
-        <v>1899.93</v>
-      </c>
+        <v>45857</v>
+      </c>
+      <c r="B57"/>
       <c r="C57" t="n">
-        <v>1820.786</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58"/>
-      <c r="C58" t="n">
-        <v>1795.072</v>
+        <v>1934.382</v>
       </c>
     </row>
   </sheetData>
@@ -2352,627 +2319,616 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2" t="n">
-        <v>4634</v>
+        <v>4605</v>
       </c>
       <c r="C2" t="n">
-        <v>4598</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3" t="n">
-        <v>4553</v>
+        <v>4711</v>
       </c>
       <c r="C3" t="n">
-        <v>4786</v>
+        <v>4863</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4" t="n">
-        <v>4526</v>
+        <v>4658</v>
       </c>
       <c r="C4" t="n">
-        <v>4671</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>4395</v>
+        <v>4767</v>
       </c>
       <c r="C5" t="n">
-        <v>4756</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>4564</v>
+        <v>4855</v>
       </c>
       <c r="C6" t="n">
-        <v>4773</v>
+        <v>5106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>4707</v>
+        <v>4505</v>
       </c>
       <c r="C7" t="n">
-        <v>4863</v>
+        <v>4912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>4659</v>
+        <v>4632</v>
       </c>
       <c r="C8" t="n">
-        <v>4869</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>4769</v>
+        <v>4308</v>
       </c>
       <c r="C9" t="n">
-        <v>4910</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>4852</v>
+        <v>4191</v>
       </c>
       <c r="C10" t="n">
-        <v>5106</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>4505</v>
+        <v>3852</v>
       </c>
       <c r="C11" t="n">
-        <v>4912</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>4632</v>
+        <v>3898</v>
       </c>
       <c r="C12" t="n">
-        <v>4840</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>4307</v>
+        <v>4001</v>
       </c>
       <c r="C13" t="n">
-        <v>4469</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>4191</v>
+        <v>4033</v>
       </c>
       <c r="C14" t="n">
-        <v>4552</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>3858</v>
+        <v>3929</v>
       </c>
       <c r="C15" t="n">
-        <v>4164</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>3898</v>
+        <v>3819</v>
       </c>
       <c r="C16" t="n">
-        <v>4295</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>4001</v>
+        <v>3903</v>
       </c>
       <c r="C17" t="n">
-        <v>4123</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>4033</v>
+        <v>4038</v>
       </c>
       <c r="C18" t="n">
-        <v>4148</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>3929</v>
+        <v>4246</v>
       </c>
       <c r="C19" t="n">
-        <v>4200</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>3820</v>
+        <v>4454</v>
       </c>
       <c r="C20" t="n">
-        <v>4121</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>3903</v>
+        <v>4760</v>
       </c>
       <c r="C21" t="n">
-        <v>4267</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>4038</v>
+        <v>5023</v>
       </c>
       <c r="C22" t="n">
-        <v>4309</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>4243</v>
+        <v>5081</v>
       </c>
       <c r="C23" t="n">
-        <v>4638</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>4452</v>
+        <v>5997</v>
       </c>
       <c r="C24" t="n">
-        <v>4741</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>4758</v>
+        <v>6031</v>
       </c>
       <c r="C25" t="n">
-        <v>5179</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>5019</v>
+        <v>6577</v>
       </c>
       <c r="C26" t="n">
-        <v>5045</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>5081</v>
+        <v>6210</v>
       </c>
       <c r="C27" t="n">
-        <v>5791</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>5997</v>
+        <v>6374</v>
       </c>
       <c r="C28" t="n">
-        <v>6131</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>6031</v>
+        <v>6854</v>
       </c>
       <c r="C29" t="n">
-        <v>6272</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>6577</v>
+        <v>7381</v>
       </c>
       <c r="C30" t="n">
-        <v>6427</v>
+        <v>6708</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>6210</v>
+        <v>6684</v>
       </c>
       <c r="C31" t="n">
-        <v>6284</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>6374</v>
+        <v>7470</v>
       </c>
       <c r="C32" t="n">
-        <v>6577</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>6854</v>
+        <v>7120</v>
       </c>
       <c r="C33" t="n">
-        <v>6766</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>7381</v>
+        <v>7621</v>
       </c>
       <c r="C34" t="n">
-        <v>6708</v>
+        <v>6819</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>6684</v>
+        <v>7422</v>
       </c>
       <c r="C35" t="n">
-        <v>7383</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>7470</v>
+        <v>8230</v>
       </c>
       <c r="C36" t="n">
-        <v>6953</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>7120</v>
+        <v>8929</v>
       </c>
       <c r="C37" t="n">
-        <v>6893</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>7621</v>
+        <v>9136</v>
       </c>
       <c r="C38" t="n">
-        <v>6819</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>7422</v>
+        <v>8246</v>
       </c>
       <c r="C39" t="n">
-        <v>6594</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>8230</v>
+        <v>7721</v>
       </c>
       <c r="C40" t="n">
-        <v>6876</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>8929</v>
+        <v>7192</v>
       </c>
       <c r="C41" t="n">
-        <v>6208</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>9136</v>
+        <v>7019</v>
       </c>
       <c r="C42" t="n">
-        <v>6241</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>8246</v>
+        <v>6640</v>
       </c>
       <c r="C43" t="n">
-        <v>5891</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>7721</v>
+        <v>6716</v>
       </c>
       <c r="C44" t="n">
-        <v>5881</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>7192</v>
+        <v>6570</v>
       </c>
       <c r="C45" t="n">
-        <v>5546</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>7019</v>
+        <v>6473</v>
       </c>
       <c r="C46" t="n">
-        <v>5274</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>6640</v>
+        <v>6377</v>
       </c>
       <c r="C47" t="n">
-        <v>5091</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>6716</v>
+        <v>6717</v>
       </c>
       <c r="C48" t="n">
-        <v>5030</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>6570</v>
+        <v>6323</v>
       </c>
       <c r="C49" t="n">
-        <v>4764</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>6473</v>
+        <v>7076</v>
       </c>
       <c r="C50" t="n">
-        <v>4737</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>6377</v>
+        <v>6738</v>
       </c>
       <c r="C51" t="n">
-        <v>4494</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>6717</v>
+        <v>7103</v>
       </c>
       <c r="C52" t="n">
-        <v>4648</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>6323</v>
+        <v>6947</v>
       </c>
       <c r="C53" t="n">
-        <v>4401</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>7076</v>
+        <v>7035</v>
       </c>
       <c r="C54" t="n">
-        <v>4634</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>6738</v>
+        <v>7226</v>
       </c>
       <c r="C55" t="n">
-        <v>4553</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>7103</v>
+        <v>7407</v>
       </c>
       <c r="C56" t="n">
-        <v>4526</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
-      </c>
-      <c r="B57" t="n">
-        <v>6949</v>
-      </c>
+        <v>45857</v>
+      </c>
+      <c r="B57"/>
       <c r="C57" t="n">
-        <v>4395</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58"/>
-      <c r="C58" t="n">
-        <v>4564</v>
+        <v>4767</v>
       </c>
     </row>
   </sheetData>
@@ -3005,7 +2961,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -3014,7 +2970,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -3023,7 +2979,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -3032,913 +2988,896 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.356374807987711</v>
+        <v>-0.335394126738794</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.184381778741866</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.105960264900662</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0373717505714741</v>
+        <v>-0.0347154262168426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.40785498489426</v>
+        <v>-0.258943781942078</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0256410256410257</v>
+        <v>0.247727272727273</v>
       </c>
       <c r="D6" t="n">
-        <v>0.113138686131387</v>
+        <v>0.122257053291536</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0499315284946803</v>
+        <v>-0.0383329957464047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.371980676328502</v>
+        <v>-0.163339382940109</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0325670498084292</v>
+        <v>0.16331096196868</v>
       </c>
       <c r="D7" t="n">
-        <v>0.12589928057554</v>
+        <v>0.13677811550152</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0456906048365945</v>
+        <v>-0.0511188563923827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.336012861736334</v>
+        <v>-0.0371819960861057</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.0455486542443064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0962199312714778</v>
+        <v>0.16566265060241</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0485956077046882</v>
+        <v>-0.0510420882233913</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.335394126738794</v>
+        <v>0.0504672897196261</v>
       </c>
       <c r="C9" t="n">
-        <v>0.184381778741866</v>
+        <v>-0.129032258064516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.105960264900662</v>
+        <v>0.143712574850299</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0368787020345094</v>
+        <v>-0.0531380969627981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.258943781942078</v>
+        <v>0.043557168784029</v>
       </c>
       <c r="C10" t="n">
-        <v>0.247727272727273</v>
+        <v>-0.175298804780876</v>
       </c>
       <c r="D10" t="n">
-        <v>0.122257053291536</v>
+        <v>0.0925373134328358</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0385355479035852</v>
+        <v>-0.0605657060672242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.163339382940109</v>
+        <v>-0.00349650349650354</v>
       </c>
       <c r="C11" t="n">
-        <v>0.16331096196868</v>
+        <v>-0.17979797979798</v>
       </c>
       <c r="D11" t="n">
-        <v>0.13677811550152</v>
+        <v>0.0501474926253687</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0511188563923827</v>
+        <v>-0.0578085991678224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0371819960861057</v>
+        <v>-0.10327868852459</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0455486542443064</v>
+        <v>-0.120689655172414</v>
       </c>
       <c r="D12" t="n">
-        <v>0.16566265060241</v>
+        <v>0.00574712643678166</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0510926750303521</v>
+        <v>-0.0704233409610984</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0504672897196261</v>
+        <v>-0.185185185185185</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.129032258064516</v>
+        <v>-0.0934182590233545</v>
       </c>
       <c r="D13" t="n">
-        <v>0.143712574850299</v>
+        <v>0.0144092219020173</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0533450613131888</v>
+        <v>-0.0695692774600211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>0.043557168784029</v>
+        <v>-0.142140468227425</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.175298804780876</v>
+        <v>-0.122661122661123</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0925373134328358</v>
+        <v>0.0705882352941176</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0606189740584883</v>
+        <v>-0.0565451285116557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.00349650349650354</v>
+        <v>-0.139767054908486</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.17979797979798</v>
+        <v>-0.112244897959184</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0501474926253687</v>
+        <v>0.113095238095238</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0575312066574203</v>
+        <v>-0.0539782893952045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.10327868852459</v>
+        <v>-0.156589147286822</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.120689655172414</v>
+        <v>-0.145593869731801</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00574712643678166</v>
+        <v>0.154761904761905</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.070137299771167</v>
+        <v>-0.0488187078109933</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.185185185185185</v>
+        <v>-0.174698795180723</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0934182590233545</v>
+        <v>-0.146153846153846</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0144092219020173</v>
+        <v>0.144092219020173</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0692190965332088</v>
+        <v>-0.0628585086042065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.142140468227425</v>
+        <v>-0.217194570135747</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.122661122661123</v>
+        <v>-0.0452674897119342</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0705882352941176</v>
+        <v>0.0988700564971752</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0561864913329349</v>
+        <v>-0.0714919808249985</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.139767054908486</v>
+        <v>-0.224340175953079</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.112244897959184</v>
+        <v>-0.0224032586558045</v>
       </c>
       <c r="D19" t="n">
-        <v>0.113095238095238</v>
+        <v>0.0657142857142856</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0539782893952045</v>
+        <v>-0.0766657052206519</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.156589147286822</v>
+        <v>-0.190553745928339</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.145593869731801</v>
+        <v>-0.12593984962406</v>
       </c>
       <c r="D20" t="n">
-        <v>0.154761904761905</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04875843780135</v>
+        <v>-0.0731829573934837</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.174698795180723</v>
+        <v>-0.117543859649123</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.146153846153846</v>
+        <v>-0.147329650092081</v>
       </c>
       <c r="D21" t="n">
-        <v>0.144092219020173</v>
+        <v>0.070336391437309</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0627987571701721</v>
+        <v>-0.0725605554672178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.217194570135747</v>
+        <v>-0.106830122591944</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0452674897119342</v>
+        <v>-0.155752212389381</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0988700564971752</v>
+        <v>0.133550488599349</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0714327987216665</v>
+        <v>-0.0571341121256951</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.224340175953079</v>
+        <v>-0.072992700729927</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0224032586558045</v>
+        <v>-0.194871794871795</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0657142857142856</v>
+        <v>0.192567567567568</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0767810787424286</v>
+        <v>-0.0692811717093852</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.190553745928339</v>
+        <v>-0.15609756097561</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.12593984962406</v>
+        <v>-0.140138408304498</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.228668941979522</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0734614313561682</v>
+        <v>-0.0580240223968211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.117543859649123</v>
+        <v>-0.163430420711974</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.147329650092081</v>
+        <v>-0.201907790143084</v>
       </c>
       <c r="D25" t="n">
-        <v>0.070336391437309</v>
+        <v>0.225589225589226</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0729315736471087</v>
+        <v>-0.0476354404234262</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.106830122591944</v>
+        <v>-0.158238172920065</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.155752212389381</v>
+        <v>-0.214397496087637</v>
       </c>
       <c r="D26" t="n">
-        <v>0.133550488599349</v>
+        <v>0.195439739413681</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0576952507269296</v>
+        <v>-0.0379757117907478</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.072992700729927</v>
+        <v>-0.141666666666667</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.194871794871795</v>
+        <v>-0.204180064308682</v>
       </c>
       <c r="D27" t="n">
-        <v>0.192567567567568</v>
+        <v>0.188925081433225</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0696666024282135</v>
+        <v>-0.0119057099625707</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.15609756097561</v>
+        <v>-0.0666666666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.140138408304498</v>
+        <v>-0.188356164383562</v>
       </c>
       <c r="D28" t="n">
-        <v>0.228668941979522</v>
+        <v>0.186885245901639</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0582949516842771</v>
+        <v>-0.014397496087637</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.163430420711974</v>
+        <v>-0.104712041884817</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.201907790143084</v>
+        <v>-0.0557692307692308</v>
       </c>
       <c r="D29" t="n">
-        <v>0.225589225589226</v>
+        <v>0.221122112211221</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0478075648694006</v>
+        <v>-0.00149689107238815</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.158238172920065</v>
+        <v>-0.0670194003527337</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.214397496087637</v>
+        <v>-0.0101214574898786</v>
       </c>
       <c r="D30" t="n">
-        <v>0.195439739413681</v>
+        <v>0.241830065359477</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0379757117907478</v>
+        <v>0.0183785836339472</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.141666666666667</v>
+        <v>-0.107615894039735</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.204180064308682</v>
+        <v>0.090717299578059</v>
       </c>
       <c r="D31" t="n">
-        <v>0.188925081433225</v>
+        <v>0.216981132075472</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0119057099625707</v>
+        <v>-0.00513960778595901</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.0666666666666667</v>
+        <v>0.0329861111111112</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.188356164383562</v>
+        <v>0.225382932166302</v>
       </c>
       <c r="D32" t="n">
-        <v>0.186885245901639</v>
+        <v>0.170149253731343</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.014397496087637</v>
+        <v>0.0208198489751887</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.104712041884817</v>
+        <v>0.227826086956522</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0557692307692308</v>
+        <v>0.260485651214128</v>
       </c>
       <c r="D33" t="n">
-        <v>0.221122112211221</v>
+        <v>0.145714285714286</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.00149689107238815</v>
+        <v>0.0257006836811398</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.0670194003527337</v>
+        <v>0.608084358523726</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0101214574898786</v>
+        <v>0.24507658643326</v>
       </c>
       <c r="D34" t="n">
-        <v>0.241830065359477</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0183785836339472</v>
+        <v>0.0301982316029663</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.107615894039735</v>
+        <v>1.40566037735849</v>
       </c>
       <c r="C35" t="n">
-        <v>0.090717299578059</v>
+        <v>0.148296593186373</v>
       </c>
       <c r="D35" t="n">
-        <v>0.216981132075472</v>
+        <v>0.218579234972678</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.00513960778595901</v>
+        <v>0.0870905022194504</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0329861111111112</v>
+        <v>2.35459662288931</v>
       </c>
       <c r="C36" t="n">
-        <v>0.225382932166302</v>
+        <v>0.265503875968992</v>
       </c>
       <c r="D36" t="n">
-        <v>0.170149253731343</v>
+        <v>0.315217391304348</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0208198489751887</v>
+        <v>0.118129644617762</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>0.227826086956522</v>
+        <v>3.80254777070064</v>
       </c>
       <c r="C37" t="n">
-        <v>0.260485651214128</v>
+        <v>0.328330206378987</v>
       </c>
       <c r="D37" t="n">
-        <v>0.145714285714286</v>
+        <v>0.464788732394366</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0257006836811398</v>
+        <v>0.215307393289806</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>0.608084358523726</v>
+        <v>5.11751662971175</v>
       </c>
       <c r="C38" t="n">
-        <v>0.24507658643326</v>
+        <v>0.497247706422018</v>
       </c>
       <c r="D38" t="n">
-        <v>0.176470588235294</v>
+        <v>0.579545454545455</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0301982316029663</v>
+        <v>0.300860372699564</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>1.40566037735849</v>
+        <v>6.05080831408776</v>
       </c>
       <c r="C39" t="n">
-        <v>0.148296593186373</v>
+        <v>0.767754318618042</v>
       </c>
       <c r="D39" t="n">
-        <v>0.218579234972678</v>
+        <v>0.67621776504298</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0870905022194504</v>
+        <v>0.369804885786802</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>2.35459662288931</v>
+        <v>6.48470588235294</v>
       </c>
       <c r="C40" t="n">
-        <v>0.265503875968992</v>
+        <v>0.808</v>
       </c>
       <c r="D40" t="n">
-        <v>0.315217391304348</v>
+        <v>0.720116618075802</v>
       </c>
       <c r="E40" t="n">
-        <v>0.118129644617762</v>
+        <v>0.405061723297965</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>3.80254777070064</v>
+        <v>6.28791208791209</v>
       </c>
       <c r="C41" t="n">
-        <v>0.328330206378987</v>
+        <v>0.846311475409836</v>
       </c>
       <c r="D41" t="n">
-        <v>0.464788732394366</v>
+        <v>0.69208211143695</v>
       </c>
       <c r="E41" t="n">
-        <v>0.215307393289806</v>
+        <v>0.370813701770024</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>5.11751662971175</v>
+        <v>6.19057815845824</v>
       </c>
       <c r="C42" t="n">
-        <v>0.497247706422018</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>0.579545454545455</v>
+        <v>0.664688427299703</v>
       </c>
       <c r="E42" t="n">
-        <v>0.300860372699564</v>
+        <v>0.335782577903683</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>6.05080831408776</v>
+        <v>6.41630901287554</v>
       </c>
       <c r="C43" t="n">
-        <v>0.767754318618042</v>
+        <v>0.568228105906314</v>
       </c>
       <c r="D43" t="n">
-        <v>0.67621776504298</v>
+        <v>0.674772036474164</v>
       </c>
       <c r="E43" t="n">
-        <v>0.369804885786802</v>
+        <v>0.311123348017621</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>6.48470588235294</v>
+        <v>6.54885654885655</v>
       </c>
       <c r="C44" t="n">
-        <v>0.808</v>
+        <v>0.441233140655106</v>
       </c>
       <c r="D44" t="n">
-        <v>0.720116618075802</v>
+        <v>0.727554179566563</v>
       </c>
       <c r="E44" t="n">
-        <v>0.405061723297965</v>
+        <v>0.316412778759372</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>6.28791208791209</v>
+        <v>7.8466819221968</v>
       </c>
       <c r="C45" t="n">
-        <v>0.846311475409836</v>
+        <v>0.446183953033268</v>
       </c>
       <c r="D45" t="n">
-        <v>0.69208211143695</v>
+        <v>0.761609907120743</v>
       </c>
       <c r="E45" t="n">
-        <v>0.370813701770024</v>
+        <v>0.336623840468277</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>6.19057815845824</v>
+        <v>8.28310502283105</v>
       </c>
       <c r="C46" t="n">
-        <v>0.729166666666667</v>
+        <v>0.482490272373541</v>
       </c>
       <c r="D46" t="n">
-        <v>0.664688427299703</v>
+        <v>0.803125</v>
       </c>
       <c r="E46" t="n">
-        <v>0.335782577903683</v>
+        <v>0.345377637345836</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>6.41630901287554</v>
+        <v>8.08102345415778</v>
       </c>
       <c r="C47" t="n">
-        <v>0.568228105906314</v>
+        <v>0.550495049504951</v>
       </c>
       <c r="D47" t="n">
-        <v>0.674772036474164</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E47" t="n">
-        <v>0.311123348017621</v>
+        <v>0.37377135348226</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>6.54885654885655</v>
+        <v>8.72767857142857</v>
       </c>
       <c r="C48" t="n">
-        <v>0.441233140655106</v>
+        <v>0.765913757700205</v>
       </c>
       <c r="D48" t="n">
-        <v>0.727554179566563</v>
+        <v>0.989966555183946</v>
       </c>
       <c r="E48" t="n">
-        <v>0.316412778759372</v>
+        <v>0.401973931234243</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>7.8466819221968</v>
+        <v>8.27467811158798</v>
       </c>
       <c r="C49" t="n">
-        <v>0.446183953033268</v>
+        <v>0.913131313131313</v>
       </c>
       <c r="D49" t="n">
-        <v>0.761609907120743</v>
+        <v>1.0551724137931</v>
       </c>
       <c r="E49" t="n">
-        <v>0.336623840468277</v>
+        <v>0.416301969365427</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>8.28310502283105</v>
+        <v>8.10084033613445</v>
       </c>
       <c r="C50" t="n">
-        <v>0.482490272373541</v>
+        <v>1.1377245508982</v>
       </c>
       <c r="D50" t="n">
-        <v>0.803125</v>
+        <v>1.12323943661972</v>
       </c>
       <c r="E50" t="n">
-        <v>0.345377637345836</v>
+        <v>0.457501237828024</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>8.08102345415778</v>
+        <v>8.80045351473923</v>
       </c>
       <c r="C51" t="n">
-        <v>0.550495049504951</v>
+        <v>1.25988700564972</v>
       </c>
       <c r="D51" t="n">
-        <v>0.919354838709677</v>
+        <v>1.08680555555556</v>
       </c>
       <c r="E51" t="n">
-        <v>0.37377135348226</v>
+        <v>0.472581706514587</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>8.72767857142857</v>
+        <v>8.76523702031603</v>
       </c>
       <c r="C52" t="n">
-        <v>0.765913757700205</v>
+        <v>1.29779411764706</v>
       </c>
       <c r="D52" t="n">
-        <v>0.989966555183946</v>
+        <v>1.08219178082192</v>
       </c>
       <c r="E52" t="n">
-        <v>0.401973931234243</v>
+        <v>0.500330469266358</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>8.27467811158798</v>
+        <v>9.38663484486874</v>
       </c>
       <c r="C53" t="n">
-        <v>0.913131313131313</v>
+        <v>1.4462962962963</v>
       </c>
       <c r="D53" t="n">
-        <v>1.0551724137931</v>
+        <v>1.05333333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>0.416301969365427</v>
+        <v>0.531999120299098</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>8.10084033613445</v>
+        <v>10.1326530612245</v>
       </c>
       <c r="C54" t="n">
-        <v>1.1377245508982</v>
+        <v>1.56015037593985</v>
       </c>
       <c r="D54" t="n">
-        <v>1.12323943661972</v>
+        <v>1.02295081967213</v>
       </c>
       <c r="E54" t="n">
-        <v>0.457501237828024</v>
+        <v>0.532187895809241</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>8.80045351473923</v>
+        <v>10.474358974359</v>
       </c>
       <c r="C55" t="n">
-        <v>1.25988700564972</v>
+        <v>1.68910891089109</v>
       </c>
       <c r="D55" t="n">
-        <v>1.08680555555556</v>
+        <v>0.993610223642172</v>
       </c>
       <c r="E55" t="n">
-        <v>0.472581706514587</v>
+        <v>0.545613364633946</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>8.76523702031603</v>
+        <v>10.1598062953995</v>
       </c>
       <c r="C56" t="n">
-        <v>1.29779411764706</v>
+        <v>1.78313253012048</v>
       </c>
       <c r="D56" t="n">
-        <v>1.08219178082192</v>
+        <v>0.981191222570533</v>
       </c>
       <c r="E56" t="n">
-        <v>0.503809208347135</v>
+        <v>0.554571630358016</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
-      </c>
-      <c r="B57" t="n">
-        <v>9.38663484486874</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1.4462962962963</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.05333333333333</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.53887784404683</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
+        <v>45857</v>
+      </c>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3970,7 +3909,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -3979,7 +3918,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45451</v>
+        <v>45479</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -3988,7 +3927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45458</v>
+        <v>45486</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -3997,913 +3936,896 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45465</v>
+        <v>45493</v>
       </c>
       <c r="B5" t="n">
-        <v>0.22424652542814</v>
+        <v>0.203128637273616</v>
       </c>
       <c r="C5" t="n">
-        <v>0.155238247246744</v>
+        <v>0.168128773568507</v>
       </c>
       <c r="D5" t="n">
-        <v>0.222194755557246</v>
+        <v>0.229695221648632</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0408020924668133</v>
+        <v>0.0432092766697589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45472</v>
+        <v>45500</v>
       </c>
       <c r="B6" t="n">
-        <v>0.198969280517381</v>
+        <v>0.189903193703067</v>
       </c>
       <c r="C6" t="n">
-        <v>0.164512366976044</v>
+        <v>0.17227411470406</v>
       </c>
       <c r="D6" t="n">
-        <v>0.223873288509709</v>
+        <v>0.228824226945179</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0418839167798797</v>
+        <v>0.0462641221417603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45479</v>
+        <v>45507</v>
       </c>
       <c r="B7" t="n">
-        <v>0.209443757725587</v>
+        <v>0.163998059194566</v>
       </c>
       <c r="C7" t="n">
-        <v>0.166512092459157</v>
+        <v>0.178472039304161</v>
       </c>
       <c r="D7" t="n">
-        <v>0.22631598554558</v>
+        <v>0.224662131353846</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0406403262364883</v>
+        <v>0.0483020346929517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45486</v>
+        <v>45514</v>
       </c>
       <c r="B8" t="n">
-        <v>0.227342995169082</v>
+        <v>0.141896234094512</v>
       </c>
       <c r="C8" t="n">
-        <v>0.16826906227731</v>
+        <v>0.164008368577342</v>
       </c>
       <c r="D8" t="n">
-        <v>0.231251966900535</v>
+        <v>0.216779135509758</v>
       </c>
       <c r="E8" t="n">
-        <v>0.040378986003538</v>
+        <v>0.0452476492494154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45493</v>
+        <v>45521</v>
       </c>
       <c r="B9" t="n">
-        <v>0.203128637273616</v>
+        <v>0.150697198413714</v>
       </c>
       <c r="C9" t="n">
-        <v>0.168128773568507</v>
+        <v>0.146800265721878</v>
       </c>
       <c r="D9" t="n">
-        <v>0.229695221648632</v>
+        <v>0.21721454719376</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0431230934365077</v>
+        <v>0.0380479624136356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45500</v>
+        <v>45528</v>
       </c>
       <c r="B10" t="n">
-        <v>0.189903193703067</v>
+        <v>0.141125650058715</v>
       </c>
       <c r="C10" t="n">
-        <v>0.17227411470406</v>
+        <v>0.121445000381526</v>
       </c>
       <c r="D10" t="n">
-        <v>0.228824226945179</v>
+        <v>0.206229660622966</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0461414434754988</v>
+        <v>0.0321595930779075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45507</v>
+        <v>45535</v>
       </c>
       <c r="B11" t="n">
-        <v>0.163998059194566</v>
+        <v>0.150051212017754</v>
       </c>
       <c r="C11" t="n">
-        <v>0.178472039304161</v>
+        <v>0.113542725070064</v>
       </c>
       <c r="D11" t="n">
-        <v>0.224662131353846</v>
+        <v>0.190311157989904</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0481661744133099</v>
+        <v>0.0299653997440217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45514</v>
+        <v>45542</v>
       </c>
       <c r="B12" t="n">
-        <v>0.141896234094512</v>
+        <v>0.16618459111228</v>
       </c>
       <c r="C12" t="n">
-        <v>0.164008368577342</v>
+        <v>0.109923011120616</v>
       </c>
       <c r="D12" t="n">
-        <v>0.216779135509758</v>
+        <v>0.170746064599434</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0451574889501936</v>
+        <v>0.0264411935258326</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45521</v>
+        <v>45549</v>
       </c>
       <c r="B13" t="n">
-        <v>0.150697198413714</v>
+        <v>0.166748779504636</v>
       </c>
       <c r="C13" t="n">
-        <v>0.146800265721878</v>
+        <v>0.107857245646856</v>
       </c>
       <c r="D13" t="n">
-        <v>0.21721454719376</v>
+        <v>0.152943428735522</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0379463858849367</v>
+        <v>0.0252014639211942</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45528</v>
+        <v>45556</v>
       </c>
       <c r="B14" t="n">
-        <v>0.141125650058715</v>
+        <v>0.178918618646422</v>
       </c>
       <c r="C14" t="n">
-        <v>0.121445000381526</v>
+        <v>0.0929242729911923</v>
       </c>
       <c r="D14" t="n">
-        <v>0.206229660622966</v>
+        <v>0.160269047895164</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0321292612236597</v>
+        <v>0.0220754806435317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45535</v>
+        <v>45563</v>
       </c>
       <c r="B15" t="n">
-        <v>0.150051212017754</v>
+        <v>0.176410636523673</v>
       </c>
       <c r="C15" t="n">
-        <v>0.113542725070064</v>
+        <v>0.073042564372044</v>
       </c>
       <c r="D15" t="n">
-        <v>0.190311157989904</v>
+        <v>0.177987507587476</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0299332380585091</v>
+        <v>0.024057906765552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45542</v>
+        <v>45570</v>
       </c>
       <c r="B16" t="n">
-        <v>0.16618459111228</v>
+        <v>0.158714881525276</v>
       </c>
       <c r="C16" t="n">
-        <v>0.109923011120616</v>
+        <v>0.0568213544385234</v>
       </c>
       <c r="D16" t="n">
-        <v>0.170746064599434</v>
+        <v>0.214439569206223</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0264084419520758</v>
+        <v>0.0292283800163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45549</v>
+        <v>45577</v>
       </c>
       <c r="B17" t="n">
-        <v>0.166748779504636</v>
+        <v>0.154573418981272</v>
       </c>
       <c r="C17" t="n">
-        <v>0.107857245646856</v>
+        <v>0.0267428243672776</v>
       </c>
       <c r="D17" t="n">
-        <v>0.152943428735522</v>
+        <v>0.245607302985014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0251653073033808</v>
+        <v>0.0317585921134413</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45556</v>
+        <v>45584</v>
       </c>
       <c r="B18" t="n">
-        <v>0.178918618646422</v>
+        <v>0.14208204675783</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0929242729911923</v>
+        <v>0.0232447479241513</v>
       </c>
       <c r="D18" t="n">
-        <v>0.160269047895164</v>
+        <v>0.264556602241351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0220390346189361</v>
+        <v>0.0339323054533622</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45563</v>
+        <v>45591</v>
       </c>
       <c r="B19" t="n">
-        <v>0.176410636523673</v>
+        <v>0.139955734930348</v>
       </c>
       <c r="C19" t="n">
-        <v>0.073042564372044</v>
+        <v>0.00699923793891788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.177987507587476</v>
+        <v>0.271015699575522</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0240213558022928</v>
+        <v>0.0304853618716452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45570</v>
+        <v>45598</v>
       </c>
       <c r="B20" t="n">
-        <v>0.158714881525276</v>
+        <v>0.132738451028947</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0568213544385234</v>
+        <v>-0.00100421536916595</v>
       </c>
       <c r="D20" t="n">
-        <v>0.214439569206223</v>
+        <v>0.271331231567172</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0291909067120428</v>
+        <v>0.0322847316163144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45577</v>
+        <v>45605</v>
       </c>
       <c r="B21" t="n">
-        <v>0.154573418981272</v>
+        <v>0.131862080650627</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0267428243672776</v>
+        <v>0.00360754558890286</v>
       </c>
       <c r="D21" t="n">
-        <v>0.245607302985014</v>
+        <v>0.269880107658429</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0317210251963711</v>
+        <v>0.0242336079972043</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c r="B22" t="n">
-        <v>0.14208204675783</v>
+        <v>0.171802338215481</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0232447479241513</v>
+        <v>0.0182650540341183</v>
       </c>
       <c r="D22" t="n">
-        <v>0.264556602241351</v>
+        <v>0.281946546683531</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0338924316275984</v>
+        <v>0.0436713211120208</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45591</v>
+        <v>45619</v>
       </c>
       <c r="B23" t="n">
-        <v>0.139955734930348</v>
+        <v>0.163226448569821</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00699923793891788</v>
+        <v>0.00391232673152375</v>
       </c>
       <c r="D23" t="n">
-        <v>0.271015699575522</v>
+        <v>0.28396557486631</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03044566180722</v>
+        <v>0.00845025245848952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45598</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>0.132738451028947</v>
+        <v>0.172058254929759</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00100421536916595</v>
+        <v>0.00358886996024999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.271331231567172</v>
+        <v>0.289604168417514</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0322430502664448</v>
+        <v>0.0225234105253962</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="B25" t="n">
-        <v>0.131862080650627</v>
+        <v>0.175715990453461</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00360754558890286</v>
+        <v>0.0137464788732393</v>
       </c>
       <c r="D25" t="n">
-        <v>0.269880107658429</v>
+        <v>0.289464319356932</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0241893425679747</v>
+        <v>0.0252655362972192</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45612</v>
+        <v>45640</v>
       </c>
       <c r="B26" t="n">
-        <v>0.171802338215481</v>
+        <v>0.160316139767055</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0182650540341183</v>
+        <v>0.00427307959852907</v>
       </c>
       <c r="D26" t="n">
-        <v>0.281946546683531</v>
+        <v>0.27904918707553</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0436234859426348</v>
+        <v>0.0166980651720676</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45619</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="n">
-        <v>0.163226448569821</v>
+        <v>0.191925988225399</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00391232673152375</v>
+        <v>0.0207675693636817</v>
       </c>
       <c r="D27" t="n">
-        <v>0.28396557486631</v>
+        <v>0.282417335539081</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00841347422011274</v>
+        <v>0.0360265168764005</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45626</v>
+        <v>45654</v>
       </c>
       <c r="B28" t="n">
-        <v>0.172058254929759</v>
+        <v>0.204941678163803</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00358886996024999</v>
+        <v>0.029792110001637</v>
       </c>
       <c r="D28" t="n">
-        <v>0.289604168417514</v>
+        <v>0.274651989635016</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0224980539169437</v>
+        <v>0.0236688517489014</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45633</v>
+        <v>45661</v>
       </c>
       <c r="B29" t="n">
-        <v>0.175715990453461</v>
+        <v>0.199917389508468</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0137464788732393</v>
+        <v>0.0384088672058887</v>
       </c>
       <c r="D29" t="n">
-        <v>0.289464319356932</v>
+        <v>0.26301531213192</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0252533992901136</v>
+        <v>0.0380884300885416</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45640</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="n">
-        <v>0.160316139767055</v>
+        <v>0.229751519411254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00427307959852907</v>
+        <v>0.0544416538274834</v>
       </c>
       <c r="D30" t="n">
-        <v>0.27904918707553</v>
+        <v>0.243298224267083</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0166980651720676</v>
+        <v>0.0472251768206466</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45647</v>
+        <v>45675</v>
       </c>
       <c r="B31" t="n">
-        <v>0.191925988225399</v>
+        <v>0.223177177904208</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0207675693636817</v>
+        <v>0.0523603485927711</v>
       </c>
       <c r="D31" t="n">
-        <v>0.282417335539081</v>
+        <v>0.219946376785161</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0360265168764005</v>
+        <v>0.0492549994167726</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45654</v>
+        <v>45682</v>
       </c>
       <c r="B32" t="n">
-        <v>0.204941678163803</v>
+        <v>0.323548512793869</v>
       </c>
       <c r="C32" t="n">
-        <v>0.029792110001637</v>
+        <v>0.0456958436387767</v>
       </c>
       <c r="D32" t="n">
-        <v>0.274651989635016</v>
+        <v>0.195079579553231</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0236688517489014</v>
+        <v>0.0535424819536205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45661</v>
+        <v>45689</v>
       </c>
       <c r="B33" t="n">
-        <v>0.199917389508468</v>
+        <v>0.396427938308811</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0384088672058887</v>
+        <v>0.0330905965002422</v>
       </c>
       <c r="D33" t="n">
-        <v>0.26301531213192</v>
+        <v>0.165360594418022</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0380884300885416</v>
+        <v>0.0410594979932879</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45668</v>
+        <v>45696</v>
       </c>
       <c r="B34" t="n">
-        <v>0.229751519411254</v>
+        <v>0.454256272401434</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0544416538274834</v>
+        <v>0.013361714479222</v>
       </c>
       <c r="D34" t="n">
-        <v>0.243298224267083</v>
+        <v>0.137436166893811</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0472251768206466</v>
+        <v>0.0297502225192396</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45675</v>
+        <v>45703</v>
       </c>
       <c r="B35" t="n">
-        <v>0.223177177904208</v>
+        <v>0.56764488741233</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0523603485927711</v>
+        <v>0.0249540856484858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.219946376785161</v>
+        <v>0.132084897906561</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0492549994167726</v>
+        <v>0.0393836319201579</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45682</v>
+        <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>0.323548512793869</v>
+        <v>0.596092346782319</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0456958436387767</v>
+        <v>0.0402161928014493</v>
       </c>
       <c r="D36" t="n">
-        <v>0.195079579553231</v>
+        <v>0.124437518881875</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0535424819536205</v>
+        <v>0.0388219584506435</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B37" t="n">
-        <v>0.396427938308811</v>
+        <v>0.713643178410795</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0330905965002422</v>
+        <v>0.0506608369270085</v>
       </c>
       <c r="D37" t="n">
-        <v>0.165360594418022</v>
+        <v>0.128568934596645</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0410594979932879</v>
+        <v>0.0421453587819811</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45696</v>
+        <v>45724</v>
       </c>
       <c r="B38" t="n">
-        <v>0.454256272401434</v>
+        <v>0.829688123863183</v>
       </c>
       <c r="C38" t="n">
-        <v>0.013361714479222</v>
+        <v>0.0686227581500982</v>
       </c>
       <c r="D38" t="n">
-        <v>0.137436166893811</v>
+        <v>0.144513088338322</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0297502225192396</v>
+        <v>0.04371691971694</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45703</v>
+        <v>45731</v>
       </c>
       <c r="B39" t="n">
-        <v>0.56764488741233</v>
+        <v>0.898953478146161</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0249540856484858</v>
+        <v>0.0768342832407474</v>
       </c>
       <c r="D39" t="n">
-        <v>0.132084897906561</v>
+        <v>0.146231918804443</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0393836319201579</v>
+        <v>0.043140956563801</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45710</v>
+        <v>45738</v>
       </c>
       <c r="B40" t="n">
-        <v>0.596092346782319</v>
+        <v>0.914512748864827</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0402161928014493</v>
+        <v>0.0794878216767891</v>
       </c>
       <c r="D40" t="n">
-        <v>0.124437518881875</v>
+        <v>0.155190199871051</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0388219584506435</v>
+        <v>0.0447403006822105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45717</v>
+        <v>45745</v>
       </c>
       <c r="B41" t="n">
-        <v>0.713643178410795</v>
+        <v>0.931867165163844</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0506608369270085</v>
+        <v>0.0741859930153286</v>
       </c>
       <c r="D41" t="n">
-        <v>0.128568934596645</v>
+        <v>0.159046015349244</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0421453587819811</v>
+        <v>0.0438698319167705</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45724</v>
+        <v>45752</v>
       </c>
       <c r="B42" t="n">
-        <v>0.829688123863183</v>
+        <v>0.931175347453488</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0686227581500982</v>
+        <v>0.0606904816971889</v>
       </c>
       <c r="D42" t="n">
-        <v>0.144513088338322</v>
+        <v>0.167423835344308</v>
       </c>
       <c r="E42" t="n">
-        <v>0.04371691971694</v>
+        <v>0.0430753319437398</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45759</v>
       </c>
       <c r="B43" t="n">
-        <v>0.898953478146161</v>
+        <v>0.950586187946511</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0768342832407474</v>
+        <v>0.0609923639732899</v>
       </c>
       <c r="D43" t="n">
-        <v>0.146231918804443</v>
+        <v>0.162972045120157</v>
       </c>
       <c r="E43" t="n">
-        <v>0.043140956563801</v>
+        <v>0.0452511193087552</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45738</v>
+        <v>45766</v>
       </c>
       <c r="B44" t="n">
-        <v>0.914512748864827</v>
+        <v>0.962573099415205</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0794878216767891</v>
+        <v>0.0631096975259888</v>
       </c>
       <c r="D44" t="n">
-        <v>0.155190199871051</v>
+        <v>0.159091649561789</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0447403006822105</v>
+        <v>0.049645518526185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45745</v>
+        <v>45773</v>
       </c>
       <c r="B45" t="n">
-        <v>0.931867165163844</v>
+        <v>0.956761599396454</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0741859930153286</v>
+        <v>0.0724971481340648</v>
       </c>
       <c r="D45" t="n">
-        <v>0.159046015349244</v>
+        <v>0.160260469950147</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0438698319167705</v>
+        <v>0.0561110996252312</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45752</v>
+        <v>45780</v>
       </c>
       <c r="B46" t="n">
-        <v>0.931175347453488</v>
+        <v>0.928278977834251</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0606904816971889</v>
+        <v>0.0701002993684856</v>
       </c>
       <c r="D46" t="n">
-        <v>0.167423835344308</v>
+        <v>0.144293412692029</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0430753319437398</v>
+        <v>0.0576952379808855</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45759</v>
+        <v>45787</v>
       </c>
       <c r="B47" t="n">
-        <v>0.950586187946511</v>
+        <v>0.901866121994244</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0609923639732899</v>
+        <v>0.0599458006377676</v>
       </c>
       <c r="D47" t="n">
-        <v>0.162972045120157</v>
+        <v>0.170182594563589</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0452511193087552</v>
+        <v>0.0624426753989049</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45766</v>
+        <v>45794</v>
       </c>
       <c r="B48" t="n">
-        <v>0.962573099415205</v>
+        <v>0.879367262723521</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0631096975259888</v>
+        <v>0.0525879012884909</v>
       </c>
       <c r="D48" t="n">
-        <v>0.159091649561789</v>
+        <v>0.194866272901458</v>
       </c>
       <c r="E48" t="n">
-        <v>0.049645518526185</v>
+        <v>0.057960192550492</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45773</v>
+        <v>45801</v>
       </c>
       <c r="B49" t="n">
-        <v>0.956761599396454</v>
+        <v>0.860871929665549</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0724971481340648</v>
+        <v>0.0559452072837434</v>
       </c>
       <c r="D49" t="n">
-        <v>0.160260469950147</v>
+        <v>0.223806825336859</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0561110996252312</v>
+        <v>0.0570924048423904</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45780</v>
+        <v>45808</v>
       </c>
       <c r="B50" t="n">
-        <v>0.928278977834251</v>
+        <v>0.834035196595594</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0701002993684856</v>
+        <v>0.0734527293128864</v>
       </c>
       <c r="D50" t="n">
-        <v>0.144293412692029</v>
+        <v>0.248352826203462</v>
       </c>
       <c r="E50" t="n">
-        <v>0.057252121171578</v>
+        <v>0.060078536714488</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45787</v>
+        <v>45815</v>
       </c>
       <c r="B51" t="n">
-        <v>0.901866121994244</v>
+        <v>0.828052718861831</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0599458006377676</v>
+        <v>0.0916460157497658</v>
       </c>
       <c r="D51" t="n">
-        <v>0.170182594563589</v>
+        <v>0.250467583497053</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0619914295308979</v>
+        <v>0.0586514909694367</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45794</v>
+        <v>45822</v>
       </c>
       <c r="B52" t="n">
-        <v>0.879367262723521</v>
+        <v>0.844489902506964</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0525879012884909</v>
+        <v>0.0953487610880168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.194866272901458</v>
+        <v>0.275139577190891</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0575031711388916</v>
+        <v>0.0586236761361623</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45801</v>
+        <v>45829</v>
       </c>
       <c r="B53" t="n">
-        <v>0.860871929665549</v>
+        <v>0.82460988987627</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0559452072837434</v>
+        <v>0.104290436057943</v>
       </c>
       <c r="D53" t="n">
-        <v>0.223806825336859</v>
+        <v>0.271276099200299</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0566304186325297</v>
+        <v>0.0565907575623272</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45808</v>
+        <v>45836</v>
       </c>
       <c r="B54" t="n">
-        <v>0.834035196595594</v>
+        <v>0.823430257058575</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0734527293128864</v>
+        <v>0.138110538504872</v>
       </c>
       <c r="D54" t="n">
-        <v>0.248352826203462</v>
+        <v>0.270097254708852</v>
       </c>
       <c r="E54" t="n">
-        <v>0.060078536714488</v>
+        <v>0.0534022849856888</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45815</v>
+        <v>45843</v>
       </c>
       <c r="B55" t="n">
-        <v>0.828052718861831</v>
+        <v>0.801316381178202</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0916460157497658</v>
+        <v>0.150429127678226</v>
       </c>
       <c r="D55" t="n">
-        <v>0.250467583497053</v>
+        <v>0.267816999817729</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0586514909694367</v>
+        <v>0.0490843807528398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45822</v>
+        <v>45850</v>
       </c>
       <c r="B56" t="n">
-        <v>0.844489902506964</v>
+        <v>0.77241596473274</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0953487610880168</v>
+        <v>0.167551622418879</v>
       </c>
       <c r="D56" t="n">
-        <v>0.275139577190891</v>
+        <v>0.253582114236743</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0587181013802645</v>
+        <v>0.0451954512302499</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45829</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.82460988987627</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.104290436057943</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.271276099200299</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.0566532474798516</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45836</v>
-      </c>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
+        <v>45857</v>
+      </c>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output/wp_figures.xlsx
+++ b/output/wp_figures.xlsx
@@ -7,11 +7,11 @@
   </bookViews>
   <sheets>
     <sheet name="All Initial" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Federal Initial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="All Continued" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Continued" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Federal Initial" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Federal Continued" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="State Fed Cont Smooth" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="State Cont Smooth" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="State Cont Smooth" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="State Fed Cont Smooth" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -28,16 +28,16 @@
     <t xml:space="preserve">ALL_yp_initial</t>
   </si>
   <si>
+    <t xml:space="preserve">ALL_continued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_yp_continued</t>
+  </si>
+  <si>
     <t xml:space="preserve">UCFE_initial</t>
   </si>
   <si>
     <t xml:space="preserve">UCFE_yp_initial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL_continued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL_yp_continued</t>
   </si>
   <si>
     <t xml:space="preserve">UCFE_continued</t>
@@ -49,21 +49,20 @@
     <t xml:space="preserve">DC</t>
   </si>
   <si>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
     <t xml:space="preserve">MD</t>
   </si>
   <si>
     <t xml:space="preserve">VA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
@@ -102,7 +101,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -407,618 +406,640 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
+        <v>45521</v>
       </c>
       <c r="B2" t="n">
-        <v>239.403</v>
+        <v>192.455</v>
       </c>
       <c r="C2" t="n">
-        <v>251.705</v>
+        <v>199.517</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
+        <v>45528</v>
       </c>
       <c r="B3" t="n">
-        <v>242.201</v>
+        <v>192.739</v>
       </c>
       <c r="C3" t="n">
-        <v>258.065</v>
+        <v>193.441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
+        <v>45535</v>
       </c>
       <c r="B4" t="n">
-        <v>280.569</v>
+        <v>190.623</v>
       </c>
       <c r="C4" t="n">
-        <v>258.328</v>
+        <v>191.353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45542</v>
       </c>
       <c r="B5" t="n">
-        <v>225.855</v>
+        <v>178.682</v>
       </c>
       <c r="C5" t="n">
-        <v>213.497</v>
+        <v>175.594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45549</v>
       </c>
       <c r="B6" t="n">
-        <v>216.673</v>
+        <v>186.832</v>
       </c>
       <c r="C6" t="n">
-        <v>205.55</v>
+        <v>176.586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45556</v>
       </c>
       <c r="B7" t="n">
-        <v>204.066</v>
+        <v>181.701</v>
       </c>
       <c r="C7" t="n">
-        <v>227.917</v>
+        <v>175.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45563</v>
       </c>
       <c r="B8" t="n">
-        <v>200.837</v>
+        <v>181.204</v>
       </c>
       <c r="C8" t="n">
-        <v>213.803</v>
+        <v>174.701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45570</v>
       </c>
       <c r="B9" t="n">
-        <v>192.455</v>
+        <v>236.171</v>
       </c>
       <c r="C9" t="n">
-        <v>199.517</v>
+        <v>199.743</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45577</v>
       </c>
       <c r="B10" t="n">
-        <v>192.739</v>
+        <v>225.23</v>
       </c>
       <c r="C10" t="n">
-        <v>193.441</v>
+        <v>182.394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45584</v>
       </c>
       <c r="B11" t="n">
-        <v>190.623</v>
+        <v>203.475</v>
       </c>
       <c r="C11" t="n">
-        <v>191.353</v>
+        <v>193.999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45591</v>
       </c>
       <c r="B12" t="n">
-        <v>178.682</v>
+        <v>201.443</v>
       </c>
       <c r="C12" t="n">
-        <v>175.594</v>
+        <v>199.306</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45598</v>
       </c>
       <c r="B13" t="n">
-        <v>186.832</v>
+        <v>212.741</v>
       </c>
       <c r="C13" t="n">
-        <v>176.586</v>
+        <v>214.161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45605</v>
       </c>
       <c r="B14" t="n">
-        <v>181.701</v>
+        <v>230.801</v>
       </c>
       <c r="C14" t="n">
-        <v>175.65</v>
+        <v>217.438</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45612</v>
       </c>
       <c r="B15" t="n">
-        <v>181.204</v>
+        <v>214.254</v>
       </c>
       <c r="C15" t="n">
-        <v>174.701</v>
+        <v>240.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45619</v>
       </c>
       <c r="B16" t="n">
-        <v>236.171</v>
+        <v>245.27</v>
       </c>
       <c r="C16" t="n">
-        <v>199.743</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45626</v>
       </c>
       <c r="B17" t="n">
-        <v>225.23</v>
+        <v>211.323</v>
       </c>
       <c r="C17" t="n">
-        <v>182.394</v>
+        <v>294.615</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45633</v>
       </c>
       <c r="B18" t="n">
-        <v>203.475</v>
+        <v>309.775</v>
       </c>
       <c r="C18" t="n">
-        <v>193.999</v>
+        <v>249.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45640</v>
       </c>
       <c r="B19" t="n">
-        <v>201.443</v>
+        <v>252.349</v>
       </c>
       <c r="C19" t="n">
-        <v>199.306</v>
+        <v>241.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45647</v>
       </c>
       <c r="B20" t="n">
-        <v>212.741</v>
+        <v>275.638</v>
       </c>
       <c r="C20" t="n">
-        <v>214.161</v>
+        <v>274.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45654</v>
       </c>
       <c r="B21" t="n">
-        <v>230.801</v>
+        <v>283.652</v>
       </c>
       <c r="C21" t="n">
-        <v>217.438</v>
+        <v>269.416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45661</v>
       </c>
       <c r="B22" t="n">
-        <v>214.254</v>
+        <v>306.295</v>
       </c>
       <c r="C22" t="n">
-        <v>240.99</v>
+        <v>318.906</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="n">
-        <v>245.27</v>
+        <v>352.63</v>
       </c>
       <c r="C23" t="n">
-        <v>199.75</v>
+        <v>291.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45675</v>
       </c>
       <c r="B24" t="n">
-        <v>211.323</v>
+        <v>284.6</v>
       </c>
       <c r="C24" t="n">
-        <v>294.615</v>
+        <v>249.947</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45682</v>
       </c>
       <c r="B25" t="n">
-        <v>309.775</v>
+        <v>228.484</v>
       </c>
       <c r="C25" t="n">
-        <v>249.09</v>
+        <v>263.919</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45689</v>
       </c>
       <c r="B26" t="n">
-        <v>252.349</v>
+        <v>241.111</v>
       </c>
       <c r="C26" t="n">
-        <v>241.04</v>
+        <v>234.729</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45696</v>
       </c>
       <c r="B27" t="n">
-        <v>275.638</v>
+        <v>232.685</v>
       </c>
       <c r="C27" t="n">
-        <v>274.84</v>
+        <v>223.985</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45703</v>
       </c>
       <c r="B28" t="n">
-        <v>283.652</v>
+        <v>223.539</v>
       </c>
       <c r="C28" t="n">
-        <v>269.416</v>
+        <v>199.337</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45710</v>
       </c>
       <c r="B29" t="n">
-        <v>306.295</v>
+        <v>220.856</v>
       </c>
       <c r="C29" t="n">
-        <v>318.906</v>
+        <v>195.604</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45717</v>
       </c>
       <c r="B30" t="n">
-        <v>352.63</v>
+        <v>226.019</v>
       </c>
       <c r="C30" t="n">
-        <v>291.33</v>
+        <v>214.425</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="n">
-        <v>284.6</v>
+        <v>214.007</v>
       </c>
       <c r="C31" t="n">
-        <v>249.947</v>
+        <v>202.723</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="n">
-        <v>228.484</v>
+        <v>207.398</v>
       </c>
       <c r="C32" t="n">
-        <v>263.919</v>
+        <v>191.773</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45738</v>
       </c>
       <c r="B33" t="n">
-        <v>241.111</v>
+        <v>199.9</v>
       </c>
       <c r="C33" t="n">
-        <v>234.729</v>
+        <v>193.923</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45745</v>
       </c>
       <c r="B34" t="n">
-        <v>232.685</v>
+        <v>200.081</v>
       </c>
       <c r="C34" t="n">
-        <v>223.985</v>
+        <v>197.349</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45752</v>
       </c>
       <c r="B35" t="n">
-        <v>223.539</v>
+        <v>216.534</v>
       </c>
       <c r="C35" t="n">
-        <v>199.337</v>
+        <v>215.265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45759</v>
       </c>
       <c r="B36" t="n">
-        <v>220.856</v>
+        <v>220.962</v>
       </c>
       <c r="C36" t="n">
-        <v>195.604</v>
+        <v>209.064</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45766</v>
       </c>
       <c r="B37" t="n">
-        <v>226.019</v>
+        <v>210.816</v>
       </c>
       <c r="C37" t="n">
-        <v>214.425</v>
+        <v>202.619</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45773</v>
       </c>
       <c r="B38" t="n">
-        <v>214.007</v>
+        <v>224.021</v>
       </c>
       <c r="C38" t="n">
-        <v>202.723</v>
+        <v>189.634</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45780</v>
       </c>
       <c r="B39" t="n">
-        <v>207.398</v>
+        <v>206.71</v>
       </c>
       <c r="C39" t="n">
-        <v>191.773</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45787</v>
       </c>
       <c r="B40" t="n">
-        <v>199.9</v>
+        <v>203.579</v>
       </c>
       <c r="C40" t="n">
-        <v>193.923</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45794</v>
       </c>
       <c r="B41" t="n">
-        <v>200.081</v>
+        <v>200.637</v>
       </c>
       <c r="C41" t="n">
-        <v>197.349</v>
+        <v>192.717</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45801</v>
       </c>
       <c r="B42" t="n">
-        <v>216.534</v>
+        <v>210.16</v>
       </c>
       <c r="C42" t="n">
-        <v>215.265</v>
+        <v>197.164</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>220.962</v>
+        <v>207.512</v>
       </c>
       <c r="C43" t="n">
-        <v>209.064</v>
+        <v>196.177</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45815</v>
       </c>
       <c r="B44" t="n">
-        <v>210.816</v>
+        <v>243.98</v>
       </c>
       <c r="C44" t="n">
-        <v>202.619</v>
+        <v>236.046</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45822</v>
       </c>
       <c r="B45" t="n">
-        <v>224.021</v>
+        <v>234.859</v>
       </c>
       <c r="C45" t="n">
-        <v>189.634</v>
+        <v>227.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45829</v>
       </c>
       <c r="B46" t="n">
-        <v>206.71</v>
+        <v>227.516</v>
       </c>
       <c r="C46" t="n">
-        <v>210.05</v>
+        <v>225.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45836</v>
       </c>
       <c r="B47" t="n">
-        <v>203.579</v>
+        <v>230.392</v>
       </c>
       <c r="C47" t="n">
-        <v>197.68</v>
+        <v>239.403</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45843</v>
       </c>
       <c r="B48" t="n">
-        <v>200.637</v>
+        <v>241.361</v>
       </c>
       <c r="C48" t="n">
-        <v>192.717</v>
+        <v>242.201</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45850</v>
       </c>
       <c r="B49" t="n">
-        <v>210.16</v>
+        <v>261.111</v>
       </c>
       <c r="C49" t="n">
-        <v>197.164</v>
+        <v>280.569</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45857</v>
       </c>
       <c r="B50" t="n">
-        <v>207.512</v>
+        <v>216.023</v>
       </c>
       <c r="C50" t="n">
-        <v>196.177</v>
+        <v>225.855</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45864</v>
       </c>
       <c r="B51" t="n">
-        <v>243.98</v>
+        <v>193.79</v>
       </c>
       <c r="C51" t="n">
-        <v>236.046</v>
+        <v>216.673</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45871</v>
       </c>
       <c r="B52" t="n">
-        <v>234.859</v>
+        <v>195.492</v>
       </c>
       <c r="C52" t="n">
-        <v>227.98</v>
+        <v>204.066</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45878</v>
       </c>
       <c r="B53" t="n">
-        <v>227.516</v>
+        <v>199.39</v>
       </c>
       <c r="C53" t="n">
-        <v>225.13</v>
+        <v>200.837</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45885</v>
       </c>
       <c r="B54" t="n">
-        <v>230.392</v>
+        <v>194.217</v>
       </c>
       <c r="C54" t="n">
-        <v>239.403</v>
+        <v>192.455</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45892</v>
       </c>
       <c r="B55" t="n">
-        <v>241.361</v>
+        <v>191.208</v>
       </c>
       <c r="C55" t="n">
-        <v>242.201</v>
+        <v>192.739</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45899</v>
       </c>
       <c r="B56" t="n">
-        <v>261.111</v>
+        <v>196.712</v>
       </c>
       <c r="C56" t="n">
-        <v>280.569</v>
+        <v>190.623</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45857</v>
+        <v>45906</v>
       </c>
       <c r="B57" t="n">
-        <v>216.023</v>
+        <v>204.862</v>
       </c>
       <c r="C57" t="n">
-        <v>225.855</v>
+        <v>178.682</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B58" t="n">
+        <v>195.433</v>
+      </c>
+      <c r="C58" t="n">
+        <v>186.832</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="B59" t="n">
+        <v>194.478</v>
+      </c>
+      <c r="C59" t="n">
+        <v>181.701</v>
       </c>
     </row>
   </sheetData>
@@ -1045,618 +1066,629 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
+        <v>45521</v>
       </c>
       <c r="B2" t="n">
-        <v>372</v>
+        <v>1843.217</v>
       </c>
       <c r="C2" t="n">
-        <v>407</v>
+        <v>1789.862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
+        <v>45528</v>
       </c>
       <c r="B3" t="n">
-        <v>327</v>
+        <v>1800.515</v>
       </c>
       <c r="C3" t="n">
-        <v>405</v>
+        <v>1747.737</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
+        <v>45535</v>
       </c>
       <c r="B4" t="n">
-        <v>476</v>
+        <v>1704.638</v>
       </c>
       <c r="C4" t="n">
-        <v>445</v>
+        <v>1655.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45542</v>
       </c>
       <c r="B5" t="n">
-        <v>392</v>
+        <v>1671.837</v>
       </c>
       <c r="C5" t="n">
-        <v>371</v>
+        <v>1645.927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45549</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>1628.081</v>
       </c>
       <c r="C6" t="n">
-        <v>385</v>
+        <v>1588.285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45556</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>1613.719</v>
       </c>
       <c r="C7" t="n">
-        <v>377</v>
+        <v>1585.277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45563</v>
       </c>
       <c r="B8" t="n">
-        <v>336</v>
+        <v>1614.385</v>
       </c>
       <c r="C8" t="n">
-        <v>348</v>
+        <v>1555.172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45570</v>
       </c>
       <c r="B9" t="n">
-        <v>285</v>
+        <v>1598.241</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>1542.397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45577</v>
       </c>
       <c r="B10" t="n">
-        <v>307</v>
+        <v>1627.825</v>
       </c>
       <c r="C10" t="n">
-        <v>371</v>
+        <v>1572.658</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45584</v>
       </c>
       <c r="B11" t="n">
-        <v>274</v>
+        <v>1616.144</v>
       </c>
       <c r="C11" t="n">
-        <v>314</v>
+        <v>1574.471</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45591</v>
       </c>
       <c r="B12" t="n">
-        <v>266</v>
+        <v>1646.982</v>
       </c>
       <c r="C12" t="n">
-        <v>272</v>
+        <v>1607.693</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45598</v>
       </c>
       <c r="B13" t="n">
-        <v>313</v>
+        <v>1647.301</v>
       </c>
       <c r="C13" t="n">
-        <v>363</v>
+        <v>1578.946</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45605</v>
       </c>
       <c r="B14" t="n">
-        <v>278</v>
+        <v>1660.894</v>
       </c>
       <c r="C14" t="n">
-        <v>363</v>
+        <v>1654.732</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45612</v>
       </c>
       <c r="B15" t="n">
-        <v>313</v>
+        <v>1721.154</v>
       </c>
       <c r="C15" t="n">
-        <v>390</v>
+        <v>1555.596</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45619</v>
       </c>
       <c r="B16" t="n">
-        <v>351</v>
+        <v>1661.071</v>
       </c>
       <c r="C16" t="n">
-        <v>464</v>
+        <v>1845.084</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45626</v>
       </c>
       <c r="B17" t="n">
-        <v>434</v>
+        <v>1933.23</v>
       </c>
       <c r="C17" t="n">
-        <v>439</v>
+        <v>1767.267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45633</v>
       </c>
       <c r="B18" t="n">
-        <v>392</v>
+        <v>1864.863</v>
       </c>
       <c r="C18" t="n">
-        <v>460</v>
+        <v>1835.427</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45640</v>
       </c>
       <c r="B19" t="n">
-        <v>533</v>
+        <v>1946.787</v>
       </c>
       <c r="C19" t="n">
-        <v>628</v>
+        <v>1836.539</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45647</v>
       </c>
       <c r="B20" t="n">
-        <v>507</v>
+        <v>1860.888</v>
       </c>
       <c r="C20" t="n">
-        <v>519</v>
+        <v>1902.054</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45654</v>
       </c>
       <c r="B21" t="n">
-        <v>622</v>
+        <v>2187.475</v>
       </c>
       <c r="C21" t="n">
-        <v>655</v>
+        <v>2104.257</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45661</v>
       </c>
       <c r="B22" t="n">
-        <v>529</v>
+        <v>2273.651</v>
       </c>
       <c r="C22" t="n">
-        <v>662</v>
+        <v>2122.561</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="n">
-        <v>760</v>
+        <v>2246.551</v>
       </c>
       <c r="C23" t="n">
-        <v>511</v>
+        <v>2053.289</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45675</v>
       </c>
       <c r="B24" t="n">
-        <v>399</v>
+        <v>2170.633</v>
       </c>
       <c r="C24" t="n">
-        <v>729</v>
+        <v>2181.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45682</v>
       </c>
       <c r="B25" t="n">
-        <v>759</v>
+        <v>2250.894</v>
       </c>
       <c r="C25" t="n">
-        <v>747</v>
+        <v>2130.018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45689</v>
       </c>
       <c r="B26" t="n">
-        <v>549</v>
+        <v>2185.828</v>
       </c>
       <c r="C26" t="n">
-        <v>514</v>
+        <v>2139.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45696</v>
       </c>
       <c r="B27" t="n">
-        <v>507</v>
+        <v>2191.042</v>
       </c>
       <c r="C27" t="n">
-        <v>580</v>
+        <v>2092.787</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45703</v>
       </c>
       <c r="B28" t="n">
-        <v>343</v>
+        <v>2160.103</v>
       </c>
       <c r="C28" t="n">
-        <v>415</v>
+        <v>2092.108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45710</v>
       </c>
       <c r="B29" t="n">
-        <v>479</v>
+        <v>2229.07</v>
       </c>
       <c r="C29" t="n">
-        <v>643</v>
+        <v>2113.581</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45717</v>
       </c>
       <c r="B30" t="n">
-        <v>597</v>
+        <v>2149.919</v>
       </c>
       <c r="C30" t="n">
-        <v>762</v>
+        <v>2078.603</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="n">
-        <v>495</v>
+        <v>2116.538</v>
       </c>
       <c r="C31" t="n">
-        <v>420</v>
+        <v>2008.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="n">
-        <v>497</v>
+        <v>2072.402</v>
       </c>
       <c r="C32" t="n">
-        <v>502</v>
+        <v>2012.613</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45738</v>
       </c>
       <c r="B33" t="n">
-        <v>599</v>
+        <v>2058.751</v>
       </c>
       <c r="C33" t="n">
-        <v>411</v>
+        <v>1937.982</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45745</v>
       </c>
       <c r="B34" t="n">
-        <v>613</v>
+        <v>1985.73</v>
       </c>
       <c r="C34" t="n">
-        <v>382</v>
+        <v>1928.017</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45752</v>
       </c>
       <c r="B35" t="n">
-        <v>613</v>
+        <v>1943.418</v>
       </c>
       <c r="C35" t="n">
-        <v>337</v>
+        <v>1848.827</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45759</v>
       </c>
       <c r="B36" t="n">
-        <v>1634</v>
+        <v>1880.372</v>
       </c>
       <c r="C36" t="n">
-        <v>330</v>
+        <v>1812.811</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45766</v>
       </c>
       <c r="B37" t="n">
-        <v>1580</v>
+        <v>1898.153</v>
       </c>
       <c r="C37" t="n">
-        <v>393</v>
+        <v>1753.465</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45773</v>
       </c>
       <c r="B38" t="n">
-        <v>1066</v>
+        <v>1838.279</v>
       </c>
       <c r="C38" t="n">
-        <v>365</v>
+        <v>1743.445</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45780</v>
       </c>
       <c r="B39" t="n">
-        <v>821</v>
+        <v>1782.724</v>
       </c>
       <c r="C39" t="n">
-        <v>362</v>
+        <v>1686.177</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45787</v>
       </c>
       <c r="B40" t="n">
-        <v>564</v>
+        <v>1779.686</v>
       </c>
       <c r="C40" t="n">
-        <v>371</v>
+        <v>1686.782</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45794</v>
       </c>
       <c r="B41" t="n">
-        <v>508</v>
+        <v>1775.51</v>
       </c>
       <c r="C41" t="n">
-        <v>322</v>
+        <v>1666.648</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45801</v>
       </c>
       <c r="B42" t="n">
-        <v>542</v>
+        <v>1755.336</v>
       </c>
       <c r="C42" t="n">
-        <v>327</v>
+        <v>1670.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>657</v>
+        <v>1826.063</v>
       </c>
       <c r="C43" t="n">
-        <v>361</v>
+        <v>1708.158</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45815</v>
       </c>
       <c r="B44" t="n">
-        <v>466</v>
+        <v>1813.454</v>
       </c>
       <c r="C44" t="n">
-        <v>365</v>
+        <v>1727.754</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45822</v>
       </c>
       <c r="B45" t="n">
-        <v>465</v>
+        <v>1862.043</v>
       </c>
       <c r="C45" t="n">
-        <v>343</v>
+        <v>1748.567</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45829</v>
       </c>
       <c r="B46" t="n">
-        <v>434</v>
+        <v>1900.787</v>
       </c>
       <c r="C46" t="n">
-        <v>385</v>
+        <v>1821.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45836</v>
       </c>
       <c r="B47" t="n">
-        <v>599</v>
+        <v>1895.589</v>
       </c>
       <c r="C47" t="n">
-        <v>386</v>
+        <v>1795.365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45843</v>
       </c>
       <c r="B48" t="n">
-        <v>592</v>
+        <v>2011.507</v>
       </c>
       <c r="C48" t="n">
-        <v>338</v>
+        <v>1945.731</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45850</v>
       </c>
       <c r="B49" t="n">
-        <v>523</v>
+        <v>2006.612</v>
       </c>
       <c r="C49" t="n">
-        <v>353</v>
+        <v>1914.075</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45857</v>
       </c>
       <c r="B50" t="n">
-        <v>553</v>
+        <v>2005.922</v>
       </c>
       <c r="C50" t="n">
-        <v>400</v>
+        <v>1934.382</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45864</v>
       </c>
       <c r="B51" t="n">
-        <v>532</v>
+        <v>1999.973</v>
       </c>
       <c r="C51" t="n">
-        <v>419</v>
+        <v>1907.041</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45871</v>
       </c>
       <c r="B52" t="n">
-        <v>472</v>
+        <v>1973.535</v>
       </c>
       <c r="C52" t="n">
-        <v>344</v>
+        <v>1883.372</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45878</v>
       </c>
       <c r="B53" t="n">
-        <v>453</v>
+        <v>1955.067</v>
       </c>
       <c r="C53" t="n">
-        <v>336</v>
+        <v>1857.167</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45885</v>
       </c>
       <c r="B54" t="n">
-        <v>438</v>
+        <v>1934.367</v>
       </c>
       <c r="C54" t="n">
-        <v>372</v>
+        <v>1843.217</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45892</v>
       </c>
       <c r="B55" t="n">
-        <v>596</v>
+        <v>1892.212</v>
       </c>
       <c r="C55" t="n">
-        <v>327</v>
+        <v>1800.515</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45899</v>
       </c>
       <c r="B56" t="n">
-        <v>789</v>
+        <v>1803.344</v>
       </c>
       <c r="C56" t="n">
-        <v>476</v>
+        <v>1704.638</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45857</v>
+        <v>45906</v>
       </c>
       <c r="B57" t="n">
-        <v>722</v>
+        <v>1759.868</v>
       </c>
       <c r="C57" t="n">
-        <v>392</v>
+        <v>1671.837</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1752.826</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1628.081</v>
       </c>
     </row>
   </sheetData>
@@ -1683,616 +1715,629 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
+        <v>45521</v>
       </c>
       <c r="B2" t="n">
-        <v>1795.365</v>
+        <v>285</v>
       </c>
       <c r="C2" t="n">
-        <v>1724.28</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
+        <v>45528</v>
       </c>
       <c r="B3" t="n">
-        <v>1945.731</v>
+        <v>307</v>
       </c>
       <c r="C3" t="n">
-        <v>1887.928</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
+        <v>45535</v>
       </c>
       <c r="B4" t="n">
-        <v>1914.075</v>
+        <v>274</v>
       </c>
       <c r="C4" t="n">
-        <v>1835.614</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45542</v>
       </c>
       <c r="B5" t="n">
-        <v>1934.382</v>
+        <v>266</v>
       </c>
       <c r="C5" t="n">
-        <v>1827.375</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45549</v>
       </c>
       <c r="B6" t="n">
-        <v>1907.041</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>1809.776</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45556</v>
       </c>
       <c r="B7" t="n">
-        <v>1883.372</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>1814.133</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45563</v>
       </c>
       <c r="B8" t="n">
-        <v>1857.167</v>
+        <v>313</v>
       </c>
       <c r="C8" t="n">
-        <v>1802.463</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45570</v>
       </c>
       <c r="B9" t="n">
-        <v>1843.217</v>
+        <v>351</v>
       </c>
       <c r="C9" t="n">
-        <v>1789.862</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45577</v>
       </c>
       <c r="B10" t="n">
-        <v>1800.515</v>
+        <v>434</v>
       </c>
       <c r="C10" t="n">
-        <v>1747.737</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45584</v>
       </c>
       <c r="B11" t="n">
-        <v>1704.638</v>
+        <v>392</v>
       </c>
       <c r="C11" t="n">
-        <v>1655.84</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45591</v>
       </c>
       <c r="B12" t="n">
-        <v>1671.837</v>
+        <v>533</v>
       </c>
       <c r="C12" t="n">
-        <v>1645.927</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45598</v>
       </c>
       <c r="B13" t="n">
-        <v>1628.081</v>
+        <v>507</v>
       </c>
       <c r="C13" t="n">
-        <v>1588.285</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45605</v>
       </c>
       <c r="B14" t="n">
-        <v>1613.719</v>
+        <v>622</v>
       </c>
       <c r="C14" t="n">
-        <v>1585.277</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45612</v>
       </c>
       <c r="B15" t="n">
-        <v>1614.385</v>
+        <v>529</v>
       </c>
       <c r="C15" t="n">
-        <v>1555.172</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45619</v>
       </c>
       <c r="B16" t="n">
-        <v>1598.241</v>
+        <v>760</v>
       </c>
       <c r="C16" t="n">
-        <v>1542.397</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45626</v>
       </c>
       <c r="B17" t="n">
-        <v>1627.825</v>
+        <v>399</v>
       </c>
       <c r="C17" t="n">
-        <v>1572.658</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45633</v>
       </c>
       <c r="B18" t="n">
-        <v>1616.144</v>
+        <v>759</v>
       </c>
       <c r="C18" t="n">
-        <v>1574.471</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45640</v>
       </c>
       <c r="B19" t="n">
-        <v>1646.982</v>
+        <v>549</v>
       </c>
       <c r="C19" t="n">
-        <v>1607.693</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45647</v>
       </c>
       <c r="B20" t="n">
-        <v>1647.301</v>
+        <v>507</v>
       </c>
       <c r="C20" t="n">
-        <v>1578.946</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45654</v>
       </c>
       <c r="B21" t="n">
-        <v>1660.894</v>
+        <v>343</v>
       </c>
       <c r="C21" t="n">
-        <v>1654.732</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45661</v>
       </c>
       <c r="B22" t="n">
-        <v>1721.154</v>
+        <v>479</v>
       </c>
       <c r="C22" t="n">
-        <v>1555.596</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="n">
-        <v>1661.071</v>
+        <v>597</v>
       </c>
       <c r="C23" t="n">
-        <v>1845.084</v>
+        <v>762</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45675</v>
       </c>
       <c r="B24" t="n">
-        <v>1933.23</v>
+        <v>495</v>
       </c>
       <c r="C24" t="n">
-        <v>1767.267</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45682</v>
       </c>
       <c r="B25" t="n">
-        <v>1864.863</v>
+        <v>497</v>
       </c>
       <c r="C25" t="n">
-        <v>1835.427</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45689</v>
       </c>
       <c r="B26" t="n">
-        <v>1946.787</v>
+        <v>599</v>
       </c>
       <c r="C26" t="n">
-        <v>1836.539</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45696</v>
       </c>
       <c r="B27" t="n">
-        <v>1860.888</v>
+        <v>613</v>
       </c>
       <c r="C27" t="n">
-        <v>1902.054</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45703</v>
       </c>
       <c r="B28" t="n">
-        <v>2187.475</v>
+        <v>613</v>
       </c>
       <c r="C28" t="n">
-        <v>2104.257</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45710</v>
       </c>
       <c r="B29" t="n">
-        <v>2273.651</v>
+        <v>1634</v>
       </c>
       <c r="C29" t="n">
-        <v>2122.561</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45717</v>
       </c>
       <c r="B30" t="n">
-        <v>2246.551</v>
+        <v>1580</v>
       </c>
       <c r="C30" t="n">
-        <v>2053.289</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="n">
-        <v>2170.633</v>
+        <v>1066</v>
       </c>
       <c r="C31" t="n">
-        <v>2181.43</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="n">
-        <v>2250.894</v>
+        <v>821</v>
       </c>
       <c r="C32" t="n">
-        <v>2130.018</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45738</v>
       </c>
       <c r="B33" t="n">
-        <v>2185.828</v>
+        <v>564</v>
       </c>
       <c r="C33" t="n">
-        <v>2139.97</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45745</v>
       </c>
       <c r="B34" t="n">
-        <v>2191.042</v>
+        <v>508</v>
       </c>
       <c r="C34" t="n">
-        <v>2092.787</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45752</v>
       </c>
       <c r="B35" t="n">
-        <v>2160.103</v>
+        <v>542</v>
       </c>
       <c r="C35" t="n">
-        <v>2092.108</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45759</v>
       </c>
       <c r="B36" t="n">
-        <v>2229.07</v>
+        <v>657</v>
       </c>
       <c r="C36" t="n">
-        <v>2113.581</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45766</v>
       </c>
       <c r="B37" t="n">
-        <v>2149.919</v>
+        <v>466</v>
       </c>
       <c r="C37" t="n">
-        <v>2078.603</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45773</v>
       </c>
       <c r="B38" t="n">
-        <v>2116.538</v>
+        <v>465</v>
       </c>
       <c r="C38" t="n">
-        <v>2008.79</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45780</v>
       </c>
       <c r="B39" t="n">
-        <v>2072.402</v>
+        <v>434</v>
       </c>
       <c r="C39" t="n">
-        <v>2012.613</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45787</v>
       </c>
       <c r="B40" t="n">
-        <v>2058.751</v>
+        <v>599</v>
       </c>
       <c r="C40" t="n">
-        <v>1937.982</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45794</v>
       </c>
       <c r="B41" t="n">
-        <v>1985.73</v>
+        <v>592</v>
       </c>
       <c r="C41" t="n">
-        <v>1928.017</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45801</v>
       </c>
       <c r="B42" t="n">
-        <v>1943.418</v>
+        <v>523</v>
       </c>
       <c r="C42" t="n">
-        <v>1848.827</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>1880.372</v>
+        <v>553</v>
       </c>
       <c r="C43" t="n">
-        <v>1812.811</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45815</v>
       </c>
       <c r="B44" t="n">
-        <v>1898.153</v>
+        <v>532</v>
       </c>
       <c r="C44" t="n">
-        <v>1753.465</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45822</v>
       </c>
       <c r="B45" t="n">
-        <v>1838.279</v>
+        <v>472</v>
       </c>
       <c r="C45" t="n">
-        <v>1743.445</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45829</v>
       </c>
       <c r="B46" t="n">
-        <v>1782.724</v>
+        <v>453</v>
       </c>
       <c r="C46" t="n">
-        <v>1686.177</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45836</v>
       </c>
       <c r="B47" t="n">
-        <v>1779.686</v>
+        <v>438</v>
       </c>
       <c r="C47" t="n">
-        <v>1686.782</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45843</v>
       </c>
       <c r="B48" t="n">
-        <v>1775.51</v>
+        <v>596</v>
       </c>
       <c r="C48" t="n">
-        <v>1666.648</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45850</v>
       </c>
       <c r="B49" t="n">
-        <v>1755.336</v>
+        <v>789</v>
       </c>
       <c r="C49" t="n">
-        <v>1670.55</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45857</v>
       </c>
       <c r="B50" t="n">
-        <v>1826.063</v>
+        <v>722</v>
       </c>
       <c r="C50" t="n">
-        <v>1708.158</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45864</v>
       </c>
       <c r="B51" t="n">
-        <v>1813.454</v>
+        <v>708</v>
       </c>
       <c r="C51" t="n">
-        <v>1727.754</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45871</v>
       </c>
       <c r="B52" t="n">
-        <v>1862.043</v>
+        <v>637</v>
       </c>
       <c r="C52" t="n">
-        <v>1748.567</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45878</v>
       </c>
       <c r="B53" t="n">
-        <v>1900.787</v>
+        <v>635</v>
       </c>
       <c r="C53" t="n">
-        <v>1821.4</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45885</v>
       </c>
       <c r="B54" t="n">
-        <v>1895.589</v>
+        <v>588</v>
       </c>
       <c r="C54" t="n">
-        <v>1795.365</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45892</v>
       </c>
       <c r="B55" t="n">
-        <v>2011.503</v>
+        <v>515</v>
       </c>
       <c r="C55" t="n">
-        <v>1945.731</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45899</v>
       </c>
       <c r="B56" t="n">
-        <v>2006.599</v>
+        <v>527</v>
       </c>
       <c r="C56" t="n">
-        <v>1914.075</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="B57"/>
+        <v>45906</v>
+      </c>
+      <c r="B57" t="n">
+        <v>572</v>
+      </c>
       <c r="C57" t="n">
-        <v>1934.382</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B58" t="n">
+        <v>635</v>
+      </c>
+      <c r="C58" t="n">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -2319,616 +2364,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
+        <v>45521</v>
       </c>
       <c r="B2" t="n">
-        <v>4605</v>
+        <v>4308</v>
       </c>
       <c r="C2" t="n">
-        <v>4773</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
+        <v>45528</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
+        <v>4191</v>
       </c>
       <c r="C3" t="n">
-        <v>4863</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
+        <v>45535</v>
       </c>
       <c r="B4" t="n">
-        <v>4658</v>
+        <v>3852</v>
       </c>
       <c r="C4" t="n">
-        <v>4869</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45542</v>
       </c>
       <c r="B5" t="n">
-        <v>4767</v>
+        <v>3898</v>
       </c>
       <c r="C5" t="n">
-        <v>4910</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45549</v>
       </c>
       <c r="B6" t="n">
-        <v>4855</v>
+        <v>4001</v>
       </c>
       <c r="C6" t="n">
-        <v>5106</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45556</v>
       </c>
       <c r="B7" t="n">
-        <v>4505</v>
+        <v>4033</v>
       </c>
       <c r="C7" t="n">
-        <v>4912</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45563</v>
       </c>
       <c r="B8" t="n">
-        <v>4632</v>
+        <v>3929</v>
       </c>
       <c r="C8" t="n">
-        <v>4840</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45570</v>
       </c>
       <c r="B9" t="n">
-        <v>4308</v>
+        <v>3819</v>
       </c>
       <c r="C9" t="n">
-        <v>4469</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45577</v>
       </c>
       <c r="B10" t="n">
-        <v>4191</v>
+        <v>3903</v>
       </c>
       <c r="C10" t="n">
-        <v>4552</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45584</v>
       </c>
       <c r="B11" t="n">
-        <v>3852</v>
+        <v>4038</v>
       </c>
       <c r="C11" t="n">
-        <v>4164</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45591</v>
       </c>
       <c r="B12" t="n">
-        <v>3898</v>
+        <v>4246</v>
       </c>
       <c r="C12" t="n">
-        <v>4295</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45598</v>
       </c>
       <c r="B13" t="n">
-        <v>4001</v>
+        <v>4454</v>
       </c>
       <c r="C13" t="n">
-        <v>4123</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45605</v>
       </c>
       <c r="B14" t="n">
-        <v>4033</v>
+        <v>4760</v>
       </c>
       <c r="C14" t="n">
-        <v>4148</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45612</v>
       </c>
       <c r="B15" t="n">
-        <v>3929</v>
+        <v>5023</v>
       </c>
       <c r="C15" t="n">
-        <v>4200</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45619</v>
       </c>
       <c r="B16" t="n">
-        <v>3819</v>
+        <v>5081</v>
       </c>
       <c r="C16" t="n">
-        <v>4121</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45626</v>
       </c>
       <c r="B17" t="n">
-        <v>3903</v>
+        <v>5997</v>
       </c>
       <c r="C17" t="n">
-        <v>4267</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45633</v>
       </c>
       <c r="B18" t="n">
-        <v>4038</v>
+        <v>6031</v>
       </c>
       <c r="C18" t="n">
-        <v>4309</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45640</v>
       </c>
       <c r="B19" t="n">
-        <v>4246</v>
+        <v>6577</v>
       </c>
       <c r="C19" t="n">
-        <v>4638</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45647</v>
       </c>
       <c r="B20" t="n">
-        <v>4454</v>
+        <v>6210</v>
       </c>
       <c r="C20" t="n">
-        <v>4741</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45654</v>
       </c>
       <c r="B21" t="n">
-        <v>4760</v>
+        <v>6374</v>
       </c>
       <c r="C21" t="n">
-        <v>5179</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45661</v>
       </c>
       <c r="B22" t="n">
-        <v>5023</v>
+        <v>6854</v>
       </c>
       <c r="C22" t="n">
-        <v>5045</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="n">
-        <v>5081</v>
+        <v>7381</v>
       </c>
       <c r="C23" t="n">
-        <v>5791</v>
+        <v>6708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45675</v>
       </c>
       <c r="B24" t="n">
-        <v>5997</v>
+        <v>6684</v>
       </c>
       <c r="C24" t="n">
-        <v>6131</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45682</v>
       </c>
       <c r="B25" t="n">
-        <v>6031</v>
+        <v>7470</v>
       </c>
       <c r="C25" t="n">
-        <v>6272</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45689</v>
       </c>
       <c r="B26" t="n">
-        <v>6577</v>
+        <v>7120</v>
       </c>
       <c r="C26" t="n">
-        <v>6427</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45696</v>
       </c>
       <c r="B27" t="n">
-        <v>6210</v>
+        <v>7621</v>
       </c>
       <c r="C27" t="n">
-        <v>6284</v>
+        <v>6819</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45703</v>
       </c>
       <c r="B28" t="n">
-        <v>6374</v>
+        <v>7422</v>
       </c>
       <c r="C28" t="n">
-        <v>6577</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45710</v>
       </c>
       <c r="B29" t="n">
-        <v>6854</v>
+        <v>8230</v>
       </c>
       <c r="C29" t="n">
-        <v>6766</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45717</v>
       </c>
       <c r="B30" t="n">
-        <v>7381</v>
+        <v>8929</v>
       </c>
       <c r="C30" t="n">
-        <v>6708</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="n">
-        <v>6684</v>
+        <v>9136</v>
       </c>
       <c r="C31" t="n">
-        <v>7383</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="n">
-        <v>7470</v>
+        <v>8246</v>
       </c>
       <c r="C32" t="n">
-        <v>6953</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45738</v>
       </c>
       <c r="B33" t="n">
-        <v>7120</v>
+        <v>7721</v>
       </c>
       <c r="C33" t="n">
-        <v>6893</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45745</v>
       </c>
       <c r="B34" t="n">
-        <v>7621</v>
+        <v>7192</v>
       </c>
       <c r="C34" t="n">
-        <v>6819</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45752</v>
       </c>
       <c r="B35" t="n">
-        <v>7422</v>
+        <v>7019</v>
       </c>
       <c r="C35" t="n">
-        <v>6594</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45759</v>
       </c>
       <c r="B36" t="n">
-        <v>8230</v>
+        <v>6640</v>
       </c>
       <c r="C36" t="n">
-        <v>6876</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45766</v>
       </c>
       <c r="B37" t="n">
-        <v>8929</v>
+        <v>6716</v>
       </c>
       <c r="C37" t="n">
-        <v>6208</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45773</v>
       </c>
       <c r="B38" t="n">
-        <v>9136</v>
+        <v>6570</v>
       </c>
       <c r="C38" t="n">
-        <v>6241</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45780</v>
       </c>
       <c r="B39" t="n">
-        <v>8246</v>
+        <v>6473</v>
       </c>
       <c r="C39" t="n">
-        <v>5891</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45787</v>
       </c>
       <c r="B40" t="n">
-        <v>7721</v>
+        <v>6377</v>
       </c>
       <c r="C40" t="n">
-        <v>5881</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45794</v>
       </c>
       <c r="B41" t="n">
-        <v>7192</v>
+        <v>6717</v>
       </c>
       <c r="C41" t="n">
-        <v>5546</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45801</v>
       </c>
       <c r="B42" t="n">
-        <v>7019</v>
+        <v>6323</v>
       </c>
       <c r="C42" t="n">
-        <v>5274</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>6640</v>
+        <v>7076</v>
       </c>
       <c r="C43" t="n">
-        <v>5091</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45815</v>
       </c>
       <c r="B44" t="n">
-        <v>6716</v>
+        <v>6738</v>
       </c>
       <c r="C44" t="n">
-        <v>5030</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45822</v>
       </c>
       <c r="B45" t="n">
-        <v>6570</v>
+        <v>7103</v>
       </c>
       <c r="C45" t="n">
-        <v>4764</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45829</v>
       </c>
       <c r="B46" t="n">
-        <v>6473</v>
+        <v>6947</v>
       </c>
       <c r="C46" t="n">
-        <v>4737</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45836</v>
       </c>
       <c r="B47" t="n">
-        <v>6377</v>
+        <v>7035</v>
       </c>
       <c r="C47" t="n">
-        <v>4494</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45843</v>
       </c>
       <c r="B48" t="n">
-        <v>6717</v>
+        <v>7226</v>
       </c>
       <c r="C48" t="n">
-        <v>4648</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45850</v>
       </c>
       <c r="B49" t="n">
-        <v>6323</v>
+        <v>7407</v>
       </c>
       <c r="C49" t="n">
-        <v>4401</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45857</v>
       </c>
       <c r="B50" t="n">
-        <v>7076</v>
+        <v>7831</v>
       </c>
       <c r="C50" t="n">
-        <v>4634</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45864</v>
       </c>
       <c r="B51" t="n">
-        <v>6738</v>
+        <v>8193</v>
       </c>
       <c r="C51" t="n">
-        <v>4553</v>
+        <v>4855</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45871</v>
       </c>
       <c r="B52" t="n">
-        <v>7103</v>
+        <v>8237</v>
       </c>
       <c r="C52" t="n">
-        <v>4568</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45878</v>
       </c>
       <c r="B53" t="n">
-        <v>6947</v>
+        <v>8456</v>
       </c>
       <c r="C53" t="n">
-        <v>4433</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45885</v>
       </c>
       <c r="B54" t="n">
-        <v>7035</v>
+        <v>8128</v>
       </c>
       <c r="C54" t="n">
-        <v>4605</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45892</v>
       </c>
       <c r="B55" t="n">
-        <v>7226</v>
+        <v>8211</v>
       </c>
       <c r="C55" t="n">
-        <v>4711</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45899</v>
       </c>
       <c r="B56" t="n">
-        <v>7407</v>
+        <v>7863</v>
       </c>
       <c r="C56" t="n">
-        <v>4658</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="B57"/>
+        <v>45906</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8168</v>
+      </c>
       <c r="C57" t="n">
-        <v>4767</v>
+        <v>3898</v>
       </c>
     </row>
   </sheetData>
@@ -2952,932 +2999,1194 @@
       <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
+        <v>45157</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.682643323527301</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.269086059042244</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>45164</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.752462149051889</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.278731577177855</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
+        <v>45171</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.69588188463487</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.285075465258575</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45178</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.335394126738794</v>
+        <v>0.659128917327129</v>
       </c>
       <c r="C5" t="n">
-        <v>0.184381778741866</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.105960264900662</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.0347154262168426</v>
+        <v>0.288155928025338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45185</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.258943781942078</v>
+        <v>0.71851908866995</v>
       </c>
       <c r="C6" t="n">
-        <v>0.247727272727273</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.122257053291536</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.0383329957464047</v>
+        <v>0.292300734442642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45192</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.163339382940109</v>
+        <v>0.688183807439825</v>
       </c>
       <c r="C7" t="n">
-        <v>0.16331096196868</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.13677811550152</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.0511188563923827</v>
+        <v>0.294048419132878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45199</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0371819960861057</v>
+        <v>0.745592754326379</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0455486542443064</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.16566265060241</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.0510420882233913</v>
+        <v>0.292430153360314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45206</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0504672897196261</v>
+        <v>0.829532114707362</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.129032258064516</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.143712574850299</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.0531380969627981</v>
+        <v>0.292538062193876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45213</v>
       </c>
       <c r="B10" t="n">
-        <v>0.043557168784029</v>
+        <v>0.82242374278648</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.175298804780876</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0925373134328358</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.0605657060672242</v>
+        <v>0.286920428436942</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45220</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00349650349650354</v>
+        <v>0.912273302404049</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.17979797979798</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0501474926253687</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.0578085991678224</v>
+        <v>0.282927690123362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45227</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.10327868852459</v>
+        <v>0.998352267799844</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.120689655172414</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.00574712643678166</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.0704233409610984</v>
+        <v>0.276427174122571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45234</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.185185185185185</v>
+        <v>1.08845296477931</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0934182590233545</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0144092219020173</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.0695692774600211</v>
+        <v>0.275848614432846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45241</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.142140468227425</v>
+        <v>1.19650167473018</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.122661122661123</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0705882352941176</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.0565451285116557</v>
+        <v>0.262878986207589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45248</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.139767054908486</v>
+        <v>1.14916869045395</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.112244897959184</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.113095238095238</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.0539782893952045</v>
+        <v>0.253808435820337</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45255</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.156589147286822</v>
+        <v>1.14369202226345</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.145593869731801</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.154761904761905</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.0488187078109933</v>
+        <v>0.229470488926282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45262</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.174698795180723</v>
+        <v>1.07848915081704</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.146153846153846</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.144092219020173</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.0628585086042065</v>
+        <v>0.20342743368623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45269</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.217194570135747</v>
+        <v>1.02695231513476</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0452674897119342</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0988700564971752</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.0714919808249985</v>
+        <v>0.182789382857749</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45276</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.224340175953079</v>
+        <v>0.936523280167553</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0224032586558045</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0657142857142856</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.0766657052206519</v>
+        <v>0.16803310758329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45283</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.190553745928339</v>
+        <v>0.880585211546066</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.12593984962406</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0588235294117647</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.0731829573934837</v>
+        <v>0.149667696227104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45290</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.117543859649123</v>
+        <v>0.827831270059606</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147329650092081</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.070336391437309</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.0725605554672178</v>
+        <v>0.137149365060206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45297</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.106830122591944</v>
+        <v>0.725096194955109</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.155752212389381</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.133550488599349</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.0571341121256951</v>
+        <v>0.127234983606052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45304</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.072992700729927</v>
+        <v>0.683745214061956</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.194871794871795</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.192567567567568</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.0692811717093852</v>
+        <v>0.112721865125587</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45311</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.15609756097561</v>
+        <v>0.59653417509502</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.140138408304498</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.228668941979522</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.0580240223968211</v>
+        <v>0.120158906584597</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45318</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.163430420711974</v>
+        <v>0.448905338435481</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.201907790143084</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.225589225589226</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.0476354404234262</v>
+        <v>0.115352464366679</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45325</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.158238172920065</v>
+        <v>0.368510431829209</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.214397496087637</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.195439739413681</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.0379757117907478</v>
+        <v>0.11182537948803</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45332</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.141666666666667</v>
+        <v>0.294063079777366</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.204180064308682</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.188925081433225</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0.0119057099625707</v>
+        <v>0.107616691372684</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45339</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0666666666666667</v>
+        <v>0.220064178348252</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.188356164383562</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.186885245901639</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.014397496087637</v>
+        <v>0.0988033469584233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45346</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.104712041884817</v>
+        <v>0.155271015739663</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0557692307692308</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.221122112211221</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.00149689107238815</v>
+        <v>0.0903828995441902</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45353</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.0670194003527337</v>
+        <v>0.141088859816846</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0101214574898786</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.241830065359477</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.0183785836339472</v>
+        <v>0.0878492655366059</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45360</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.107615894039735</v>
+        <v>0.107121807465619</v>
       </c>
       <c r="C31" t="n">
-        <v>0.090717299578059</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.216981132075472</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.00513960778595901</v>
+        <v>0.084035657662493</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45367</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0329861111111112</v>
+        <v>0.0716237866365093</v>
       </c>
       <c r="C32" t="n">
-        <v>0.225382932166302</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.170149253731343</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.0208198489751887</v>
+        <v>0.0756771842295227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45374</v>
       </c>
       <c r="B33" t="n">
-        <v>0.227826086956522</v>
+        <v>0.0515586979477527</v>
       </c>
       <c r="C33" t="n">
-        <v>0.260485651214128</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.145714285714286</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.0257006836811398</v>
+        <v>0.0706704847488504</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45381</v>
       </c>
       <c r="B34" t="n">
-        <v>0.608084358523726</v>
+        <v>0.0234076074724285</v>
       </c>
       <c r="C34" t="n">
-        <v>0.24507658643326</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.176470588235294</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.0301982316029663</v>
+        <v>0.0672873676665622</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45388</v>
       </c>
       <c r="B35" t="n">
-        <v>1.40566037735849</v>
+        <v>-0.013405178078591</v>
       </c>
       <c r="C35" t="n">
-        <v>0.148296593186373</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.218579234972678</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.0870905022194504</v>
+        <v>0.0588975018865721</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45395</v>
       </c>
       <c r="B36" t="n">
-        <v>2.35459662288931</v>
+        <v>-0.0276095475596723</v>
       </c>
       <c r="C36" t="n">
-        <v>0.265503875968992</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.315217391304348</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.118129644617762</v>
+        <v>0.0498411285611142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45402</v>
       </c>
       <c r="B37" t="n">
-        <v>3.80254777070064</v>
+        <v>0.00954045246304247</v>
       </c>
       <c r="C37" t="n">
-        <v>0.328330206378987</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.464788732394366</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.215307393289806</v>
+        <v>0.0465875645822198</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45409</v>
       </c>
       <c r="B38" t="n">
-        <v>5.11751662971175</v>
+        <v>0.0323711239838387</v>
       </c>
       <c r="C38" t="n">
-        <v>0.497247706422018</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.579545454545455</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.300860372699564</v>
+        <v>0.0401800167043784</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45416</v>
       </c>
       <c r="B39" t="n">
-        <v>6.05080831408776</v>
+        <v>0.0972322627284932</v>
       </c>
       <c r="C39" t="n">
-        <v>0.767754318618042</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.67621776504298</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.369804885786802</v>
+        <v>0.0431098725616055</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45423</v>
       </c>
       <c r="B40" t="n">
-        <v>6.48470588235294</v>
+        <v>0.14658292527145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.808</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.720116618075802</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.405061723297965</v>
+        <v>0.0460089809272537</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45430</v>
       </c>
       <c r="B41" t="n">
-        <v>6.28791208791209</v>
+        <v>0.174474959612278</v>
       </c>
       <c r="C41" t="n">
-        <v>0.846311475409836</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.69208211143695</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.370813701770024</v>
+        <v>0.045447728861981</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45437</v>
       </c>
       <c r="B42" t="n">
-        <v>6.19057815845824</v>
+        <v>0.200282854656223</v>
       </c>
       <c r="C42" t="n">
-        <v>0.729166666666667</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.664688427299703</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.335782577903683</v>
+        <v>0.0446505258703753</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>6.41630901287554</v>
+        <v>0.218417499324872</v>
       </c>
       <c r="C43" t="n">
-        <v>0.568228105906314</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.674772036474164</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.311123348017621</v>
+        <v>0.0420175845375934</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45451</v>
       </c>
       <c r="B44" t="n">
-        <v>6.54885654885655</v>
+        <v>0.223254324151185</v>
       </c>
       <c r="C44" t="n">
-        <v>0.441233140655106</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.727554179566563</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.316412778759372</v>
+        <v>0.0388086026617791</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45458</v>
       </c>
       <c r="B45" t="n">
-        <v>7.8466819221968</v>
+        <v>0.23546808625047</v>
       </c>
       <c r="C45" t="n">
-        <v>0.446183953033268</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.761609907120743</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.336623840468277</v>
+        <v>0.0407852482714004</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45465</v>
       </c>
       <c r="B46" t="n">
-        <v>8.28310502283105</v>
+        <v>0.22424652542814</v>
       </c>
       <c r="C46" t="n">
-        <v>0.482490272373541</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.803125</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.345377637345836</v>
+        <v>0.040985152109636</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45472</v>
       </c>
       <c r="B47" t="n">
-        <v>8.08102345415778</v>
+        <v>0.198969280517381</v>
       </c>
       <c r="C47" t="n">
-        <v>0.550495049504951</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.919354838709677</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.37377135348226</v>
+        <v>0.0421079680110672</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45479</v>
       </c>
       <c r="B48" t="n">
-        <v>8.72767857142857</v>
+        <v>0.209443757725587</v>
       </c>
       <c r="C48" t="n">
-        <v>0.765913757700205</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.989966555183946</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.401973931234243</v>
+        <v>0.0408530223130144</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45486</v>
       </c>
       <c r="B49" t="n">
-        <v>8.27467811158798</v>
+        <v>0.227342995169082</v>
       </c>
       <c r="C49" t="n">
-        <v>0.913131313131313</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.0551724137931</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.416301969365427</v>
+        <v>0.040555460529621</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45493</v>
       </c>
       <c r="B50" t="n">
-        <v>8.10084033613445</v>
+        <v>0.203128637273616</v>
       </c>
       <c r="C50" t="n">
-        <v>1.1377245508982</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.12323943661972</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.457501237828024</v>
+        <v>0.0432092766697589</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45500</v>
       </c>
       <c r="B51" t="n">
-        <v>8.80045351473923</v>
+        <v>0.189903193703067</v>
       </c>
       <c r="C51" t="n">
-        <v>1.25988700564972</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.08680555555556</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.472581706514587</v>
+        <v>0.0462641221417603</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45507</v>
       </c>
       <c r="B52" t="n">
-        <v>8.76523702031603</v>
+        <v>0.163998059194566</v>
       </c>
       <c r="C52" t="n">
-        <v>1.29779411764706</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.08219178082192</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.500330469266358</v>
+        <v>0.0483020346929517</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45514</v>
       </c>
       <c r="B53" t="n">
-        <v>9.38663484486874</v>
+        <v>0.141896234094512</v>
       </c>
       <c r="C53" t="n">
-        <v>1.4462962962963</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.05333333333333</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.531999120299098</v>
+        <v>0.0452476492494154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45521</v>
       </c>
       <c r="B54" t="n">
-        <v>10.1326530612245</v>
+        <v>0.150697198413714</v>
       </c>
       <c r="C54" t="n">
-        <v>1.56015037593985</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.02295081967213</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.532187895809241</v>
+        <v>0.0380479624136356</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45528</v>
       </c>
       <c r="B55" t="n">
-        <v>10.474358974359</v>
+        <v>0.141125650058715</v>
       </c>
       <c r="C55" t="n">
-        <v>1.68910891089109</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.993610223642172</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.545613364633946</v>
+        <v>0.0321595930779075</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45535</v>
       </c>
       <c r="B56" t="n">
-        <v>10.1598062953995</v>
+        <v>0.150051212017754</v>
       </c>
       <c r="C56" t="n">
-        <v>1.78313253012048</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.981191222570533</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.554571630358016</v>
+        <v>0.0299653997440217</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.16618459111228</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.0264411935258326</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45549</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.166748779504636</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.0252014639211942</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45556</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.178918618646422</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.0220754806435317</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45563</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.176410636523673</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.024057906765552</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.158714881525276</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.0292283800163</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45577</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.154573418981272</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.0317585921134413</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.14208204675783</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0339323054533622</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.139955734930348</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.0304853618716452</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.132738451028947</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0322847316163144</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.131862080650627</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0242336079972043</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.171802338215481</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0436713211120208</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.163226448569821</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.00845025245848952</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.172058254929759</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.0225234105253962</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.175715990453461</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0252655362972192</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.160316139767055</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0166980651720676</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.191925988225399</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.0360265168764005</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.204941678163803</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0236688517489014</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.199917389508468</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.0380884300885416</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.229751519411254</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.0472251768206466</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.223177177904208</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.0492549994167726</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.323548512793869</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.0535424819536205</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.396427938308811</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.0410594979932879</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.454256272401434</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.0297502225192396</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.56764488741233</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.0393836319201579</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.596092346782319</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0388219584506435</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.713643178410795</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.0421453587819811</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.829688123863183</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.04371691971694</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.898953478146161</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.043140956563801</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.914512748864827</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.0447403006822105</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.931867165163844</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.0438698319167705</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.931175347453488</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.0430753319437398</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.950586187946511</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.0452511193087552</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.962573099415205</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.049645518526185</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.956761599396454</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0561110996252312</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.928278977834251</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.0576952379808855</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.901866121994244</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.0624426753989049</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.879367262723521</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.057960192550492</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.860871929665549</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0570924048423904</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.834035196595594</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.060078536714488</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.828052718861831</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.0586514909694367</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.844489902506964</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.0586236761361623</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.82460988987627</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.0565907575623272</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.823430257058575</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.0534022849856888</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.801316381178202</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.0490849278689021</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.77241596473274</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.0451977249998696</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
         <v>45857</v>
       </c>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
+      <c r="B102" t="n">
+        <v>0.777726182184042</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.0434909671228332</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.783645072992701</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.0419134400496337</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.788245102125886</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.0454480832898061</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.763553821333433</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.0464965400776212</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.726848249027237</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.0496802943665406</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.677790436987761</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.0502297383181087</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.639268220276087</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.0526613075472375</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.59488913942127</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.0526457410728771</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3898,934 +4207,1833 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45472</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
+        <v>45157</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0428849902534114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.304347826086957</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.181372549019608</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.278547164881108</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45479</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>45164</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0657640232108316</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.3008356545961</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.178921568627451</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.278183635804368</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45486</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
+        <v>45171</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.00174520069808026</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.302816901408451</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.171149144254279</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.291804180418042</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45493</v>
+        <v>45178</v>
       </c>
       <c r="B5" t="n">
-        <v>0.203128637273616</v>
+        <v>-0.0302066772655007</v>
       </c>
       <c r="C5" t="n">
-        <v>0.168128773568507</v>
+        <v>-0.347398030942335</v>
       </c>
       <c r="D5" t="n">
-        <v>0.229695221648632</v>
+        <v>-0.123425692695214</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0432092766697589</v>
+        <v>-0.302418389336739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45500</v>
+        <v>45185</v>
       </c>
       <c r="B6" t="n">
-        <v>0.189903193703067</v>
+        <v>0.045774647887324</v>
       </c>
       <c r="C6" t="n">
-        <v>0.17227411470406</v>
+        <v>-0.355677154582763</v>
       </c>
       <c r="D6" t="n">
-        <v>0.228824226945179</v>
+        <v>-0.123737373737374</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0462641221417603</v>
+        <v>-0.298907483939605</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45507</v>
+        <v>45192</v>
       </c>
       <c r="B7" t="n">
-        <v>0.163998059194566</v>
+        <v>0.0774774774774776</v>
       </c>
       <c r="C7" t="n">
-        <v>0.178472039304161</v>
+        <v>-0.362068965517241</v>
       </c>
       <c r="D7" t="n">
-        <v>0.224662131353846</v>
+        <v>-0.116883116883117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0483020346929517</v>
+        <v>-0.300029287477511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45514</v>
+        <v>45199</v>
       </c>
       <c r="B8" t="n">
-        <v>0.141896234094512</v>
+        <v>0.0599647266313934</v>
       </c>
       <c r="C8" t="n">
-        <v>0.164008368577342</v>
+        <v>-0.334239130434783</v>
       </c>
       <c r="D8" t="n">
-        <v>0.216779135509758</v>
+        <v>0.00298507462686559</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0452476492494154</v>
+        <v>-0.288400322566954</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45521</v>
+        <v>45206</v>
       </c>
       <c r="B9" t="n">
-        <v>0.150697198413714</v>
+        <v>0.329896907216495</v>
       </c>
       <c r="C9" t="n">
-        <v>0.146800265721878</v>
+        <v>-0.330769230769231</v>
       </c>
       <c r="D9" t="n">
-        <v>0.21721454719376</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0380479624136356</v>
+        <v>-0.273650571290986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45528</v>
+        <v>45213</v>
       </c>
       <c r="B10" t="n">
-        <v>0.141125650058715</v>
+        <v>0.443478260869565</v>
       </c>
       <c r="C10" t="n">
-        <v>0.121445000381526</v>
+        <v>-0.346733668341708</v>
       </c>
       <c r="D10" t="n">
-        <v>0.206229660622966</v>
+        <v>0.388</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0321595930779075</v>
+        <v>-0.270253771692683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45535</v>
+        <v>45220</v>
       </c>
       <c r="B11" t="n">
-        <v>0.150051212017754</v>
+        <v>0.42274678111588</v>
       </c>
       <c r="C11" t="n">
-        <v>0.113542725070064</v>
+        <v>-0.443298969072165</v>
       </c>
       <c r="D11" t="n">
-        <v>0.190311157989904</v>
+        <v>0.616438356164384</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0299653997440217</v>
+        <v>-0.260136614414572</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45542</v>
+        <v>45227</v>
       </c>
       <c r="B12" t="n">
-        <v>0.16618459111228</v>
+        <v>0.883977900552486</v>
       </c>
       <c r="C12" t="n">
-        <v>0.109923011120616</v>
+        <v>-0.435632183908046</v>
       </c>
       <c r="D12" t="n">
-        <v>0.170746064599434</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0264411935258326</v>
+        <v>-0.241688538932633</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45549</v>
+        <v>45234</v>
       </c>
       <c r="B13" t="n">
-        <v>0.166748779504636</v>
+        <v>0.392290249433107</v>
       </c>
       <c r="C13" t="n">
-        <v>0.107857245646856</v>
+        <v>-0.344827586206897</v>
       </c>
       <c r="D13" t="n">
-        <v>0.152943428735522</v>
+        <v>0.40495867768595</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0252014639211942</v>
+        <v>-0.219313883212314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45556</v>
+        <v>45241</v>
       </c>
       <c r="B14" t="n">
-        <v>0.178918618646422</v>
+        <v>0.0458715596330275</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0929242729911923</v>
+        <v>-0.316120906801008</v>
       </c>
       <c r="D14" t="n">
-        <v>0.160269047895164</v>
+        <v>0.351239669421488</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0220754806435317</v>
+        <v>-0.195128194189668</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45563</v>
+        <v>45248</v>
       </c>
       <c r="B15" t="n">
-        <v>0.176410636523673</v>
+        <v>-0.0370994940978078</v>
       </c>
       <c r="C15" t="n">
-        <v>0.073042564372044</v>
+        <v>-0.129429892141757</v>
       </c>
       <c r="D15" t="n">
-        <v>0.177987507587476</v>
+        <v>0.263374485596708</v>
       </c>
       <c r="E15" t="n">
-        <v>0.024057906765552</v>
+        <v>-0.173183179383356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45570</v>
+        <v>45255</v>
       </c>
       <c r="B16" t="n">
-        <v>0.158714881525276</v>
+        <v>-0.121794871794872</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0568213544385234</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="D16" t="n">
-        <v>0.214439569206223</v>
+        <v>0.1699604743083</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0292283800163</v>
+        <v>-0.1644795105064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45577</v>
+        <v>45262</v>
       </c>
       <c r="B17" t="n">
-        <v>0.154573418981272</v>
+        <v>0.143122676579926</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0267428243672776</v>
+        <v>-0.114854517611026</v>
       </c>
       <c r="D17" t="n">
-        <v>0.245607302985014</v>
+        <v>0.135658914728682</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0317585921134413</v>
+        <v>-0.148820047659313</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45584</v>
+        <v>45269</v>
       </c>
       <c r="B18" t="n">
-        <v>0.14208204675783</v>
+        <v>0.253549695740365</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0232447479241513</v>
+        <v>-0.0337941628264209</v>
       </c>
       <c r="D18" t="n">
-        <v>0.264556602241351</v>
+        <v>0.104089219330855</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0339323054533622</v>
+        <v>-0.132452308955837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45591</v>
+        <v>45276</v>
       </c>
       <c r="B19" t="n">
-        <v>0.139955734930348</v>
+        <v>0.128913443830571</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00699923793891788</v>
+        <v>-0.0739130434782609</v>
       </c>
       <c r="D19" t="n">
-        <v>0.271015699575522</v>
+        <v>0.0696864111498259</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0304853618716452</v>
+        <v>-0.120050035739814</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45598</v>
+        <v>45283</v>
       </c>
       <c r="B20" t="n">
-        <v>0.132738451028947</v>
+        <v>0.0928961748633881</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.00100421536916595</v>
+        <v>-0.075780089153046</v>
       </c>
       <c r="D20" t="n">
-        <v>0.271331231567172</v>
+        <v>0.0848056537102473</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0322847316163144</v>
+        <v>-0.104223141674989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45605</v>
+        <v>45290</v>
       </c>
       <c r="B21" t="n">
-        <v>0.131862080650627</v>
+        <v>-0.0442477876106194</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00360754558890286</v>
+        <v>-0.0363036303630363</v>
       </c>
       <c r="D21" t="n">
-        <v>0.269880107658429</v>
+        <v>0.105072463768116</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0242336079972043</v>
+        <v>-0.103283749649172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45612</v>
+        <v>45297</v>
       </c>
       <c r="B22" t="n">
-        <v>0.171802338215481</v>
+        <v>0.0591497227356748</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0182650540341183</v>
+        <v>-0.148936170212766</v>
       </c>
       <c r="D22" t="n">
-        <v>0.281946546683531</v>
+        <v>0.10989010989011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0436713211120208</v>
+        <v>-0.0940890125173852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45619</v>
+        <v>45304</v>
       </c>
       <c r="B23" t="n">
-        <v>0.163226448569821</v>
+        <v>0.159509202453988</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00391232673152375</v>
+        <v>-0.0817843866171004</v>
       </c>
       <c r="D23" t="n">
-        <v>0.28396557486631</v>
+        <v>0.141791044776119</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00845025245848952</v>
+        <v>-0.0896678073905078</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45311</v>
       </c>
       <c r="B24" t="n">
-        <v>0.172058254929759</v>
+        <v>0.203187250996016</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00358886996024999</v>
+        <v>-0.136612021857924</v>
       </c>
       <c r="D24" t="n">
-        <v>0.289604168417514</v>
+        <v>0.218390804597701</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0225234105253962</v>
+        <v>-0.0779107286905082</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45633</v>
+        <v>45318</v>
       </c>
       <c r="B25" t="n">
-        <v>0.175715990453461</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0137464788732393</v>
+        <v>-0.145794392523364</v>
       </c>
       <c r="D25" t="n">
-        <v>0.289464319356932</v>
+        <v>0.334661354581673</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0252655362972192</v>
+        <v>-0.0774895508525177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45640</v>
+        <v>45325</v>
       </c>
       <c r="B26" t="n">
-        <v>0.160316139767055</v>
+        <v>-0.0858505564387917</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00427307959852907</v>
+        <v>-0.0773930753564155</v>
       </c>
       <c r="D26" t="n">
-        <v>0.27904918707553</v>
+        <v>0.464435146443515</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0166980651720676</v>
+        <v>-0.0851426138782461</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45647</v>
+        <v>45332</v>
       </c>
       <c r="B27" t="n">
-        <v>0.191925988225399</v>
+        <v>-0.145645645645646</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0207675693636817</v>
+        <v>-0.173598553345389</v>
       </c>
       <c r="D27" t="n">
-        <v>0.282417335539081</v>
+        <v>0.558951965065502</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0360265168764005</v>
+        <v>-0.0977869274318065</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45654</v>
+        <v>45339</v>
       </c>
       <c r="B28" t="n">
-        <v>0.204941678163803</v>
+        <v>-0.217134416543575</v>
       </c>
       <c r="C28" t="n">
-        <v>0.029792110001637</v>
+        <v>-0.207936507936508</v>
       </c>
       <c r="D28" t="n">
-        <v>0.274651989635016</v>
+        <v>0.570815450643777</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0236688517489014</v>
+        <v>-0.101993081864602</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45661</v>
+        <v>45346</v>
       </c>
       <c r="B29" t="n">
-        <v>0.199917389508468</v>
+        <v>-0.212703101920236</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0384088672058887</v>
+        <v>-0.247813411078717</v>
       </c>
       <c r="D29" t="n">
-        <v>0.26301531213192</v>
+        <v>0.508196721311475</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0380884300885416</v>
+        <v>-0.0815340429126542</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45668</v>
+        <v>45353</v>
       </c>
       <c r="B30" t="n">
-        <v>0.229751519411254</v>
+        <v>-0.269767441860465</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0544416538274834</v>
+        <v>-0.1996996996997</v>
       </c>
       <c r="D30" t="n">
-        <v>0.243298224267083</v>
+        <v>0.448979591836735</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0472251768206466</v>
+        <v>-0.0735962520103489</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45675</v>
+        <v>45360</v>
       </c>
       <c r="B31" t="n">
-        <v>0.223177177904208</v>
+        <v>-0.276083467094703</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0523603485927711</v>
+        <v>-0.17921686746988</v>
       </c>
       <c r="D31" t="n">
-        <v>0.219946376785161</v>
+        <v>0.430894308943089</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0492549994167726</v>
+        <v>-0.0595428156748912</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45682</v>
+        <v>45367</v>
       </c>
       <c r="B32" t="n">
-        <v>0.323548512793869</v>
+        <v>-0.325545171339564</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0456958436387767</v>
+        <v>-0.097053726169844</v>
       </c>
       <c r="D32" t="n">
-        <v>0.195079579553231</v>
+        <v>0.478813559322034</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0535424819536205</v>
+        <v>-0.0646537334470864</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45689</v>
+        <v>45374</v>
       </c>
       <c r="B33" t="n">
-        <v>0.396427938308811</v>
+        <v>-0.292845257903494</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0330905965002422</v>
+        <v>-0.145299145299145</v>
       </c>
       <c r="D33" t="n">
-        <v>0.165360594418022</v>
+        <v>0.491304347826087</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0410594979932879</v>
+        <v>-0.0767676767676768</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45696</v>
+        <v>45381</v>
       </c>
       <c r="B34" t="n">
-        <v>0.454256272401434</v>
+        <v>-0.246688741721854</v>
       </c>
       <c r="C34" t="n">
-        <v>0.013361714479222</v>
+        <v>-0.149825783972125</v>
       </c>
       <c r="D34" t="n">
-        <v>0.137436166893811</v>
+        <v>0.469827586206897</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0297502225192396</v>
+        <v>-0.0682249644043664</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45703</v>
+        <v>45388</v>
       </c>
       <c r="B35" t="n">
-        <v>0.56764488741233</v>
+        <v>-0.209813874788494</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0249540856484858</v>
+        <v>-0.139784946236559</v>
       </c>
       <c r="D35" t="n">
-        <v>0.132084897906561</v>
+        <v>0.44017094017094</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0393836319201579</v>
+        <v>-0.0620666749699008</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45710</v>
+        <v>45395</v>
       </c>
       <c r="B36" t="n">
-        <v>0.596092346782319</v>
+        <v>-0.190972222222222</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0402161928014493</v>
+        <v>-0.0907407407407408</v>
       </c>
       <c r="D36" t="n">
-        <v>0.124437518881875</v>
+        <v>0.376569037656904</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0388219584506435</v>
+        <v>-0.0505816233172134</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45402</v>
       </c>
       <c r="B37" t="n">
-        <v>0.713643178410795</v>
+        <v>-0.191596638655462</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0506608369270085</v>
+        <v>0.013671875</v>
       </c>
       <c r="D37" t="n">
-        <v>0.128568934596645</v>
+        <v>0.292</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0421453587819811</v>
+        <v>-0.0369740170154058</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45409</v>
       </c>
       <c r="B38" t="n">
-        <v>0.829688123863183</v>
+        <v>-0.298555377207063</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0686227581500982</v>
+        <v>-0.019193857965451</v>
       </c>
       <c r="D38" t="n">
-        <v>0.144513088338322</v>
+        <v>0.218867924528302</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04371691971694</v>
+        <v>-0.040047619047619</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45731</v>
+        <v>45416</v>
       </c>
       <c r="B39" t="n">
-        <v>0.898953478146161</v>
+        <v>-0.244827586206897</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0768342832407474</v>
+        <v>0.0798319327731092</v>
       </c>
       <c r="D39" t="n">
-        <v>0.146231918804443</v>
+        <v>0.172161172161172</v>
       </c>
       <c r="E39" t="n">
-        <v>0.043140956563801</v>
+        <v>-0.0232465528398627</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45738</v>
+        <v>45423</v>
       </c>
       <c r="B40" t="n">
-        <v>0.914512748864827</v>
+        <v>-0.206429780033841</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0794878216767891</v>
+        <v>0.0222672064777327</v>
       </c>
       <c r="D40" t="n">
-        <v>0.155190199871051</v>
+        <v>0.0954063604240283</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0447403006822105</v>
+        <v>-0.00595642405559327</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45745</v>
+        <v>45430</v>
       </c>
       <c r="B41" t="n">
-        <v>0.931867165163844</v>
+        <v>-0.287758346581876</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0741859930153286</v>
+        <v>0.0124740124740124</v>
       </c>
       <c r="D41" t="n">
-        <v>0.159046015349244</v>
+        <v>0.0602836879432624</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0438698319167705</v>
+        <v>0.00615251767499592</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45752</v>
+        <v>45437</v>
       </c>
       <c r="B42" t="n">
-        <v>0.931175347453488</v>
+        <v>-0.234811165845649</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0606904816971889</v>
+        <v>0.0668103448275863</v>
       </c>
       <c r="D42" t="n">
-        <v>0.167423835344308</v>
+        <v>0.0394265232974911</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0430753319437398</v>
+        <v>0.0251808647860468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45759</v>
+        <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>0.950586187946511</v>
+        <v>-0.282051282051282</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0609923639732899</v>
+        <v>0.08207343412527</v>
       </c>
       <c r="D43" t="n">
-        <v>0.162972045120157</v>
+        <v>0.01067615658363</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0452511193087552</v>
+        <v>0.0246913580246915</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45766</v>
+        <v>45451</v>
       </c>
       <c r="B44" t="n">
-        <v>0.962573099415205</v>
+        <v>-0.371794871794872</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0631096975259888</v>
+        <v>0.139484978540773</v>
       </c>
       <c r="D44" t="n">
-        <v>0.159091649561789</v>
+        <v>0.0140845070422535</v>
       </c>
       <c r="E44" t="n">
-        <v>0.049645518526185</v>
+        <v>0.00573571586146038</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45773</v>
+        <v>45458</v>
       </c>
       <c r="B45" t="n">
-        <v>0.956761599396454</v>
+        <v>-0.338805970149254</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0724971481340648</v>
+        <v>0.177489177489178</v>
       </c>
       <c r="D45" t="n">
-        <v>0.160260469950147</v>
+        <v>0.0428571428571429</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0561110996252312</v>
+        <v>-0.0123483653375401</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45780</v>
+        <v>45465</v>
       </c>
       <c r="B46" t="n">
-        <v>0.928278977834251</v>
+        <v>-0.356374807987711</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0701002993684856</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="D46" t="n">
-        <v>0.144293412692029</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0576952379808855</v>
+        <v>-0.0331189197809793</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45787</v>
+        <v>45472</v>
       </c>
       <c r="B47" t="n">
-        <v>0.901866121994244</v>
+        <v>-0.40785498489426</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0599458006377676</v>
+        <v>-0.0256410256410257</v>
       </c>
       <c r="D47" t="n">
-        <v>0.170182594563589</v>
+        <v>0.113138686131387</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0624426753989049</v>
+        <v>-0.0435584114610765</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45794</v>
+        <v>45479</v>
       </c>
       <c r="B48" t="n">
-        <v>0.879367262723521</v>
+        <v>-0.371980676328502</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0525879012884909</v>
+        <v>-0.0325670498084292</v>
       </c>
       <c r="D48" t="n">
-        <v>0.194866272901458</v>
+        <v>0.12589928057554</v>
       </c>
       <c r="E48" t="n">
-        <v>0.057960192550492</v>
+        <v>-0.0391333997796779</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45801</v>
+        <v>45486</v>
       </c>
       <c r="B49" t="n">
-        <v>0.860871929665549</v>
+        <v>-0.336012861736334</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0559452072837434</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.223806825336859</v>
+        <v>0.0962199312714778</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0570924048423904</v>
+        <v>-0.0443383001920981</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45808</v>
+        <v>45493</v>
       </c>
       <c r="B50" t="n">
-        <v>0.834035196595594</v>
+        <v>-0.335394126738794</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0734527293128864</v>
+        <v>0.184381778741866</v>
       </c>
       <c r="D50" t="n">
-        <v>0.248352826203462</v>
+        <v>0.105960264900662</v>
       </c>
       <c r="E50" t="n">
-        <v>0.060078536714488</v>
+        <v>-0.0347154262168426</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45815</v>
+        <v>45500</v>
       </c>
       <c r="B51" t="n">
-        <v>0.828052718861831</v>
+        <v>-0.258943781942078</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0916460157497658</v>
+        <v>0.247727272727273</v>
       </c>
       <c r="D51" t="n">
-        <v>0.250467583497053</v>
+        <v>0.122257053291536</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0586514909694367</v>
+        <v>-0.0383329957464047</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45822</v>
+        <v>45507</v>
       </c>
       <c r="B52" t="n">
-        <v>0.844489902506964</v>
+        <v>-0.163339382940109</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0953487610880168</v>
+        <v>0.16331096196868</v>
       </c>
       <c r="D52" t="n">
-        <v>0.275139577190891</v>
+        <v>0.13677811550152</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0586236761361623</v>
+        <v>-0.0511188563923827</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45829</v>
+        <v>45514</v>
       </c>
       <c r="B53" t="n">
-        <v>0.82460988987627</v>
+        <v>-0.0371819960861057</v>
       </c>
       <c r="C53" t="n">
-        <v>0.104290436057943</v>
+        <v>0.0455486542443064</v>
       </c>
       <c r="D53" t="n">
-        <v>0.271276099200299</v>
+        <v>0.16566265060241</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0565907575623272</v>
+        <v>-0.0510420882233913</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45836</v>
+        <v>45521</v>
       </c>
       <c r="B54" t="n">
-        <v>0.823430257058575</v>
+        <v>0.0504672897196261</v>
       </c>
       <c r="C54" t="n">
-        <v>0.138110538504872</v>
+        <v>-0.129032258064516</v>
       </c>
       <c r="D54" t="n">
-        <v>0.270097254708852</v>
+        <v>0.143712574850299</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0534022849856888</v>
+        <v>-0.0531380969627981</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45843</v>
+        <v>45528</v>
       </c>
       <c r="B55" t="n">
-        <v>0.801316381178202</v>
+        <v>0.043557168784029</v>
       </c>
       <c r="C55" t="n">
-        <v>0.150429127678226</v>
+        <v>-0.175298804780876</v>
       </c>
       <c r="D55" t="n">
-        <v>0.267816999817729</v>
+        <v>0.0925373134328358</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0490843807528398</v>
+        <v>-0.0605657060672242</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45850</v>
+        <v>45535</v>
       </c>
       <c r="B56" t="n">
-        <v>0.77241596473274</v>
+        <v>-0.00349650349650354</v>
       </c>
       <c r="C56" t="n">
-        <v>0.167551622418879</v>
+        <v>-0.17979797979798</v>
       </c>
       <c r="D56" t="n">
-        <v>0.253582114236743</v>
+        <v>0.0501474926253687</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0451954512302499</v>
+        <v>-0.0578085991678224</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.10327868852459</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.120689655172414</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.00574712643678166</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.0704233409610984</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45549</v>
+      </c>
+      <c r="B58" t="n">
+        <v>-0.185185185185185</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.0934182590233545</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.0144092219020173</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.0695692774600211</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45556</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.142140468227425</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.122661122661123</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.0705882352941176</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.0565451285116557</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45563</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.139767054908486</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.112244897959184</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.113095238095238</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.0539782893952045</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.156589147286822</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.145593869731801</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.154761904761905</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.0488187078109933</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45577</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.174698795180723</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.146153846153846</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.144092219020173</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.0628585086042065</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.217194570135747</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.0452674897119342</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.0988700564971752</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.0714919808249985</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.224340175953079</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.0224032586558045</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.0657142857142856</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.0766657052206519</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.190553745928339</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.12593984962406</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.0588235294117647</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.0731829573934837</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.117543859649123</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.147329650092081</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.070336391437309</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.0725605554672178</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B67" t="n">
+        <v>-0.106830122591944</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.155752212389381</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.133550488599349</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.0571341121256951</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.072992700729927</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.194871794871795</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.192567567567568</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.0692811717093852</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.15609756097561</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.140138408304498</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.228668941979522</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.0580240223968211</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B70" t="n">
+        <v>-0.163430420711974</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.201907790143084</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.225589225589226</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.0476354404234262</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B71" t="n">
+        <v>-0.158238172920065</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.214397496087637</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.195439739413681</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.0379757117907478</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B72" t="n">
+        <v>-0.141666666666667</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.204180064308682</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.188925081433225</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.0119057099625707</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B73" t="n">
+        <v>-0.0666666666666667</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.188356164383562</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.186885245901639</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.014397496087637</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B74" t="n">
+        <v>-0.104712041884817</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.0557692307692308</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.221122112211221</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.00149689107238815</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B75" t="n">
+        <v>-0.0670194003527337</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.0101214574898786</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.241830065359477</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0183785836339472</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B76" t="n">
+        <v>-0.107615894039735</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.090717299578059</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.216981132075472</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.00513960778595901</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.0329861111111112</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.225382932166302</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.170149253731343</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.0208198489751887</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.227826086956522</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.260485651214128</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.145714285714286</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0257006836811398</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.608084358523726</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.24507658643326</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.176470588235294</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.0301982316029663</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1.40566037735849</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.148296593186373</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.218579234972678</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.0870905022194504</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2.35459662288931</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.265503875968992</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.315217391304348</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.118129644617762</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.80254777070064</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.328330206378987</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.464788732394366</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.215307393289806</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B83" t="n">
+        <v>5.11751662971175</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.497247706422018</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.579545454545455</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.300860372699564</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B84" t="n">
+        <v>6.05080831408776</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.767754318618042</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.67621776504298</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.369804885786802</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B85" t="n">
+        <v>6.48470588235294</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.808</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.720116618075802</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.405061723297965</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B86" t="n">
+        <v>6.28791208791209</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.846311475409836</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.69208211143695</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.370813701770024</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B87" t="n">
+        <v>6.19057815845824</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.664688427299703</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.335782577903683</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B88" t="n">
+        <v>6.41630901287554</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.568228105906314</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.674772036474164</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.311123348017621</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B89" t="n">
+        <v>6.54885654885655</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.441233140655106</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.727554179566563</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.316412778759372</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7.8466819221968</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.446183953033268</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.761609907120743</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.336623840468277</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8.28310502283105</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.482490272373541</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.803125</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.345377637345836</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8.08102345415778</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.550495049504951</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.919354838709677</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.37377135348226</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8.72767857142857</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.765913757700205</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.989966555183946</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.401973931234243</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8.27467811158798</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.913131313131313</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1.0551724137931</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.416301969365427</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8.10084033613445</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1.1377245508982</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.12323943661972</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.457501237828024</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8.80045351473923</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1.25988700564972</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.08680555555556</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.472581706514587</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8.76523702031603</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.29779411764706</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.08219178082192</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.500330469266358</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.38663484486874</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1.4462962962963</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.05333333333333</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.531999120299098</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10.1326530612245</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1.56015037593985</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.02295081967213</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.532187895809241</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10.474358974359</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1.68910891089109</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.993610223642172</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.545613364633946</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10.1598062953995</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1.78313253012048</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.981191222570533</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.554571630358016</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
         <v>45857</v>
       </c>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
+      <c r="B102" t="n">
+        <v>10.5139534883721</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1.70695970695971</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.934131736526946</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.574035537057788</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11.2735632183908</v>
+      </c>
+      <c r="C103" t="n">
+        <v>2.04918032786885</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.88268156424581</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.614290979937865</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11.4056399132321</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2.67884615384615</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.86096256684492</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.685813148788927</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11.3678861788618</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3.29306930693069</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.850129198966408</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.744069513300283</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B106" t="n">
+        <v>10.1708185053381</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4.50462962962963</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.921465968586388</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.804043715846995</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B107" t="n">
+        <v>10.0591304347826</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4.91304347826087</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.02732240437158</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.87298707189839</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B108" t="n">
+        <v>10.1368421052632</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5.20689655172414</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.09831460674157</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.922981805334746</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output/wp_figures.xlsx
+++ b/output/wp_figures.xlsx
@@ -406,639 +406,628 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B2" t="n">
-        <v>192.455</v>
+        <v>192.739</v>
       </c>
       <c r="C2" t="n">
-        <v>199.517</v>
+        <v>193.441</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B3" t="n">
-        <v>192.739</v>
+        <v>190.623</v>
       </c>
       <c r="C3" t="n">
-        <v>193.441</v>
+        <v>191.353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B4" t="n">
-        <v>190.623</v>
+        <v>178.682</v>
       </c>
       <c r="C4" t="n">
-        <v>191.353</v>
+        <v>175.594</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B5" t="n">
-        <v>178.682</v>
+        <v>186.832</v>
       </c>
       <c r="C5" t="n">
-        <v>175.594</v>
+        <v>176.586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B6" t="n">
-        <v>186.832</v>
+        <v>181.701</v>
       </c>
       <c r="C6" t="n">
-        <v>176.586</v>
+        <v>175.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B7" t="n">
-        <v>181.701</v>
+        <v>181.204</v>
       </c>
       <c r="C7" t="n">
-        <v>175.65</v>
+        <v>174.701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B8" t="n">
-        <v>181.204</v>
+        <v>236.171</v>
       </c>
       <c r="C8" t="n">
-        <v>174.701</v>
+        <v>199.743</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B9" t="n">
-        <v>236.171</v>
+        <v>225.23</v>
       </c>
       <c r="C9" t="n">
-        <v>199.743</v>
+        <v>182.394</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B10" t="n">
-        <v>225.23</v>
+        <v>203.475</v>
       </c>
       <c r="C10" t="n">
-        <v>182.394</v>
+        <v>193.999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B11" t="n">
-        <v>203.475</v>
+        <v>201.443</v>
       </c>
       <c r="C11" t="n">
-        <v>193.999</v>
+        <v>199.306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B12" t="n">
-        <v>201.443</v>
+        <v>212.741</v>
       </c>
       <c r="C12" t="n">
-        <v>199.306</v>
+        <v>214.161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B13" t="n">
-        <v>212.741</v>
+        <v>230.801</v>
       </c>
       <c r="C13" t="n">
-        <v>214.161</v>
+        <v>217.438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B14" t="n">
-        <v>230.801</v>
+        <v>214.254</v>
       </c>
       <c r="C14" t="n">
-        <v>217.438</v>
+        <v>240.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B15" t="n">
-        <v>214.254</v>
+        <v>245.27</v>
       </c>
       <c r="C15" t="n">
-        <v>240.99</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B16" t="n">
-        <v>245.27</v>
+        <v>211.323</v>
       </c>
       <c r="C16" t="n">
-        <v>199.75</v>
+        <v>294.615</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B17" t="n">
-        <v>211.323</v>
+        <v>309.775</v>
       </c>
       <c r="C17" t="n">
-        <v>294.615</v>
+        <v>249.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B18" t="n">
-        <v>309.775</v>
+        <v>252.349</v>
       </c>
       <c r="C18" t="n">
-        <v>249.09</v>
+        <v>241.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B19" t="n">
-        <v>252.349</v>
+        <v>275.638</v>
       </c>
       <c r="C19" t="n">
-        <v>241.04</v>
+        <v>274.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B20" t="n">
-        <v>275.638</v>
+        <v>283.652</v>
       </c>
       <c r="C20" t="n">
-        <v>274.84</v>
+        <v>269.416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B21" t="n">
-        <v>283.652</v>
+        <v>306.295</v>
       </c>
       <c r="C21" t="n">
-        <v>269.416</v>
+        <v>318.906</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="n">
-        <v>306.295</v>
+        <v>352.63</v>
       </c>
       <c r="C22" t="n">
-        <v>318.906</v>
+        <v>291.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B23" t="n">
-        <v>352.63</v>
+        <v>284.6</v>
       </c>
       <c r="C23" t="n">
-        <v>291.33</v>
+        <v>249.947</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B24" t="n">
-        <v>284.6</v>
+        <v>228.484</v>
       </c>
       <c r="C24" t="n">
-        <v>249.947</v>
+        <v>263.919</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B25" t="n">
-        <v>228.484</v>
+        <v>241.111</v>
       </c>
       <c r="C25" t="n">
-        <v>263.919</v>
+        <v>234.729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B26" t="n">
-        <v>241.111</v>
+        <v>232.685</v>
       </c>
       <c r="C26" t="n">
-        <v>234.729</v>
+        <v>223.985</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B27" t="n">
-        <v>232.685</v>
+        <v>223.539</v>
       </c>
       <c r="C27" t="n">
-        <v>223.985</v>
+        <v>199.337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B28" t="n">
-        <v>223.539</v>
+        <v>220.856</v>
       </c>
       <c r="C28" t="n">
-        <v>199.337</v>
+        <v>195.604</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B29" t="n">
-        <v>220.856</v>
+        <v>226.019</v>
       </c>
       <c r="C29" t="n">
-        <v>195.604</v>
+        <v>214.425</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="n">
-        <v>226.019</v>
+        <v>214.007</v>
       </c>
       <c r="C30" t="n">
-        <v>214.425</v>
+        <v>202.723</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B31" t="n">
-        <v>214.007</v>
+        <v>207.398</v>
       </c>
       <c r="C31" t="n">
-        <v>202.723</v>
+        <v>191.773</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B32" t="n">
-        <v>207.398</v>
+        <v>199.9</v>
       </c>
       <c r="C32" t="n">
-        <v>191.773</v>
+        <v>193.923</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>199.9</v>
+        <v>200.081</v>
       </c>
       <c r="C33" t="n">
-        <v>193.923</v>
+        <v>197.349</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B34" t="n">
-        <v>200.081</v>
+        <v>216.534</v>
       </c>
       <c r="C34" t="n">
-        <v>197.349</v>
+        <v>215.265</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B35" t="n">
-        <v>216.534</v>
+        <v>220.962</v>
       </c>
       <c r="C35" t="n">
-        <v>215.265</v>
+        <v>209.064</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B36" t="n">
-        <v>220.962</v>
+        <v>210.816</v>
       </c>
       <c r="C36" t="n">
-        <v>209.064</v>
+        <v>202.619</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B37" t="n">
-        <v>210.816</v>
+        <v>224.021</v>
       </c>
       <c r="C37" t="n">
-        <v>202.619</v>
+        <v>189.634</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B38" t="n">
-        <v>224.021</v>
+        <v>206.71</v>
       </c>
       <c r="C38" t="n">
-        <v>189.634</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B39" t="n">
-        <v>206.71</v>
+        <v>203.579</v>
       </c>
       <c r="C39" t="n">
-        <v>210.05</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B40" t="n">
-        <v>203.579</v>
+        <v>200.637</v>
       </c>
       <c r="C40" t="n">
-        <v>197.68</v>
+        <v>192.717</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B41" t="n">
-        <v>200.637</v>
+        <v>210.16</v>
       </c>
       <c r="C41" t="n">
-        <v>192.717</v>
+        <v>197.164</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B42" t="n">
-        <v>210.16</v>
+        <v>207.512</v>
       </c>
       <c r="C42" t="n">
-        <v>197.164</v>
+        <v>196.177</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B43" t="n">
-        <v>207.512</v>
+        <v>243.98</v>
       </c>
       <c r="C43" t="n">
-        <v>196.177</v>
+        <v>236.046</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B44" t="n">
-        <v>243.98</v>
+        <v>234.859</v>
       </c>
       <c r="C44" t="n">
-        <v>236.046</v>
+        <v>227.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B45" t="n">
-        <v>234.859</v>
+        <v>227.516</v>
       </c>
       <c r="C45" t="n">
-        <v>227.98</v>
+        <v>225.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B46" t="n">
-        <v>227.516</v>
+        <v>230.392</v>
       </c>
       <c r="C46" t="n">
-        <v>225.13</v>
+        <v>239.403</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B47" t="n">
-        <v>230.392</v>
+        <v>241.361</v>
       </c>
       <c r="C47" t="n">
-        <v>239.403</v>
+        <v>242.201</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B48" t="n">
-        <v>241.361</v>
+        <v>261.111</v>
       </c>
       <c r="C48" t="n">
-        <v>242.201</v>
+        <v>280.569</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B49" t="n">
-        <v>261.111</v>
+        <v>216.023</v>
       </c>
       <c r="C49" t="n">
-        <v>280.569</v>
+        <v>225.855</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B50" t="n">
-        <v>216.023</v>
+        <v>193.79</v>
       </c>
       <c r="C50" t="n">
-        <v>225.855</v>
+        <v>216.673</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B51" t="n">
-        <v>193.79</v>
+        <v>195.492</v>
       </c>
       <c r="C51" t="n">
-        <v>216.673</v>
+        <v>204.066</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B52" t="n">
-        <v>195.492</v>
+        <v>199.39</v>
       </c>
       <c r="C52" t="n">
-        <v>204.066</v>
+        <v>200.837</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B53" t="n">
-        <v>199.39</v>
+        <v>194.217</v>
       </c>
       <c r="C53" t="n">
-        <v>200.837</v>
+        <v>192.455</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B54" t="n">
-        <v>194.217</v>
+        <v>191.208</v>
       </c>
       <c r="C54" t="n">
-        <v>192.455</v>
+        <v>192.739</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B55" t="n">
-        <v>191.208</v>
+        <v>196.712</v>
       </c>
       <c r="C55" t="n">
-        <v>192.739</v>
+        <v>190.623</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B56" t="n">
-        <v>196.712</v>
+        <v>204.862</v>
       </c>
       <c r="C56" t="n">
-        <v>190.623</v>
+        <v>178.682</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="B57" t="n">
-        <v>204.862</v>
+        <v>195.433</v>
       </c>
       <c r="C57" t="n">
-        <v>178.682</v>
+        <v>186.832</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45913</v>
+        <v>45920</v>
       </c>
       <c r="B58" t="n">
-        <v>195.433</v>
+        <v>180.611</v>
       </c>
       <c r="C58" t="n">
-        <v>186.832</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>45920</v>
-      </c>
-      <c r="B59" t="n">
-        <v>194.478</v>
-      </c>
-      <c r="C59" t="n">
         <v>181.701</v>
       </c>
     </row>
@@ -1066,628 +1055,617 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B2" t="n">
-        <v>1843.217</v>
+        <v>1800.515</v>
       </c>
       <c r="C2" t="n">
-        <v>1789.862</v>
+        <v>1747.737</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B3" t="n">
-        <v>1800.515</v>
+        <v>1704.638</v>
       </c>
       <c r="C3" t="n">
-        <v>1747.737</v>
+        <v>1655.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B4" t="n">
-        <v>1704.638</v>
+        <v>1671.837</v>
       </c>
       <c r="C4" t="n">
-        <v>1655.84</v>
+        <v>1645.927</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B5" t="n">
-        <v>1671.837</v>
+        <v>1628.081</v>
       </c>
       <c r="C5" t="n">
-        <v>1645.927</v>
+        <v>1588.285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B6" t="n">
-        <v>1628.081</v>
+        <v>1613.719</v>
       </c>
       <c r="C6" t="n">
-        <v>1588.285</v>
+        <v>1585.277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B7" t="n">
-        <v>1613.719</v>
+        <v>1614.385</v>
       </c>
       <c r="C7" t="n">
-        <v>1585.277</v>
+        <v>1555.172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B8" t="n">
-        <v>1614.385</v>
+        <v>1598.241</v>
       </c>
       <c r="C8" t="n">
-        <v>1555.172</v>
+        <v>1542.397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B9" t="n">
-        <v>1598.241</v>
+        <v>1627.825</v>
       </c>
       <c r="C9" t="n">
-        <v>1542.397</v>
+        <v>1572.658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B10" t="n">
-        <v>1627.825</v>
+        <v>1616.144</v>
       </c>
       <c r="C10" t="n">
-        <v>1572.658</v>
+        <v>1574.471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B11" t="n">
-        <v>1616.144</v>
+        <v>1646.982</v>
       </c>
       <c r="C11" t="n">
-        <v>1574.471</v>
+        <v>1607.693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B12" t="n">
-        <v>1646.982</v>
+        <v>1647.301</v>
       </c>
       <c r="C12" t="n">
-        <v>1607.693</v>
+        <v>1578.946</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B13" t="n">
-        <v>1647.301</v>
+        <v>1660.894</v>
       </c>
       <c r="C13" t="n">
-        <v>1578.946</v>
+        <v>1654.732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B14" t="n">
-        <v>1660.894</v>
+        <v>1721.154</v>
       </c>
       <c r="C14" t="n">
-        <v>1654.732</v>
+        <v>1555.596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B15" t="n">
-        <v>1721.154</v>
+        <v>1661.071</v>
       </c>
       <c r="C15" t="n">
-        <v>1555.596</v>
+        <v>1845.084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B16" t="n">
-        <v>1661.071</v>
+        <v>1933.23</v>
       </c>
       <c r="C16" t="n">
-        <v>1845.084</v>
+        <v>1767.267</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B17" t="n">
-        <v>1933.23</v>
+        <v>1864.863</v>
       </c>
       <c r="C17" t="n">
-        <v>1767.267</v>
+        <v>1835.427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B18" t="n">
-        <v>1864.863</v>
+        <v>1946.787</v>
       </c>
       <c r="C18" t="n">
-        <v>1835.427</v>
+        <v>1836.539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B19" t="n">
-        <v>1946.787</v>
+        <v>1860.888</v>
       </c>
       <c r="C19" t="n">
-        <v>1836.539</v>
+        <v>1902.054</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B20" t="n">
-        <v>1860.888</v>
+        <v>2187.475</v>
       </c>
       <c r="C20" t="n">
-        <v>1902.054</v>
+        <v>2104.257</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B21" t="n">
-        <v>2187.475</v>
+        <v>2273.651</v>
       </c>
       <c r="C21" t="n">
-        <v>2104.257</v>
+        <v>2122.561</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="n">
-        <v>2273.651</v>
+        <v>2246.551</v>
       </c>
       <c r="C22" t="n">
-        <v>2122.561</v>
+        <v>2053.289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B23" t="n">
-        <v>2246.551</v>
+        <v>2170.633</v>
       </c>
       <c r="C23" t="n">
-        <v>2053.289</v>
+        <v>2181.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B24" t="n">
-        <v>2170.633</v>
+        <v>2250.894</v>
       </c>
       <c r="C24" t="n">
-        <v>2181.43</v>
+        <v>2130.018</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B25" t="n">
-        <v>2250.894</v>
+        <v>2185.828</v>
       </c>
       <c r="C25" t="n">
-        <v>2130.018</v>
+        <v>2139.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B26" t="n">
-        <v>2185.828</v>
+        <v>2191.042</v>
       </c>
       <c r="C26" t="n">
-        <v>2139.97</v>
+        <v>2092.787</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B27" t="n">
-        <v>2191.042</v>
+        <v>2160.103</v>
       </c>
       <c r="C27" t="n">
-        <v>2092.787</v>
+        <v>2092.108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B28" t="n">
-        <v>2160.103</v>
+        <v>2229.07</v>
       </c>
       <c r="C28" t="n">
-        <v>2092.108</v>
+        <v>2113.581</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B29" t="n">
-        <v>2229.07</v>
+        <v>2149.919</v>
       </c>
       <c r="C29" t="n">
-        <v>2113.581</v>
+        <v>2078.603</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="n">
-        <v>2149.919</v>
+        <v>2116.538</v>
       </c>
       <c r="C30" t="n">
-        <v>2078.603</v>
+        <v>2008.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B31" t="n">
-        <v>2116.538</v>
+        <v>2072.402</v>
       </c>
       <c r="C31" t="n">
-        <v>2008.79</v>
+        <v>2012.613</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B32" t="n">
-        <v>2072.402</v>
+        <v>2058.751</v>
       </c>
       <c r="C32" t="n">
-        <v>2012.613</v>
+        <v>1937.982</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>2058.751</v>
+        <v>1985.73</v>
       </c>
       <c r="C33" t="n">
-        <v>1937.982</v>
+        <v>1928.017</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B34" t="n">
-        <v>1985.73</v>
+        <v>1943.418</v>
       </c>
       <c r="C34" t="n">
-        <v>1928.017</v>
+        <v>1848.827</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B35" t="n">
-        <v>1943.418</v>
+        <v>1880.372</v>
       </c>
       <c r="C35" t="n">
-        <v>1848.827</v>
+        <v>1812.811</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B36" t="n">
-        <v>1880.372</v>
+        <v>1898.153</v>
       </c>
       <c r="C36" t="n">
-        <v>1812.811</v>
+        <v>1753.465</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B37" t="n">
-        <v>1898.153</v>
+        <v>1838.279</v>
       </c>
       <c r="C37" t="n">
-        <v>1753.465</v>
+        <v>1743.445</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B38" t="n">
-        <v>1838.279</v>
+        <v>1782.724</v>
       </c>
       <c r="C38" t="n">
-        <v>1743.445</v>
+        <v>1686.177</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B39" t="n">
-        <v>1782.724</v>
+        <v>1779.686</v>
       </c>
       <c r="C39" t="n">
-        <v>1686.177</v>
+        <v>1686.782</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B40" t="n">
-        <v>1779.686</v>
+        <v>1775.51</v>
       </c>
       <c r="C40" t="n">
-        <v>1686.782</v>
+        <v>1666.648</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B41" t="n">
-        <v>1775.51</v>
+        <v>1755.336</v>
       </c>
       <c r="C41" t="n">
-        <v>1666.648</v>
+        <v>1670.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B42" t="n">
-        <v>1755.336</v>
+        <v>1826.063</v>
       </c>
       <c r="C42" t="n">
-        <v>1670.55</v>
+        <v>1708.158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B43" t="n">
-        <v>1826.063</v>
+        <v>1813.454</v>
       </c>
       <c r="C43" t="n">
-        <v>1708.158</v>
+        <v>1727.754</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B44" t="n">
-        <v>1813.454</v>
+        <v>1862.043</v>
       </c>
       <c r="C44" t="n">
-        <v>1727.754</v>
+        <v>1748.567</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B45" t="n">
-        <v>1862.043</v>
+        <v>1900.787</v>
       </c>
       <c r="C45" t="n">
-        <v>1748.567</v>
+        <v>1821.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B46" t="n">
-        <v>1900.787</v>
+        <v>1895.589</v>
       </c>
       <c r="C46" t="n">
-        <v>1821.4</v>
+        <v>1795.365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B47" t="n">
-        <v>1895.589</v>
+        <v>2011.507</v>
       </c>
       <c r="C47" t="n">
-        <v>1795.365</v>
+        <v>1945.731</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B48" t="n">
-        <v>2011.507</v>
+        <v>2006.612</v>
       </c>
       <c r="C48" t="n">
-        <v>1945.731</v>
+        <v>1914.075</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B49" t="n">
-        <v>2006.612</v>
+        <v>2005.922</v>
       </c>
       <c r="C49" t="n">
-        <v>1914.075</v>
+        <v>1934.382</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B50" t="n">
-        <v>2005.922</v>
+        <v>1999.973</v>
       </c>
       <c r="C50" t="n">
-        <v>1934.382</v>
+        <v>1907.041</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B51" t="n">
-        <v>1999.973</v>
+        <v>1973.535</v>
       </c>
       <c r="C51" t="n">
-        <v>1907.041</v>
+        <v>1883.372</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B52" t="n">
-        <v>1973.535</v>
+        <v>1955.067</v>
       </c>
       <c r="C52" t="n">
-        <v>1883.372</v>
+        <v>1857.167</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B53" t="n">
-        <v>1955.067</v>
+        <v>1934.367</v>
       </c>
       <c r="C53" t="n">
-        <v>1857.167</v>
+        <v>1843.217</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B54" t="n">
-        <v>1934.367</v>
+        <v>1892.212</v>
       </c>
       <c r="C54" t="n">
-        <v>1843.217</v>
+        <v>1800.515</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B55" t="n">
-        <v>1892.212</v>
+        <v>1803.344</v>
       </c>
       <c r="C55" t="n">
-        <v>1800.515</v>
+        <v>1704.638</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B56" t="n">
-        <v>1803.344</v>
+        <v>1759.868</v>
       </c>
       <c r="C56" t="n">
-        <v>1704.638</v>
+        <v>1671.837</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="B57" t="n">
-        <v>1759.868</v>
+        <v>1727.777</v>
       </c>
       <c r="C57" t="n">
-        <v>1671.837</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45913</v>
-      </c>
-      <c r="B58" t="n">
-        <v>1752.826</v>
-      </c>
-      <c r="C58" t="n">
         <v>1628.081</v>
       </c>
     </row>
@@ -1715,54 +1693,54 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B2" t="n">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C2" t="n">
-        <v>343</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B3" t="n">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="C3" t="n">
-        <v>371</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B4" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C4" t="n">
-        <v>314</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B5" t="n">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="C5" t="n">
-        <v>272</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
         <v>363</v>
@@ -1770,573 +1748,562 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>363</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B8" t="n">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="C8" t="n">
-        <v>390</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B9" t="n">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B10" t="n">
-        <v>434</v>
+        <v>392</v>
       </c>
       <c r="C10" t="n">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B11" t="n">
-        <v>392</v>
+        <v>533</v>
       </c>
       <c r="C11" t="n">
-        <v>460</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B12" t="n">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="C12" t="n">
-        <v>628</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B13" t="n">
-        <v>507</v>
+        <v>622</v>
       </c>
       <c r="C13" t="n">
-        <v>519</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B14" t="n">
-        <v>622</v>
+        <v>529</v>
       </c>
       <c r="C14" t="n">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B15" t="n">
-        <v>529</v>
+        <v>760</v>
       </c>
       <c r="C15" t="n">
-        <v>662</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B16" t="n">
-        <v>760</v>
+        <v>399</v>
       </c>
       <c r="C16" t="n">
-        <v>511</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B17" t="n">
-        <v>399</v>
+        <v>759</v>
       </c>
       <c r="C17" t="n">
-        <v>729</v>
+        <v>747</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B18" t="n">
-        <v>759</v>
+        <v>549</v>
       </c>
       <c r="C18" t="n">
-        <v>747</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B19" t="n">
-        <v>549</v>
+        <v>507</v>
       </c>
       <c r="C19" t="n">
-        <v>514</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B20" t="n">
-        <v>507</v>
+        <v>343</v>
       </c>
       <c r="C20" t="n">
-        <v>580</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B21" t="n">
-        <v>343</v>
+        <v>479</v>
       </c>
       <c r="C21" t="n">
-        <v>415</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="n">
-        <v>479</v>
+        <v>597</v>
       </c>
       <c r="C22" t="n">
-        <v>643</v>
+        <v>762</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B23" t="n">
-        <v>597</v>
+        <v>495</v>
       </c>
       <c r="C23" t="n">
-        <v>762</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B24" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C24" t="n">
-        <v>420</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B25" t="n">
-        <v>497</v>
+        <v>599</v>
       </c>
       <c r="C25" t="n">
-        <v>502</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B26" t="n">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="C26" t="n">
-        <v>411</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B27" t="n">
         <v>613</v>
       </c>
       <c r="C27" t="n">
-        <v>382</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B28" t="n">
-        <v>613</v>
+        <v>1634</v>
       </c>
       <c r="C28" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B29" t="n">
-        <v>1634</v>
+        <v>1580</v>
       </c>
       <c r="C29" t="n">
-        <v>330</v>
+        <v>393</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="n">
-        <v>1580</v>
+        <v>1066</v>
       </c>
       <c r="C30" t="n">
-        <v>393</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B31" t="n">
-        <v>1066</v>
+        <v>821</v>
       </c>
       <c r="C31" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B32" t="n">
-        <v>821</v>
+        <v>564</v>
       </c>
       <c r="C32" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="C33" t="n">
-        <v>371</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B34" t="n">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="C34" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B35" t="n">
-        <v>542</v>
+        <v>657</v>
       </c>
       <c r="C35" t="n">
-        <v>327</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B36" t="n">
-        <v>657</v>
+        <v>466</v>
       </c>
       <c r="C36" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B37" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C37" t="n">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B38" t="n">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C38" t="n">
-        <v>343</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B39" t="n">
-        <v>434</v>
+        <v>599</v>
       </c>
       <c r="C39" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B40" t="n">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C40" t="n">
-        <v>386</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B41" t="n">
-        <v>592</v>
+        <v>523</v>
       </c>
       <c r="C41" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B42" t="n">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="C42" t="n">
-        <v>353</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B43" t="n">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="C43" t="n">
-        <v>400</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B44" t="n">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="C44" t="n">
-        <v>419</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B45" t="n">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="C45" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B46" t="n">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C46" t="n">
-        <v>336</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B47" t="n">
-        <v>438</v>
+        <v>596</v>
       </c>
       <c r="C47" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B48" t="n">
-        <v>596</v>
+        <v>789</v>
       </c>
       <c r="C48" t="n">
-        <v>327</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B49" t="n">
-        <v>789</v>
+        <v>722</v>
       </c>
       <c r="C49" t="n">
-        <v>476</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B50" t="n">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="C50" t="n">
-        <v>392</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B51" t="n">
-        <v>708</v>
+        <v>637</v>
       </c>
       <c r="C51" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B52" t="n">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C52" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B53" t="n">
-        <v>635</v>
+        <v>588</v>
       </c>
       <c r="C53" t="n">
-        <v>336</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B54" t="n">
-        <v>588</v>
+        <v>515</v>
       </c>
       <c r="C54" t="n">
-        <v>285</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B55" t="n">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C55" t="n">
-        <v>307</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B56" t="n">
-        <v>527</v>
+        <v>572</v>
       </c>
       <c r="C56" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="B57" t="n">
-        <v>572</v>
+        <v>635</v>
       </c>
       <c r="C57" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45913</v>
-      </c>
-      <c r="B58" t="n">
-        <v>635</v>
-      </c>
-      <c r="C58" t="n">
         <v>313</v>
       </c>
     </row>
@@ -2364,617 +2331,606 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B2" t="n">
-        <v>4308</v>
+        <v>4191</v>
       </c>
       <c r="C2" t="n">
-        <v>4469</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B3" t="n">
-        <v>4191</v>
+        <v>3852</v>
       </c>
       <c r="C3" t="n">
-        <v>4552</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B4" t="n">
-        <v>3852</v>
+        <v>3898</v>
       </c>
       <c r="C4" t="n">
-        <v>4164</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B5" t="n">
-        <v>3898</v>
+        <v>4001</v>
       </c>
       <c r="C5" t="n">
-        <v>4295</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B6" t="n">
-        <v>4001</v>
+        <v>4033</v>
       </c>
       <c r="C6" t="n">
-        <v>4123</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B7" t="n">
-        <v>4033</v>
+        <v>3929</v>
       </c>
       <c r="C7" t="n">
-        <v>4148</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B8" t="n">
-        <v>3929</v>
+        <v>3819</v>
       </c>
       <c r="C8" t="n">
-        <v>4200</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B9" t="n">
-        <v>3819</v>
+        <v>3903</v>
       </c>
       <c r="C9" t="n">
-        <v>4121</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B10" t="n">
-        <v>3903</v>
+        <v>4038</v>
       </c>
       <c r="C10" t="n">
-        <v>4267</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B11" t="n">
-        <v>4038</v>
+        <v>4246</v>
       </c>
       <c r="C11" t="n">
-        <v>4309</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B12" t="n">
-        <v>4246</v>
+        <v>4454</v>
       </c>
       <c r="C12" t="n">
-        <v>4638</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B13" t="n">
-        <v>4454</v>
+        <v>4760</v>
       </c>
       <c r="C13" t="n">
-        <v>4741</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B14" t="n">
-        <v>4760</v>
+        <v>5023</v>
       </c>
       <c r="C14" t="n">
-        <v>5179</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B15" t="n">
-        <v>5023</v>
+        <v>5081</v>
       </c>
       <c r="C15" t="n">
-        <v>5045</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B16" t="n">
-        <v>5081</v>
+        <v>5997</v>
       </c>
       <c r="C16" t="n">
-        <v>5791</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B17" t="n">
-        <v>5997</v>
+        <v>6031</v>
       </c>
       <c r="C17" t="n">
-        <v>6131</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B18" t="n">
-        <v>6031</v>
+        <v>6577</v>
       </c>
       <c r="C18" t="n">
-        <v>6272</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B19" t="n">
-        <v>6577</v>
+        <v>6210</v>
       </c>
       <c r="C19" t="n">
-        <v>6427</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B20" t="n">
-        <v>6210</v>
+        <v>6374</v>
       </c>
       <c r="C20" t="n">
-        <v>6284</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B21" t="n">
-        <v>6374</v>
+        <v>6854</v>
       </c>
       <c r="C21" t="n">
-        <v>6577</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="n">
-        <v>6854</v>
+        <v>7381</v>
       </c>
       <c r="C22" t="n">
-        <v>6766</v>
+        <v>6708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B23" t="n">
-        <v>7381</v>
+        <v>6684</v>
       </c>
       <c r="C23" t="n">
-        <v>6708</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B24" t="n">
-        <v>6684</v>
+        <v>7470</v>
       </c>
       <c r="C24" t="n">
-        <v>7383</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B25" t="n">
-        <v>7470</v>
+        <v>7120</v>
       </c>
       <c r="C25" t="n">
-        <v>6953</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B26" t="n">
-        <v>7120</v>
+        <v>7621</v>
       </c>
       <c r="C26" t="n">
-        <v>6893</v>
+        <v>6819</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B27" t="n">
-        <v>7621</v>
+        <v>7422</v>
       </c>
       <c r="C27" t="n">
-        <v>6819</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B28" t="n">
-        <v>7422</v>
+        <v>8230</v>
       </c>
       <c r="C28" t="n">
-        <v>6594</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B29" t="n">
-        <v>8230</v>
+        <v>8929</v>
       </c>
       <c r="C29" t="n">
-        <v>6876</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="n">
-        <v>8929</v>
+        <v>9136</v>
       </c>
       <c r="C30" t="n">
-        <v>6208</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B31" t="n">
-        <v>9136</v>
+        <v>8246</v>
       </c>
       <c r="C31" t="n">
-        <v>6241</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B32" t="n">
-        <v>8246</v>
+        <v>7721</v>
       </c>
       <c r="C32" t="n">
-        <v>5891</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>7721</v>
+        <v>7192</v>
       </c>
       <c r="C33" t="n">
-        <v>5881</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B34" t="n">
-        <v>7192</v>
+        <v>7019</v>
       </c>
       <c r="C34" t="n">
-        <v>5546</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B35" t="n">
-        <v>7019</v>
+        <v>6640</v>
       </c>
       <c r="C35" t="n">
-        <v>5274</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B36" t="n">
-        <v>6640</v>
+        <v>6716</v>
       </c>
       <c r="C36" t="n">
-        <v>5091</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B37" t="n">
-        <v>6716</v>
+        <v>6570</v>
       </c>
       <c r="C37" t="n">
-        <v>5030</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B38" t="n">
-        <v>6570</v>
+        <v>6473</v>
       </c>
       <c r="C38" t="n">
-        <v>4764</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B39" t="n">
-        <v>6473</v>
+        <v>6377</v>
       </c>
       <c r="C39" t="n">
-        <v>4737</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B40" t="n">
-        <v>6377</v>
+        <v>6717</v>
       </c>
       <c r="C40" t="n">
-        <v>4494</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B41" t="n">
-        <v>6717</v>
+        <v>6323</v>
       </c>
       <c r="C41" t="n">
-        <v>4648</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B42" t="n">
-        <v>6323</v>
+        <v>7076</v>
       </c>
       <c r="C42" t="n">
-        <v>4401</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B43" t="n">
-        <v>7076</v>
+        <v>6738</v>
       </c>
       <c r="C43" t="n">
-        <v>4634</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B44" t="n">
-        <v>6738</v>
+        <v>7103</v>
       </c>
       <c r="C44" t="n">
-        <v>4553</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B45" t="n">
-        <v>7103</v>
+        <v>6947</v>
       </c>
       <c r="C45" t="n">
-        <v>4568</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B46" t="n">
-        <v>6947</v>
+        <v>7035</v>
       </c>
       <c r="C46" t="n">
-        <v>4433</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B47" t="n">
-        <v>7035</v>
+        <v>7226</v>
       </c>
       <c r="C47" t="n">
-        <v>4605</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B48" t="n">
-        <v>7226</v>
+        <v>7407</v>
       </c>
       <c r="C48" t="n">
-        <v>4711</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B49" t="n">
-        <v>7407</v>
+        <v>7831</v>
       </c>
       <c r="C49" t="n">
-        <v>4658</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B50" t="n">
-        <v>7831</v>
+        <v>8193</v>
       </c>
       <c r="C50" t="n">
-        <v>4767</v>
+        <v>4855</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B51" t="n">
-        <v>8193</v>
+        <v>8237</v>
       </c>
       <c r="C51" t="n">
-        <v>4855</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B52" t="n">
-        <v>8237</v>
+        <v>8456</v>
       </c>
       <c r="C52" t="n">
-        <v>4505</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B53" t="n">
-        <v>8456</v>
+        <v>8128</v>
       </c>
       <c r="C53" t="n">
-        <v>4632</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B54" t="n">
-        <v>8128</v>
+        <v>8211</v>
       </c>
       <c r="C54" t="n">
-        <v>4308</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B55" t="n">
-        <v>8211</v>
+        <v>7863</v>
       </c>
       <c r="C55" t="n">
-        <v>4191</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B56" t="n">
-        <v>7863</v>
+        <v>8168</v>
       </c>
       <c r="C56" t="n">
-        <v>3852</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="B57" t="n">
-        <v>8168</v>
-      </c>
-      <c r="C57" t="n">
         <v>3898</v>
       </c>
     </row>
@@ -3002,1190 +2958,1190 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45157</v>
+        <v>45164</v>
       </c>
       <c r="B2" t="n">
-        <v>0.682643323527301</v>
+        <v>0.752462149051889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.269086059042244</v>
+        <v>0.278731577177855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45164</v>
+        <v>45171</v>
       </c>
       <c r="B3" t="n">
-        <v>0.752462149051889</v>
+        <v>0.69588188463487</v>
       </c>
       <c r="C3" t="n">
-        <v>0.278731577177855</v>
+        <v>0.285075465258575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45171</v>
+        <v>45178</v>
       </c>
       <c r="B4" t="n">
-        <v>0.69588188463487</v>
+        <v>0.659128917327129</v>
       </c>
       <c r="C4" t="n">
-        <v>0.285075465258575</v>
+        <v>0.288155928025338</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45178</v>
+        <v>45185</v>
       </c>
       <c r="B5" t="n">
-        <v>0.659128917327129</v>
+        <v>0.71851908866995</v>
       </c>
       <c r="C5" t="n">
-        <v>0.288155928025338</v>
+        <v>0.292300734442642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45185</v>
+        <v>45192</v>
       </c>
       <c r="B6" t="n">
-        <v>0.71851908866995</v>
+        <v>0.688183807439825</v>
       </c>
       <c r="C6" t="n">
-        <v>0.292300734442642</v>
+        <v>0.294048419132878</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45192</v>
+        <v>45199</v>
       </c>
       <c r="B7" t="n">
-        <v>0.688183807439825</v>
+        <v>0.745592754326379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.294048419132878</v>
+        <v>0.292430153360314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45199</v>
+        <v>45206</v>
       </c>
       <c r="B8" t="n">
-        <v>0.745592754326379</v>
+        <v>0.829532114707362</v>
       </c>
       <c r="C8" t="n">
-        <v>0.292430153360314</v>
+        <v>0.292538062193876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45206</v>
+        <v>45213</v>
       </c>
       <c r="B9" t="n">
-        <v>0.829532114707362</v>
+        <v>0.82242374278648</v>
       </c>
       <c r="C9" t="n">
-        <v>0.292538062193876</v>
+        <v>0.286920428436942</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45213</v>
+        <v>45220</v>
       </c>
       <c r="B10" t="n">
-        <v>0.82242374278648</v>
+        <v>0.912273302404049</v>
       </c>
       <c r="C10" t="n">
-        <v>0.286920428436942</v>
+        <v>0.282927690123362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45220</v>
+        <v>45227</v>
       </c>
       <c r="B11" t="n">
-        <v>0.912273302404049</v>
+        <v>0.998352267799844</v>
       </c>
       <c r="C11" t="n">
-        <v>0.282927690123362</v>
+        <v>0.276427174122571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45227</v>
+        <v>45234</v>
       </c>
       <c r="B12" t="n">
-        <v>0.998352267799844</v>
+        <v>1.08845296477931</v>
       </c>
       <c r="C12" t="n">
-        <v>0.276427174122571</v>
+        <v>0.275848614432846</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45234</v>
+        <v>45241</v>
       </c>
       <c r="B13" t="n">
-        <v>1.08845296477931</v>
+        <v>1.19650167473018</v>
       </c>
       <c r="C13" t="n">
-        <v>0.275848614432846</v>
+        <v>0.262878986207589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45241</v>
+        <v>45248</v>
       </c>
       <c r="B14" t="n">
-        <v>1.19650167473018</v>
+        <v>1.14916869045395</v>
       </c>
       <c r="C14" t="n">
-        <v>0.262878986207589</v>
+        <v>0.253808435820337</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45248</v>
+        <v>45255</v>
       </c>
       <c r="B15" t="n">
-        <v>1.14916869045395</v>
+        <v>1.14369202226345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.253808435820337</v>
+        <v>0.229470488926282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45255</v>
+        <v>45262</v>
       </c>
       <c r="B16" t="n">
-        <v>1.14369202226345</v>
+        <v>1.07848915081704</v>
       </c>
       <c r="C16" t="n">
-        <v>0.229470488926282</v>
+        <v>0.20342743368623</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45262</v>
+        <v>45269</v>
       </c>
       <c r="B17" t="n">
-        <v>1.07848915081704</v>
+        <v>1.02695231513476</v>
       </c>
       <c r="C17" t="n">
-        <v>0.20342743368623</v>
+        <v>0.182789382857749</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45269</v>
+        <v>45276</v>
       </c>
       <c r="B18" t="n">
-        <v>1.02695231513476</v>
+        <v>0.936523280167553</v>
       </c>
       <c r="C18" t="n">
-        <v>0.182789382857749</v>
+        <v>0.16803310758329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45276</v>
+        <v>45283</v>
       </c>
       <c r="B19" t="n">
-        <v>0.936523280167553</v>
+        <v>0.880585211546066</v>
       </c>
       <c r="C19" t="n">
-        <v>0.16803310758329</v>
+        <v>0.149667696227104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45283</v>
+        <v>45290</v>
       </c>
       <c r="B20" t="n">
-        <v>0.880585211546066</v>
+        <v>0.827831270059606</v>
       </c>
       <c r="C20" t="n">
-        <v>0.149667696227104</v>
+        <v>0.137149365060206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45290</v>
+        <v>45297</v>
       </c>
       <c r="B21" t="n">
-        <v>0.827831270059606</v>
+        <v>0.725096194955109</v>
       </c>
       <c r="C21" t="n">
-        <v>0.137149365060206</v>
+        <v>0.127234983606052</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45297</v>
+        <v>45304</v>
       </c>
       <c r="B22" t="n">
-        <v>0.725096194955109</v>
+        <v>0.683745214061956</v>
       </c>
       <c r="C22" t="n">
-        <v>0.127234983606052</v>
+        <v>0.112721865125587</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45304</v>
+        <v>45311</v>
       </c>
       <c r="B23" t="n">
-        <v>0.683745214061956</v>
+        <v>0.59653417509502</v>
       </c>
       <c r="C23" t="n">
-        <v>0.112721865125587</v>
+        <v>0.120158906584597</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45311</v>
+        <v>45318</v>
       </c>
       <c r="B24" t="n">
-        <v>0.59653417509502</v>
+        <v>0.448905338435481</v>
       </c>
       <c r="C24" t="n">
-        <v>0.120158906584597</v>
+        <v>0.115352464366679</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45318</v>
+        <v>45325</v>
       </c>
       <c r="B25" t="n">
-        <v>0.448905338435481</v>
+        <v>0.368510431829209</v>
       </c>
       <c r="C25" t="n">
-        <v>0.115352464366679</v>
+        <v>0.11182537948803</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45325</v>
+        <v>45332</v>
       </c>
       <c r="B26" t="n">
-        <v>0.368510431829209</v>
+        <v>0.294063079777366</v>
       </c>
       <c r="C26" t="n">
-        <v>0.11182537948803</v>
+        <v>0.107616691372684</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45332</v>
+        <v>45339</v>
       </c>
       <c r="B27" t="n">
-        <v>0.294063079777366</v>
+        <v>0.220064178348252</v>
       </c>
       <c r="C27" t="n">
-        <v>0.107616691372684</v>
+        <v>0.0988033469584233</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45339</v>
+        <v>45346</v>
       </c>
       <c r="B28" t="n">
-        <v>0.220064178348252</v>
+        <v>0.155271015739663</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0988033469584233</v>
+        <v>0.0903828995441902</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45346</v>
+        <v>45353</v>
       </c>
       <c r="B29" t="n">
-        <v>0.155271015739663</v>
+        <v>0.141088859816846</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0903828995441902</v>
+        <v>0.0878492655366059</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45353</v>
+        <v>45360</v>
       </c>
       <c r="B30" t="n">
-        <v>0.141088859816846</v>
+        <v>0.107121807465619</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0878492655366059</v>
+        <v>0.084035657662493</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45360</v>
+        <v>45367</v>
       </c>
       <c r="B31" t="n">
-        <v>0.107121807465619</v>
+        <v>0.0716237866365093</v>
       </c>
       <c r="C31" t="n">
-        <v>0.084035657662493</v>
+        <v>0.0756771842295227</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45367</v>
+        <v>45374</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0716237866365093</v>
+        <v>0.0515586979477527</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0756771842295227</v>
+        <v>0.0706704847488504</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45374</v>
+        <v>45381</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0515586979477527</v>
+        <v>0.0234076074724285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0706704847488504</v>
+        <v>0.0672873676665622</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45381</v>
+        <v>45388</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0234076074724285</v>
+        <v>-0.013405178078591</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0672873676665622</v>
+        <v>0.0588975018865721</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45388</v>
+        <v>45395</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.013405178078591</v>
+        <v>-0.0276095475596723</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0588975018865721</v>
+        <v>0.0498411285611142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45395</v>
+        <v>45402</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.0276095475596723</v>
+        <v>0.00954045246304247</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0498411285611142</v>
+        <v>0.0465875645822198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45402</v>
+        <v>45409</v>
       </c>
       <c r="B37" t="n">
-        <v>0.00954045246304247</v>
+        <v>0.0323711239838387</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0465875645822198</v>
+        <v>0.0401800167043784</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45409</v>
+        <v>45416</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0323711239838387</v>
+        <v>0.0972322627284932</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0401800167043784</v>
+        <v>0.0431098725616055</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45416</v>
+        <v>45423</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0972322627284932</v>
+        <v>0.14658292527145</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0431098725616055</v>
+        <v>0.0460089809272537</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45423</v>
+        <v>45430</v>
       </c>
       <c r="B40" t="n">
-        <v>0.14658292527145</v>
+        <v>0.174474959612278</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0460089809272537</v>
+        <v>0.045447728861981</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45430</v>
+        <v>45437</v>
       </c>
       <c r="B41" t="n">
-        <v>0.174474959612278</v>
+        <v>0.200282854656223</v>
       </c>
       <c r="C41" t="n">
-        <v>0.045447728861981</v>
+        <v>0.0446505258703753</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45437</v>
+        <v>45444</v>
       </c>
       <c r="B42" t="n">
-        <v>0.200282854656223</v>
+        <v>0.218417499324872</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0446505258703753</v>
+        <v>0.0420175845375934</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45444</v>
+        <v>45451</v>
       </c>
       <c r="B43" t="n">
-        <v>0.218417499324872</v>
+        <v>0.223254324151185</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0420175845375934</v>
+        <v>0.0388086026617791</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45451</v>
+        <v>45458</v>
       </c>
       <c r="B44" t="n">
-        <v>0.223254324151185</v>
+        <v>0.23546808625047</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0388086026617791</v>
+        <v>0.0407852482714004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45458</v>
+        <v>45465</v>
       </c>
       <c r="B45" t="n">
-        <v>0.23546808625047</v>
+        <v>0.22424652542814</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0407852482714004</v>
+        <v>0.040985152109636</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45465</v>
+        <v>45472</v>
       </c>
       <c r="B46" t="n">
-        <v>0.22424652542814</v>
+        <v>0.198969280517381</v>
       </c>
       <c r="C46" t="n">
-        <v>0.040985152109636</v>
+        <v>0.0421079680110672</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45472</v>
+        <v>45479</v>
       </c>
       <c r="B47" t="n">
-        <v>0.198969280517381</v>
+        <v>0.209443757725587</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0421079680110672</v>
+        <v>0.0408530223130144</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45479</v>
+        <v>45486</v>
       </c>
       <c r="B48" t="n">
-        <v>0.209443757725587</v>
+        <v>0.227342995169082</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0408530223130144</v>
+        <v>0.040555460529621</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45486</v>
+        <v>45493</v>
       </c>
       <c r="B49" t="n">
-        <v>0.227342995169082</v>
+        <v>0.203128637273616</v>
       </c>
       <c r="C49" t="n">
-        <v>0.040555460529621</v>
+        <v>0.0432092766697589</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45493</v>
+        <v>45500</v>
       </c>
       <c r="B50" t="n">
-        <v>0.203128637273616</v>
+        <v>0.189903193703067</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0432092766697589</v>
+        <v>0.0462641221417603</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45500</v>
+        <v>45507</v>
       </c>
       <c r="B51" t="n">
-        <v>0.189903193703067</v>
+        <v>0.163998059194566</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0462641221417603</v>
+        <v>0.0483020346929517</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45507</v>
+        <v>45514</v>
       </c>
       <c r="B52" t="n">
-        <v>0.163998059194566</v>
+        <v>0.141896234094512</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0483020346929517</v>
+        <v>0.0452476492494154</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45514</v>
+        <v>45521</v>
       </c>
       <c r="B53" t="n">
-        <v>0.141896234094512</v>
+        <v>0.150697198413714</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0452476492494154</v>
+        <v>0.0380479624136356</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B54" t="n">
-        <v>0.150697198413714</v>
+        <v>0.141125650058715</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0380479624136356</v>
+        <v>0.0321595930779075</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B55" t="n">
-        <v>0.141125650058715</v>
+        <v>0.150051212017754</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0321595930779075</v>
+        <v>0.0299653997440217</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B56" t="n">
-        <v>0.150051212017754</v>
+        <v>0.16618459111228</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0299653997440217</v>
+        <v>0.0264411935258326</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B57" t="n">
-        <v>0.16618459111228</v>
+        <v>0.166748779504636</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0264411935258326</v>
+        <v>0.0252014639211942</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B58" t="n">
-        <v>0.166748779504636</v>
+        <v>0.178918618646422</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0252014639211942</v>
+        <v>0.0220754806435317</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B59" t="n">
-        <v>0.178918618646422</v>
+        <v>0.176410636523673</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0220754806435317</v>
+        <v>0.024057906765552</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B60" t="n">
-        <v>0.176410636523673</v>
+        <v>0.158714881525276</v>
       </c>
       <c r="C60" t="n">
-        <v>0.024057906765552</v>
+        <v>0.0292283800163</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B61" t="n">
-        <v>0.158714881525276</v>
+        <v>0.154573418981272</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0292283800163</v>
+        <v>0.0317585921134413</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B62" t="n">
-        <v>0.154573418981272</v>
+        <v>0.14208204675783</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0317585921134413</v>
+        <v>0.0339323054533622</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B63" t="n">
-        <v>0.14208204675783</v>
+        <v>0.139955734930348</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0339323054533622</v>
+        <v>0.0304853618716452</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B64" t="n">
-        <v>0.139955734930348</v>
+        <v>0.132738451028947</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0304853618716452</v>
+        <v>0.0322847316163144</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B65" t="n">
-        <v>0.132738451028947</v>
+        <v>0.131862080650627</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0322847316163144</v>
+        <v>0.0242336079972043</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B66" t="n">
-        <v>0.131862080650627</v>
+        <v>0.171802338215481</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0242336079972043</v>
+        <v>0.0436713211120208</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B67" t="n">
-        <v>0.171802338215481</v>
+        <v>0.163226448569821</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0436713211120208</v>
+        <v>0.00845025245848952</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B68" t="n">
-        <v>0.163226448569821</v>
+        <v>0.172058254929759</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00845025245848952</v>
+        <v>0.0225234105253962</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B69" t="n">
-        <v>0.172058254929759</v>
+        <v>0.175715990453461</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0225234105253962</v>
+        <v>0.0252655362972192</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B70" t="n">
-        <v>0.175715990453461</v>
+        <v>0.160316139767055</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0252655362972192</v>
+        <v>0.0166980651720676</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B71" t="n">
-        <v>0.160316139767055</v>
+        <v>0.191925988225399</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0166980651720676</v>
+        <v>0.0360265168764005</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B72" t="n">
-        <v>0.191925988225399</v>
+        <v>0.204941678163803</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0360265168764005</v>
+        <v>0.0236688517489014</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B73" t="n">
-        <v>0.204941678163803</v>
+        <v>0.199917389508468</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0236688517489014</v>
+        <v>0.0380884300885416</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B74" t="n">
-        <v>0.199917389508468</v>
+        <v>0.229751519411254</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0380884300885416</v>
+        <v>0.0472251768206466</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B75" t="n">
-        <v>0.229751519411254</v>
+        <v>0.223177177904208</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0472251768206466</v>
+        <v>0.0492549994167726</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B76" t="n">
-        <v>0.223177177904208</v>
+        <v>0.323548512793869</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0492549994167726</v>
+        <v>0.0535424819536205</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B77" t="n">
-        <v>0.323548512793869</v>
+        <v>0.396427938308811</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0535424819536205</v>
+        <v>0.0410594979932879</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B78" t="n">
-        <v>0.396427938308811</v>
+        <v>0.454256272401434</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0410594979932879</v>
+        <v>0.0297502225192396</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B79" t="n">
-        <v>0.454256272401434</v>
+        <v>0.56764488741233</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0297502225192396</v>
+        <v>0.0393836319201579</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B80" t="n">
-        <v>0.56764488741233</v>
+        <v>0.596092346782319</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0393836319201579</v>
+        <v>0.0388219584506435</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B81" t="n">
-        <v>0.596092346782319</v>
+        <v>0.713643178410795</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0388219584506435</v>
+        <v>0.0421453587819811</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B82" t="n">
-        <v>0.713643178410795</v>
+        <v>0.829688123863183</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0421453587819811</v>
+        <v>0.04371691971694</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B83" t="n">
-        <v>0.829688123863183</v>
+        <v>0.898953478146161</v>
       </c>
       <c r="C83" t="n">
-        <v>0.04371691971694</v>
+        <v>0.043140956563801</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B84" t="n">
-        <v>0.898953478146161</v>
+        <v>0.914512748864827</v>
       </c>
       <c r="C84" t="n">
-        <v>0.043140956563801</v>
+        <v>0.0447403006822105</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B85" t="n">
-        <v>0.914512748864827</v>
+        <v>0.931867165163844</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0447403006822105</v>
+        <v>0.0438698319167705</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B86" t="n">
-        <v>0.931867165163844</v>
+        <v>0.931175347453488</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0438698319167705</v>
+        <v>0.0430753319437398</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B87" t="n">
-        <v>0.931175347453488</v>
+        <v>0.950586187946511</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0430753319437398</v>
+        <v>0.0452511193087552</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B88" t="n">
-        <v>0.950586187946511</v>
+        <v>0.962573099415205</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0452511193087552</v>
+        <v>0.049645518526185</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B89" t="n">
-        <v>0.962573099415205</v>
+        <v>0.956761599396454</v>
       </c>
       <c r="C89" t="n">
-        <v>0.049645518526185</v>
+        <v>0.0561110996252312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B90" t="n">
-        <v>0.956761599396454</v>
+        <v>0.928278977834251</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0561110996252312</v>
+        <v>0.0576952379808855</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B91" t="n">
-        <v>0.928278977834251</v>
+        <v>0.901866121994244</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0576952379808855</v>
+        <v>0.0624426753989049</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B92" t="n">
-        <v>0.901866121994244</v>
+        <v>0.879367262723521</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0624426753989049</v>
+        <v>0.057960192550492</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B93" t="n">
-        <v>0.879367262723521</v>
+        <v>0.860871929665549</v>
       </c>
       <c r="C93" t="n">
-        <v>0.057960192550492</v>
+        <v>0.0570924048423904</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B94" t="n">
-        <v>0.860871929665549</v>
+        <v>0.834035196595594</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0570924048423904</v>
+        <v>0.060078536714488</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B95" t="n">
-        <v>0.834035196595594</v>
+        <v>0.828052718861831</v>
       </c>
       <c r="C95" t="n">
-        <v>0.060078536714488</v>
+        <v>0.0586514909694367</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B96" t="n">
-        <v>0.828052718861831</v>
+        <v>0.844489902506964</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0586514909694367</v>
+        <v>0.0586236761361623</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B97" t="n">
-        <v>0.844489902506964</v>
+        <v>0.82460988987627</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0586236761361623</v>
+        <v>0.0565907575623272</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B98" t="n">
-        <v>0.82460988987627</v>
+        <v>0.823430257058575</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0565907575623272</v>
+        <v>0.0534022849856888</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B99" t="n">
-        <v>0.823430257058575</v>
+        <v>0.801316381178202</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0534022849856888</v>
+        <v>0.0490849278689021</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B100" t="n">
-        <v>0.801316381178202</v>
+        <v>0.77241596473274</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0490849278689021</v>
+        <v>0.0451977249998696</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B101" t="n">
-        <v>0.77241596473274</v>
+        <v>0.777726182184042</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0451977249998696</v>
+        <v>0.0434909671228332</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B102" t="n">
-        <v>0.777726182184042</v>
+        <v>0.783645072992701</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0434909671228332</v>
+        <v>0.0419134400496337</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B103" t="n">
-        <v>0.783645072992701</v>
+        <v>0.788245102125886</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0419134400496337</v>
+        <v>0.0454480832898061</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B104" t="n">
-        <v>0.788245102125886</v>
+        <v>0.763553821333433</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0454480832898061</v>
+        <v>0.0464965400776212</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B105" t="n">
-        <v>0.763553821333433</v>
+        <v>0.726848249027237</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0464965400776212</v>
+        <v>0.0496802943665406</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B106" t="n">
-        <v>0.726848249027237</v>
+        <v>0.677790436987761</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0496802943665406</v>
+        <v>0.0502297383181087</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B107" t="n">
-        <v>0.677790436987761</v>
+        <v>0.639268220276087</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0502297383181087</v>
+        <v>0.0526613075472375</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B108" t="n">
-        <v>0.639268220276087</v>
+        <v>0.59488913942127</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0526613075472375</v>
+        <v>0.0526457410728771</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="B109" t="n">
-        <v>0.59488913942127</v>
+        <v>0.621650671785029</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0526457410728771</v>
+        <v>0.0555659154768555</v>
       </c>
     </row>
   </sheetData>
@@ -4218,1821 +4174,1821 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45157</v>
+        <v>45164</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0428849902534114</v>
+        <v>0.0657640232108316</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.304347826086957</v>
+        <v>-0.3008356545961</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.181372549019608</v>
+        <v>-0.178921568627451</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.278547164881108</v>
+        <v>-0.278183635804368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45164</v>
+        <v>45171</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0657640232108316</v>
+        <v>-0.00174520069808026</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3008356545961</v>
+        <v>-0.302816901408451</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.178921568627451</v>
+        <v>-0.171149144254279</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.278183635804368</v>
+        <v>-0.291804180418042</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45171</v>
+        <v>45178</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00174520069808026</v>
+        <v>-0.0302066772655007</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.302816901408451</v>
+        <v>-0.347398030942335</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.171149144254279</v>
+        <v>-0.123425692695214</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.291804180418042</v>
+        <v>-0.302418389336739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45178</v>
+        <v>45185</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0302066772655007</v>
+        <v>0.045774647887324</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.347398030942335</v>
+        <v>-0.355677154582763</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.123425692695214</v>
+        <v>-0.123737373737374</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.302418389336739</v>
+        <v>-0.298907483939605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45185</v>
+        <v>45192</v>
       </c>
       <c r="B6" t="n">
-        <v>0.045774647887324</v>
+        <v>0.0774774774774776</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.355677154582763</v>
+        <v>-0.362068965517241</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.123737373737374</v>
+        <v>-0.116883116883117</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.298907483939605</v>
+        <v>-0.300029287477511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45192</v>
+        <v>45199</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0774774774774776</v>
+        <v>0.0599647266313934</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.362068965517241</v>
+        <v>-0.334239130434783</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.116883116883117</v>
+        <v>0.00298507462686559</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.300029287477511</v>
+        <v>-0.288400322566954</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45199</v>
+        <v>45206</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0599647266313934</v>
+        <v>0.329896907216495</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.334239130434783</v>
+        <v>-0.330769230769231</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00298507462686559</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.288400322566954</v>
+        <v>-0.273650571290986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45206</v>
+        <v>45213</v>
       </c>
       <c r="B9" t="n">
-        <v>0.329896907216495</v>
+        <v>0.443478260869565</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.330769230769231</v>
+        <v>-0.346733668341708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.166666666666667</v>
+        <v>0.388</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.273650571290986</v>
+        <v>-0.270253771692683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45213</v>
+        <v>45220</v>
       </c>
       <c r="B10" t="n">
-        <v>0.443478260869565</v>
+        <v>0.42274678111588</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.346733668341708</v>
+        <v>-0.443298969072165</v>
       </c>
       <c r="D10" t="n">
-        <v>0.388</v>
+        <v>0.616438356164384</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.270253771692683</v>
+        <v>-0.260136614414572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45220</v>
+        <v>45227</v>
       </c>
       <c r="B11" t="n">
-        <v>0.42274678111588</v>
+        <v>0.883977900552486</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.443298969072165</v>
+        <v>-0.435632183908046</v>
       </c>
       <c r="D11" t="n">
-        <v>0.616438356164384</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.260136614414572</v>
+        <v>-0.241688538932633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45227</v>
+        <v>45234</v>
       </c>
       <c r="B12" t="n">
-        <v>0.883977900552486</v>
+        <v>0.392290249433107</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.435632183908046</v>
+        <v>-0.344827586206897</v>
       </c>
       <c r="D12" t="n">
-        <v>0.555555555555556</v>
+        <v>0.40495867768595</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.241688538932633</v>
+        <v>-0.219313883212314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45234</v>
+        <v>45241</v>
       </c>
       <c r="B13" t="n">
-        <v>0.392290249433107</v>
+        <v>0.0458715596330275</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.344827586206897</v>
+        <v>-0.316120906801008</v>
       </c>
       <c r="D13" t="n">
-        <v>0.40495867768595</v>
+        <v>0.351239669421488</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.219313883212314</v>
+        <v>-0.195128194189668</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45241</v>
+        <v>45248</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0458715596330275</v>
+        <v>-0.0370994940978078</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.316120906801008</v>
+        <v>-0.129429892141757</v>
       </c>
       <c r="D14" t="n">
-        <v>0.351239669421488</v>
+        <v>0.263374485596708</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.195128194189668</v>
+        <v>-0.173183179383356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45248</v>
+        <v>45255</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0370994940978078</v>
+        <v>-0.121794871794872</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.129429892141757</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="D15" t="n">
-        <v>0.263374485596708</v>
+        <v>0.1699604743083</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.173183179383356</v>
+        <v>-0.1644795105064</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45255</v>
+        <v>45262</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.121794871794872</v>
+        <v>0.143122676579926</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0714285714285714</v>
+        <v>-0.114854517611026</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1699604743083</v>
+        <v>0.135658914728682</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1644795105064</v>
+        <v>-0.148820047659313</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45262</v>
+        <v>45269</v>
       </c>
       <c r="B17" t="n">
-        <v>0.143122676579926</v>
+        <v>0.253549695740365</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.114854517611026</v>
+        <v>-0.0337941628264209</v>
       </c>
       <c r="D17" t="n">
-        <v>0.135658914728682</v>
+        <v>0.104089219330855</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.148820047659313</v>
+        <v>-0.132452308955837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45269</v>
+        <v>45276</v>
       </c>
       <c r="B18" t="n">
-        <v>0.253549695740365</v>
+        <v>0.128913443830571</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0337941628264209</v>
+        <v>-0.0739130434782609</v>
       </c>
       <c r="D18" t="n">
-        <v>0.104089219330855</v>
+        <v>0.0696864111498259</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.132452308955837</v>
+        <v>-0.120050035739814</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45276</v>
+        <v>45283</v>
       </c>
       <c r="B19" t="n">
-        <v>0.128913443830571</v>
+        <v>0.0928961748633881</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0739130434782609</v>
+        <v>-0.075780089153046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0696864111498259</v>
+        <v>0.0848056537102473</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.120050035739814</v>
+        <v>-0.104223141674989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45283</v>
+        <v>45290</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0928961748633881</v>
+        <v>-0.0442477876106194</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.075780089153046</v>
+        <v>-0.0363036303630363</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0848056537102473</v>
+        <v>0.105072463768116</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.104223141674989</v>
+        <v>-0.103283749649172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45290</v>
+        <v>45297</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0442477876106194</v>
+        <v>0.0591497227356748</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0363036303630363</v>
+        <v>-0.148936170212766</v>
       </c>
       <c r="D21" t="n">
-        <v>0.105072463768116</v>
+        <v>0.10989010989011</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.103283749649172</v>
+        <v>-0.0940890125173852</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45297</v>
+        <v>45304</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0591497227356748</v>
+        <v>0.159509202453988</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.148936170212766</v>
+        <v>-0.0817843866171004</v>
       </c>
       <c r="D22" t="n">
-        <v>0.10989010989011</v>
+        <v>0.141791044776119</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0940890125173852</v>
+        <v>-0.0896678073905078</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45304</v>
+        <v>45311</v>
       </c>
       <c r="B23" t="n">
-        <v>0.159509202453988</v>
+        <v>0.203187250996016</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0817843866171004</v>
+        <v>-0.136612021857924</v>
       </c>
       <c r="D23" t="n">
-        <v>0.141791044776119</v>
+        <v>0.218390804597701</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0896678073905078</v>
+        <v>-0.0779107286905082</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45311</v>
+        <v>45318</v>
       </c>
       <c r="B24" t="n">
-        <v>0.203187250996016</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.136612021857924</v>
+        <v>-0.145794392523364</v>
       </c>
       <c r="D24" t="n">
-        <v>0.218390804597701</v>
+        <v>0.334661354581673</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0779107286905082</v>
+        <v>-0.0774895508525177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45318</v>
+        <v>45325</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0.0858505564387917</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.145794392523364</v>
+        <v>-0.0773930753564155</v>
       </c>
       <c r="D25" t="n">
-        <v>0.334661354581673</v>
+        <v>0.464435146443515</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0774895508525177</v>
+        <v>-0.0851426138782461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45325</v>
+        <v>45332</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0858505564387917</v>
+        <v>-0.145645645645646</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0773930753564155</v>
+        <v>-0.173598553345389</v>
       </c>
       <c r="D26" t="n">
-        <v>0.464435146443515</v>
+        <v>0.558951965065502</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0851426138782461</v>
+        <v>-0.0977869274318065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45332</v>
+        <v>45339</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.145645645645646</v>
+        <v>-0.217134416543575</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.173598553345389</v>
+        <v>-0.207936507936508</v>
       </c>
       <c r="D27" t="n">
-        <v>0.558951965065502</v>
+        <v>0.570815450643777</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0977869274318065</v>
+        <v>-0.101993081864602</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45339</v>
+        <v>45346</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.217134416543575</v>
+        <v>-0.212703101920236</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.207936507936508</v>
+        <v>-0.247813411078717</v>
       </c>
       <c r="D28" t="n">
-        <v>0.570815450643777</v>
+        <v>0.508196721311475</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.101993081864602</v>
+        <v>-0.0815340429126542</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45346</v>
+        <v>45353</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.212703101920236</v>
+        <v>-0.269767441860465</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.247813411078717</v>
+        <v>-0.1996996996997</v>
       </c>
       <c r="D29" t="n">
-        <v>0.508196721311475</v>
+        <v>0.448979591836735</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0815340429126542</v>
+        <v>-0.0735962520103489</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45353</v>
+        <v>45360</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.269767441860465</v>
+        <v>-0.276083467094703</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1996996996997</v>
+        <v>-0.17921686746988</v>
       </c>
       <c r="D30" t="n">
-        <v>0.448979591836735</v>
+        <v>0.430894308943089</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0735962520103489</v>
+        <v>-0.0595428156748912</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45360</v>
+        <v>45367</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.276083467094703</v>
+        <v>-0.325545171339564</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.17921686746988</v>
+        <v>-0.097053726169844</v>
       </c>
       <c r="D31" t="n">
-        <v>0.430894308943089</v>
+        <v>0.478813559322034</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0595428156748912</v>
+        <v>-0.0646537334470864</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45367</v>
+        <v>45374</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.325545171339564</v>
+        <v>-0.292845257903494</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.097053726169844</v>
+        <v>-0.145299145299145</v>
       </c>
       <c r="D32" t="n">
-        <v>0.478813559322034</v>
+        <v>0.491304347826087</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0646537334470864</v>
+        <v>-0.0767676767676768</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45374</v>
+        <v>45381</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.292845257903494</v>
+        <v>-0.246688741721854</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.145299145299145</v>
+        <v>-0.149825783972125</v>
       </c>
       <c r="D33" t="n">
-        <v>0.491304347826087</v>
+        <v>0.469827586206897</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0767676767676768</v>
+        <v>-0.0682249644043664</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45381</v>
+        <v>45388</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.246688741721854</v>
+        <v>-0.209813874788494</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.149825783972125</v>
+        <v>-0.139784946236559</v>
       </c>
       <c r="D34" t="n">
-        <v>0.469827586206897</v>
+        <v>0.44017094017094</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0682249644043664</v>
+        <v>-0.0620666749699008</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45388</v>
+        <v>45395</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.209813874788494</v>
+        <v>-0.190972222222222</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.139784946236559</v>
+        <v>-0.0907407407407408</v>
       </c>
       <c r="D35" t="n">
-        <v>0.44017094017094</v>
+        <v>0.376569037656904</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0620666749699008</v>
+        <v>-0.0505816233172134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45395</v>
+        <v>45402</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.190972222222222</v>
+        <v>-0.191596638655462</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0907407407407408</v>
+        <v>0.013671875</v>
       </c>
       <c r="D36" t="n">
-        <v>0.376569037656904</v>
+        <v>0.292</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0505816233172134</v>
+        <v>-0.0369740170154058</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45402</v>
+        <v>45409</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.191596638655462</v>
+        <v>-0.298555377207063</v>
       </c>
       <c r="C37" t="n">
-        <v>0.013671875</v>
+        <v>-0.019193857965451</v>
       </c>
       <c r="D37" t="n">
-        <v>0.292</v>
+        <v>0.218867924528302</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0369740170154058</v>
+        <v>-0.040047619047619</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45409</v>
+        <v>45416</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.298555377207063</v>
+        <v>-0.244827586206897</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.019193857965451</v>
+        <v>0.0798319327731092</v>
       </c>
       <c r="D38" t="n">
-        <v>0.218867924528302</v>
+        <v>0.172161172161172</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.040047619047619</v>
+        <v>-0.0232465528398627</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45416</v>
+        <v>45423</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.244827586206897</v>
+        <v>-0.206429780033841</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0798319327731092</v>
+        <v>0.0222672064777327</v>
       </c>
       <c r="D39" t="n">
-        <v>0.172161172161172</v>
+        <v>0.0954063604240283</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0232465528398627</v>
+        <v>-0.00595642405559327</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45423</v>
+        <v>45430</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.206429780033841</v>
+        <v>-0.287758346581876</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0222672064777327</v>
+        <v>0.0124740124740124</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0954063604240283</v>
+        <v>0.0602836879432624</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.00595642405559327</v>
+        <v>0.00615251767499592</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45430</v>
+        <v>45437</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.287758346581876</v>
+        <v>-0.234811165845649</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0124740124740124</v>
+        <v>0.0668103448275863</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0602836879432624</v>
+        <v>0.0394265232974911</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00615251767499592</v>
+        <v>0.0251808647860468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45437</v>
+        <v>45444</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.234811165845649</v>
+        <v>-0.282051282051282</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0668103448275863</v>
+        <v>0.08207343412527</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0394265232974911</v>
+        <v>0.01067615658363</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0251808647860468</v>
+        <v>0.0246913580246915</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45444</v>
+        <v>45451</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.282051282051282</v>
+        <v>-0.371794871794872</v>
       </c>
       <c r="C43" t="n">
-        <v>0.08207343412527</v>
+        <v>0.139484978540773</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01067615658363</v>
+        <v>0.0140845070422535</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0246913580246915</v>
+        <v>0.00573571586146038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45451</v>
+        <v>45458</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.371794871794872</v>
+        <v>-0.338805970149254</v>
       </c>
       <c r="C44" t="n">
-        <v>0.139484978540773</v>
+        <v>0.177489177489178</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0140845070422535</v>
+        <v>0.0428571428571429</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00573571586146038</v>
+        <v>-0.0123483653375401</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45458</v>
+        <v>45465</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.338805970149254</v>
+        <v>-0.356374807987711</v>
       </c>
       <c r="C45" t="n">
-        <v>0.177489177489178</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0428571428571429</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0123483653375401</v>
+        <v>-0.0331189197809793</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45465</v>
+        <v>45472</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.356374807987711</v>
+        <v>-0.40785498489426</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0588235294117647</v>
+        <v>-0.0256410256410257</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.113138686131387</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0331189197809793</v>
+        <v>-0.0435584114610765</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45472</v>
+        <v>45479</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.40785498489426</v>
+        <v>-0.371980676328502</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0256410256410257</v>
+        <v>-0.0325670498084292</v>
       </c>
       <c r="D47" t="n">
-        <v>0.113138686131387</v>
+        <v>0.12589928057554</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0435584114610765</v>
+        <v>-0.0391333997796779</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45479</v>
+        <v>45486</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.371980676328502</v>
+        <v>-0.336012861736334</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0325670498084292</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.12589928057554</v>
+        <v>0.0962199312714778</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0391333997796779</v>
+        <v>-0.0443383001920981</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45486</v>
+        <v>45493</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.336012861736334</v>
+        <v>-0.335394126738794</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.184381778741866</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0962199312714778</v>
+        <v>0.105960264900662</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0443383001920981</v>
+        <v>-0.0347154262168426</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45493</v>
+        <v>45500</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.335394126738794</v>
+        <v>-0.258943781942078</v>
       </c>
       <c r="C50" t="n">
-        <v>0.184381778741866</v>
+        <v>0.247727272727273</v>
       </c>
       <c r="D50" t="n">
-        <v>0.105960264900662</v>
+        <v>0.122257053291536</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0347154262168426</v>
+        <v>-0.0383329957464047</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45500</v>
+        <v>45507</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.258943781942078</v>
+        <v>-0.163339382940109</v>
       </c>
       <c r="C51" t="n">
-        <v>0.247727272727273</v>
+        <v>0.16331096196868</v>
       </c>
       <c r="D51" t="n">
-        <v>0.122257053291536</v>
+        <v>0.13677811550152</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0383329957464047</v>
+        <v>-0.0511188563923827</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45507</v>
+        <v>45514</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.163339382940109</v>
+        <v>-0.0371819960861057</v>
       </c>
       <c r="C52" t="n">
-        <v>0.16331096196868</v>
+        <v>0.0455486542443064</v>
       </c>
       <c r="D52" t="n">
-        <v>0.13677811550152</v>
+        <v>0.16566265060241</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0511188563923827</v>
+        <v>-0.0510420882233913</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45514</v>
+        <v>45521</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.0371819960861057</v>
+        <v>0.0504672897196261</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0455486542443064</v>
+        <v>-0.129032258064516</v>
       </c>
       <c r="D53" t="n">
-        <v>0.16566265060241</v>
+        <v>0.143712574850299</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0510420882233913</v>
+        <v>-0.0531380969627981</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0504672897196261</v>
+        <v>0.043557168784029</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.129032258064516</v>
+        <v>-0.175298804780876</v>
       </c>
       <c r="D54" t="n">
-        <v>0.143712574850299</v>
+        <v>0.0925373134328358</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0531380969627981</v>
+        <v>-0.0605657060672242</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45528</v>
+        <v>45535</v>
       </c>
       <c r="B55" t="n">
-        <v>0.043557168784029</v>
+        <v>-0.00349650349650354</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.175298804780876</v>
+        <v>-0.17979797979798</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0925373134328358</v>
+        <v>0.0501474926253687</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0605657060672242</v>
+        <v>-0.0578085991678224</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.00349650349650354</v>
+        <v>-0.10327868852459</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.17979797979798</v>
+        <v>-0.120689655172414</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0501474926253687</v>
+        <v>0.00574712643678166</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0578085991678224</v>
+        <v>-0.0704233409610984</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.10327868852459</v>
+        <v>-0.185185185185185</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.120689655172414</v>
+        <v>-0.0934182590233545</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00574712643678166</v>
+        <v>0.0144092219020173</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0704233409610984</v>
+        <v>-0.0695692774600211</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.185185185185185</v>
+        <v>-0.142140468227425</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0934182590233545</v>
+        <v>-0.122661122661123</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0144092219020173</v>
+        <v>0.0705882352941176</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0695692774600211</v>
+        <v>-0.0565451285116557</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45556</v>
+        <v>45563</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.142140468227425</v>
+        <v>-0.139767054908486</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.122661122661123</v>
+        <v>-0.112244897959184</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0705882352941176</v>
+        <v>0.113095238095238</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0565451285116557</v>
+        <v>-0.0539782893952045</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45563</v>
+        <v>45570</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.139767054908486</v>
+        <v>-0.156589147286822</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.112244897959184</v>
+        <v>-0.145593869731801</v>
       </c>
       <c r="D60" t="n">
-        <v>0.113095238095238</v>
+        <v>0.154761904761905</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0539782893952045</v>
+        <v>-0.0488187078109933</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45570</v>
+        <v>45577</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.156589147286822</v>
+        <v>-0.174698795180723</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.145593869731801</v>
+        <v>-0.146153846153846</v>
       </c>
       <c r="D61" t="n">
-        <v>0.154761904761905</v>
+        <v>0.144092219020173</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0488187078109933</v>
+        <v>-0.0628585086042065</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45577</v>
+        <v>45584</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.174698795180723</v>
+        <v>-0.217194570135747</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.146153846153846</v>
+        <v>-0.0452674897119342</v>
       </c>
       <c r="D62" t="n">
-        <v>0.144092219020173</v>
+        <v>0.0988700564971752</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0628585086042065</v>
+        <v>-0.0714919808249985</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45584</v>
+        <v>45591</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.217194570135747</v>
+        <v>-0.224340175953079</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0452674897119342</v>
+        <v>-0.0224032586558045</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0988700564971752</v>
+        <v>0.0657142857142856</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0714919808249985</v>
+        <v>-0.0766657052206519</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45591</v>
+        <v>45598</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.224340175953079</v>
+        <v>-0.190553745928339</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0224032586558045</v>
+        <v>-0.12593984962406</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0657142857142856</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0766657052206519</v>
+        <v>-0.0731829573934837</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.190553745928339</v>
+        <v>-0.117543859649123</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.12593984962406</v>
+        <v>-0.147329650092081</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.070336391437309</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0731829573934837</v>
+        <v>-0.0725605554672178</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.117543859649123</v>
+        <v>-0.106830122591944</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.147329650092081</v>
+        <v>-0.155752212389381</v>
       </c>
       <c r="D66" t="n">
-        <v>0.070336391437309</v>
+        <v>0.133550488599349</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0725605554672178</v>
+        <v>-0.0571341121256951</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.106830122591944</v>
+        <v>-0.072992700729927</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.155752212389381</v>
+        <v>-0.194871794871795</v>
       </c>
       <c r="D67" t="n">
-        <v>0.133550488599349</v>
+        <v>0.192567567567568</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0571341121256951</v>
+        <v>-0.0692811717093852</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.072992700729927</v>
+        <v>-0.15609756097561</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.194871794871795</v>
+        <v>-0.140138408304498</v>
       </c>
       <c r="D68" t="n">
-        <v>0.192567567567568</v>
+        <v>0.228668941979522</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0692811717093852</v>
+        <v>-0.0580240223968211</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.15609756097561</v>
+        <v>-0.163430420711974</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.140138408304498</v>
+        <v>-0.201907790143084</v>
       </c>
       <c r="D69" t="n">
-        <v>0.228668941979522</v>
+        <v>0.225589225589226</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0580240223968211</v>
+        <v>-0.0476354404234262</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.163430420711974</v>
+        <v>-0.158238172920065</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.201907790143084</v>
+        <v>-0.214397496087637</v>
       </c>
       <c r="D70" t="n">
-        <v>0.225589225589226</v>
+        <v>0.195439739413681</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.0476354404234262</v>
+        <v>-0.0379757117907478</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.158238172920065</v>
+        <v>-0.141666666666667</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.214397496087637</v>
+        <v>-0.204180064308682</v>
       </c>
       <c r="D71" t="n">
-        <v>0.195439739413681</v>
+        <v>0.188925081433225</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.0379757117907478</v>
+        <v>-0.0119057099625707</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45647</v>
+        <v>45654</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.141666666666667</v>
+        <v>-0.0666666666666667</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.204180064308682</v>
+        <v>-0.188356164383562</v>
       </c>
       <c r="D72" t="n">
-        <v>0.188925081433225</v>
+        <v>0.186885245901639</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.0119057099625707</v>
+        <v>-0.014397496087637</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45654</v>
+        <v>45661</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.0666666666666667</v>
+        <v>-0.104712041884817</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.188356164383562</v>
+        <v>-0.0557692307692308</v>
       </c>
       <c r="D73" t="n">
-        <v>0.186885245901639</v>
+        <v>0.221122112211221</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.014397496087637</v>
+        <v>-0.00149689107238815</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45661</v>
+        <v>45668</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.104712041884817</v>
+        <v>-0.0670194003527337</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0557692307692308</v>
+        <v>-0.0101214574898786</v>
       </c>
       <c r="D74" t="n">
-        <v>0.221122112211221</v>
+        <v>0.241830065359477</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.00149689107238815</v>
+        <v>0.0183785836339472</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45668</v>
+        <v>45675</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.0670194003527337</v>
+        <v>-0.107615894039735</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0101214574898786</v>
+        <v>0.090717299578059</v>
       </c>
       <c r="D75" t="n">
-        <v>0.241830065359477</v>
+        <v>0.216981132075472</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0183785836339472</v>
+        <v>-0.00513960778595901</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.107615894039735</v>
+        <v>0.0329861111111112</v>
       </c>
       <c r="C76" t="n">
-        <v>0.090717299578059</v>
+        <v>0.225382932166302</v>
       </c>
       <c r="D76" t="n">
-        <v>0.216981132075472</v>
+        <v>0.170149253731343</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.00513960778595901</v>
+        <v>0.0208198489751887</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45682</v>
+        <v>45689</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0329861111111112</v>
+        <v>0.227826086956522</v>
       </c>
       <c r="C77" t="n">
-        <v>0.225382932166302</v>
+        <v>0.260485651214128</v>
       </c>
       <c r="D77" t="n">
-        <v>0.170149253731343</v>
+        <v>0.145714285714286</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0208198489751887</v>
+        <v>0.0257006836811398</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="B78" t="n">
-        <v>0.227826086956522</v>
+        <v>0.608084358523726</v>
       </c>
       <c r="C78" t="n">
-        <v>0.260485651214128</v>
+        <v>0.24507658643326</v>
       </c>
       <c r="D78" t="n">
-        <v>0.145714285714286</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0257006836811398</v>
+        <v>0.0301982316029663</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45696</v>
+        <v>45703</v>
       </c>
       <c r="B79" t="n">
-        <v>0.608084358523726</v>
+        <v>1.40566037735849</v>
       </c>
       <c r="C79" t="n">
-        <v>0.24507658643326</v>
+        <v>0.148296593186373</v>
       </c>
       <c r="D79" t="n">
-        <v>0.176470588235294</v>
+        <v>0.218579234972678</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0301982316029663</v>
+        <v>0.0870905022194504</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45703</v>
+        <v>45710</v>
       </c>
       <c r="B80" t="n">
-        <v>1.40566037735849</v>
+        <v>2.35459662288931</v>
       </c>
       <c r="C80" t="n">
-        <v>0.148296593186373</v>
+        <v>0.265503875968992</v>
       </c>
       <c r="D80" t="n">
-        <v>0.218579234972678</v>
+        <v>0.315217391304348</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0870905022194504</v>
+        <v>0.118129644617762</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B81" t="n">
-        <v>2.35459662288931</v>
+        <v>3.80254777070064</v>
       </c>
       <c r="C81" t="n">
-        <v>0.265503875968992</v>
+        <v>0.328330206378987</v>
       </c>
       <c r="D81" t="n">
-        <v>0.315217391304348</v>
+        <v>0.464788732394366</v>
       </c>
       <c r="E81" t="n">
-        <v>0.118129644617762</v>
+        <v>0.215307393289806</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45717</v>
+        <v>45724</v>
       </c>
       <c r="B82" t="n">
-        <v>3.80254777070064</v>
+        <v>5.11751662971175</v>
       </c>
       <c r="C82" t="n">
-        <v>0.328330206378987</v>
+        <v>0.497247706422018</v>
       </c>
       <c r="D82" t="n">
-        <v>0.464788732394366</v>
+        <v>0.579545454545455</v>
       </c>
       <c r="E82" t="n">
-        <v>0.215307393289806</v>
+        <v>0.300860372699564</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45724</v>
+        <v>45731</v>
       </c>
       <c r="B83" t="n">
-        <v>5.11751662971175</v>
+        <v>6.05080831408776</v>
       </c>
       <c r="C83" t="n">
-        <v>0.497247706422018</v>
+        <v>0.767754318618042</v>
       </c>
       <c r="D83" t="n">
-        <v>0.579545454545455</v>
+        <v>0.67621776504298</v>
       </c>
       <c r="E83" t="n">
-        <v>0.300860372699564</v>
+        <v>0.369804885786802</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45731</v>
+        <v>45738</v>
       </c>
       <c r="B84" t="n">
-        <v>6.05080831408776</v>
+        <v>6.48470588235294</v>
       </c>
       <c r="C84" t="n">
-        <v>0.767754318618042</v>
+        <v>0.808</v>
       </c>
       <c r="D84" t="n">
-        <v>0.67621776504298</v>
+        <v>0.720116618075802</v>
       </c>
       <c r="E84" t="n">
-        <v>0.369804885786802</v>
+        <v>0.405061723297965</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45738</v>
+        <v>45745</v>
       </c>
       <c r="B85" t="n">
-        <v>6.48470588235294</v>
+        <v>6.28791208791209</v>
       </c>
       <c r="C85" t="n">
-        <v>0.808</v>
+        <v>0.846311475409836</v>
       </c>
       <c r="D85" t="n">
-        <v>0.720116618075802</v>
+        <v>0.69208211143695</v>
       </c>
       <c r="E85" t="n">
-        <v>0.405061723297965</v>
+        <v>0.370813701770024</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="B86" t="n">
-        <v>6.28791208791209</v>
+        <v>6.19057815845824</v>
       </c>
       <c r="C86" t="n">
-        <v>0.846311475409836</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D86" t="n">
-        <v>0.69208211143695</v>
+        <v>0.664688427299703</v>
       </c>
       <c r="E86" t="n">
-        <v>0.370813701770024</v>
+        <v>0.335782577903683</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="B87" t="n">
-        <v>6.19057815845824</v>
+        <v>6.41630901287554</v>
       </c>
       <c r="C87" t="n">
-        <v>0.729166666666667</v>
+        <v>0.568228105906314</v>
       </c>
       <c r="D87" t="n">
-        <v>0.664688427299703</v>
+        <v>0.674772036474164</v>
       </c>
       <c r="E87" t="n">
-        <v>0.335782577903683</v>
+        <v>0.311123348017621</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45759</v>
+        <v>45766</v>
       </c>
       <c r="B88" t="n">
-        <v>6.41630901287554</v>
+        <v>6.54885654885655</v>
       </c>
       <c r="C88" t="n">
-        <v>0.568228105906314</v>
+        <v>0.441233140655106</v>
       </c>
       <c r="D88" t="n">
-        <v>0.674772036474164</v>
+        <v>0.727554179566563</v>
       </c>
       <c r="E88" t="n">
-        <v>0.311123348017621</v>
+        <v>0.316412778759372</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45766</v>
+        <v>45773</v>
       </c>
       <c r="B89" t="n">
-        <v>6.54885654885655</v>
+        <v>7.8466819221968</v>
       </c>
       <c r="C89" t="n">
-        <v>0.441233140655106</v>
+        <v>0.446183953033268</v>
       </c>
       <c r="D89" t="n">
-        <v>0.727554179566563</v>
+        <v>0.761609907120743</v>
       </c>
       <c r="E89" t="n">
-        <v>0.316412778759372</v>
+        <v>0.336623840468277</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45773</v>
+        <v>45780</v>
       </c>
       <c r="B90" t="n">
-        <v>7.8466819221968</v>
+        <v>8.28310502283105</v>
       </c>
       <c r="C90" t="n">
-        <v>0.446183953033268</v>
+        <v>0.482490272373541</v>
       </c>
       <c r="D90" t="n">
-        <v>0.761609907120743</v>
+        <v>0.803125</v>
       </c>
       <c r="E90" t="n">
-        <v>0.336623840468277</v>
+        <v>0.345377637345836</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="B91" t="n">
-        <v>8.28310502283105</v>
+        <v>8.08102345415778</v>
       </c>
       <c r="C91" t="n">
-        <v>0.482490272373541</v>
+        <v>0.550495049504951</v>
       </c>
       <c r="D91" t="n">
-        <v>0.803125</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E91" t="n">
-        <v>0.345377637345836</v>
+        <v>0.37377135348226</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45787</v>
+        <v>45794</v>
       </c>
       <c r="B92" t="n">
-        <v>8.08102345415778</v>
+        <v>8.72767857142857</v>
       </c>
       <c r="C92" t="n">
-        <v>0.550495049504951</v>
+        <v>0.765913757700205</v>
       </c>
       <c r="D92" t="n">
-        <v>0.919354838709677</v>
+        <v>0.989966555183946</v>
       </c>
       <c r="E92" t="n">
-        <v>0.37377135348226</v>
+        <v>0.401973931234243</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45794</v>
+        <v>45801</v>
       </c>
       <c r="B93" t="n">
-        <v>8.72767857142857</v>
+        <v>8.27467811158798</v>
       </c>
       <c r="C93" t="n">
-        <v>0.765913757700205</v>
+        <v>0.913131313131313</v>
       </c>
       <c r="D93" t="n">
-        <v>0.989966555183946</v>
+        <v>1.0551724137931</v>
       </c>
       <c r="E93" t="n">
-        <v>0.401973931234243</v>
+        <v>0.416301969365427</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45801</v>
+        <v>45808</v>
       </c>
       <c r="B94" t="n">
-        <v>8.27467811158798</v>
+        <v>8.10084033613445</v>
       </c>
       <c r="C94" t="n">
-        <v>0.913131313131313</v>
+        <v>1.1377245508982</v>
       </c>
       <c r="D94" t="n">
-        <v>1.0551724137931</v>
+        <v>1.12323943661972</v>
       </c>
       <c r="E94" t="n">
-        <v>0.416301969365427</v>
+        <v>0.457501237828024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B95" t="n">
-        <v>8.10084033613445</v>
+        <v>8.80045351473923</v>
       </c>
       <c r="C95" t="n">
-        <v>1.1377245508982</v>
+        <v>1.25988700564972</v>
       </c>
       <c r="D95" t="n">
-        <v>1.12323943661972</v>
+        <v>1.08680555555556</v>
       </c>
       <c r="E95" t="n">
-        <v>0.457501237828024</v>
+        <v>0.472581706514587</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45815</v>
+        <v>45822</v>
       </c>
       <c r="B96" t="n">
-        <v>8.80045351473923</v>
+        <v>8.76523702031603</v>
       </c>
       <c r="C96" t="n">
-        <v>1.25988700564972</v>
+        <v>1.29779411764706</v>
       </c>
       <c r="D96" t="n">
-        <v>1.08680555555556</v>
+        <v>1.08219178082192</v>
       </c>
       <c r="E96" t="n">
-        <v>0.472581706514587</v>
+        <v>0.500330469266358</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45822</v>
+        <v>45829</v>
       </c>
       <c r="B97" t="n">
-        <v>8.76523702031603</v>
+        <v>9.38663484486874</v>
       </c>
       <c r="C97" t="n">
-        <v>1.29779411764706</v>
+        <v>1.4462962962963</v>
       </c>
       <c r="D97" t="n">
-        <v>1.08219178082192</v>
+        <v>1.05333333333333</v>
       </c>
       <c r="E97" t="n">
-        <v>0.500330469266358</v>
+        <v>0.531999120299098</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45829</v>
+        <v>45836</v>
       </c>
       <c r="B98" t="n">
-        <v>9.38663484486874</v>
+        <v>10.1326530612245</v>
       </c>
       <c r="C98" t="n">
-        <v>1.4462962962963</v>
+        <v>1.56015037593985</v>
       </c>
       <c r="D98" t="n">
-        <v>1.05333333333333</v>
+        <v>1.02295081967213</v>
       </c>
       <c r="E98" t="n">
-        <v>0.531999120299098</v>
+        <v>0.532187895809241</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45836</v>
+        <v>45843</v>
       </c>
       <c r="B99" t="n">
-        <v>10.1326530612245</v>
+        <v>10.474358974359</v>
       </c>
       <c r="C99" t="n">
-        <v>1.56015037593985</v>
+        <v>1.68910891089109</v>
       </c>
       <c r="D99" t="n">
-        <v>1.02295081967213</v>
+        <v>0.993610223642172</v>
       </c>
       <c r="E99" t="n">
-        <v>0.532187895809241</v>
+        <v>0.545613364633946</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45843</v>
+        <v>45850</v>
       </c>
       <c r="B100" t="n">
-        <v>10.474358974359</v>
+        <v>10.1598062953995</v>
       </c>
       <c r="C100" t="n">
-        <v>1.68910891089109</v>
+        <v>1.78313253012048</v>
       </c>
       <c r="D100" t="n">
-        <v>0.993610223642172</v>
+        <v>0.981191222570533</v>
       </c>
       <c r="E100" t="n">
-        <v>0.545613364633946</v>
+        <v>0.554571630358016</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45850</v>
+        <v>45857</v>
       </c>
       <c r="B101" t="n">
-        <v>10.1598062953995</v>
+        <v>10.5139534883721</v>
       </c>
       <c r="C101" t="n">
-        <v>1.78313253012048</v>
+        <v>1.70695970695971</v>
       </c>
       <c r="D101" t="n">
-        <v>0.981191222570533</v>
+        <v>0.934131736526946</v>
       </c>
       <c r="E101" t="n">
-        <v>0.554571630358016</v>
+        <v>0.574035537057788</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45857</v>
+        <v>45864</v>
       </c>
       <c r="B102" t="n">
-        <v>10.5139534883721</v>
+        <v>11.2735632183908</v>
       </c>
       <c r="C102" t="n">
-        <v>1.70695970695971</v>
+        <v>2.04918032786885</v>
       </c>
       <c r="D102" t="n">
-        <v>0.934131736526946</v>
+        <v>0.88268156424581</v>
       </c>
       <c r="E102" t="n">
-        <v>0.574035537057788</v>
+        <v>0.614290979937865</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="B103" t="n">
-        <v>11.2735632183908</v>
+        <v>11.4056399132321</v>
       </c>
       <c r="C103" t="n">
-        <v>2.04918032786885</v>
+        <v>2.67884615384615</v>
       </c>
       <c r="D103" t="n">
-        <v>0.88268156424581</v>
+        <v>0.86096256684492</v>
       </c>
       <c r="E103" t="n">
-        <v>0.614290979937865</v>
+        <v>0.685813148788927</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45871</v>
+        <v>45878</v>
       </c>
       <c r="B104" t="n">
-        <v>11.4056399132321</v>
+        <v>11.3678861788618</v>
       </c>
       <c r="C104" t="n">
-        <v>2.67884615384615</v>
+        <v>3.29306930693069</v>
       </c>
       <c r="D104" t="n">
-        <v>0.86096256684492</v>
+        <v>0.850129198966408</v>
       </c>
       <c r="E104" t="n">
-        <v>0.685813148788927</v>
+        <v>0.744069513300283</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="B105" t="n">
-        <v>11.3678861788618</v>
+        <v>10.1708185053381</v>
       </c>
       <c r="C105" t="n">
-        <v>3.29306930693069</v>
+        <v>4.50462962962963</v>
       </c>
       <c r="D105" t="n">
-        <v>0.850129198966408</v>
+        <v>0.921465968586388</v>
       </c>
       <c r="E105" t="n">
-        <v>0.744069513300283</v>
+        <v>0.804043715846995</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="B106" t="n">
-        <v>10.1708185053381</v>
+        <v>10.0591304347826</v>
       </c>
       <c r="C106" t="n">
-        <v>4.50462962962963</v>
+        <v>4.91304347826087</v>
       </c>
       <c r="D106" t="n">
-        <v>0.921465968586388</v>
+        <v>1.02732240437158</v>
       </c>
       <c r="E106" t="n">
-        <v>0.804043715846995</v>
+        <v>0.87298707189839</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45892</v>
+        <v>45899</v>
       </c>
       <c r="B107" t="n">
-        <v>10.0591304347826</v>
+        <v>10.1368421052632</v>
       </c>
       <c r="C107" t="n">
-        <v>4.91304347826087</v>
+        <v>5.20689655172414</v>
       </c>
       <c r="D107" t="n">
-        <v>1.02732240437158</v>
+        <v>1.09831460674157</v>
       </c>
       <c r="E107" t="n">
-        <v>0.87298707189839</v>
+        <v>0.922981805334746</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45899</v>
+        <v>45906</v>
       </c>
       <c r="B108" t="n">
-        <v>10.1368421052632</v>
+        <v>10.4680073126143</v>
       </c>
       <c r="C108" t="n">
-        <v>5.20689655172414</v>
+        <v>5.42647058823529</v>
       </c>
       <c r="D108" t="n">
-        <v>1.09831460674157</v>
+        <v>1.16857142857143</v>
       </c>
       <c r="E108" t="n">
-        <v>0.922981805334746</v>
+        <v>0.992122592159518</v>
       </c>
     </row>
   </sheetData>

--- a/output/wp_figures.xlsx
+++ b/output/wp_figures.xlsx
@@ -406,629 +406,1212 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45528</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>192.739</v>
+        <v>174.701</v>
       </c>
       <c r="C2" t="n">
-        <v>193.441</v>
+        <v>167.378</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45535</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>190.623</v>
+        <v>199.743</v>
       </c>
       <c r="C3" t="n">
-        <v>191.353</v>
+        <v>198.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45542</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>178.682</v>
+        <v>182.394</v>
       </c>
       <c r="C4" t="n">
-        <v>175.594</v>
+        <v>178.773</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45549</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>186.832</v>
+        <v>193.999</v>
       </c>
       <c r="C5" t="n">
-        <v>176.586</v>
+        <v>184.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45556</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>181.701</v>
+        <v>199.306</v>
       </c>
       <c r="C6" t="n">
-        <v>175.65</v>
+        <v>185.973</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45563</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>181.204</v>
+        <v>214.161</v>
       </c>
       <c r="C7" t="n">
-        <v>174.701</v>
+        <v>206.079</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45570</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>236.171</v>
+        <v>217.438</v>
       </c>
       <c r="C8" t="n">
-        <v>199.743</v>
+        <v>200.237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45577</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>225.23</v>
+        <v>240.99</v>
       </c>
       <c r="C9" t="n">
-        <v>182.394</v>
+        <v>249.258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45584</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>203.475</v>
+        <v>199.75</v>
       </c>
       <c r="C10" t="n">
-        <v>193.999</v>
+        <v>199.323</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45591</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>201.443</v>
+        <v>294.615</v>
       </c>
       <c r="C11" t="n">
-        <v>199.306</v>
+        <v>287.976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45598</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>212.741</v>
+        <v>249.09</v>
       </c>
       <c r="C12" t="n">
-        <v>214.161</v>
+        <v>250.038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45605</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>230.801</v>
+        <v>241.04</v>
       </c>
       <c r="C13" t="n">
-        <v>217.438</v>
+        <v>248.444</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45612</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>214.254</v>
+        <v>274.84</v>
       </c>
       <c r="C14" t="n">
-        <v>240.99</v>
+        <v>269.877</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45619</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>245.27</v>
+        <v>269.416</v>
       </c>
       <c r="C15" t="n">
-        <v>199.75</v>
+        <v>278.487</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45626</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>211.323</v>
+        <v>318.906</v>
       </c>
       <c r="C16" t="n">
-        <v>294.615</v>
+        <v>342.411</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45633</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>309.775</v>
+        <v>291.33</v>
       </c>
       <c r="C17" t="n">
-        <v>249.09</v>
+        <v>292.116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45640</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>252.349</v>
+        <v>249.947</v>
       </c>
       <c r="C18" t="n">
-        <v>241.04</v>
+        <v>228.356</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45647</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>275.638</v>
+        <v>263.919</v>
       </c>
       <c r="C19" t="n">
-        <v>274.84</v>
+        <v>227.941</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45654</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>283.652</v>
+        <v>234.729</v>
       </c>
       <c r="C20" t="n">
-        <v>269.416</v>
+        <v>237.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45661</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>306.295</v>
+        <v>223.985</v>
       </c>
       <c r="C21" t="n">
-        <v>318.906</v>
+        <v>227.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45668</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>352.63</v>
+        <v>199.337</v>
       </c>
       <c r="C22" t="n">
-        <v>291.33</v>
+        <v>211.588</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45675</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>284.6</v>
+        <v>195.604</v>
       </c>
       <c r="C23" t="n">
-        <v>249.947</v>
+        <v>193.414</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45682</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>228.484</v>
+        <v>214.425</v>
       </c>
       <c r="C24" t="n">
-        <v>263.919</v>
+        <v>230.148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45689</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>241.111</v>
+        <v>202.723</v>
       </c>
       <c r="C25" t="n">
-        <v>234.729</v>
+        <v>210.665</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45696</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>232.685</v>
+        <v>191.773</v>
       </c>
       <c r="C26" t="n">
-        <v>223.985</v>
+        <v>204.021</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>223.539</v>
+        <v>193.923</v>
       </c>
       <c r="C27" t="n">
-        <v>199.337</v>
+        <v>214.153</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45710</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>220.856</v>
+        <v>197.349</v>
       </c>
       <c r="C28" t="n">
-        <v>195.604</v>
+        <v>195.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45717</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>226.019</v>
+        <v>215.265</v>
       </c>
       <c r="C29" t="n">
-        <v>214.425</v>
+        <v>223.382</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45724</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>214.007</v>
+        <v>209.064</v>
       </c>
       <c r="C30" t="n">
-        <v>202.723</v>
+        <v>216.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45731</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>207.398</v>
+        <v>202.619</v>
       </c>
       <c r="C31" t="n">
-        <v>191.773</v>
+        <v>203.233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45738</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>199.9</v>
+        <v>189.634</v>
       </c>
       <c r="C32" t="n">
-        <v>193.923</v>
+        <v>192.152</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45745</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>200.081</v>
+        <v>210.05</v>
       </c>
       <c r="C33" t="n">
-        <v>197.349</v>
+        <v>203.898</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45752</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>216.534</v>
+        <v>197.68</v>
       </c>
       <c r="C34" t="n">
-        <v>215.265</v>
+        <v>199.654</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45759</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>220.962</v>
+        <v>192.717</v>
       </c>
       <c r="C35" t="n">
-        <v>209.064</v>
+        <v>201.921</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45766</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>210.816</v>
+        <v>197.164</v>
       </c>
       <c r="C36" t="n">
-        <v>202.619</v>
+        <v>208.053</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45773</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>224.021</v>
+        <v>196.177</v>
       </c>
       <c r="C37" t="n">
-        <v>189.634</v>
+        <v>219.975</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45780</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>206.71</v>
+        <v>236.046</v>
       </c>
       <c r="C38" t="n">
-        <v>210.05</v>
+        <v>250.795</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45787</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>203.579</v>
+        <v>227.98</v>
       </c>
       <c r="C39" t="n">
-        <v>197.68</v>
+        <v>249.813</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45794</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>200.637</v>
+        <v>225.13</v>
       </c>
       <c r="C40" t="n">
-        <v>192.717</v>
+        <v>229.726</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45801</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>210.16</v>
+        <v>239.403</v>
       </c>
       <c r="C41" t="n">
-        <v>197.164</v>
+        <v>251.705</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45808</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>207.512</v>
+        <v>242.201</v>
       </c>
       <c r="C42" t="n">
-        <v>196.177</v>
+        <v>258.065</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45815</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>243.98</v>
+        <v>280.569</v>
       </c>
       <c r="C43" t="n">
-        <v>236.046</v>
+        <v>258.328</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45822</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>234.859</v>
+        <v>225.855</v>
       </c>
       <c r="C44" t="n">
-        <v>227.98</v>
+        <v>213.497</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45829</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>227.516</v>
+        <v>216.673</v>
       </c>
       <c r="C45" t="n">
-        <v>225.13</v>
+        <v>205.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45836</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>230.392</v>
+        <v>204.066</v>
       </c>
       <c r="C46" t="n">
-        <v>239.403</v>
+        <v>227.917</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45843</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>241.361</v>
+        <v>200.837</v>
       </c>
       <c r="C47" t="n">
-        <v>242.201</v>
+        <v>213.803</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45850</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>261.111</v>
+        <v>192.455</v>
       </c>
       <c r="C48" t="n">
-        <v>280.569</v>
+        <v>199.517</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45857</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>216.023</v>
+        <v>192.739</v>
       </c>
       <c r="C49" t="n">
-        <v>225.855</v>
+        <v>193.441</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45864</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>193.79</v>
+        <v>190.623</v>
       </c>
       <c r="C50" t="n">
-        <v>216.673</v>
+        <v>191.353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45871</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>195.492</v>
+        <v>178.682</v>
       </c>
       <c r="C51" t="n">
-        <v>204.066</v>
+        <v>175.594</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45878</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>199.39</v>
+        <v>186.832</v>
       </c>
       <c r="C52" t="n">
-        <v>200.837</v>
+        <v>176.586</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45885</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>194.217</v>
+        <v>181.701</v>
       </c>
       <c r="C53" t="n">
-        <v>192.455</v>
+        <v>175.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45892</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>191.208</v>
+        <v>181.204</v>
       </c>
       <c r="C54" t="n">
-        <v>192.739</v>
+        <v>174.701</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45899</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>196.712</v>
+        <v>236.171</v>
       </c>
       <c r="C55" t="n">
-        <v>190.623</v>
+        <v>199.743</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45906</v>
+        <v>45577</v>
       </c>
       <c r="B56" t="n">
-        <v>204.862</v>
+        <v>225.23</v>
       </c>
       <c r="C56" t="n">
-        <v>178.682</v>
+        <v>182.394</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45913</v>
+        <v>45584</v>
       </c>
       <c r="B57" t="n">
-        <v>195.433</v>
+        <v>203.475</v>
       </c>
       <c r="C57" t="n">
-        <v>186.832</v>
+        <v>193.999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B58" t="n">
+        <v>201.443</v>
+      </c>
+      <c r="C58" t="n">
+        <v>199.306</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B59" t="n">
+        <v>212.741</v>
+      </c>
+      <c r="C59" t="n">
+        <v>214.161</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B60" t="n">
+        <v>230.801</v>
+      </c>
+      <c r="C60" t="n">
+        <v>217.438</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B61" t="n">
+        <v>214.254</v>
+      </c>
+      <c r="C61" t="n">
+        <v>240.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B62" t="n">
+        <v>245.27</v>
+      </c>
+      <c r="C62" t="n">
+        <v>199.75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B63" t="n">
+        <v>211.323</v>
+      </c>
+      <c r="C63" t="n">
+        <v>294.615</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>309.775</v>
+      </c>
+      <c r="C64" t="n">
+        <v>249.09</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B65" t="n">
+        <v>252.349</v>
+      </c>
+      <c r="C65" t="n">
+        <v>241.04</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B66" t="n">
+        <v>275.638</v>
+      </c>
+      <c r="C66" t="n">
+        <v>274.84</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B67" t="n">
+        <v>283.652</v>
+      </c>
+      <c r="C67" t="n">
+        <v>269.416</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B68" t="n">
+        <v>306.295</v>
+      </c>
+      <c r="C68" t="n">
+        <v>318.906</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B69" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="C69" t="n">
+        <v>291.33</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="C70" t="n">
+        <v>249.947</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B71" t="n">
+        <v>228.484</v>
+      </c>
+      <c r="C71" t="n">
+        <v>263.919</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>241.111</v>
+      </c>
+      <c r="C72" t="n">
+        <v>234.729</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B73" t="n">
+        <v>232.685</v>
+      </c>
+      <c r="C73" t="n">
+        <v>223.985</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B74" t="n">
+        <v>223.539</v>
+      </c>
+      <c r="C74" t="n">
+        <v>199.337</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B75" t="n">
+        <v>220.856</v>
+      </c>
+      <c r="C75" t="n">
+        <v>195.604</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B76" t="n">
+        <v>226.019</v>
+      </c>
+      <c r="C76" t="n">
+        <v>214.425</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>214.007</v>
+      </c>
+      <c r="C77" t="n">
+        <v>202.723</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B78" t="n">
+        <v>207.398</v>
+      </c>
+      <c r="C78" t="n">
+        <v>191.773</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B79" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="C79" t="n">
+        <v>193.923</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B80" t="n">
+        <v>200.081</v>
+      </c>
+      <c r="C80" t="n">
+        <v>197.349</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B81" t="n">
+        <v>216.534</v>
+      </c>
+      <c r="C81" t="n">
+        <v>215.265</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B82" t="n">
+        <v>220.962</v>
+      </c>
+      <c r="C82" t="n">
+        <v>209.064</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B83" t="n">
+        <v>210.816</v>
+      </c>
+      <c r="C83" t="n">
+        <v>202.619</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B84" t="n">
+        <v>224.021</v>
+      </c>
+      <c r="C84" t="n">
+        <v>189.634</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B85" t="n">
+        <v>206.71</v>
+      </c>
+      <c r="C85" t="n">
+        <v>210.05</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B86" t="n">
+        <v>203.579</v>
+      </c>
+      <c r="C86" t="n">
+        <v>197.68</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B87" t="n">
+        <v>200.637</v>
+      </c>
+      <c r="C87" t="n">
+        <v>192.717</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B88" t="n">
+        <v>210.16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>197.164</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B89" t="n">
+        <v>207.512</v>
+      </c>
+      <c r="C89" t="n">
+        <v>196.177</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B90" t="n">
+        <v>243.98</v>
+      </c>
+      <c r="C90" t="n">
+        <v>236.046</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B91" t="n">
+        <v>234.859</v>
+      </c>
+      <c r="C91" t="n">
+        <v>227.98</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B92" t="n">
+        <v>227.516</v>
+      </c>
+      <c r="C92" t="n">
+        <v>225.13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B93" t="n">
+        <v>230.392</v>
+      </c>
+      <c r="C93" t="n">
+        <v>239.403</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B94" t="n">
+        <v>241.361</v>
+      </c>
+      <c r="C94" t="n">
+        <v>242.201</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B95" t="n">
+        <v>261.111</v>
+      </c>
+      <c r="C95" t="n">
+        <v>280.569</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45857</v>
+      </c>
+      <c r="B96" t="n">
+        <v>216.023</v>
+      </c>
+      <c r="C96" t="n">
+        <v>225.855</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B97" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="C97" t="n">
+        <v>216.673</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B98" t="n">
+        <v>195.492</v>
+      </c>
+      <c r="C98" t="n">
+        <v>204.066</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B99" t="n">
+        <v>199.39</v>
+      </c>
+      <c r="C99" t="n">
+        <v>200.837</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B100" t="n">
+        <v>194.217</v>
+      </c>
+      <c r="C100" t="n">
+        <v>192.455</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B101" t="n">
+        <v>191.208</v>
+      </c>
+      <c r="C101" t="n">
+        <v>192.739</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B102" t="n">
+        <v>196.712</v>
+      </c>
+      <c r="C102" t="n">
+        <v>190.623</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B103" t="n">
+        <v>204.862</v>
+      </c>
+      <c r="C103" t="n">
+        <v>178.682</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B104" t="n">
+        <v>195.433</v>
+      </c>
+      <c r="C104" t="n">
+        <v>186.832</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
         <v>45920</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B105" t="n">
+        <v>180.992</v>
+      </c>
+      <c r="C105" t="n">
+        <v>181.701</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="B106" t="n">
+        <v>179.121</v>
+      </c>
+      <c r="C106" t="n">
+        <v>181.204</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="B107" t="n">
+        <v>207.062</v>
+      </c>
+      <c r="C107" t="n">
+        <v>236.171</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B108" t="n">
+        <v>210.729</v>
+      </c>
+      <c r="C108" t="n">
+        <v>225.23</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="B109" t="n">
+        <v>205.626</v>
+      </c>
+      <c r="C109" t="n">
+        <v>203.475</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B110" t="n">
+        <v>193.829</v>
+      </c>
+      <c r="C110" t="n">
+        <v>201.443</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B111" t="n">
         <v>180.611</v>
       </c>
-      <c r="C58" t="n">
-        <v>181.701</v>
+      <c r="C111" t="n">
+        <v>212.741</v>
       </c>
     </row>
   </sheetData>
@@ -1055,618 +1638,1201 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45528</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>1800.515</v>
+        <v>1555.172</v>
       </c>
       <c r="C2" t="n">
-        <v>1747.737</v>
+        <v>1201.432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45535</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>1704.638</v>
+        <v>1542.397</v>
       </c>
       <c r="C3" t="n">
-        <v>1655.84</v>
+        <v>1199.269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45542</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>1671.837</v>
+        <v>1572.658</v>
       </c>
       <c r="C4" t="n">
-        <v>1645.927</v>
+        <v>1226.861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45549</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>1628.081</v>
+        <v>1574.471</v>
       </c>
       <c r="C5" t="n">
-        <v>1588.285</v>
+        <v>1239.975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45556</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>1613.719</v>
+        <v>1607.693</v>
       </c>
       <c r="C6" t="n">
-        <v>1585.277</v>
+        <v>1267.368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45563</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>1614.385</v>
+        <v>1578.946</v>
       </c>
       <c r="C7" t="n">
-        <v>1555.172</v>
+        <v>1230.153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45570</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>1598.241</v>
+        <v>1654.732</v>
       </c>
       <c r="C8" t="n">
-        <v>1542.397</v>
+        <v>1342.834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45577</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>1627.825</v>
+        <v>1555.596</v>
       </c>
       <c r="C9" t="n">
-        <v>1572.658</v>
+        <v>1261.674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45584</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>1616.144</v>
+        <v>1845.084</v>
       </c>
       <c r="C10" t="n">
-        <v>1574.471</v>
+        <v>1561.449</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45591</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>1646.982</v>
+        <v>1767.267</v>
       </c>
       <c r="C11" t="n">
-        <v>1607.693</v>
+        <v>1503.416</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45598</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>1647.301</v>
+        <v>1835.427</v>
       </c>
       <c r="C12" t="n">
-        <v>1578.946</v>
+        <v>1594.527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45605</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>1660.894</v>
+        <v>1836.539</v>
       </c>
       <c r="C13" t="n">
-        <v>1654.732</v>
+        <v>1577.004</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45612</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>1721.154</v>
+        <v>1902.054</v>
       </c>
       <c r="C14" t="n">
-        <v>1555.596</v>
+        <v>1710.626</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45619</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>1661.071</v>
+        <v>2104.257</v>
       </c>
       <c r="C15" t="n">
-        <v>1845.084</v>
+        <v>1870.058</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45626</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>1933.23</v>
+        <v>2122.561</v>
       </c>
       <c r="C16" t="n">
-        <v>1767.267</v>
+        <v>1908.639</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45633</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>1864.863</v>
+        <v>2053.289</v>
       </c>
       <c r="C17" t="n">
-        <v>1835.427</v>
+        <v>1863.962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45640</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>1946.787</v>
+        <v>2181.43</v>
       </c>
       <c r="C18" t="n">
-        <v>1836.539</v>
+        <v>1911.213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45647</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>1860.888</v>
+        <v>2130.018</v>
       </c>
       <c r="C19" t="n">
-        <v>1902.054</v>
+        <v>1925.707</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45654</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>2187.475</v>
+        <v>2139.97</v>
       </c>
       <c r="C20" t="n">
-        <v>2104.257</v>
+        <v>1948.437</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45661</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>2273.651</v>
+        <v>2092.787</v>
       </c>
       <c r="C21" t="n">
-        <v>2122.561</v>
+        <v>1928.688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45668</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>2246.551</v>
+        <v>2092.108</v>
       </c>
       <c r="C22" t="n">
-        <v>2053.289</v>
+        <v>1891.796</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45675</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>2170.633</v>
+        <v>2113.581</v>
       </c>
       <c r="C23" t="n">
-        <v>2181.43</v>
+        <v>1970.054</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45682</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>2250.894</v>
+        <v>2078.603</v>
       </c>
       <c r="C24" t="n">
-        <v>2130.018</v>
+        <v>1910.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45689</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>2185.828</v>
+        <v>2008.79</v>
       </c>
       <c r="C25" t="n">
-        <v>2139.97</v>
+        <v>1878.293</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45696</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>2191.042</v>
+        <v>2012.613</v>
       </c>
       <c r="C26" t="n">
-        <v>2092.787</v>
+        <v>1877.339</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>2160.103</v>
+        <v>1937.982</v>
       </c>
       <c r="C27" t="n">
-        <v>2092.108</v>
+        <v>1841.752</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45710</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>2229.07</v>
+        <v>1928.017</v>
       </c>
       <c r="C28" t="n">
-        <v>2113.581</v>
+        <v>1792.755</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45717</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>2149.919</v>
+        <v>1848.827</v>
       </c>
       <c r="C29" t="n">
-        <v>2078.603</v>
+        <v>1785.781</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45724</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>2116.538</v>
+        <v>1812.811</v>
       </c>
       <c r="C30" t="n">
-        <v>2008.79</v>
+        <v>1749.975</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45731</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>2072.402</v>
+        <v>1753.465</v>
       </c>
       <c r="C31" t="n">
-        <v>2012.613</v>
+        <v>1687.739</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45738</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>2058.751</v>
+        <v>1743.445</v>
       </c>
       <c r="C32" t="n">
-        <v>1937.982</v>
+        <v>1658.533</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45745</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>1985.73</v>
+        <v>1686.177</v>
       </c>
       <c r="C33" t="n">
-        <v>1928.017</v>
+        <v>1610.523</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45752</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>1943.418</v>
+        <v>1686.782</v>
       </c>
       <c r="C34" t="n">
-        <v>1848.827</v>
+        <v>1610.901</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45759</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>1880.372</v>
+        <v>1666.648</v>
       </c>
       <c r="C35" t="n">
-        <v>1812.811</v>
+        <v>1608.222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45766</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>1898.153</v>
+        <v>1670.55</v>
       </c>
       <c r="C36" t="n">
-        <v>1753.465</v>
+        <v>1593.705</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45773</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>1838.279</v>
+        <v>1708.158</v>
       </c>
       <c r="C37" t="n">
-        <v>1743.445</v>
+        <v>1647.848</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45780</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>1782.724</v>
+        <v>1727.754</v>
       </c>
       <c r="C38" t="n">
-        <v>1686.177</v>
+        <v>1670.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45787</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>1779.686</v>
+        <v>1748.567</v>
       </c>
       <c r="C39" t="n">
-        <v>1686.782</v>
+        <v>1674.548</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45794</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>1775.51</v>
+        <v>1821.4</v>
       </c>
       <c r="C40" t="n">
-        <v>1666.648</v>
+        <v>1737.351</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45801</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>1755.336</v>
+        <v>1795.365</v>
       </c>
       <c r="C41" t="n">
-        <v>1670.55</v>
+        <v>1724.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45808</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>1826.063</v>
+        <v>1945.731</v>
       </c>
       <c r="C42" t="n">
-        <v>1708.158</v>
+        <v>1887.928</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45815</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>1813.454</v>
+        <v>1914.075</v>
       </c>
       <c r="C43" t="n">
-        <v>1727.754</v>
+        <v>1835.614</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45822</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>1862.043</v>
+        <v>1934.382</v>
       </c>
       <c r="C44" t="n">
-        <v>1748.567</v>
+        <v>1827.375</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45829</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>1900.787</v>
+        <v>1907.041</v>
       </c>
       <c r="C45" t="n">
-        <v>1821.4</v>
+        <v>1809.776</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45836</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>1895.589</v>
+        <v>1883.372</v>
       </c>
       <c r="C46" t="n">
-        <v>1795.365</v>
+        <v>1814.133</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45843</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>2011.507</v>
+        <v>1857.167</v>
       </c>
       <c r="C47" t="n">
-        <v>1945.731</v>
+        <v>1802.463</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45850</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>2006.612</v>
+        <v>1843.217</v>
       </c>
       <c r="C48" t="n">
-        <v>1914.075</v>
+        <v>1789.862</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45857</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>2005.922</v>
+        <v>1800.515</v>
       </c>
       <c r="C49" t="n">
-        <v>1934.382</v>
+        <v>1747.737</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45864</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>1999.973</v>
+        <v>1704.638</v>
       </c>
       <c r="C50" t="n">
-        <v>1907.041</v>
+        <v>1655.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45871</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>1973.535</v>
+        <v>1671.837</v>
       </c>
       <c r="C51" t="n">
-        <v>1883.372</v>
+        <v>1645.927</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45878</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>1955.067</v>
+        <v>1628.081</v>
       </c>
       <c r="C52" t="n">
-        <v>1857.167</v>
+        <v>1588.285</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45885</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>1934.367</v>
+        <v>1613.719</v>
       </c>
       <c r="C53" t="n">
-        <v>1843.217</v>
+        <v>1585.277</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45892</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>1892.212</v>
+        <v>1614.385</v>
       </c>
       <c r="C54" t="n">
-        <v>1800.515</v>
+        <v>1555.172</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45899</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>1803.344</v>
+        <v>1598.241</v>
       </c>
       <c r="C55" t="n">
-        <v>1704.638</v>
+        <v>1542.397</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45906</v>
+        <v>45577</v>
       </c>
       <c r="B56" t="n">
-        <v>1759.868</v>
+        <v>1627.825</v>
       </c>
       <c r="C56" t="n">
-        <v>1671.837</v>
+        <v>1572.658</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1616.144</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1574.471</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1646.982</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1607.693</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1647.301</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1578.946</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1660.894</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1654.732</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1721.154</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1555.596</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1661.071</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1845.084</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1933.23</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1767.267</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1864.863</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1835.427</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1946.787</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1836.539</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1860.888</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1902.054</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2187.475</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2104.257</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2273.651</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2122.561</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2246.551</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2053.289</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2170.633</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2181.43</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2250.894</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2130.018</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2185.828</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2139.97</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2191.042</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2092.787</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2160.103</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2092.108</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2229.07</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2113.581</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2149.919</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2078.603</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2116.538</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2008.79</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2072.402</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2012.613</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2058.751</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1937.982</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1985.73</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1928.017</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1943.418</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1848.827</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1880.372</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1812.811</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1898.153</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1753.465</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1838.279</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1743.445</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1782.724</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1686.177</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1779.686</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1686.782</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1775.51</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1666.648</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1755.336</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1670.55</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1826.063</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1708.158</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1813.454</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1727.754</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1862.043</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1748.567</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1900.787</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1821.4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1895.589</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1795.365</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2011.507</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1945.731</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2006.612</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1914.075</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45857</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2005.922</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1934.382</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1999.973</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1907.041</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1973.535</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1883.372</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1955.067</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1857.167</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1934.367</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1843.217</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1892.212</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1800.515</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1803.347</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1704.638</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1759.884</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1671.837</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
         <v>45913</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B104" t="n">
+        <v>1718.818</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1628.081</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1695.661</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1613.719</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1683.253</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1614.385</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1651.557</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1598.241</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1673.837</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1627.825</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1608.059</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1616.144</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B110" t="n">
         <v>1727.777</v>
       </c>
-      <c r="C57" t="n">
-        <v>1628.081</v>
+      <c r="C110" t="n">
+        <v>1646.982</v>
       </c>
     </row>
   </sheetData>
@@ -1693,538 +2859,538 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45528</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>307</v>
+        <v>390</v>
       </c>
       <c r="C2" t="n">
-        <v>371</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45535</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>464</v>
       </c>
       <c r="C3" t="n">
-        <v>314</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45542</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>266</v>
+        <v>439</v>
       </c>
       <c r="C4" t="n">
-        <v>272</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45549</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>313</v>
+        <v>460</v>
       </c>
       <c r="C5" t="n">
-        <v>363</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45556</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>628</v>
       </c>
       <c r="C6" t="n">
-        <v>363</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45563</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>390</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45570</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>351</v>
+        <v>655</v>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45577</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>434</v>
+        <v>662</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>731</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45584</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>392</v>
+        <v>511</v>
       </c>
       <c r="C10" t="n">
-        <v>460</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45591</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>533</v>
+        <v>729</v>
       </c>
       <c r="C11" t="n">
-        <v>628</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45598</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>507</v>
+        <v>747</v>
       </c>
       <c r="C12" t="n">
-        <v>519</v>
+        <v>780</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45605</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>622</v>
+        <v>514</v>
       </c>
       <c r="C13" t="n">
-        <v>655</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45612</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="C14" t="n">
-        <v>662</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45619</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>760</v>
+        <v>415</v>
       </c>
       <c r="C15" t="n">
-        <v>511</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45626</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>399</v>
+        <v>643</v>
       </c>
       <c r="C16" t="n">
-        <v>729</v>
+        <v>948</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45633</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C17" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45640</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>549</v>
+        <v>420</v>
       </c>
       <c r="C18" t="n">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45647</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C19" t="n">
-        <v>580</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45654</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="C20" t="n">
-        <v>415</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45661</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>479</v>
+        <v>382</v>
       </c>
       <c r="C21" t="n">
-        <v>643</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45668</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>597</v>
+        <v>337</v>
       </c>
       <c r="C22" t="n">
-        <v>762</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45675</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>495</v>
+        <v>330</v>
       </c>
       <c r="C23" t="n">
-        <v>420</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45682</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="C24" t="n">
-        <v>502</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45689</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>599</v>
+        <v>365</v>
       </c>
       <c r="C25" t="n">
-        <v>411</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45696</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>613</v>
+        <v>362</v>
       </c>
       <c r="C26" t="n">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>613</v>
+        <v>371</v>
       </c>
       <c r="C27" t="n">
-        <v>337</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45710</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>1634</v>
+        <v>322</v>
       </c>
       <c r="C28" t="n">
-        <v>330</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45717</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>1580</v>
+        <v>327</v>
       </c>
       <c r="C29" t="n">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45724</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>1066</v>
+        <v>361</v>
       </c>
       <c r="C30" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45731</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>821</v>
+        <v>365</v>
       </c>
       <c r="C31" t="n">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45738</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>564</v>
+        <v>343</v>
       </c>
       <c r="C32" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45745</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>508</v>
+        <v>385</v>
       </c>
       <c r="C33" t="n">
-        <v>322</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45752</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>542</v>
+        <v>386</v>
       </c>
       <c r="C34" t="n">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45759</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>657</v>
+        <v>338</v>
       </c>
       <c r="C35" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45766</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>466</v>
+        <v>353</v>
       </c>
       <c r="C36" t="n">
-        <v>365</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45773</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="C37" t="n">
-        <v>343</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45780</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C38" t="n">
-        <v>385</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45787</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>599</v>
+        <v>344</v>
       </c>
       <c r="C39" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45794</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>592</v>
+        <v>336</v>
       </c>
       <c r="C40" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45801</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>523</v>
+        <v>372</v>
       </c>
       <c r="C41" t="n">
-        <v>353</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45808</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>553</v>
+        <v>327</v>
       </c>
       <c r="C42" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45815</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="C43" t="n">
-        <v>419</v>
+        <v>445</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45822</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="C44" t="n">
-        <v>344</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45829</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>453</v>
+        <v>314</v>
       </c>
       <c r="C45" t="n">
-        <v>336</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45836</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="C46" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45843</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>596</v>
+        <v>336</v>
       </c>
       <c r="C47" t="n">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45850</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>789</v>
+        <v>285</v>
       </c>
       <c r="C48" t="n">
-        <v>476</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45857</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>722</v>
+        <v>307</v>
       </c>
       <c r="C49" t="n">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45864</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>708</v>
+        <v>274</v>
       </c>
       <c r="C50" t="n">
         <v>314</v>
@@ -2232,79 +3398,662 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45871</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>637</v>
+        <v>266</v>
       </c>
       <c r="C51" t="n">
-        <v>334</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45878</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>635</v>
+        <v>313</v>
       </c>
       <c r="C52" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45885</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>588</v>
+        <v>278</v>
       </c>
       <c r="C53" t="n">
-        <v>285</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45892</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>515</v>
+        <v>313</v>
       </c>
       <c r="C54" t="n">
-        <v>307</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45899</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>527</v>
+        <v>351</v>
       </c>
       <c r="C55" t="n">
-        <v>274</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45906</v>
+        <v>45577</v>
       </c>
       <c r="B56" t="n">
-        <v>572</v>
+        <v>434</v>
       </c>
       <c r="C56" t="n">
-        <v>266</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="B57" t="n">
+        <v>392</v>
+      </c>
+      <c r="C57" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B58" t="n">
+        <v>533</v>
+      </c>
+      <c r="C58" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B59" t="n">
+        <v>507</v>
+      </c>
+      <c r="C59" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B60" t="n">
+        <v>622</v>
+      </c>
+      <c r="C60" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B61" t="n">
+        <v>529</v>
+      </c>
+      <c r="C61" t="n">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B62" t="n">
+        <v>760</v>
+      </c>
+      <c r="C62" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B63" t="n">
+        <v>399</v>
+      </c>
+      <c r="C63" t="n">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>759</v>
+      </c>
+      <c r="C64" t="n">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B65" t="n">
+        <v>549</v>
+      </c>
+      <c r="C65" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B66" t="n">
+        <v>507</v>
+      </c>
+      <c r="C66" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B67" t="n">
+        <v>343</v>
+      </c>
+      <c r="C67" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B68" t="n">
+        <v>479</v>
+      </c>
+      <c r="C68" t="n">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B69" t="n">
+        <v>597</v>
+      </c>
+      <c r="C69" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>495</v>
+      </c>
+      <c r="C70" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B71" t="n">
+        <v>497</v>
+      </c>
+      <c r="C71" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>599</v>
+      </c>
+      <c r="C72" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B73" t="n">
+        <v>613</v>
+      </c>
+      <c r="C73" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B74" t="n">
+        <v>613</v>
+      </c>
+      <c r="C74" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C75" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C76" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C77" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B78" t="n">
+        <v>821</v>
+      </c>
+      <c r="C78" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B79" t="n">
+        <v>564</v>
+      </c>
+      <c r="C79" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B80" t="n">
+        <v>508</v>
+      </c>
+      <c r="C80" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B81" t="n">
+        <v>542</v>
+      </c>
+      <c r="C81" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B82" t="n">
+        <v>657</v>
+      </c>
+      <c r="C82" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B83" t="n">
+        <v>466</v>
+      </c>
+      <c r="C83" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B84" t="n">
+        <v>465</v>
+      </c>
+      <c r="C84" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B85" t="n">
+        <v>434</v>
+      </c>
+      <c r="C85" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B86" t="n">
+        <v>599</v>
+      </c>
+      <c r="C86" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B87" t="n">
+        <v>592</v>
+      </c>
+      <c r="C87" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B88" t="n">
+        <v>523</v>
+      </c>
+      <c r="C88" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B89" t="n">
+        <v>553</v>
+      </c>
+      <c r="C89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B90" t="n">
+        <v>532</v>
+      </c>
+      <c r="C90" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B91" t="n">
+        <v>472</v>
+      </c>
+      <c r="C91" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B92" t="n">
+        <v>453</v>
+      </c>
+      <c r="C92" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B93" t="n">
+        <v>438</v>
+      </c>
+      <c r="C93" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B94" t="n">
+        <v>596</v>
+      </c>
+      <c r="C94" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B95" t="n">
+        <v>789</v>
+      </c>
+      <c r="C95" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45857</v>
+      </c>
+      <c r="B96" t="n">
+        <v>722</v>
+      </c>
+      <c r="C96" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B97" t="n">
+        <v>708</v>
+      </c>
+      <c r="C97" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B98" t="n">
+        <v>637</v>
+      </c>
+      <c r="C98" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B99" t="n">
+        <v>635</v>
+      </c>
+      <c r="C99" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B100" t="n">
+        <v>588</v>
+      </c>
+      <c r="C100" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B101" t="n">
+        <v>515</v>
+      </c>
+      <c r="C101" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B102" t="n">
+        <v>527</v>
+      </c>
+      <c r="C102" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B103" t="n">
+        <v>572</v>
+      </c>
+      <c r="C103" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
         <v>45913</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B104" t="n">
         <v>635</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C104" t="n">
         <v>313</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="B105" t="n">
+        <v>530</v>
+      </c>
+      <c r="C105" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="B106" t="n">
+        <v>588</v>
+      </c>
+      <c r="C106" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="B107" t="n">
+        <v>3272</v>
+      </c>
+      <c r="C107" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B108" t="n">
+        <v>7287</v>
+      </c>
+      <c r="C108" t="n">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="B109" t="n">
+        <v>10062</v>
+      </c>
+      <c r="C109" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B110" t="n">
+        <v>8865</v>
+      </c>
+      <c r="C110" t="n">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -2331,607 +4080,1190 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45528</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>4191</v>
+        <v>4200</v>
       </c>
       <c r="C2" t="n">
-        <v>4552</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45535</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>3852</v>
+        <v>4121</v>
       </c>
       <c r="C3" t="n">
-        <v>4164</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45542</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>3898</v>
+        <v>4267</v>
       </c>
       <c r="C4" t="n">
-        <v>4295</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45549</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>4001</v>
+        <v>4309</v>
       </c>
       <c r="C5" t="n">
-        <v>4123</v>
+        <v>5659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45556</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>4033</v>
+        <v>4638</v>
       </c>
       <c r="C6" t="n">
-        <v>4148</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45563</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>3929</v>
+        <v>4741</v>
       </c>
       <c r="C7" t="n">
-        <v>4200</v>
+        <v>5684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45570</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>3819</v>
+        <v>5179</v>
       </c>
       <c r="C8" t="n">
-        <v>4121</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45577</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>3903</v>
+        <v>5045</v>
       </c>
       <c r="C9" t="n">
-        <v>4267</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45584</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>4038</v>
+        <v>5791</v>
       </c>
       <c r="C10" t="n">
-        <v>4309</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45591</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>4246</v>
+        <v>6131</v>
       </c>
       <c r="C11" t="n">
-        <v>4638</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45598</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>4454</v>
+        <v>6272</v>
       </c>
       <c r="C12" t="n">
-        <v>4741</v>
+        <v>7068</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45605</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>4760</v>
+        <v>6427</v>
       </c>
       <c r="C13" t="n">
-        <v>5179</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45612</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>5023</v>
+        <v>6284</v>
       </c>
       <c r="C14" t="n">
-        <v>5045</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45619</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>5081</v>
+        <v>6577</v>
       </c>
       <c r="C15" t="n">
-        <v>5791</v>
+        <v>7328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45626</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>5997</v>
+        <v>6766</v>
       </c>
       <c r="C16" t="n">
-        <v>6131</v>
+        <v>7324</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45633</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>6031</v>
+        <v>6708</v>
       </c>
       <c r="C17" t="n">
-        <v>6272</v>
+        <v>7289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45640</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>6577</v>
+        <v>7383</v>
       </c>
       <c r="C18" t="n">
-        <v>6427</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45647</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>6210</v>
+        <v>6953</v>
       </c>
       <c r="C19" t="n">
-        <v>6284</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45654</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>6374</v>
+        <v>6893</v>
       </c>
       <c r="C20" t="n">
-        <v>6577</v>
+        <v>7715</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45661</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>6854</v>
+        <v>6819</v>
       </c>
       <c r="C21" t="n">
-        <v>6766</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45668</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>7381</v>
+        <v>6594</v>
       </c>
       <c r="C22" t="n">
-        <v>6708</v>
+        <v>7078</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45675</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>6684</v>
+        <v>6876</v>
       </c>
       <c r="C23" t="n">
-        <v>7383</v>
+        <v>6962</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45682</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>7470</v>
+        <v>6208</v>
       </c>
       <c r="C24" t="n">
-        <v>6953</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45689</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>7120</v>
+        <v>6241</v>
       </c>
       <c r="C25" t="n">
-        <v>6893</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45696</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>7621</v>
+        <v>5891</v>
       </c>
       <c r="C26" t="n">
-        <v>6819</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>7422</v>
+        <v>5881</v>
       </c>
       <c r="C27" t="n">
-        <v>6594</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45710</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>8230</v>
+        <v>5546</v>
       </c>
       <c r="C28" t="n">
-        <v>6876</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45717</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>8929</v>
+        <v>5274</v>
       </c>
       <c r="C29" t="n">
-        <v>6208</v>
+        <v>5601</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45724</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>9136</v>
+        <v>5091</v>
       </c>
       <c r="C30" t="n">
-        <v>6241</v>
+        <v>5343</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45731</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>8246</v>
+        <v>5030</v>
       </c>
       <c r="C31" t="n">
-        <v>5891</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45738</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>7721</v>
+        <v>4764</v>
       </c>
       <c r="C32" t="n">
-        <v>5881</v>
+        <v>5026</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45745</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>7192</v>
+        <v>4737</v>
       </c>
       <c r="C33" t="n">
-        <v>5546</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45752</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>7019</v>
+        <v>4494</v>
       </c>
       <c r="C34" t="n">
-        <v>5274</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45759</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>6640</v>
+        <v>4648</v>
       </c>
       <c r="C35" t="n">
-        <v>5091</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45766</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>6716</v>
+        <v>4401</v>
       </c>
       <c r="C36" t="n">
-        <v>5030</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45773</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>6570</v>
+        <v>4634</v>
       </c>
       <c r="C37" t="n">
-        <v>4764</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45780</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>6473</v>
+        <v>4553</v>
       </c>
       <c r="C38" t="n">
-        <v>4737</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45787</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>6377</v>
+        <v>4568</v>
       </c>
       <c r="C39" t="n">
-        <v>4494</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45794</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>6717</v>
+        <v>4433</v>
       </c>
       <c r="C40" t="n">
-        <v>4648</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45801</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>6323</v>
+        <v>4605</v>
       </c>
       <c r="C41" t="n">
-        <v>4401</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45808</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>7076</v>
+        <v>4711</v>
       </c>
       <c r="C42" t="n">
-        <v>4634</v>
+        <v>4863</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45815</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>6738</v>
+        <v>4658</v>
       </c>
       <c r="C43" t="n">
-        <v>4553</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45822</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>7103</v>
+        <v>4767</v>
       </c>
       <c r="C44" t="n">
-        <v>4568</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45829</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>6947</v>
+        <v>4855</v>
       </c>
       <c r="C45" t="n">
-        <v>4433</v>
+        <v>5106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45836</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>7035</v>
+        <v>4505</v>
       </c>
       <c r="C46" t="n">
-        <v>4605</v>
+        <v>4912</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45843</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>7226</v>
+        <v>4632</v>
       </c>
       <c r="C47" t="n">
-        <v>4711</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45850</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>7407</v>
+        <v>4308</v>
       </c>
       <c r="C48" t="n">
-        <v>4658</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45857</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>7831</v>
+        <v>4191</v>
       </c>
       <c r="C49" t="n">
-        <v>4767</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45864</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>8193</v>
+        <v>3852</v>
       </c>
       <c r="C50" t="n">
-        <v>4855</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45871</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>8237</v>
+        <v>3898</v>
       </c>
       <c r="C51" t="n">
-        <v>4505</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45878</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>8456</v>
+        <v>4001</v>
       </c>
       <c r="C52" t="n">
-        <v>4632</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45885</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>8128</v>
+        <v>4033</v>
       </c>
       <c r="C53" t="n">
-        <v>4308</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45892</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>8211</v>
+        <v>3929</v>
       </c>
       <c r="C54" t="n">
-        <v>4191</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45899</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>7863</v>
+        <v>3819</v>
       </c>
       <c r="C55" t="n">
-        <v>3852</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
+        <v>45577</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3903</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4038</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4246</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4638</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4454</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45605</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45612</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5023</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5045</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5081</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5791</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5997</v>
+      </c>
+      <c r="C63" t="n">
+        <v>6131</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6031</v>
+      </c>
+      <c r="C64" t="n">
+        <v>6272</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6577</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6427</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6210</v>
+      </c>
+      <c r="C66" t="n">
+        <v>6284</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6374</v>
+      </c>
+      <c r="C67" t="n">
+        <v>6577</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45661</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6854</v>
+      </c>
+      <c r="C68" t="n">
+        <v>6766</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7381</v>
+      </c>
+      <c r="C69" t="n">
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6684</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7383</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7470</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6953</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7120</v>
+      </c>
+      <c r="C72" t="n">
+        <v>6893</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7621</v>
+      </c>
+      <c r="C73" t="n">
+        <v>6819</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7422</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6594</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8230</v>
+      </c>
+      <c r="C75" t="n">
+        <v>6876</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8929</v>
+      </c>
+      <c r="C76" t="n">
+        <v>6208</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>9136</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6241</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8246</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5891</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7721</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5881</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7192</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5546</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7019</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B82" t="n">
+        <v>6640</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5091</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B83" t="n">
+        <v>6716</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45773</v>
+      </c>
+      <c r="B84" t="n">
+        <v>6570</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B85" t="n">
+        <v>6473</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4737</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B86" t="n">
+        <v>6377</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B87" t="n">
+        <v>6717</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B88" t="n">
+        <v>6323</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7076</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B90" t="n">
+        <v>6738</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7103</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6947</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45836</v>
+      </c>
+      <c r="B93" t="n">
+        <v>7035</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B94" t="n">
+        <v>7226</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B95" t="n">
+        <v>7407</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45857</v>
+      </c>
+      <c r="B96" t="n">
+        <v>7831</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4767</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8193</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4855</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8237</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4505</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8456</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8128</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8211</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B102" t="n">
+        <v>7863</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
         <v>45906</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B103" t="n">
         <v>8168</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C103" t="n">
         <v>3898</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8223</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8459</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="B106" t="n">
+        <v>8672</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="B107" t="n">
+        <v>9988</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B108" t="n">
+        <v>14464</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="B109" t="n">
+        <v>20594</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4038</v>
       </c>
     </row>
   </sheetData>
@@ -2958,1190 +5290,1190 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45164</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>0.752462149051889</v>
+        <v>0.745592754326379</v>
       </c>
       <c r="C2" t="n">
-        <v>0.278731577177855</v>
+        <v>0.292430153360314</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45171</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>0.69588188463487</v>
+        <v>0.829532114707362</v>
       </c>
       <c r="C3" t="n">
-        <v>0.285075465258575</v>
+        <v>0.292538062193876</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45178</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>0.659128917327129</v>
+        <v>0.82242374278648</v>
       </c>
       <c r="C4" t="n">
-        <v>0.288155928025338</v>
+        <v>0.286920428436942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45185</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>0.71851908866995</v>
+        <v>0.912273302404049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.292300734442642</v>
+        <v>0.282927690123362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45192</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>0.688183807439825</v>
+        <v>0.998352267799844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.294048419132878</v>
+        <v>0.276427174122571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45199</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>0.745592754326379</v>
+        <v>1.08845296477931</v>
       </c>
       <c r="C7" t="n">
-        <v>0.292430153360314</v>
+        <v>0.275848614432846</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45206</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>0.829532114707362</v>
+        <v>1.19650167473018</v>
       </c>
       <c r="C8" t="n">
-        <v>0.292538062193876</v>
+        <v>0.262878986207589</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45213</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>0.82242374278648</v>
+        <v>1.14916869045395</v>
       </c>
       <c r="C9" t="n">
-        <v>0.286920428436942</v>
+        <v>0.253808435820337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45220</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>0.912273302404049</v>
+        <v>1.14369202226345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.282927690123362</v>
+        <v>0.229470488926282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45227</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>0.998352267799844</v>
+        <v>1.07848915081704</v>
       </c>
       <c r="C11" t="n">
-        <v>0.276427174122571</v>
+        <v>0.20342743368623</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45234</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>1.08845296477931</v>
+        <v>1.02695231513476</v>
       </c>
       <c r="C12" t="n">
-        <v>0.275848614432846</v>
+        <v>0.182789382857749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45241</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>1.19650167473018</v>
+        <v>0.936523280167553</v>
       </c>
       <c r="C13" t="n">
-        <v>0.262878986207589</v>
+        <v>0.16803310758329</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45248</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>1.14916869045395</v>
+        <v>0.880585211546066</v>
       </c>
       <c r="C14" t="n">
-        <v>0.253808435820337</v>
+        <v>0.149667696227104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45255</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>1.14369202226345</v>
+        <v>0.827831270059606</v>
       </c>
       <c r="C15" t="n">
-        <v>0.229470488926282</v>
+        <v>0.137149365060206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45262</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>1.07848915081704</v>
+        <v>0.725096194955109</v>
       </c>
       <c r="C16" t="n">
-        <v>0.20342743368623</v>
+        <v>0.127234983606052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45269</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>1.02695231513476</v>
+        <v>0.683745214061956</v>
       </c>
       <c r="C17" t="n">
-        <v>0.182789382857749</v>
+        <v>0.112721865125587</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45276</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>0.936523280167553</v>
+        <v>0.59653417509502</v>
       </c>
       <c r="C18" t="n">
-        <v>0.16803310758329</v>
+        <v>0.120158906584597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45283</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>0.880585211546066</v>
+        <v>0.448905338435481</v>
       </c>
       <c r="C19" t="n">
-        <v>0.149667696227104</v>
+        <v>0.115352464366679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45290</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>0.827831270059606</v>
+        <v>0.368510431829209</v>
       </c>
       <c r="C20" t="n">
-        <v>0.137149365060206</v>
+        <v>0.11182537948803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45297</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>0.725096194955109</v>
+        <v>0.294063079777366</v>
       </c>
       <c r="C21" t="n">
-        <v>0.127234983606052</v>
+        <v>0.107616691372684</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45304</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>0.683745214061956</v>
+        <v>0.220064178348252</v>
       </c>
       <c r="C22" t="n">
-        <v>0.112721865125587</v>
+        <v>0.0988033469584233</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45311</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>0.59653417509502</v>
+        <v>0.155271015739663</v>
       </c>
       <c r="C23" t="n">
-        <v>0.120158906584597</v>
+        <v>0.0903828995441902</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45318</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>0.448905338435481</v>
+        <v>0.141088859816846</v>
       </c>
       <c r="C24" t="n">
-        <v>0.115352464366679</v>
+        <v>0.0878492655366059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45325</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>0.368510431829209</v>
+        <v>0.107121807465619</v>
       </c>
       <c r="C25" t="n">
-        <v>0.11182537948803</v>
+        <v>0.084035657662493</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45332</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>0.294063079777366</v>
+        <v>0.0716237866365093</v>
       </c>
       <c r="C26" t="n">
-        <v>0.107616691372684</v>
+        <v>0.0756771842295227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45339</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>0.220064178348252</v>
+        <v>0.0515586979477527</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0988033469584233</v>
+        <v>0.0706704847488504</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45346</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>0.155271015739663</v>
+        <v>0.0234076074724285</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0903828995441902</v>
+        <v>0.0672873676665622</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45353</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>0.141088859816846</v>
+        <v>-0.013405178078591</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0878492655366059</v>
+        <v>0.0588975018865721</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45360</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>0.107121807465619</v>
+        <v>-0.0276095475596723</v>
       </c>
       <c r="C30" t="n">
-        <v>0.084035657662493</v>
+        <v>0.0498411285611142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45367</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0716237866365093</v>
+        <v>0.00954045246304247</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0756771842295227</v>
+        <v>0.0465875645822198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45374</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0515586979477527</v>
+        <v>0.0323711239838387</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0706704847488504</v>
+        <v>0.0401800167043784</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45381</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0234076074724285</v>
+        <v>0.0972322627284932</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0672873676665622</v>
+        <v>0.0431098725616055</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45388</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.013405178078591</v>
+        <v>0.14658292527145</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0588975018865721</v>
+        <v>0.0460089809272537</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45395</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.0276095475596723</v>
+        <v>0.174474959612278</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0498411285611142</v>
+        <v>0.045447728861981</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45402</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>0.00954045246304247</v>
+        <v>0.200282854656223</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0465875645822198</v>
+        <v>0.0446505258703753</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45409</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0323711239838387</v>
+        <v>0.218417499324872</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0401800167043784</v>
+        <v>0.0420175845375934</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45416</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0972322627284932</v>
+        <v>0.223254324151185</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0431098725616055</v>
+        <v>0.0388086026617791</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45423</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>0.14658292527145</v>
+        <v>0.23546808625047</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0460089809272537</v>
+        <v>0.0407852482714004</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45430</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>0.174474959612278</v>
+        <v>0.22424652542814</v>
       </c>
       <c r="C40" t="n">
-        <v>0.045447728861981</v>
+        <v>0.040985152109636</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45437</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>0.200282854656223</v>
+        <v>0.198969280517381</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0446505258703753</v>
+        <v>0.0421079680110672</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45444</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>0.218417499324872</v>
+        <v>0.209443757725587</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0420175845375934</v>
+        <v>0.0408530223130144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45451</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>0.223254324151185</v>
+        <v>0.227342995169082</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0388086026617791</v>
+        <v>0.040555460529621</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45458</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>0.23546808625047</v>
+        <v>0.203128637273616</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0407852482714004</v>
+        <v>0.0432092766697589</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45465</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>0.22424652542814</v>
+        <v>0.189903193703067</v>
       </c>
       <c r="C45" t="n">
-        <v>0.040985152109636</v>
+        <v>0.0462641221417603</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45472</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>0.198969280517381</v>
+        <v>0.163998059194566</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0421079680110672</v>
+        <v>0.0483020346929517</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45479</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>0.209443757725587</v>
+        <v>0.141896234094512</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0408530223130144</v>
+        <v>0.0452476492494154</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45486</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>0.227342995169082</v>
+        <v>0.150697198413714</v>
       </c>
       <c r="C48" t="n">
-        <v>0.040555460529621</v>
+        <v>0.0380479624136356</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45493</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>0.203128637273616</v>
+        <v>0.141125650058715</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0432092766697589</v>
+        <v>0.0321595930779075</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45500</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>0.189903193703067</v>
+        <v>0.150051212017754</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0462641221417603</v>
+        <v>0.0299653997440217</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45507</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>0.163998059194566</v>
+        <v>0.16618459111228</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0483020346929517</v>
+        <v>0.0264411935258326</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45514</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>0.141896234094512</v>
+        <v>0.166748779504636</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0452476492494154</v>
+        <v>0.0252014639211942</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45521</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>0.150697198413714</v>
+        <v>0.178918618646422</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0380479624136356</v>
+        <v>0.0220754806435317</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45528</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>0.141125650058715</v>
+        <v>0.176410636523673</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0321595930779075</v>
+        <v>0.024057906765552</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45535</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>0.150051212017754</v>
+        <v>0.158714881525276</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0299653997440217</v>
+        <v>0.0292283800163</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45542</v>
+        <v>45577</v>
       </c>
       <c r="B56" t="n">
-        <v>0.16618459111228</v>
+        <v>0.154573418981272</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0264411935258326</v>
+        <v>0.0317585921134413</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45549</v>
+        <v>45584</v>
       </c>
       <c r="B57" t="n">
-        <v>0.166748779504636</v>
+        <v>0.14208204675783</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0252014639211942</v>
+        <v>0.0339323054533622</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45556</v>
+        <v>45591</v>
       </c>
       <c r="B58" t="n">
-        <v>0.178918618646422</v>
+        <v>0.139955734930348</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0220754806435317</v>
+        <v>0.0304853618716452</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45563</v>
+        <v>45598</v>
       </c>
       <c r="B59" t="n">
-        <v>0.176410636523673</v>
+        <v>0.132738451028947</v>
       </c>
       <c r="C59" t="n">
-        <v>0.024057906765552</v>
+        <v>0.0322847316163144</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45570</v>
+        <v>45605</v>
       </c>
       <c r="B60" t="n">
-        <v>0.158714881525276</v>
+        <v>0.131862080650627</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0292283800163</v>
+        <v>0.0242336079972043</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45577</v>
+        <v>45612</v>
       </c>
       <c r="B61" t="n">
-        <v>0.154573418981272</v>
+        <v>0.171802338215481</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0317585921134413</v>
+        <v>0.0436713211120208</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45584</v>
+        <v>45619</v>
       </c>
       <c r="B62" t="n">
-        <v>0.14208204675783</v>
+        <v>0.163226448569821</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0339323054533622</v>
+        <v>0.00845025245848952</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45591</v>
+        <v>45626</v>
       </c>
       <c r="B63" t="n">
-        <v>0.139955734930348</v>
+        <v>0.172058254929759</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0304853618716452</v>
+        <v>0.0225234105253962</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45598</v>
+        <v>45633</v>
       </c>
       <c r="B64" t="n">
-        <v>0.132738451028947</v>
+        <v>0.175715990453461</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0322847316163144</v>
+        <v>0.0252655362972192</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45605</v>
+        <v>45640</v>
       </c>
       <c r="B65" t="n">
-        <v>0.131862080650627</v>
+        <v>0.160316139767055</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0242336079972043</v>
+        <v>0.0166980651720676</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45612</v>
+        <v>45647</v>
       </c>
       <c r="B66" t="n">
-        <v>0.171802338215481</v>
+        <v>0.191925988225399</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0436713211120208</v>
+        <v>0.0360265168764005</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45619</v>
+        <v>45654</v>
       </c>
       <c r="B67" t="n">
-        <v>0.163226448569821</v>
+        <v>0.204941678163803</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00845025245848952</v>
+        <v>0.0236688517489014</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45626</v>
+        <v>45661</v>
       </c>
       <c r="B68" t="n">
-        <v>0.172058254929759</v>
+        <v>0.199917389508468</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0225234105253962</v>
+        <v>0.0380884300885416</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45633</v>
+        <v>45668</v>
       </c>
       <c r="B69" t="n">
-        <v>0.175715990453461</v>
+        <v>0.229751519411254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0252655362972192</v>
+        <v>0.0472251768206466</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45640</v>
+        <v>45675</v>
       </c>
       <c r="B70" t="n">
-        <v>0.160316139767055</v>
+        <v>0.223177177904208</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0166980651720676</v>
+        <v>0.0492549994167726</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45647</v>
+        <v>45682</v>
       </c>
       <c r="B71" t="n">
-        <v>0.191925988225399</v>
+        <v>0.323548512793869</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0360265168764005</v>
+        <v>0.0535424819536205</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45654</v>
+        <v>45689</v>
       </c>
       <c r="B72" t="n">
-        <v>0.204941678163803</v>
+        <v>0.396427938308811</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0236688517489014</v>
+        <v>0.0410594979932879</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45661</v>
+        <v>45696</v>
       </c>
       <c r="B73" t="n">
-        <v>0.199917389508468</v>
+        <v>0.454256272401434</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0380884300885416</v>
+        <v>0.0297502225192396</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45668</v>
+        <v>45703</v>
       </c>
       <c r="B74" t="n">
-        <v>0.229751519411254</v>
+        <v>0.56764488741233</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0472251768206466</v>
+        <v>0.0393836319201579</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45675</v>
+        <v>45710</v>
       </c>
       <c r="B75" t="n">
-        <v>0.223177177904208</v>
+        <v>0.596092346782319</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0492549994167726</v>
+        <v>0.0388219584506435</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45682</v>
+        <v>45717</v>
       </c>
       <c r="B76" t="n">
-        <v>0.323548512793869</v>
+        <v>0.713643178410795</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0535424819536205</v>
+        <v>0.0421453587819811</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45689</v>
+        <v>45724</v>
       </c>
       <c r="B77" t="n">
-        <v>0.396427938308811</v>
+        <v>0.829688123863183</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0410594979932879</v>
+        <v>0.04371691971694</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45696</v>
+        <v>45731</v>
       </c>
       <c r="B78" t="n">
-        <v>0.454256272401434</v>
+        <v>0.898953478146161</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0297502225192396</v>
+        <v>0.043140956563801</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45703</v>
+        <v>45738</v>
       </c>
       <c r="B79" t="n">
-        <v>0.56764488741233</v>
+        <v>0.914512748864827</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0393836319201579</v>
+        <v>0.0447403006822105</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45710</v>
+        <v>45745</v>
       </c>
       <c r="B80" t="n">
-        <v>0.596092346782319</v>
+        <v>0.931867165163844</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0388219584506435</v>
+        <v>0.0438698319167705</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45717</v>
+        <v>45752</v>
       </c>
       <c r="B81" t="n">
-        <v>0.713643178410795</v>
+        <v>0.931175347453488</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0421453587819811</v>
+        <v>0.0430753319437398</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45724</v>
+        <v>45759</v>
       </c>
       <c r="B82" t="n">
-        <v>0.829688123863183</v>
+        <v>0.950586187946511</v>
       </c>
       <c r="C82" t="n">
-        <v>0.04371691971694</v>
+        <v>0.0452511193087552</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45731</v>
+        <v>45766</v>
       </c>
       <c r="B83" t="n">
-        <v>0.898953478146161</v>
+        <v>0.962573099415205</v>
       </c>
       <c r="C83" t="n">
-        <v>0.043140956563801</v>
+        <v>0.049645518526185</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45738</v>
+        <v>45773</v>
       </c>
       <c r="B84" t="n">
-        <v>0.914512748864827</v>
+        <v>0.956761599396454</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0447403006822105</v>
+        <v>0.0561110996252312</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45745</v>
+        <v>45780</v>
       </c>
       <c r="B85" t="n">
-        <v>0.931867165163844</v>
+        <v>0.928278977834251</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0438698319167705</v>
+        <v>0.0576952379808855</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45752</v>
+        <v>45787</v>
       </c>
       <c r="B86" t="n">
-        <v>0.931175347453488</v>
+        <v>0.901866121994244</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0430753319437398</v>
+        <v>0.0624426753989049</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45759</v>
+        <v>45794</v>
       </c>
       <c r="B87" t="n">
-        <v>0.950586187946511</v>
+        <v>0.879367262723521</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0452511193087552</v>
+        <v>0.057960192550492</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45766</v>
+        <v>45801</v>
       </c>
       <c r="B88" t="n">
-        <v>0.962573099415205</v>
+        <v>0.860871929665549</v>
       </c>
       <c r="C88" t="n">
-        <v>0.049645518526185</v>
+        <v>0.0570924048423904</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45773</v>
+        <v>45808</v>
       </c>
       <c r="B89" t="n">
-        <v>0.956761599396454</v>
+        <v>0.834035196595594</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0561110996252312</v>
+        <v>0.060078536714488</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45780</v>
+        <v>45815</v>
       </c>
       <c r="B90" t="n">
-        <v>0.928278977834251</v>
+        <v>0.828052718861831</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0576952379808855</v>
+        <v>0.0586514909694367</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45787</v>
+        <v>45822</v>
       </c>
       <c r="B91" t="n">
-        <v>0.901866121994244</v>
+        <v>0.844489902506964</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0624426753989049</v>
+        <v>0.0586236761361623</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45794</v>
+        <v>45829</v>
       </c>
       <c r="B92" t="n">
-        <v>0.879367262723521</v>
+        <v>0.82460988987627</v>
       </c>
       <c r="C92" t="n">
-        <v>0.057960192550492</v>
+        <v>0.0565907575623272</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45801</v>
+        <v>45836</v>
       </c>
       <c r="B93" t="n">
-        <v>0.860871929665549</v>
+        <v>0.823430257058575</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0570924048423904</v>
+        <v>0.0534022849856888</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45808</v>
+        <v>45843</v>
       </c>
       <c r="B94" t="n">
-        <v>0.834035196595594</v>
+        <v>0.801316381178202</v>
       </c>
       <c r="C94" t="n">
-        <v>0.060078536714488</v>
+        <v>0.0490849278689021</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45815</v>
+        <v>45850</v>
       </c>
       <c r="B95" t="n">
-        <v>0.828052718861831</v>
+        <v>0.77241596473274</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0586514909694367</v>
+        <v>0.0451977249998696</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45822</v>
+        <v>45857</v>
       </c>
       <c r="B96" t="n">
-        <v>0.844489902506964</v>
+        <v>0.777726182184042</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0586236761361623</v>
+        <v>0.0434909671228332</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45829</v>
+        <v>45864</v>
       </c>
       <c r="B97" t="n">
-        <v>0.82460988987627</v>
+        <v>0.783645072992701</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0565907575623272</v>
+        <v>0.0419134400496337</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45836</v>
+        <v>45871</v>
       </c>
       <c r="B98" t="n">
-        <v>0.823430257058575</v>
+        <v>0.788245102125886</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0534022849856888</v>
+        <v>0.0454480832898061</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45843</v>
+        <v>45878</v>
       </c>
       <c r="B99" t="n">
-        <v>0.801316381178202</v>
+        <v>0.763553821333433</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0490849278689021</v>
+        <v>0.0464965400776212</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45850</v>
+        <v>45885</v>
       </c>
       <c r="B100" t="n">
-        <v>0.77241596473274</v>
+        <v>0.726848249027237</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0451977249998696</v>
+        <v>0.0496802943665406</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45857</v>
+        <v>45892</v>
       </c>
       <c r="B101" t="n">
-        <v>0.777726182184042</v>
+        <v>0.677790436987761</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0434909671228332</v>
+        <v>0.0502297383181087</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45864</v>
+        <v>45899</v>
       </c>
       <c r="B102" t="n">
-        <v>0.783645072992701</v>
+        <v>0.639268220276087</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0419134400496337</v>
+        <v>0.0526617238937224</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45871</v>
+        <v>45906</v>
       </c>
       <c r="B103" t="n">
-        <v>0.788245102125886</v>
+        <v>0.59488913942127</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0454480832898061</v>
+        <v>0.0526484475457774</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45878</v>
+        <v>45913</v>
       </c>
       <c r="B104" t="n">
-        <v>0.763553821333433</v>
+        <v>0.566833013435701</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0464965400776212</v>
+        <v>0.0542521892864896</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45885</v>
+        <v>45920</v>
       </c>
       <c r="B105" t="n">
-        <v>0.726848249027237</v>
+        <v>0.555817332233871</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0496802943665406</v>
+        <v>0.0543094688570662</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45892</v>
+        <v>45927</v>
       </c>
       <c r="B106" t="n">
-        <v>0.677790436987761</v>
+        <v>0.532291092384028</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0502297383181087</v>
+        <v>0.0504891068075444</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45899</v>
+        <v>45934</v>
       </c>
       <c r="B107" t="n">
-        <v>0.639268220276087</v>
+        <v>0.529032513250534</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0526613075472375</v>
+        <v>0.0456838454728585</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45906</v>
+        <v>45941</v>
       </c>
       <c r="B108" t="n">
-        <v>0.59488913942127</v>
+        <v>0.520197468949575</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0526457410728771</v>
+        <v>0.0387560290478868</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45913</v>
+        <v>45948</v>
       </c>
       <c r="B109" t="n">
-        <v>0.621650671785029</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0555659154768555</v>
+        <v>0.0247980553217291</v>
       </c>
     </row>
   </sheetData>
@@ -4174,1821 +6506,1821 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45164</v>
+        <v>45199</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0657640232108316</v>
+        <v>0.0599647266313934</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3008356545961</v>
+        <v>-0.334239130434783</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.178921568627451</v>
+        <v>0.00298507462686559</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.278183635804368</v>
+        <v>-0.288400322566954</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45171</v>
+        <v>45206</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.00174520069808026</v>
+        <v>0.329896907216495</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.302816901408451</v>
+        <v>-0.330769230769231</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.171149144254279</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.291804180418042</v>
+        <v>-0.273650571290986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45178</v>
+        <v>45213</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0302066772655007</v>
+        <v>0.443478260869565</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.347398030942335</v>
+        <v>-0.346733668341708</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.123425692695214</v>
+        <v>0.388</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.302418389336739</v>
+        <v>-0.270253771692683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45185</v>
+        <v>45220</v>
       </c>
       <c r="B5" t="n">
-        <v>0.045774647887324</v>
+        <v>0.42274678111588</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.355677154582763</v>
+        <v>-0.443298969072165</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.123737373737374</v>
+        <v>0.616438356164384</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.298907483939605</v>
+        <v>-0.260136614414572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45192</v>
+        <v>45227</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0774774774774776</v>
+        <v>0.883977900552486</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.362068965517241</v>
+        <v>-0.435632183908046</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.116883116883117</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.300029287477511</v>
+        <v>-0.241688538932633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45199</v>
+        <v>45234</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0599647266313934</v>
+        <v>0.392290249433107</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.334239130434783</v>
+        <v>-0.344827586206897</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00298507462686559</v>
+        <v>0.40495867768595</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.288400322566954</v>
+        <v>-0.219313883212314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45206</v>
+        <v>45241</v>
       </c>
       <c r="B8" t="n">
-        <v>0.329896907216495</v>
+        <v>0.0458715596330275</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.330769230769231</v>
+        <v>-0.316120906801008</v>
       </c>
       <c r="D8" t="n">
-        <v>0.166666666666667</v>
+        <v>0.351239669421488</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.273650571290986</v>
+        <v>-0.195128194189668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45213</v>
+        <v>45248</v>
       </c>
       <c r="B9" t="n">
-        <v>0.443478260869565</v>
+        <v>-0.0370994940978078</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.346733668341708</v>
+        <v>-0.129429892141757</v>
       </c>
       <c r="D9" t="n">
-        <v>0.388</v>
+        <v>0.263374485596708</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.270253771692683</v>
+        <v>-0.173183179383356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45220</v>
+        <v>45255</v>
       </c>
       <c r="B10" t="n">
-        <v>0.42274678111588</v>
+        <v>-0.121794871794872</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.443298969072165</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="D10" t="n">
-        <v>0.616438356164384</v>
+        <v>0.1699604743083</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.260136614414572</v>
+        <v>-0.1644795105064</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45227</v>
+        <v>45262</v>
       </c>
       <c r="B11" t="n">
-        <v>0.883977900552486</v>
+        <v>0.143122676579926</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.435632183908046</v>
+        <v>-0.114854517611026</v>
       </c>
       <c r="D11" t="n">
-        <v>0.555555555555556</v>
+        <v>0.135658914728682</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.241688538932633</v>
+        <v>-0.148820047659313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45234</v>
+        <v>45269</v>
       </c>
       <c r="B12" t="n">
-        <v>0.392290249433107</v>
+        <v>0.253549695740365</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.344827586206897</v>
+        <v>-0.0337941628264209</v>
       </c>
       <c r="D12" t="n">
-        <v>0.40495867768595</v>
+        <v>0.104089219330855</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.219313883212314</v>
+        <v>-0.132452308955837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45241</v>
+        <v>45276</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0458715596330275</v>
+        <v>0.128913443830571</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.316120906801008</v>
+        <v>-0.0739130434782609</v>
       </c>
       <c r="D13" t="n">
-        <v>0.351239669421488</v>
+        <v>0.0696864111498259</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.195128194189668</v>
+        <v>-0.120050035739814</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45248</v>
+        <v>45283</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0370994940978078</v>
+        <v>0.0928961748633881</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.129429892141757</v>
+        <v>-0.075780089153046</v>
       </c>
       <c r="D14" t="n">
-        <v>0.263374485596708</v>
+        <v>0.0848056537102473</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.173183179383356</v>
+        <v>-0.104223141674989</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45255</v>
+        <v>45290</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.121794871794872</v>
+        <v>-0.0442477876106194</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0714285714285714</v>
+        <v>-0.0363036303630363</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1699604743083</v>
+        <v>0.105072463768116</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1644795105064</v>
+        <v>-0.103283749649172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45262</v>
+        <v>45297</v>
       </c>
       <c r="B16" t="n">
-        <v>0.143122676579926</v>
+        <v>0.0591497227356748</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.114854517611026</v>
+        <v>-0.148936170212766</v>
       </c>
       <c r="D16" t="n">
-        <v>0.135658914728682</v>
+        <v>0.10989010989011</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.148820047659313</v>
+        <v>-0.0940890125173852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45269</v>
+        <v>45304</v>
       </c>
       <c r="B17" t="n">
-        <v>0.253549695740365</v>
+        <v>0.159509202453988</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0337941628264209</v>
+        <v>-0.0817843866171004</v>
       </c>
       <c r="D17" t="n">
-        <v>0.104089219330855</v>
+        <v>0.141791044776119</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.132452308955837</v>
+        <v>-0.0896678073905078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45276</v>
+        <v>45311</v>
       </c>
       <c r="B18" t="n">
-        <v>0.128913443830571</v>
+        <v>0.203187250996016</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0739130434782609</v>
+        <v>-0.136612021857924</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0696864111498259</v>
+        <v>0.218390804597701</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.120050035739814</v>
+        <v>-0.0779107286905082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45283</v>
+        <v>45318</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0928961748633881</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.075780089153046</v>
+        <v>-0.145794392523364</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0848056537102473</v>
+        <v>0.334661354581673</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.104223141674989</v>
+        <v>-0.0774895508525177</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45290</v>
+        <v>45325</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0442477876106194</v>
+        <v>-0.0858505564387917</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0363036303630363</v>
+        <v>-0.0773930753564155</v>
       </c>
       <c r="D20" t="n">
-        <v>0.105072463768116</v>
+        <v>0.464435146443515</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.103283749649172</v>
+        <v>-0.0851426138782461</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45297</v>
+        <v>45332</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0591497227356748</v>
+        <v>-0.145645645645646</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.148936170212766</v>
+        <v>-0.173598553345389</v>
       </c>
       <c r="D21" t="n">
-        <v>0.10989010989011</v>
+        <v>0.558951965065502</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0940890125173852</v>
+        <v>-0.0977869274318065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45304</v>
+        <v>45339</v>
       </c>
       <c r="B22" t="n">
-        <v>0.159509202453988</v>
+        <v>-0.217134416543575</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0817843866171004</v>
+        <v>-0.207936507936508</v>
       </c>
       <c r="D22" t="n">
-        <v>0.141791044776119</v>
+        <v>0.570815450643777</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0896678073905078</v>
+        <v>-0.101993081864602</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45311</v>
+        <v>45346</v>
       </c>
       <c r="B23" t="n">
-        <v>0.203187250996016</v>
+        <v>-0.212703101920236</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.136612021857924</v>
+        <v>-0.247813411078717</v>
       </c>
       <c r="D23" t="n">
-        <v>0.218390804597701</v>
+        <v>0.508196721311475</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0779107286905082</v>
+        <v>-0.0815340429126542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45318</v>
+        <v>45353</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0.269767441860465</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.145794392523364</v>
+        <v>-0.1996996996997</v>
       </c>
       <c r="D24" t="n">
-        <v>0.334661354581673</v>
+        <v>0.448979591836735</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0774895508525177</v>
+        <v>-0.0735962520103489</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45325</v>
+        <v>45360</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0858505564387917</v>
+        <v>-0.276083467094703</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0773930753564155</v>
+        <v>-0.17921686746988</v>
       </c>
       <c r="D25" t="n">
-        <v>0.464435146443515</v>
+        <v>0.430894308943089</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0851426138782461</v>
+        <v>-0.0595428156748912</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45332</v>
+        <v>45367</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.145645645645646</v>
+        <v>-0.325545171339564</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.173598553345389</v>
+        <v>-0.097053726169844</v>
       </c>
       <c r="D26" t="n">
-        <v>0.558951965065502</v>
+        <v>0.478813559322034</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0977869274318065</v>
+        <v>-0.0646537334470864</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45339</v>
+        <v>45374</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.217134416543575</v>
+        <v>-0.292845257903494</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.207936507936508</v>
+        <v>-0.145299145299145</v>
       </c>
       <c r="D27" t="n">
-        <v>0.570815450643777</v>
+        <v>0.491304347826087</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.101993081864602</v>
+        <v>-0.0767676767676768</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45346</v>
+        <v>45381</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.212703101920236</v>
+        <v>-0.246688741721854</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.247813411078717</v>
+        <v>-0.149825783972125</v>
       </c>
       <c r="D28" t="n">
-        <v>0.508196721311475</v>
+        <v>0.469827586206897</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0815340429126542</v>
+        <v>-0.0682249644043664</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45353</v>
+        <v>45388</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.269767441860465</v>
+        <v>-0.209813874788494</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1996996996997</v>
+        <v>-0.139784946236559</v>
       </c>
       <c r="D29" t="n">
-        <v>0.448979591836735</v>
+        <v>0.44017094017094</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0735962520103489</v>
+        <v>-0.0620666749699008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45360</v>
+        <v>45395</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.276083467094703</v>
+        <v>-0.190972222222222</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.17921686746988</v>
+        <v>-0.0907407407407408</v>
       </c>
       <c r="D30" t="n">
-        <v>0.430894308943089</v>
+        <v>0.376569037656904</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0595428156748912</v>
+        <v>-0.0505816233172134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45367</v>
+        <v>45402</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.325545171339564</v>
+        <v>-0.191596638655462</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.097053726169844</v>
+        <v>0.013671875</v>
       </c>
       <c r="D31" t="n">
-        <v>0.478813559322034</v>
+        <v>0.292</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0646537334470864</v>
+        <v>-0.0369740170154058</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45374</v>
+        <v>45409</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.292845257903494</v>
+        <v>-0.298555377207063</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.145299145299145</v>
+        <v>-0.019193857965451</v>
       </c>
       <c r="D32" t="n">
-        <v>0.491304347826087</v>
+        <v>0.218867924528302</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0767676767676768</v>
+        <v>-0.040047619047619</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45381</v>
+        <v>45416</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.246688741721854</v>
+        <v>-0.244827586206897</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.149825783972125</v>
+        <v>0.0798319327731092</v>
       </c>
       <c r="D33" t="n">
-        <v>0.469827586206897</v>
+        <v>0.172161172161172</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0682249644043664</v>
+        <v>-0.0232465528398627</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45388</v>
+        <v>45423</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.209813874788494</v>
+        <v>-0.206429780033841</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.139784946236559</v>
+        <v>0.0222672064777327</v>
       </c>
       <c r="D34" t="n">
-        <v>0.44017094017094</v>
+        <v>0.0954063604240283</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0620666749699008</v>
+        <v>-0.00595642405559327</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45395</v>
+        <v>45430</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.190972222222222</v>
+        <v>-0.287758346581876</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0907407407407408</v>
+        <v>0.0124740124740124</v>
       </c>
       <c r="D35" t="n">
-        <v>0.376569037656904</v>
+        <v>0.0602836879432624</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0505816233172134</v>
+        <v>0.00615251767499592</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45402</v>
+        <v>45437</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.191596638655462</v>
+        <v>-0.234811165845649</v>
       </c>
       <c r="C36" t="n">
-        <v>0.013671875</v>
+        <v>0.0668103448275863</v>
       </c>
       <c r="D36" t="n">
-        <v>0.292</v>
+        <v>0.0394265232974911</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0369740170154058</v>
+        <v>0.0251808647860468</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45409</v>
+        <v>45444</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.298555377207063</v>
+        <v>-0.282051282051282</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.019193857965451</v>
+        <v>0.08207343412527</v>
       </c>
       <c r="D37" t="n">
-        <v>0.218867924528302</v>
+        <v>0.01067615658363</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.040047619047619</v>
+        <v>0.0246913580246915</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45416</v>
+        <v>45451</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.244827586206897</v>
+        <v>-0.371794871794872</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0798319327731092</v>
+        <v>0.139484978540773</v>
       </c>
       <c r="D38" t="n">
-        <v>0.172161172161172</v>
+        <v>0.0140845070422535</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0232465528398627</v>
+        <v>0.00573571586146038</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45423</v>
+        <v>45458</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.206429780033841</v>
+        <v>-0.338805970149254</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0222672064777327</v>
+        <v>0.177489177489178</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0954063604240283</v>
+        <v>0.0428571428571429</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.00595642405559327</v>
+        <v>-0.0123483653375401</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45430</v>
+        <v>45465</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.287758346581876</v>
+        <v>-0.356374807987711</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0124740124740124</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0602836879432624</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00615251767499592</v>
+        <v>-0.0331189197809793</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45437</v>
+        <v>45472</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.234811165845649</v>
+        <v>-0.40785498489426</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0668103448275863</v>
+        <v>-0.0256410256410257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0394265232974911</v>
+        <v>0.113138686131387</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0251808647860468</v>
+        <v>-0.0435584114610765</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45444</v>
+        <v>45479</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.282051282051282</v>
+        <v>-0.371980676328502</v>
       </c>
       <c r="C42" t="n">
-        <v>0.08207343412527</v>
+        <v>-0.0325670498084292</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01067615658363</v>
+        <v>0.12589928057554</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0246913580246915</v>
+        <v>-0.0391333997796779</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45451</v>
+        <v>45486</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.371794871794872</v>
+        <v>-0.336012861736334</v>
       </c>
       <c r="C43" t="n">
-        <v>0.139484978540773</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0140845070422535</v>
+        <v>0.0962199312714778</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00573571586146038</v>
+        <v>-0.0443383001920981</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45458</v>
+        <v>45493</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.338805970149254</v>
+        <v>-0.335394126738794</v>
       </c>
       <c r="C44" t="n">
-        <v>0.177489177489178</v>
+        <v>0.184381778741866</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0428571428571429</v>
+        <v>0.105960264900662</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0123483653375401</v>
+        <v>-0.0347154262168426</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45465</v>
+        <v>45500</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.356374807987711</v>
+        <v>-0.258943781942078</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.247727272727273</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.122257053291536</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0331189197809793</v>
+        <v>-0.0383329957464047</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45472</v>
+        <v>45507</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.40785498489426</v>
+        <v>-0.163339382940109</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0256410256410257</v>
+        <v>0.16331096196868</v>
       </c>
       <c r="D46" t="n">
-        <v>0.113138686131387</v>
+        <v>0.13677811550152</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0435584114610765</v>
+        <v>-0.0511188563923827</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45479</v>
+        <v>45514</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.371980676328502</v>
+        <v>-0.0371819960861057</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0325670498084292</v>
+        <v>0.0455486542443064</v>
       </c>
       <c r="D47" t="n">
-        <v>0.12589928057554</v>
+        <v>0.16566265060241</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0391333997796779</v>
+        <v>-0.0510420882233913</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45486</v>
+        <v>45521</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.336012861736334</v>
+        <v>0.0504672897196261</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>-0.129032258064516</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0962199312714778</v>
+        <v>0.143712574850299</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0443383001920981</v>
+        <v>-0.0531380969627981</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45493</v>
+        <v>45528</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.335394126738794</v>
+        <v>0.043557168784029</v>
       </c>
       <c r="C49" t="n">
-        <v>0.184381778741866</v>
+        <v>-0.175298804780876</v>
       </c>
       <c r="D49" t="n">
-        <v>0.105960264900662</v>
+        <v>0.0925373134328358</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0347154262168426</v>
+        <v>-0.0605657060672242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45500</v>
+        <v>45535</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.258943781942078</v>
+        <v>-0.00349650349650354</v>
       </c>
       <c r="C50" t="n">
-        <v>0.247727272727273</v>
+        <v>-0.17979797979798</v>
       </c>
       <c r="D50" t="n">
-        <v>0.122257053291536</v>
+        <v>0.0501474926253687</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0383329957464047</v>
+        <v>-0.0578085991678224</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45507</v>
+        <v>45542</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.163339382940109</v>
+        <v>-0.10327868852459</v>
       </c>
       <c r="C51" t="n">
-        <v>0.16331096196868</v>
+        <v>-0.120689655172414</v>
       </c>
       <c r="D51" t="n">
-        <v>0.13677811550152</v>
+        <v>0.00574712643678166</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0511188563923827</v>
+        <v>-0.0704233409610984</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45514</v>
+        <v>45549</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.0371819960861057</v>
+        <v>-0.185185185185185</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0455486542443064</v>
+        <v>-0.0934182590233545</v>
       </c>
       <c r="D52" t="n">
-        <v>0.16566265060241</v>
+        <v>0.0144092219020173</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0510420882233913</v>
+        <v>-0.0695692774600211</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45521</v>
+        <v>45556</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0504672897196261</v>
+        <v>-0.142140468227425</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.129032258064516</v>
+        <v>-0.122661122661123</v>
       </c>
       <c r="D53" t="n">
-        <v>0.143712574850299</v>
+        <v>0.0705882352941176</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0531380969627981</v>
+        <v>-0.0565451285116557</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45528</v>
+        <v>45563</v>
       </c>
       <c r="B54" t="n">
-        <v>0.043557168784029</v>
+        <v>-0.139767054908486</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.175298804780876</v>
+        <v>-0.112244897959184</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0925373134328358</v>
+        <v>0.113095238095238</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0605657060672242</v>
+        <v>-0.0539782893952045</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45535</v>
+        <v>45570</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.00349650349650354</v>
+        <v>-0.156589147286822</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.17979797979798</v>
+        <v>-0.145593869731801</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0501474926253687</v>
+        <v>0.154761904761905</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0578085991678224</v>
+        <v>-0.0488187078109933</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45542</v>
+        <v>45577</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.10327868852459</v>
+        <v>-0.174698795180723</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.120689655172414</v>
+        <v>-0.146153846153846</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00574712643678166</v>
+        <v>0.144092219020173</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0704233409610984</v>
+        <v>-0.0628585086042065</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45549</v>
+        <v>45584</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.185185185185185</v>
+        <v>-0.217194570135747</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0934182590233545</v>
+        <v>-0.0452674897119342</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0144092219020173</v>
+        <v>0.0988700564971752</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0695692774600211</v>
+        <v>-0.0714919808249985</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45556</v>
+        <v>45591</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.142140468227425</v>
+        <v>-0.224340175953079</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.122661122661123</v>
+        <v>-0.0224032586558045</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0705882352941176</v>
+        <v>0.0657142857142856</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0565451285116557</v>
+        <v>-0.0766657052206519</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45563</v>
+        <v>45598</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.139767054908486</v>
+        <v>-0.190553745928339</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.112244897959184</v>
+        <v>-0.12593984962406</v>
       </c>
       <c r="D59" t="n">
-        <v>0.113095238095238</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0539782893952045</v>
+        <v>-0.0731829573934837</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45570</v>
+        <v>45605</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.156589147286822</v>
+        <v>-0.117543859649123</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.145593869731801</v>
+        <v>-0.147329650092081</v>
       </c>
       <c r="D60" t="n">
-        <v>0.154761904761905</v>
+        <v>0.070336391437309</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0488187078109933</v>
+        <v>-0.0725605554672178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45577</v>
+        <v>45612</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.174698795180723</v>
+        <v>-0.106830122591944</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.146153846153846</v>
+        <v>-0.155752212389381</v>
       </c>
       <c r="D61" t="n">
-        <v>0.144092219020173</v>
+        <v>0.133550488599349</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0628585086042065</v>
+        <v>-0.0571341121256951</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45584</v>
+        <v>45619</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.217194570135747</v>
+        <v>-0.072992700729927</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0452674897119342</v>
+        <v>-0.194871794871795</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0988700564971752</v>
+        <v>0.192567567567568</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0714919808249985</v>
+        <v>-0.0692811717093852</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45591</v>
+        <v>45626</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.224340175953079</v>
+        <v>-0.15609756097561</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0224032586558045</v>
+        <v>-0.140138408304498</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0657142857142856</v>
+        <v>0.228668941979522</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0766657052206519</v>
+        <v>-0.0580240223968211</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45598</v>
+        <v>45633</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.190553745928339</v>
+        <v>-0.163430420711974</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.12593984962406</v>
+        <v>-0.201907790143084</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.225589225589226</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0731829573934837</v>
+        <v>-0.0476354404234262</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45605</v>
+        <v>45640</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.117543859649123</v>
+        <v>-0.158238172920065</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.147329650092081</v>
+        <v>-0.214397496087637</v>
       </c>
       <c r="D65" t="n">
-        <v>0.070336391437309</v>
+        <v>0.195439739413681</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0725605554672178</v>
+        <v>-0.0379757117907478</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45612</v>
+        <v>45647</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.106830122591944</v>
+        <v>-0.141666666666667</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.155752212389381</v>
+        <v>-0.204180064308682</v>
       </c>
       <c r="D66" t="n">
-        <v>0.133550488599349</v>
+        <v>0.188925081433225</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0571341121256951</v>
+        <v>-0.0119057099625707</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45619</v>
+        <v>45654</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.072992700729927</v>
+        <v>-0.0666666666666667</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.194871794871795</v>
+        <v>-0.188356164383562</v>
       </c>
       <c r="D67" t="n">
-        <v>0.192567567567568</v>
+        <v>0.186885245901639</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0692811717093852</v>
+        <v>-0.014397496087637</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45626</v>
+        <v>45661</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.15609756097561</v>
+        <v>-0.104712041884817</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.140138408304498</v>
+        <v>-0.0557692307692308</v>
       </c>
       <c r="D68" t="n">
-        <v>0.228668941979522</v>
+        <v>0.221122112211221</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0580240223968211</v>
+        <v>-0.00149689107238815</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45633</v>
+        <v>45668</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.163430420711974</v>
+        <v>-0.0670194003527337</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.201907790143084</v>
+        <v>-0.0101214574898786</v>
       </c>
       <c r="D69" t="n">
-        <v>0.225589225589226</v>
+        <v>0.241830065359477</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0476354404234262</v>
+        <v>0.0183785836339472</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45640</v>
+        <v>45675</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.158238172920065</v>
+        <v>-0.107615894039735</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.214397496087637</v>
+        <v>0.090717299578059</v>
       </c>
       <c r="D70" t="n">
-        <v>0.195439739413681</v>
+        <v>0.216981132075472</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.0379757117907478</v>
+        <v>-0.00513960778595901</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45647</v>
+        <v>45682</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.141666666666667</v>
+        <v>0.0329861111111112</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.204180064308682</v>
+        <v>0.225382932166302</v>
       </c>
       <c r="D71" t="n">
-        <v>0.188925081433225</v>
+        <v>0.170149253731343</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.0119057099625707</v>
+        <v>0.0208198489751887</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45654</v>
+        <v>45689</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.0666666666666667</v>
+        <v>0.227826086956522</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.188356164383562</v>
+        <v>0.260485651214128</v>
       </c>
       <c r="D72" t="n">
-        <v>0.186885245901639</v>
+        <v>0.145714285714286</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.014397496087637</v>
+        <v>0.0257006836811398</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45661</v>
+        <v>45696</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.104712041884817</v>
+        <v>0.608084358523726</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0557692307692308</v>
+        <v>0.24507658643326</v>
       </c>
       <c r="D73" t="n">
-        <v>0.221122112211221</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.00149689107238815</v>
+        <v>0.0301982316029663</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45668</v>
+        <v>45703</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.0670194003527337</v>
+        <v>1.40566037735849</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0101214574898786</v>
+        <v>0.148296593186373</v>
       </c>
       <c r="D74" t="n">
-        <v>0.241830065359477</v>
+        <v>0.218579234972678</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0183785836339472</v>
+        <v>0.0870905022194504</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45675</v>
+        <v>45710</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.107615894039735</v>
+        <v>2.35459662288931</v>
       </c>
       <c r="C75" t="n">
-        <v>0.090717299578059</v>
+        <v>0.265503875968992</v>
       </c>
       <c r="D75" t="n">
-        <v>0.216981132075472</v>
+        <v>0.315217391304348</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.00513960778595901</v>
+        <v>0.118129644617762</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45682</v>
+        <v>45717</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0329861111111112</v>
+        <v>3.80254777070064</v>
       </c>
       <c r="C76" t="n">
-        <v>0.225382932166302</v>
+        <v>0.328330206378987</v>
       </c>
       <c r="D76" t="n">
-        <v>0.170149253731343</v>
+        <v>0.464788732394366</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0208198489751887</v>
+        <v>0.215307393289806</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45689</v>
+        <v>45724</v>
       </c>
       <c r="B77" t="n">
-        <v>0.227826086956522</v>
+        <v>5.11751662971175</v>
       </c>
       <c r="C77" t="n">
-        <v>0.260485651214128</v>
+        <v>0.497247706422018</v>
       </c>
       <c r="D77" t="n">
-        <v>0.145714285714286</v>
+        <v>0.579545454545455</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0257006836811398</v>
+        <v>0.300860372699564</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45696</v>
+        <v>45731</v>
       </c>
       <c r="B78" t="n">
-        <v>0.608084358523726</v>
+        <v>6.05080831408776</v>
       </c>
       <c r="C78" t="n">
-        <v>0.24507658643326</v>
+        <v>0.767754318618042</v>
       </c>
       <c r="D78" t="n">
-        <v>0.176470588235294</v>
+        <v>0.67621776504298</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0301982316029663</v>
+        <v>0.369804885786802</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45703</v>
+        <v>45738</v>
       </c>
       <c r="B79" t="n">
-        <v>1.40566037735849</v>
+        <v>6.48470588235294</v>
       </c>
       <c r="C79" t="n">
-        <v>0.148296593186373</v>
+        <v>0.808</v>
       </c>
       <c r="D79" t="n">
-        <v>0.218579234972678</v>
+        <v>0.720116618075802</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0870905022194504</v>
+        <v>0.405061723297965</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45710</v>
+        <v>45745</v>
       </c>
       <c r="B80" t="n">
-        <v>2.35459662288931</v>
+        <v>6.28791208791209</v>
       </c>
       <c r="C80" t="n">
-        <v>0.265503875968992</v>
+        <v>0.846311475409836</v>
       </c>
       <c r="D80" t="n">
-        <v>0.315217391304348</v>
+        <v>0.69208211143695</v>
       </c>
       <c r="E80" t="n">
-        <v>0.118129644617762</v>
+        <v>0.370813701770024</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45717</v>
+        <v>45752</v>
       </c>
       <c r="B81" t="n">
-        <v>3.80254777070064</v>
+        <v>6.19057815845824</v>
       </c>
       <c r="C81" t="n">
-        <v>0.328330206378987</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>0.464788732394366</v>
+        <v>0.664688427299703</v>
       </c>
       <c r="E81" t="n">
-        <v>0.215307393289806</v>
+        <v>0.335782577903683</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45724</v>
+        <v>45759</v>
       </c>
       <c r="B82" t="n">
-        <v>5.11751662971175</v>
+        <v>6.41630901287554</v>
       </c>
       <c r="C82" t="n">
-        <v>0.497247706422018</v>
+        <v>0.568228105906314</v>
       </c>
       <c r="D82" t="n">
-        <v>0.579545454545455</v>
+        <v>0.674772036474164</v>
       </c>
       <c r="E82" t="n">
-        <v>0.300860372699564</v>
+        <v>0.311123348017621</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45731</v>
+        <v>45766</v>
       </c>
       <c r="B83" t="n">
-        <v>6.05080831408776</v>
+        <v>6.54885654885655</v>
       </c>
       <c r="C83" t="n">
-        <v>0.767754318618042</v>
+        <v>0.441233140655106</v>
       </c>
       <c r="D83" t="n">
-        <v>0.67621776504298</v>
+        <v>0.727554179566563</v>
       </c>
       <c r="E83" t="n">
-        <v>0.369804885786802</v>
+        <v>0.316412778759372</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45738</v>
+        <v>45773</v>
       </c>
       <c r="B84" t="n">
-        <v>6.48470588235294</v>
+        <v>7.8466819221968</v>
       </c>
       <c r="C84" t="n">
-        <v>0.808</v>
+        <v>0.446183953033268</v>
       </c>
       <c r="D84" t="n">
-        <v>0.720116618075802</v>
+        <v>0.761609907120743</v>
       </c>
       <c r="E84" t="n">
-        <v>0.405061723297965</v>
+        <v>0.336623840468277</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45745</v>
+        <v>45780</v>
       </c>
       <c r="B85" t="n">
-        <v>6.28791208791209</v>
+        <v>8.28310502283105</v>
       </c>
       <c r="C85" t="n">
-        <v>0.846311475409836</v>
+        <v>0.482490272373541</v>
       </c>
       <c r="D85" t="n">
-        <v>0.69208211143695</v>
+        <v>0.803125</v>
       </c>
       <c r="E85" t="n">
-        <v>0.370813701770024</v>
+        <v>0.345377637345836</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45752</v>
+        <v>45787</v>
       </c>
       <c r="B86" t="n">
-        <v>6.19057815845824</v>
+        <v>8.08102345415778</v>
       </c>
       <c r="C86" t="n">
-        <v>0.729166666666667</v>
+        <v>0.550495049504951</v>
       </c>
       <c r="D86" t="n">
-        <v>0.664688427299703</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E86" t="n">
-        <v>0.335782577903683</v>
+        <v>0.37377135348226</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45759</v>
+        <v>45794</v>
       </c>
       <c r="B87" t="n">
-        <v>6.41630901287554</v>
+        <v>8.72767857142857</v>
       </c>
       <c r="C87" t="n">
-        <v>0.568228105906314</v>
+        <v>0.765913757700205</v>
       </c>
       <c r="D87" t="n">
-        <v>0.674772036474164</v>
+        <v>0.989966555183946</v>
       </c>
       <c r="E87" t="n">
-        <v>0.311123348017621</v>
+        <v>0.401973931234243</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45766</v>
+        <v>45801</v>
       </c>
       <c r="B88" t="n">
-        <v>6.54885654885655</v>
+        <v>8.27467811158798</v>
       </c>
       <c r="C88" t="n">
-        <v>0.441233140655106</v>
+        <v>0.913131313131313</v>
       </c>
       <c r="D88" t="n">
-        <v>0.727554179566563</v>
+        <v>1.0551724137931</v>
       </c>
       <c r="E88" t="n">
-        <v>0.316412778759372</v>
+        <v>0.416301969365427</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45773</v>
+        <v>45808</v>
       </c>
       <c r="B89" t="n">
-        <v>7.8466819221968</v>
+        <v>8.10084033613445</v>
       </c>
       <c r="C89" t="n">
-        <v>0.446183953033268</v>
+        <v>1.1377245508982</v>
       </c>
       <c r="D89" t="n">
-        <v>0.761609907120743</v>
+        <v>1.12323943661972</v>
       </c>
       <c r="E89" t="n">
-        <v>0.336623840468277</v>
+        <v>0.457501237828024</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45780</v>
+        <v>45815</v>
       </c>
       <c r="B90" t="n">
-        <v>8.28310502283105</v>
+        <v>8.80045351473923</v>
       </c>
       <c r="C90" t="n">
-        <v>0.482490272373541</v>
+        <v>1.25988700564972</v>
       </c>
       <c r="D90" t="n">
-        <v>0.803125</v>
+        <v>1.08680555555556</v>
       </c>
       <c r="E90" t="n">
-        <v>0.345377637345836</v>
+        <v>0.472581706514587</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45787</v>
+        <v>45822</v>
       </c>
       <c r="B91" t="n">
-        <v>8.08102345415778</v>
+        <v>8.76523702031603</v>
       </c>
       <c r="C91" t="n">
-        <v>0.550495049504951</v>
+        <v>1.29779411764706</v>
       </c>
       <c r="D91" t="n">
-        <v>0.919354838709677</v>
+        <v>1.08219178082192</v>
       </c>
       <c r="E91" t="n">
-        <v>0.37377135348226</v>
+        <v>0.500330469266358</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45794</v>
+        <v>45829</v>
       </c>
       <c r="B92" t="n">
-        <v>8.72767857142857</v>
+        <v>9.38663484486874</v>
       </c>
       <c r="C92" t="n">
-        <v>0.765913757700205</v>
+        <v>1.4462962962963</v>
       </c>
       <c r="D92" t="n">
-        <v>0.989966555183946</v>
+        <v>1.05333333333333</v>
       </c>
       <c r="E92" t="n">
-        <v>0.401973931234243</v>
+        <v>0.531999120299098</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45801</v>
+        <v>45836</v>
       </c>
       <c r="B93" t="n">
-        <v>8.27467811158798</v>
+        <v>10.1326530612245</v>
       </c>
       <c r="C93" t="n">
-        <v>0.913131313131313</v>
+        <v>1.56015037593985</v>
       </c>
       <c r="D93" t="n">
-        <v>1.0551724137931</v>
+        <v>1.02295081967213</v>
       </c>
       <c r="E93" t="n">
-        <v>0.416301969365427</v>
+        <v>0.532187895809241</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45808</v>
+        <v>45843</v>
       </c>
       <c r="B94" t="n">
-        <v>8.10084033613445</v>
+        <v>10.474358974359</v>
       </c>
       <c r="C94" t="n">
-        <v>1.1377245508982</v>
+        <v>1.68910891089109</v>
       </c>
       <c r="D94" t="n">
-        <v>1.12323943661972</v>
+        <v>0.993610223642172</v>
       </c>
       <c r="E94" t="n">
-        <v>0.457501237828024</v>
+        <v>0.545613364633946</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45815</v>
+        <v>45850</v>
       </c>
       <c r="B95" t="n">
-        <v>8.80045351473923</v>
+        <v>10.1598062953995</v>
       </c>
       <c r="C95" t="n">
-        <v>1.25988700564972</v>
+        <v>1.78313253012048</v>
       </c>
       <c r="D95" t="n">
-        <v>1.08680555555556</v>
+        <v>0.981191222570533</v>
       </c>
       <c r="E95" t="n">
-        <v>0.472581706514587</v>
+        <v>0.554571630358016</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45822</v>
+        <v>45857</v>
       </c>
       <c r="B96" t="n">
-        <v>8.76523702031603</v>
+        <v>10.5139534883721</v>
       </c>
       <c r="C96" t="n">
-        <v>1.29779411764706</v>
+        <v>1.70695970695971</v>
       </c>
       <c r="D96" t="n">
-        <v>1.08219178082192</v>
+        <v>0.934131736526946</v>
       </c>
       <c r="E96" t="n">
-        <v>0.500330469266358</v>
+        <v>0.574035537057788</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45829</v>
+        <v>45864</v>
       </c>
       <c r="B97" t="n">
-        <v>9.38663484486874</v>
+        <v>11.2735632183908</v>
       </c>
       <c r="C97" t="n">
-        <v>1.4462962962963</v>
+        <v>2.04918032786885</v>
       </c>
       <c r="D97" t="n">
-        <v>1.05333333333333</v>
+        <v>0.88268156424581</v>
       </c>
       <c r="E97" t="n">
-        <v>0.531999120299098</v>
+        <v>0.614290979937865</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45836</v>
+        <v>45871</v>
       </c>
       <c r="B98" t="n">
-        <v>10.1326530612245</v>
+        <v>11.4056399132321</v>
       </c>
       <c r="C98" t="n">
-        <v>1.56015037593985</v>
+        <v>2.67884615384615</v>
       </c>
       <c r="D98" t="n">
-        <v>1.02295081967213</v>
+        <v>0.86096256684492</v>
       </c>
       <c r="E98" t="n">
-        <v>0.532187895809241</v>
+        <v>0.685813148788927</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45843</v>
+        <v>45878</v>
       </c>
       <c r="B99" t="n">
-        <v>10.474358974359</v>
+        <v>11.3678861788618</v>
       </c>
       <c r="C99" t="n">
-        <v>1.68910891089109</v>
+        <v>3.29306930693069</v>
       </c>
       <c r="D99" t="n">
-        <v>0.993610223642172</v>
+        <v>0.850129198966408</v>
       </c>
       <c r="E99" t="n">
-        <v>0.545613364633946</v>
+        <v>0.744069513300283</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45850</v>
+        <v>45885</v>
       </c>
       <c r="B100" t="n">
-        <v>10.1598062953995</v>
+        <v>10.1708185053381</v>
       </c>
       <c r="C100" t="n">
-        <v>1.78313253012048</v>
+        <v>4.50462962962963</v>
       </c>
       <c r="D100" t="n">
-        <v>0.981191222570533</v>
+        <v>0.921465968586388</v>
       </c>
       <c r="E100" t="n">
-        <v>0.554571630358016</v>
+        <v>0.804043715846995</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45857</v>
+        <v>45892</v>
       </c>
       <c r="B101" t="n">
-        <v>10.5139534883721</v>
+        <v>10.0591304347826</v>
       </c>
       <c r="C101" t="n">
-        <v>1.70695970695971</v>
+        <v>4.91304347826087</v>
       </c>
       <c r="D101" t="n">
-        <v>0.934131736526946</v>
+        <v>1.02732240437158</v>
       </c>
       <c r="E101" t="n">
-        <v>0.574035537057788</v>
+        <v>0.87298707189839</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45864</v>
+        <v>45899</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2735632183908</v>
+        <v>10.1368421052632</v>
       </c>
       <c r="C102" t="n">
-        <v>2.04918032786885</v>
+        <v>5.20689655172414</v>
       </c>
       <c r="D102" t="n">
-        <v>0.88268156424581</v>
+        <v>1.09831460674157</v>
       </c>
       <c r="E102" t="n">
-        <v>0.614290979937865</v>
+        <v>0.922981805334746</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45871</v>
+        <v>45906</v>
       </c>
       <c r="B103" t="n">
-        <v>11.4056399132321</v>
+        <v>10.4680073126143</v>
       </c>
       <c r="C103" t="n">
-        <v>2.67884615384615</v>
+        <v>5.42647058823529</v>
       </c>
       <c r="D103" t="n">
-        <v>0.86096256684492</v>
+        <v>1.16857142857143</v>
       </c>
       <c r="E103" t="n">
-        <v>0.685813148788927</v>
+        <v>0.992122592159518</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45878</v>
+        <v>45913</v>
       </c>
       <c r="B104" t="n">
-        <v>11.3678861788618</v>
+        <v>11.8780991735537</v>
       </c>
       <c r="C104" t="n">
-        <v>3.29306930693069</v>
+        <v>5.36533957845433</v>
       </c>
       <c r="D104" t="n">
-        <v>0.850129198966408</v>
+        <v>1.18181818181818</v>
       </c>
       <c r="E104" t="n">
-        <v>0.744069513300283</v>
+        <v>1.03644461171748</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45885</v>
+        <v>45920</v>
       </c>
       <c r="B105" t="n">
-        <v>10.1708185053381</v>
+        <v>11.0818713450292</v>
       </c>
       <c r="C105" t="n">
-        <v>4.50462962962963</v>
+        <v>5.86018957345972</v>
       </c>
       <c r="D105" t="n">
-        <v>0.921465968586388</v>
+        <v>1.13186813186813</v>
       </c>
       <c r="E105" t="n">
-        <v>0.804043715846995</v>
+        <v>1.07254181449569</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45892</v>
+        <v>45927</v>
       </c>
       <c r="B106" t="n">
-        <v>10.0591304347826</v>
+        <v>11.0773694390716</v>
       </c>
       <c r="C106" t="n">
-        <v>4.91304347826087</v>
+        <v>6.11954022988506</v>
       </c>
       <c r="D106" t="n">
-        <v>1.02732240437158</v>
+        <v>1.09090909090909</v>
       </c>
       <c r="E106" t="n">
-        <v>0.87298707189839</v>
+        <v>1.11348590883299</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45899</v>
+        <v>45934</v>
       </c>
       <c r="B107" t="n">
-        <v>10.1368421052632</v>
+        <v>10.8235294117647</v>
       </c>
       <c r="C107" t="n">
-        <v>5.20689655172414</v>
+        <v>6.7780269058296</v>
       </c>
       <c r="D107" t="n">
-        <v>1.09831460674157</v>
+        <v>0.997422680412371</v>
       </c>
       <c r="E107" t="n">
-        <v>0.922981805334746</v>
+        <v>1.23938664301103</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45906</v>
+        <v>45941</v>
       </c>
       <c r="B108" t="n">
-        <v>10.4680073126143</v>
+        <v>11.3193430656934</v>
       </c>
       <c r="C108" t="n">
-        <v>5.42647058823529</v>
+        <v>9.54054054054054</v>
       </c>
       <c r="D108" t="n">
-        <v>1.16857142857143</v>
+        <v>1.13098236775819</v>
       </c>
       <c r="E108" t="n">
-        <v>0.992122592159518</v>
+        <v>1.65130068859985</v>
       </c>
     </row>
   </sheetData>

--- a/output/wp_figures.xlsx
+++ b/output/wp_figures.xlsx
@@ -406,640 +406,629 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>203.475</v>
+        <v>306.295</v>
       </c>
       <c r="C2" t="n">
-        <v>193.999</v>
+        <v>318.906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>201.443</v>
+        <v>352.63</v>
       </c>
       <c r="C3" t="n">
-        <v>199.306</v>
+        <v>291.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>212.741</v>
+        <v>284.6</v>
       </c>
       <c r="C4" t="n">
-        <v>214.161</v>
+        <v>249.947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>230.801</v>
+        <v>228.484</v>
       </c>
       <c r="C5" t="n">
-        <v>217.438</v>
+        <v>263.919</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>214.254</v>
+        <v>241.111</v>
       </c>
       <c r="C6" t="n">
-        <v>240.99</v>
+        <v>234.729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>245.27</v>
+        <v>232.685</v>
       </c>
       <c r="C7" t="n">
-        <v>199.75</v>
+        <v>223.985</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>211.323</v>
+        <v>223.539</v>
       </c>
       <c r="C8" t="n">
-        <v>294.615</v>
+        <v>199.337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>309.775</v>
+        <v>220.856</v>
       </c>
       <c r="C9" t="n">
-        <v>249.09</v>
+        <v>195.604</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>252.349</v>
+        <v>226.019</v>
       </c>
       <c r="C10" t="n">
-        <v>241.04</v>
+        <v>214.425</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>275.638</v>
+        <v>214.007</v>
       </c>
       <c r="C11" t="n">
-        <v>274.84</v>
+        <v>202.723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>283.652</v>
+        <v>207.398</v>
       </c>
       <c r="C12" t="n">
-        <v>269.416</v>
+        <v>191.773</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>306.295</v>
+        <v>199.9</v>
       </c>
       <c r="C13" t="n">
-        <v>318.906</v>
+        <v>193.923</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>352.63</v>
+        <v>200.081</v>
       </c>
       <c r="C14" t="n">
-        <v>291.33</v>
+        <v>197.349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>284.6</v>
+        <v>216.534</v>
       </c>
       <c r="C15" t="n">
-        <v>249.947</v>
+        <v>215.265</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>228.484</v>
+        <v>220.962</v>
       </c>
       <c r="C16" t="n">
-        <v>263.919</v>
+        <v>209.064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>241.111</v>
+        <v>210.816</v>
       </c>
       <c r="C17" t="n">
-        <v>234.729</v>
+        <v>202.619</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>232.685</v>
+        <v>224.021</v>
       </c>
       <c r="C18" t="n">
-        <v>223.985</v>
+        <v>189.634</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>223.539</v>
+        <v>206.71</v>
       </c>
       <c r="C19" t="n">
-        <v>199.337</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>220.856</v>
+        <v>203.579</v>
       </c>
       <c r="C20" t="n">
-        <v>195.604</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>226.019</v>
+        <v>200.637</v>
       </c>
       <c r="C21" t="n">
-        <v>214.425</v>
+        <v>192.717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>214.007</v>
+        <v>210.16</v>
       </c>
       <c r="C22" t="n">
-        <v>202.723</v>
+        <v>197.164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>207.398</v>
+        <v>207.512</v>
       </c>
       <c r="C23" t="n">
-        <v>191.773</v>
+        <v>196.177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>199.9</v>
+        <v>243.98</v>
       </c>
       <c r="C24" t="n">
-        <v>193.923</v>
+        <v>236.046</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>200.081</v>
+        <v>234.859</v>
       </c>
       <c r="C25" t="n">
-        <v>197.349</v>
+        <v>227.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>216.534</v>
+        <v>227.516</v>
       </c>
       <c r="C26" t="n">
-        <v>215.265</v>
+        <v>225.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>220.962</v>
+        <v>230.392</v>
       </c>
       <c r="C27" t="n">
-        <v>209.064</v>
+        <v>239.403</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>210.816</v>
+        <v>241.361</v>
       </c>
       <c r="C28" t="n">
-        <v>202.619</v>
+        <v>242.201</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>224.021</v>
+        <v>261.111</v>
       </c>
       <c r="C29" t="n">
-        <v>189.634</v>
+        <v>280.569</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>206.71</v>
+        <v>216.023</v>
       </c>
       <c r="C30" t="n">
-        <v>210.05</v>
+        <v>225.855</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>203.579</v>
+        <v>193.79</v>
       </c>
       <c r="C31" t="n">
-        <v>197.68</v>
+        <v>216.673</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>200.637</v>
+        <v>195.492</v>
       </c>
       <c r="C32" t="n">
-        <v>192.717</v>
+        <v>204.066</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>210.16</v>
+        <v>199.39</v>
       </c>
       <c r="C33" t="n">
-        <v>197.164</v>
+        <v>200.837</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>207.512</v>
+        <v>194.217</v>
       </c>
       <c r="C34" t="n">
-        <v>196.177</v>
+        <v>192.455</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>243.98</v>
+        <v>191.208</v>
       </c>
       <c r="C35" t="n">
-        <v>236.046</v>
+        <v>192.739</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>234.859</v>
+        <v>196.712</v>
       </c>
       <c r="C36" t="n">
-        <v>227.98</v>
+        <v>190.623</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>227.516</v>
+        <v>204.862</v>
       </c>
       <c r="C37" t="n">
-        <v>225.13</v>
+        <v>178.682</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>230.392</v>
+        <v>195.433</v>
       </c>
       <c r="C38" t="n">
-        <v>239.403</v>
+        <v>186.832</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>241.361</v>
+        <v>180.992</v>
       </c>
       <c r="C39" t="n">
-        <v>242.201</v>
+        <v>181.701</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>261.111</v>
+        <v>179.162</v>
       </c>
       <c r="C40" t="n">
-        <v>280.569</v>
+        <v>181.204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>216.023</v>
+        <v>207.124</v>
       </c>
       <c r="C41" t="n">
-        <v>225.855</v>
+        <v>236.171</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>193.79</v>
+        <v>210.777</v>
       </c>
       <c r="C42" t="n">
-        <v>216.673</v>
+        <v>225.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>195.492</v>
+        <v>205.653</v>
       </c>
       <c r="C43" t="n">
-        <v>204.066</v>
+        <v>203.475</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>199.39</v>
+        <v>203.012</v>
       </c>
       <c r="C44" t="n">
-        <v>200.837</v>
+        <v>201.443</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>194.217</v>
+        <v>216.026</v>
       </c>
       <c r="C45" t="n">
-        <v>192.455</v>
+        <v>212.741</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>191.208</v>
+        <v>238.729</v>
       </c>
       <c r="C46" t="n">
-        <v>192.739</v>
+        <v>230.801</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>196.712</v>
+        <v>218.228</v>
       </c>
       <c r="C47" t="n">
-        <v>190.623</v>
+        <v>214.254</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>204.862</v>
+        <v>244.713</v>
       </c>
       <c r="C48" t="n">
-        <v>178.682</v>
+        <v>245.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>195.433</v>
+        <v>198.173</v>
       </c>
       <c r="C49" t="n">
-        <v>186.832</v>
+        <v>211.323</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>180.992</v>
+        <v>314.915</v>
       </c>
       <c r="C50" t="n">
-        <v>181.701</v>
+        <v>309.775</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>179.191</v>
+        <v>255.177</v>
       </c>
       <c r="C51" t="n">
-        <v>181.204</v>
+        <v>252.349</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>207.132</v>
+        <v>264.566</v>
       </c>
       <c r="C52" t="n">
-        <v>236.171</v>
+        <v>275.638</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>210.799</v>
+        <v>271.346</v>
       </c>
       <c r="C53" t="n">
-        <v>225.23</v>
+        <v>283.652</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>205.696</v>
+        <v>298.7</v>
       </c>
       <c r="C54" t="n">
-        <v>203.475</v>
+        <v>306.295</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>203.056</v>
+        <v>330.963</v>
       </c>
       <c r="C55" t="n">
-        <v>201.443</v>
+        <v>352.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>216.081</v>
+        <v>272.436</v>
       </c>
       <c r="C56" t="n">
-        <v>212.741</v>
+        <v>284.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45969</v>
+        <v>46046</v>
       </c>
       <c r="B57" t="n">
-        <v>238.766</v>
+        <v>231.633</v>
       </c>
       <c r="C57" t="n">
-        <v>230.801</v>
+        <v>228.484</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45976</v>
+        <v>46053</v>
       </c>
       <c r="B58" t="n">
-        <v>212.399</v>
+        <v>251.651</v>
       </c>
       <c r="C58" t="n">
-        <v>214.254</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B59" t="n">
-        <v>216.671</v>
-      </c>
-      <c r="C59" t="n">
-        <v>245.27</v>
+        <v>241.111</v>
       </c>
     </row>
   </sheetData>
@@ -1066,629 +1055,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>1616.144</v>
+        <v>2273.651</v>
       </c>
       <c r="C2" t="n">
-        <v>1574.471</v>
+        <v>2122.561</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>1646.982</v>
+        <v>2246.551</v>
       </c>
       <c r="C3" t="n">
-        <v>1607.693</v>
+        <v>2053.289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>1647.301</v>
+        <v>2170.633</v>
       </c>
       <c r="C4" t="n">
-        <v>1578.946</v>
+        <v>2181.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>1660.894</v>
+        <v>2250.894</v>
       </c>
       <c r="C5" t="n">
-        <v>1654.732</v>
+        <v>2130.018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>1721.154</v>
+        <v>2185.828</v>
       </c>
       <c r="C6" t="n">
-        <v>1555.596</v>
+        <v>2139.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>1661.071</v>
+        <v>2191.042</v>
       </c>
       <c r="C7" t="n">
-        <v>1845.084</v>
+        <v>2092.787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>1933.23</v>
+        <v>2160.103</v>
       </c>
       <c r="C8" t="n">
-        <v>1767.267</v>
+        <v>2092.108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>1864.863</v>
+        <v>2229.07</v>
       </c>
       <c r="C9" t="n">
-        <v>1835.427</v>
+        <v>2113.581</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>1946.787</v>
+        <v>2149.919</v>
       </c>
       <c r="C10" t="n">
-        <v>1836.539</v>
+        <v>2078.603</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>1860.888</v>
+        <v>2116.538</v>
       </c>
       <c r="C11" t="n">
-        <v>1902.054</v>
+        <v>2008.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>2187.475</v>
+        <v>2072.402</v>
       </c>
       <c r="C12" t="n">
-        <v>2104.257</v>
+        <v>2012.613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>2273.651</v>
+        <v>2058.751</v>
       </c>
       <c r="C13" t="n">
-        <v>2122.561</v>
+        <v>1937.982</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>2246.551</v>
+        <v>1985.73</v>
       </c>
       <c r="C14" t="n">
-        <v>2053.289</v>
+        <v>1928.017</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>2170.633</v>
+        <v>1943.418</v>
       </c>
       <c r="C15" t="n">
-        <v>2181.43</v>
+        <v>1848.827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>2250.894</v>
+        <v>1880.372</v>
       </c>
       <c r="C16" t="n">
-        <v>2130.018</v>
+        <v>1812.811</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>2185.828</v>
+        <v>1898.153</v>
       </c>
       <c r="C17" t="n">
-        <v>2139.97</v>
+        <v>1753.465</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>2191.042</v>
+        <v>1838.279</v>
       </c>
       <c r="C18" t="n">
-        <v>2092.787</v>
+        <v>1743.445</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>2160.103</v>
+        <v>1782.724</v>
       </c>
       <c r="C19" t="n">
-        <v>2092.108</v>
+        <v>1686.177</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>2229.07</v>
+        <v>1779.686</v>
       </c>
       <c r="C20" t="n">
-        <v>2113.581</v>
+        <v>1686.782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>2149.919</v>
+        <v>1775.51</v>
       </c>
       <c r="C21" t="n">
-        <v>2078.603</v>
+        <v>1666.648</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>2116.538</v>
+        <v>1755.336</v>
       </c>
       <c r="C22" t="n">
-        <v>2008.79</v>
+        <v>1670.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>2072.402</v>
+        <v>1826.063</v>
       </c>
       <c r="C23" t="n">
-        <v>2012.613</v>
+        <v>1708.158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>2058.751</v>
+        <v>1813.454</v>
       </c>
       <c r="C24" t="n">
-        <v>1937.982</v>
+        <v>1727.754</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>1985.73</v>
+        <v>1862.043</v>
       </c>
       <c r="C25" t="n">
-        <v>1928.017</v>
+        <v>1748.567</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>1943.418</v>
+        <v>1900.787</v>
       </c>
       <c r="C26" t="n">
-        <v>1848.827</v>
+        <v>1821.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>1880.372</v>
+        <v>1895.589</v>
       </c>
       <c r="C27" t="n">
-        <v>1812.811</v>
+        <v>1795.365</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>1898.153</v>
+        <v>2011.507</v>
       </c>
       <c r="C28" t="n">
-        <v>1753.465</v>
+        <v>1945.731</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>1838.279</v>
+        <v>2006.612</v>
       </c>
       <c r="C29" t="n">
-        <v>1743.445</v>
+        <v>1914.075</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>1782.724</v>
+        <v>2005.922</v>
       </c>
       <c r="C30" t="n">
-        <v>1686.177</v>
+        <v>1934.382</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>1779.686</v>
+        <v>1999.973</v>
       </c>
       <c r="C31" t="n">
-        <v>1686.782</v>
+        <v>1907.041</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>1775.51</v>
+        <v>1973.535</v>
       </c>
       <c r="C32" t="n">
-        <v>1666.648</v>
+        <v>1883.372</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>1755.336</v>
+        <v>1955.067</v>
       </c>
       <c r="C33" t="n">
-        <v>1670.55</v>
+        <v>1857.167</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>1826.063</v>
+        <v>1934.367</v>
       </c>
       <c r="C34" t="n">
-        <v>1708.158</v>
+        <v>1843.217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>1813.454</v>
+        <v>1892.212</v>
       </c>
       <c r="C35" t="n">
-        <v>1727.754</v>
+        <v>1800.515</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>1862.043</v>
+        <v>1803.347</v>
       </c>
       <c r="C36" t="n">
-        <v>1748.567</v>
+        <v>1704.638</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>1900.787</v>
+        <v>1759.884</v>
       </c>
       <c r="C37" t="n">
-        <v>1821.4</v>
+        <v>1671.837</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>1895.589</v>
+        <v>1718.818</v>
       </c>
       <c r="C38" t="n">
-        <v>1795.365</v>
+        <v>1628.081</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>2011.507</v>
+        <v>1696.023</v>
       </c>
       <c r="C39" t="n">
-        <v>1945.731</v>
+        <v>1613.719</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>2006.612</v>
+        <v>1683.703</v>
       </c>
       <c r="C40" t="n">
-        <v>1914.075</v>
+        <v>1614.385</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>2005.922</v>
+        <v>1651.988</v>
       </c>
       <c r="C41" t="n">
-        <v>1934.382</v>
+        <v>1598.241</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>1999.973</v>
+        <v>1674.202</v>
       </c>
       <c r="C42" t="n">
-        <v>1907.041</v>
+        <v>1627.825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>1973.535</v>
+        <v>1708.691</v>
       </c>
       <c r="C43" t="n">
-        <v>1883.372</v>
+        <v>1616.144</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>1955.067</v>
+        <v>1712.402</v>
       </c>
       <c r="C44" t="n">
-        <v>1857.167</v>
+        <v>1646.982</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>1934.367</v>
+        <v>1720.202</v>
       </c>
       <c r="C45" t="n">
-        <v>1843.217</v>
+        <v>1647.301</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>1892.212</v>
+        <v>1708.938</v>
       </c>
       <c r="C46" t="n">
-        <v>1800.515</v>
+        <v>1660.894</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>1803.347</v>
+        <v>1781.543</v>
       </c>
       <c r="C47" t="n">
-        <v>1704.638</v>
+        <v>1721.154</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>1759.884</v>
+        <v>1696.513</v>
       </c>
       <c r="C48" t="n">
-        <v>1671.837</v>
+        <v>1661.071</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>1718.818</v>
+        <v>1956.626</v>
       </c>
       <c r="C49" t="n">
-        <v>1628.081</v>
+        <v>1933.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>1695.993</v>
+        <v>1870.127</v>
       </c>
       <c r="C50" t="n">
-        <v>1613.719</v>
+        <v>1864.863</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>1683.585</v>
+        <v>1984.259</v>
       </c>
       <c r="C51" t="n">
-        <v>1614.385</v>
+        <v>1946.787</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>1651.89</v>
+        <v>1871.131</v>
       </c>
       <c r="C52" t="n">
-        <v>1598.241</v>
+        <v>1860.888</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>1674.17</v>
+        <v>2183.177</v>
       </c>
       <c r="C53" t="n">
-        <v>1627.825</v>
+        <v>2187.475</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>1708.565</v>
+        <v>2299.237</v>
       </c>
       <c r="C54" t="n">
-        <v>1616.144</v>
+        <v>2273.651</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>1712.36</v>
+        <v>2228.751</v>
       </c>
       <c r="C55" t="n">
-        <v>1646.982</v>
+        <v>2246.551</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>1720.188</v>
+        <v>2136.751</v>
       </c>
       <c r="C56" t="n">
-        <v>1647.301</v>
+        <v>2170.633</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45969</v>
+        <v>46046</v>
       </c>
       <c r="B57" t="n">
-        <v>1640.621</v>
+        <v>2214.483</v>
       </c>
       <c r="C57" t="n">
-        <v>1660.894</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B58" t="n">
-        <v>1727.145</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1721.154</v>
+        <v>2250.894</v>
       </c>
     </row>
   </sheetData>
@@ -1715,629 +1693,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>392</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>460</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>533</v>
+        <v>597</v>
       </c>
       <c r="C3" t="n">
-        <v>628</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C4" t="n">
-        <v>519</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>622</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>655</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>529</v>
+        <v>599</v>
       </c>
       <c r="C6" t="n">
-        <v>662</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>760</v>
+        <v>613</v>
       </c>
       <c r="C7" t="n">
-        <v>511</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>399</v>
+        <v>613</v>
       </c>
       <c r="C8" t="n">
-        <v>729</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>759</v>
+        <v>1634</v>
       </c>
       <c r="C9" t="n">
-        <v>747</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>549</v>
+        <v>1580</v>
       </c>
       <c r="C10" t="n">
-        <v>514</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>507</v>
+        <v>1066</v>
       </c>
       <c r="C11" t="n">
-        <v>580</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>343</v>
+        <v>821</v>
       </c>
       <c r="C12" t="n">
-        <v>415</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>479</v>
+        <v>564</v>
       </c>
       <c r="C13" t="n">
-        <v>643</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>597</v>
+        <v>508</v>
       </c>
       <c r="C14" t="n">
-        <v>762</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="C15" t="n">
-        <v>420</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>497</v>
+        <v>657</v>
       </c>
       <c r="C16" t="n">
-        <v>502</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>599</v>
+        <v>466</v>
       </c>
       <c r="C17" t="n">
-        <v>411</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>613</v>
+        <v>465</v>
       </c>
       <c r="C18" t="n">
-        <v>382</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>613</v>
+        <v>434</v>
       </c>
       <c r="C19" t="n">
-        <v>337</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>1634</v>
+        <v>599</v>
       </c>
       <c r="C20" t="n">
-        <v>330</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>1580</v>
+        <v>592</v>
       </c>
       <c r="C21" t="n">
-        <v>393</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>1066</v>
+        <v>523</v>
       </c>
       <c r="C22" t="n">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>821</v>
+        <v>553</v>
       </c>
       <c r="C23" t="n">
-        <v>362</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>564</v>
+        <v>532</v>
       </c>
       <c r="C24" t="n">
-        <v>371</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="C25" t="n">
-        <v>322</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>542</v>
+        <v>453</v>
       </c>
       <c r="C26" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>657</v>
+        <v>438</v>
       </c>
       <c r="C27" t="n">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>466</v>
+        <v>596</v>
       </c>
       <c r="C28" t="n">
-        <v>365</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>465</v>
+        <v>789</v>
       </c>
       <c r="C29" t="n">
-        <v>343</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>434</v>
+        <v>722</v>
       </c>
       <c r="C30" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>599</v>
+        <v>708</v>
       </c>
       <c r="C31" t="n">
-        <v>386</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="C32" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>523</v>
+        <v>635</v>
       </c>
       <c r="C33" t="n">
-        <v>353</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>553</v>
+        <v>588</v>
       </c>
       <c r="C34" t="n">
-        <v>400</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C35" t="n">
-        <v>419</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="C36" t="n">
-        <v>344</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C37" t="n">
-        <v>336</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>438</v>
+        <v>635</v>
       </c>
       <c r="C38" t="n">
-        <v>372</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>596</v>
+        <v>530</v>
       </c>
       <c r="C39" t="n">
-        <v>327</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>789</v>
+        <v>588</v>
       </c>
       <c r="C40" t="n">
-        <v>476</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>722</v>
+        <v>3272</v>
       </c>
       <c r="C41" t="n">
-        <v>392</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>708</v>
+        <v>7291</v>
       </c>
       <c r="C42" t="n">
-        <v>314</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>637</v>
+        <v>10064</v>
       </c>
       <c r="C43" t="n">
-        <v>334</v>
+        <v>392</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>635</v>
+        <v>9436</v>
       </c>
       <c r="C44" t="n">
-        <v>336</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>588</v>
+        <v>7483</v>
       </c>
       <c r="C45" t="n">
-        <v>285</v>
+        <v>507</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>515</v>
+        <v>5721</v>
       </c>
       <c r="C46" t="n">
-        <v>307</v>
+        <v>622</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>527</v>
+        <v>1724</v>
       </c>
       <c r="C47" t="n">
-        <v>274</v>
+        <v>529</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>572</v>
+        <v>1126</v>
       </c>
       <c r="C48" t="n">
-        <v>266</v>
+        <v>760</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C49" t="n">
-        <v>313</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>530</v>
+        <v>1091</v>
       </c>
       <c r="C50" t="n">
-        <v>278</v>
+        <v>759</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>588</v>
+        <v>805</v>
       </c>
       <c r="C51" t="n">
-        <v>313</v>
+        <v>549</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>3272</v>
+        <v>817</v>
       </c>
       <c r="C52" t="n">
-        <v>351</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>7287</v>
+        <v>476</v>
       </c>
       <c r="C53" t="n">
-        <v>434</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>10062</v>
+        <v>646</v>
       </c>
       <c r="C54" t="n">
-        <v>392</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>9435</v>
+        <v>1010</v>
       </c>
       <c r="C55" t="n">
-        <v>533</v>
+        <v>597</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>7482</v>
+        <v>798</v>
       </c>
       <c r="C56" t="n">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45969</v>
+        <v>46046</v>
       </c>
       <c r="B57" t="n">
-        <v>5719</v>
+        <v>568</v>
       </c>
       <c r="C57" t="n">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B58" t="n">
-        <v>1716</v>
-      </c>
-      <c r="C58" t="n">
-        <v>529</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -2364,618 +2331,607 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>4038</v>
+        <v>6854</v>
       </c>
       <c r="C2" t="n">
-        <v>4309</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>4246</v>
+        <v>7381</v>
       </c>
       <c r="C3" t="n">
-        <v>4638</v>
+        <v>6708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>4454</v>
+        <v>6684</v>
       </c>
       <c r="C4" t="n">
-        <v>4741</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>4760</v>
+        <v>7470</v>
       </c>
       <c r="C5" t="n">
-        <v>5179</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>5023</v>
+        <v>7120</v>
       </c>
       <c r="C6" t="n">
-        <v>5045</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>5081</v>
+        <v>7621</v>
       </c>
       <c r="C7" t="n">
-        <v>5791</v>
+        <v>6819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>5997</v>
+        <v>7422</v>
       </c>
       <c r="C8" t="n">
-        <v>6131</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>6031</v>
+        <v>8230</v>
       </c>
       <c r="C9" t="n">
-        <v>6272</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>6577</v>
+        <v>8929</v>
       </c>
       <c r="C10" t="n">
-        <v>6427</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>6210</v>
+        <v>9136</v>
       </c>
       <c r="C11" t="n">
-        <v>6284</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>6374</v>
+        <v>8246</v>
       </c>
       <c r="C12" t="n">
-        <v>6577</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>6854</v>
+        <v>7721</v>
       </c>
       <c r="C13" t="n">
-        <v>6766</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>7381</v>
+        <v>7192</v>
       </c>
       <c r="C14" t="n">
-        <v>6708</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>6684</v>
+        <v>7019</v>
       </c>
       <c r="C15" t="n">
-        <v>7383</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>7470</v>
+        <v>6640</v>
       </c>
       <c r="C16" t="n">
-        <v>6953</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>7120</v>
+        <v>6716</v>
       </c>
       <c r="C17" t="n">
-        <v>6893</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>7621</v>
+        <v>6570</v>
       </c>
       <c r="C18" t="n">
-        <v>6819</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>7422</v>
+        <v>6473</v>
       </c>
       <c r="C19" t="n">
-        <v>6594</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>8230</v>
+        <v>6377</v>
       </c>
       <c r="C20" t="n">
-        <v>6876</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>8929</v>
+        <v>6717</v>
       </c>
       <c r="C21" t="n">
-        <v>6208</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>9136</v>
+        <v>6323</v>
       </c>
       <c r="C22" t="n">
-        <v>6241</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>8246</v>
+        <v>7076</v>
       </c>
       <c r="C23" t="n">
-        <v>5891</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>7721</v>
+        <v>6738</v>
       </c>
       <c r="C24" t="n">
-        <v>5881</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>7192</v>
+        <v>7103</v>
       </c>
       <c r="C25" t="n">
-        <v>5546</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>7019</v>
+        <v>6947</v>
       </c>
       <c r="C26" t="n">
-        <v>5274</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>6640</v>
+        <v>7035</v>
       </c>
       <c r="C27" t="n">
-        <v>5091</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>6716</v>
+        <v>7226</v>
       </c>
       <c r="C28" t="n">
-        <v>5030</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>6570</v>
+        <v>7407</v>
       </c>
       <c r="C29" t="n">
-        <v>4764</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>6473</v>
+        <v>7831</v>
       </c>
       <c r="C30" t="n">
-        <v>4737</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>6377</v>
+        <v>8193</v>
       </c>
       <c r="C31" t="n">
-        <v>4494</v>
+        <v>4855</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>6717</v>
+        <v>8237</v>
       </c>
       <c r="C32" t="n">
-        <v>4648</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>6323</v>
+        <v>8456</v>
       </c>
       <c r="C33" t="n">
-        <v>4401</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>7076</v>
+        <v>8128</v>
       </c>
       <c r="C34" t="n">
-        <v>4634</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>6738</v>
+        <v>8211</v>
       </c>
       <c r="C35" t="n">
-        <v>4553</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>7103</v>
+        <v>7863</v>
       </c>
       <c r="C36" t="n">
-        <v>4568</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>6947</v>
+        <v>8168</v>
       </c>
       <c r="C37" t="n">
-        <v>4433</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>7035</v>
+        <v>8223</v>
       </c>
       <c r="C38" t="n">
-        <v>4605</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>7226</v>
+        <v>8469</v>
       </c>
       <c r="C39" t="n">
-        <v>4711</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>7407</v>
+        <v>8678</v>
       </c>
       <c r="C40" t="n">
-        <v>4658</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>7831</v>
+        <v>9996</v>
       </c>
       <c r="C41" t="n">
-        <v>4767</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>8193</v>
+        <v>14464</v>
       </c>
       <c r="C42" t="n">
-        <v>4855</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>8237</v>
+        <v>23194</v>
       </c>
       <c r="C43" t="n">
-        <v>4505</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>8456</v>
+        <v>30651</v>
       </c>
       <c r="C44" t="n">
-        <v>4632</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>8128</v>
+        <v>38873</v>
       </c>
       <c r="C45" t="n">
-        <v>4308</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>8211</v>
+        <v>33085</v>
       </c>
       <c r="C46" t="n">
-        <v>4191</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>7863</v>
+        <v>17862</v>
       </c>
       <c r="C47" t="n">
-        <v>3852</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>8168</v>
+        <v>12732</v>
       </c>
       <c r="C48" t="n">
-        <v>3898</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>8223</v>
+        <v>14077</v>
       </c>
       <c r="C49" t="n">
-        <v>4001</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>8463</v>
+        <v>12887</v>
       </c>
       <c r="C50" t="n">
-        <v>4033</v>
+        <v>6031</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>8676</v>
+        <v>13386</v>
       </c>
       <c r="C51" t="n">
-        <v>3929</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>9992</v>
+        <v>12129</v>
       </c>
       <c r="C52" t="n">
-        <v>3819</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>14468</v>
+        <v>12803</v>
       </c>
       <c r="C53" t="n">
-        <v>3903</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>23188</v>
+        <v>12977</v>
       </c>
       <c r="C54" t="n">
-        <v>4038</v>
+        <v>6854</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>30649</v>
+        <v>13360</v>
       </c>
       <c r="C55" t="n">
-        <v>4246</v>
+        <v>7381</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>38867</v>
+        <v>12565</v>
       </c>
       <c r="C56" t="n">
-        <v>4454</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B57" t="n">
-        <v>32573</v>
-      </c>
-      <c r="C57" t="n">
-        <v>4760</v>
+        <v>6684</v>
       </c>
     </row>
   </sheetData>
@@ -3002,618 +2958,618 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>0.14208204675783</v>
+        <v>0.199917389508468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0339323054533622</v>
+        <v>0.0380884300885416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>0.139955734930348</v>
+        <v>0.229751519411254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0304853618716452</v>
+        <v>0.0472251768206466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>0.132738451028947</v>
+        <v>0.223177177904208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0322847316163144</v>
+        <v>0.0492549994167726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>0.131862080650627</v>
+        <v>0.323548512793869</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0242336079972043</v>
+        <v>0.0535424819536205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>0.171802338215481</v>
+        <v>0.396427938308811</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0436713211120208</v>
+        <v>0.0410594979932879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>0.163226448569821</v>
+        <v>0.454256272401434</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00845025245848952</v>
+        <v>0.0297502225192396</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>0.172058254929759</v>
+        <v>0.56764488741233</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0225234105253962</v>
+        <v>0.0393836319201579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>0.175715990453461</v>
+        <v>0.596092346782319</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0252655362972192</v>
+        <v>0.0388219584506435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>0.160316139767055</v>
+        <v>0.713643178410795</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0166980651720676</v>
+        <v>0.0421453587819811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>0.191925988225399</v>
+        <v>0.829688123863183</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0360265168764005</v>
+        <v>0.04371691971694</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>0.204941678163803</v>
+        <v>0.898953478146161</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0236688517489014</v>
+        <v>0.043140956563801</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>0.199917389508468</v>
+        <v>0.914512748864827</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0380884300885416</v>
+        <v>0.0447403006822105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>0.229751519411254</v>
+        <v>0.931867165163844</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0472251768206466</v>
+        <v>0.0438698319167705</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>0.223177177904208</v>
+        <v>0.931175347453488</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0492549994167726</v>
+        <v>0.0430753319437398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>0.323548512793869</v>
+        <v>0.950586187946511</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0535424819536205</v>
+        <v>0.0452511193087552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>0.396427938308811</v>
+        <v>0.962573099415205</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0410594979932879</v>
+        <v>0.049645518526185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.454256272401434</v>
+        <v>0.956761599396454</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0297502225192396</v>
+        <v>0.0561110996252312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>0.56764488741233</v>
+        <v>0.928278977834251</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0393836319201579</v>
+        <v>0.0576952379808855</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>0.596092346782319</v>
+        <v>0.901866121994244</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0388219584506435</v>
+        <v>0.0624426753989049</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>0.713643178410795</v>
+        <v>0.879367262723521</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0421453587819811</v>
+        <v>0.057960192550492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>0.829688123863183</v>
+        <v>0.860871929665549</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04371691971694</v>
+        <v>0.0570924048423904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>0.898953478146161</v>
+        <v>0.834035196595594</v>
       </c>
       <c r="C23" t="n">
-        <v>0.043140956563801</v>
+        <v>0.060078536714488</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>0.914512748864827</v>
+        <v>0.828052718861831</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0447403006822105</v>
+        <v>0.0586514909694367</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>0.931867165163844</v>
+        <v>0.844489902506964</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0438698319167705</v>
+        <v>0.0586236761361623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>0.931175347453488</v>
+        <v>0.82460988987627</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0430753319437398</v>
+        <v>0.0565907575623272</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>0.950586187946511</v>
+        <v>0.823430257058575</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0452511193087552</v>
+        <v>0.0534022849856888</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>0.962573099415205</v>
+        <v>0.801316381178202</v>
       </c>
       <c r="C28" t="n">
-        <v>0.049645518526185</v>
+        <v>0.0490849278689021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>0.956761599396454</v>
+        <v>0.77241596473274</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0561110996252312</v>
+        <v>0.0451977249998696</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>0.928278977834251</v>
+        <v>0.777726182184042</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0576952379808855</v>
+        <v>0.0434909671228332</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>0.901866121994244</v>
+        <v>0.783645072992701</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0624426753989049</v>
+        <v>0.0419134400496337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>0.879367262723521</v>
+        <v>0.788245102125886</v>
       </c>
       <c r="C32" t="n">
-        <v>0.057960192550492</v>
+        <v>0.0454480832898061</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>0.860871929665549</v>
+        <v>0.763553821333433</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0570924048423904</v>
+        <v>0.0464965400776212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>0.834035196595594</v>
+        <v>0.726848249027237</v>
       </c>
       <c r="C34" t="n">
-        <v>0.060078536714488</v>
+        <v>0.0496802943665406</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>0.828052718861831</v>
+        <v>0.677790436987761</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0586514909694367</v>
+        <v>0.0502297383181087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>0.844489902506964</v>
+        <v>0.639268220276087</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0586236761361623</v>
+        <v>0.0526617238937224</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>0.82460988987627</v>
+        <v>0.59488913942127</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0565907575623272</v>
+        <v>0.0526484475457774</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>0.823430257058575</v>
+        <v>0.566833013435701</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0534022849856888</v>
+        <v>0.0542521892864896</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>0.801316381178202</v>
+        <v>0.555817332233871</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0490849278689021</v>
+        <v>0.0543641658891478</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>0.77241596473274</v>
+        <v>0.532291092384028</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0451977249998696</v>
+        <v>0.0506134936432505</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>0.777726182184042</v>
+        <v>0.529032513250534</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0434909671228332</v>
+        <v>0.0458764265017526</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>0.783645072992701</v>
+        <v>0.520197468949575</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0419134400496337</v>
+        <v>0.0390051703007512</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>0.788245102125886</v>
+        <v>0.530338727743231</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0454480832898061</v>
+        <v>0.0405769604567112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>0.763553821333433</v>
+        <v>0.549832495812395</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0464965400776212</v>
+        <v>0.0397724400819086</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>0.726848249027237</v>
+        <v>0.594549771964871</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0496802943665406</v>
+        <v>0.0424035353791807</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>0.677790436987761</v>
+        <v>0.610306500505221</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0502297383181087</v>
+        <v>0.0424438252217476</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>0.639268220276087</v>
+        <v>0.573659224093168</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0526617238937224</v>
+        <v>0.0369595216294698</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>0.59488913942127</v>
+        <v>0.513522562404672</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0526484475457774</v>
+        <v>0.0324009553959244</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>0.566833013435701</v>
+        <v>0.42137673191115</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0542521892864896</v>
+        <v>0.0239768681297337</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>0.555817332233871</v>
+        <v>0.346938775510204</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0543596329859366</v>
+        <v>0.0173378115008276</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>0.532291092384028</v>
+        <v>0.291173729117373</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0505908221510283</v>
+        <v>0.0137151866114156</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>0.529032513250534</v>
+        <v>0.251305390911657</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0458383131203302</v>
+        <v>0.0100417209675605</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>0.520197468949575</v>
+        <v>0.210749106554249</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0389620973727063</v>
+        <v>0.00619350120667739</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>0.530338727743231</v>
+        <v>0.195352839931153</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0405190351880518</v>
+        <v>0.00834498254341831</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>0.549832495812395</v>
+        <v>0.164133942980097</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0397265175695218</v>
+        <v>0.00160248536365204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>0.594549771964871</v>
+        <v>0.146401002836973</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0423708049185012</v>
+        <v>-0.00342339927305968</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45969</v>
+        <v>46046</v>
       </c>
       <c r="B57" t="n">
-        <v>0.610306500505221</v>
+        <v>0.168400392541708</v>
       </c>
       <c r="C57" t="n">
-        <v>0.032019893716956</v>
+        <v>-0.0069904824894601</v>
       </c>
     </row>
   </sheetData>
@@ -3646,937 +3602,937 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45584</v>
+        <v>45661</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.217194570135747</v>
+        <v>-0.104712041884817</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0452674897119342</v>
+        <v>-0.0557692307692308</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0988700564971752</v>
+        <v>0.221122112211221</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0714919808249985</v>
+        <v>-0.00149689107238815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45591</v>
+        <v>45668</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.224340175953079</v>
+        <v>-0.0670194003527337</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0224032586558045</v>
+        <v>-0.0101214574898786</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0657142857142856</v>
+        <v>0.241830065359477</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0766657052206519</v>
+        <v>0.0183785836339472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45598</v>
+        <v>45675</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.190553745928339</v>
+        <v>-0.107615894039735</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.12593984962406</v>
+        <v>0.090717299578059</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.216981132075472</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0731829573934837</v>
+        <v>-0.00513960778595901</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45605</v>
+        <v>45682</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.117543859649123</v>
+        <v>0.0329861111111112</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.147329650092081</v>
+        <v>0.225382932166302</v>
       </c>
       <c r="D5" t="n">
-        <v>0.070336391437309</v>
+        <v>0.170149253731343</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0725605554672178</v>
+        <v>0.0208198489751887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45612</v>
+        <v>45689</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.106830122591944</v>
+        <v>0.227826086956522</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.155752212389381</v>
+        <v>0.260485651214128</v>
       </c>
       <c r="D6" t="n">
-        <v>0.133550488599349</v>
+        <v>0.145714285714286</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0571341121256951</v>
+        <v>0.0257006836811398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45619</v>
+        <v>45696</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.072992700729927</v>
+        <v>0.608084358523726</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.194871794871795</v>
+        <v>0.24507658643326</v>
       </c>
       <c r="D7" t="n">
-        <v>0.192567567567568</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0692811717093852</v>
+        <v>0.0301982316029663</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45626</v>
+        <v>45703</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.15609756097561</v>
+        <v>1.40566037735849</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.140138408304498</v>
+        <v>0.148296593186373</v>
       </c>
       <c r="D8" t="n">
-        <v>0.228668941979522</v>
+        <v>0.218579234972678</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0580240223968211</v>
+        <v>0.0870905022194504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45633</v>
+        <v>45710</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.163430420711974</v>
+        <v>2.35459662288931</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.201907790143084</v>
+        <v>0.265503875968992</v>
       </c>
       <c r="D9" t="n">
-        <v>0.225589225589226</v>
+        <v>0.315217391304348</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0476354404234262</v>
+        <v>0.118129644617762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45640</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.158238172920065</v>
+        <v>3.80254777070064</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.214397496087637</v>
+        <v>0.328330206378987</v>
       </c>
       <c r="D10" t="n">
-        <v>0.195439739413681</v>
+        <v>0.464788732394366</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0379757117907478</v>
+        <v>0.215307393289806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45647</v>
+        <v>45724</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.141666666666667</v>
+        <v>5.11751662971175</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.204180064308682</v>
+        <v>0.497247706422018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.188925081433225</v>
+        <v>0.579545454545455</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0119057099625707</v>
+        <v>0.300860372699564</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45654</v>
+        <v>45731</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0666666666666667</v>
+        <v>6.05080831408776</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.188356164383562</v>
+        <v>0.767754318618042</v>
       </c>
       <c r="D12" t="n">
-        <v>0.186885245901639</v>
+        <v>0.67621776504298</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.014397496087637</v>
+        <v>0.369804885786802</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45661</v>
+        <v>45738</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.104712041884817</v>
+        <v>6.48470588235294</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0557692307692308</v>
+        <v>0.808</v>
       </c>
       <c r="D13" t="n">
-        <v>0.221122112211221</v>
+        <v>0.720116618075802</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00149689107238815</v>
+        <v>0.405061723297965</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45668</v>
+        <v>45745</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0670194003527337</v>
+        <v>6.28791208791209</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0101214574898786</v>
+        <v>0.846311475409836</v>
       </c>
       <c r="D14" t="n">
-        <v>0.241830065359477</v>
+        <v>0.69208211143695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0183785836339472</v>
+        <v>0.370813701770024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45675</v>
+        <v>45752</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.107615894039735</v>
+        <v>6.19057815845824</v>
       </c>
       <c r="C15" t="n">
-        <v>0.090717299578059</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.216981132075472</v>
+        <v>0.664688427299703</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.00513960778595901</v>
+        <v>0.335782577903683</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0329861111111112</v>
+        <v>6.41630901287554</v>
       </c>
       <c r="C16" t="n">
-        <v>0.225382932166302</v>
+        <v>0.568228105906314</v>
       </c>
       <c r="D16" t="n">
-        <v>0.170149253731343</v>
+        <v>0.674772036474164</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0208198489751887</v>
+        <v>0.311123348017621</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45766</v>
       </c>
       <c r="B17" t="n">
-        <v>0.227826086956522</v>
+        <v>6.54885654885655</v>
       </c>
       <c r="C17" t="n">
-        <v>0.260485651214128</v>
+        <v>0.441233140655106</v>
       </c>
       <c r="D17" t="n">
-        <v>0.145714285714286</v>
+        <v>0.727554179566563</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0257006836811398</v>
+        <v>0.316412778759372</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45696</v>
+        <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.608084358523726</v>
+        <v>7.8466819221968</v>
       </c>
       <c r="C18" t="n">
-        <v>0.24507658643326</v>
+        <v>0.446183953033268</v>
       </c>
       <c r="D18" t="n">
-        <v>0.176470588235294</v>
+        <v>0.761609907120743</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0301982316029663</v>
+        <v>0.336623840468277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45703</v>
+        <v>45780</v>
       </c>
       <c r="B19" t="n">
-        <v>1.40566037735849</v>
+        <v>8.28310502283105</v>
       </c>
       <c r="C19" t="n">
-        <v>0.148296593186373</v>
+        <v>0.482490272373541</v>
       </c>
       <c r="D19" t="n">
-        <v>0.218579234972678</v>
+        <v>0.803125</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0870905022194504</v>
+        <v>0.345377637345836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45710</v>
+        <v>45787</v>
       </c>
       <c r="B20" t="n">
-        <v>2.35459662288931</v>
+        <v>8.08102345415778</v>
       </c>
       <c r="C20" t="n">
-        <v>0.265503875968992</v>
+        <v>0.550495049504951</v>
       </c>
       <c r="D20" t="n">
-        <v>0.315217391304348</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E20" t="n">
-        <v>0.118129644617762</v>
+        <v>0.37377135348226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45717</v>
+        <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>3.80254777070064</v>
+        <v>8.72767857142857</v>
       </c>
       <c r="C21" t="n">
-        <v>0.328330206378987</v>
+        <v>0.765913757700205</v>
       </c>
       <c r="D21" t="n">
-        <v>0.464788732394366</v>
+        <v>0.989966555183946</v>
       </c>
       <c r="E21" t="n">
-        <v>0.215307393289806</v>
+        <v>0.401973931234243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45724</v>
+        <v>45801</v>
       </c>
       <c r="B22" t="n">
-        <v>5.11751662971175</v>
+        <v>8.27467811158798</v>
       </c>
       <c r="C22" t="n">
-        <v>0.497247706422018</v>
+        <v>0.913131313131313</v>
       </c>
       <c r="D22" t="n">
-        <v>0.579545454545455</v>
+        <v>1.0551724137931</v>
       </c>
       <c r="E22" t="n">
-        <v>0.300860372699564</v>
+        <v>0.416301969365427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45808</v>
       </c>
       <c r="B23" t="n">
-        <v>6.05080831408776</v>
+        <v>8.10084033613445</v>
       </c>
       <c r="C23" t="n">
-        <v>0.767754318618042</v>
+        <v>1.1377245508982</v>
       </c>
       <c r="D23" t="n">
-        <v>0.67621776504298</v>
+        <v>1.12323943661972</v>
       </c>
       <c r="E23" t="n">
-        <v>0.369804885786802</v>
+        <v>0.457501237828024</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45815</v>
       </c>
       <c r="B24" t="n">
-        <v>6.48470588235294</v>
+        <v>8.80045351473923</v>
       </c>
       <c r="C24" t="n">
-        <v>0.808</v>
+        <v>1.25988700564972</v>
       </c>
       <c r="D24" t="n">
-        <v>0.720116618075802</v>
+        <v>1.08680555555556</v>
       </c>
       <c r="E24" t="n">
-        <v>0.405061723297965</v>
+        <v>0.472581706514587</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45745</v>
+        <v>45822</v>
       </c>
       <c r="B25" t="n">
-        <v>6.28791208791209</v>
+        <v>8.76523702031603</v>
       </c>
       <c r="C25" t="n">
-        <v>0.846311475409836</v>
+        <v>1.29779411764706</v>
       </c>
       <c r="D25" t="n">
-        <v>0.69208211143695</v>
+        <v>1.08219178082192</v>
       </c>
       <c r="E25" t="n">
-        <v>0.370813701770024</v>
+        <v>0.500330469266358</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45752</v>
+        <v>45829</v>
       </c>
       <c r="B26" t="n">
-        <v>6.19057815845824</v>
+        <v>9.38663484486874</v>
       </c>
       <c r="C26" t="n">
-        <v>0.729166666666667</v>
+        <v>1.4462962962963</v>
       </c>
       <c r="D26" t="n">
-        <v>0.664688427299703</v>
+        <v>1.05333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>0.335782577903683</v>
+        <v>0.531999120299098</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45759</v>
+        <v>45836</v>
       </c>
       <c r="B27" t="n">
-        <v>6.41630901287554</v>
+        <v>10.1326530612245</v>
       </c>
       <c r="C27" t="n">
-        <v>0.568228105906314</v>
+        <v>1.56015037593985</v>
       </c>
       <c r="D27" t="n">
-        <v>0.674772036474164</v>
+        <v>1.02295081967213</v>
       </c>
       <c r="E27" t="n">
-        <v>0.311123348017621</v>
+        <v>0.532187895809241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45766</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="n">
-        <v>6.54885654885655</v>
+        <v>10.474358974359</v>
       </c>
       <c r="C28" t="n">
-        <v>0.441233140655106</v>
+        <v>1.68910891089109</v>
       </c>
       <c r="D28" t="n">
-        <v>0.727554179566563</v>
+        <v>0.993610223642172</v>
       </c>
       <c r="E28" t="n">
-        <v>0.316412778759372</v>
+        <v>0.545613364633946</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45773</v>
+        <v>45850</v>
       </c>
       <c r="B29" t="n">
-        <v>7.8466819221968</v>
+        <v>10.1598062953995</v>
       </c>
       <c r="C29" t="n">
-        <v>0.446183953033268</v>
+        <v>1.78313253012048</v>
       </c>
       <c r="D29" t="n">
-        <v>0.761609907120743</v>
+        <v>0.981191222570533</v>
       </c>
       <c r="E29" t="n">
-        <v>0.336623840468277</v>
+        <v>0.554571630358016</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
+        <v>45857</v>
       </c>
       <c r="B30" t="n">
-        <v>8.28310502283105</v>
+        <v>10.5139534883721</v>
       </c>
       <c r="C30" t="n">
-        <v>0.482490272373541</v>
+        <v>1.70695970695971</v>
       </c>
       <c r="D30" t="n">
-        <v>0.803125</v>
+        <v>0.934131736526946</v>
       </c>
       <c r="E30" t="n">
-        <v>0.345377637345836</v>
+        <v>0.574035537057788</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45787</v>
+        <v>45864</v>
       </c>
       <c r="B31" t="n">
-        <v>8.08102345415778</v>
+        <v>11.2735632183908</v>
       </c>
       <c r="C31" t="n">
-        <v>0.550495049504951</v>
+        <v>2.04918032786885</v>
       </c>
       <c r="D31" t="n">
-        <v>0.919354838709677</v>
+        <v>0.88268156424581</v>
       </c>
       <c r="E31" t="n">
-        <v>0.37377135348226</v>
+        <v>0.614290979937865</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45794</v>
+        <v>45871</v>
       </c>
       <c r="B32" t="n">
-        <v>8.72767857142857</v>
+        <v>11.4056399132321</v>
       </c>
       <c r="C32" t="n">
-        <v>0.765913757700205</v>
+        <v>2.67884615384615</v>
       </c>
       <c r="D32" t="n">
-        <v>0.989966555183946</v>
+        <v>0.86096256684492</v>
       </c>
       <c r="E32" t="n">
-        <v>0.401973931234243</v>
+        <v>0.685813148788927</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45801</v>
+        <v>45878</v>
       </c>
       <c r="B33" t="n">
-        <v>8.27467811158798</v>
+        <v>11.3678861788618</v>
       </c>
       <c r="C33" t="n">
-        <v>0.913131313131313</v>
+        <v>3.29306930693069</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0551724137931</v>
+        <v>0.850129198966408</v>
       </c>
       <c r="E33" t="n">
-        <v>0.416301969365427</v>
+        <v>0.744069513300283</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45808</v>
+        <v>45885</v>
       </c>
       <c r="B34" t="n">
-        <v>8.10084033613445</v>
+        <v>10.1708185053381</v>
       </c>
       <c r="C34" t="n">
-        <v>1.1377245508982</v>
+        <v>4.50462962962963</v>
       </c>
       <c r="D34" t="n">
-        <v>1.12323943661972</v>
+        <v>0.921465968586388</v>
       </c>
       <c r="E34" t="n">
-        <v>0.457501237828024</v>
+        <v>0.804043715846995</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45815</v>
+        <v>45892</v>
       </c>
       <c r="B35" t="n">
-        <v>8.80045351473923</v>
+        <v>10.0591304347826</v>
       </c>
       <c r="C35" t="n">
-        <v>1.25988700564972</v>
+        <v>4.91304347826087</v>
       </c>
       <c r="D35" t="n">
-        <v>1.08680555555556</v>
+        <v>1.02732240437158</v>
       </c>
       <c r="E35" t="n">
-        <v>0.472581706514587</v>
+        <v>0.87298707189839</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45822</v>
+        <v>45899</v>
       </c>
       <c r="B36" t="n">
-        <v>8.76523702031603</v>
+        <v>10.1368421052632</v>
       </c>
       <c r="C36" t="n">
-        <v>1.29779411764706</v>
+        <v>5.20689655172414</v>
       </c>
       <c r="D36" t="n">
-        <v>1.08219178082192</v>
+        <v>1.09831460674157</v>
       </c>
       <c r="E36" t="n">
-        <v>0.500330469266358</v>
+        <v>0.922981805334746</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45829</v>
+        <v>45906</v>
       </c>
       <c r="B37" t="n">
-        <v>9.38663484486874</v>
+        <v>10.4680073126143</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4462962962963</v>
+        <v>5.42647058823529</v>
       </c>
       <c r="D37" t="n">
-        <v>1.05333333333333</v>
+        <v>1.16857142857143</v>
       </c>
       <c r="E37" t="n">
-        <v>0.531999120299098</v>
+        <v>0.992122592159518</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45836</v>
+        <v>45913</v>
       </c>
       <c r="B38" t="n">
-        <v>10.1326530612245</v>
+        <v>11.8780991735537</v>
       </c>
       <c r="C38" t="n">
-        <v>1.56015037593985</v>
+        <v>5.36533957845433</v>
       </c>
       <c r="D38" t="n">
-        <v>1.02295081967213</v>
+        <v>1.18181818181818</v>
       </c>
       <c r="E38" t="n">
-        <v>0.532187895809241</v>
+        <v>1.03644461171748</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45843</v>
+        <v>45920</v>
       </c>
       <c r="B39" t="n">
-        <v>10.474358974359</v>
+        <v>11.0818713450292</v>
       </c>
       <c r="C39" t="n">
-        <v>1.68910891089109</v>
+        <v>5.86018957345972</v>
       </c>
       <c r="D39" t="n">
-        <v>0.993610223642172</v>
+        <v>1.13186813186813</v>
       </c>
       <c r="E39" t="n">
-        <v>0.545613364633946</v>
+        <v>1.07317536746072</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45850</v>
+        <v>45927</v>
       </c>
       <c r="B40" t="n">
-        <v>10.1598062953995</v>
+        <v>11.0773694390716</v>
       </c>
       <c r="C40" t="n">
-        <v>1.78313253012048</v>
+        <v>6.11954022988506</v>
       </c>
       <c r="D40" t="n">
-        <v>0.981191222570533</v>
+        <v>1.09090909090909</v>
       </c>
       <c r="E40" t="n">
-        <v>0.554571630358016</v>
+        <v>1.11449467246706</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45857</v>
+        <v>45934</v>
       </c>
       <c r="B41" t="n">
-        <v>10.5139534883721</v>
+        <v>10.8235294117647</v>
       </c>
       <c r="C41" t="n">
-        <v>1.70695970695971</v>
+        <v>6.7780269058296</v>
       </c>
       <c r="D41" t="n">
-        <v>0.934131736526946</v>
+        <v>0.997422680412371</v>
       </c>
       <c r="E41" t="n">
-        <v>0.574035537057788</v>
+        <v>1.2409073628184</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45864</v>
+        <v>45941</v>
       </c>
       <c r="B42" t="n">
-        <v>11.2735632183908</v>
+        <v>11.3193430656934</v>
       </c>
       <c r="C42" t="n">
-        <v>2.04918032786885</v>
+        <v>9.54054054054054</v>
       </c>
       <c r="D42" t="n">
-        <v>0.88268156424581</v>
+        <v>1.13098236775819</v>
       </c>
       <c r="E42" t="n">
-        <v>0.614290979937865</v>
+        <v>1.65283091048202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45871</v>
+        <v>45948</v>
       </c>
       <c r="B43" t="n">
-        <v>11.4056399132321</v>
+        <v>13.344894026975</v>
       </c>
       <c r="C43" t="n">
-        <v>2.67884615384615</v>
+        <v>13.5646551724138</v>
       </c>
       <c r="D43" t="n">
-        <v>0.86096256684492</v>
+        <v>1.72750642673522</v>
       </c>
       <c r="E43" t="n">
-        <v>0.685813148788927</v>
+        <v>2.59054114347632</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45878</v>
+        <v>45955</v>
       </c>
       <c r="B44" t="n">
-        <v>11.3678861788618</v>
+        <v>14.7901701323251</v>
       </c>
       <c r="C44" t="n">
-        <v>3.29306930693069</v>
+        <v>18.91875</v>
       </c>
       <c r="D44" t="n">
-        <v>0.850129198966408</v>
+        <v>2.61930294906166</v>
       </c>
       <c r="E44" t="n">
-        <v>0.744069513300283</v>
+        <v>3.89222791453205</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45885</v>
+        <v>45962</v>
       </c>
       <c r="B45" t="n">
-        <v>10.1708185053381</v>
+        <v>17.7967806841046</v>
       </c>
       <c r="C45" t="n">
-        <v>4.50462962962963</v>
+        <v>26.3354838709677</v>
       </c>
       <c r="D45" t="n">
-        <v>0.921465968586388</v>
+        <v>3.63888888888889</v>
       </c>
       <c r="E45" t="n">
-        <v>0.804043715846995</v>
+        <v>5.44083889189352</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45892</v>
+        <v>45969</v>
       </c>
       <c r="B46" t="n">
-        <v>10.0591304347826</v>
+        <v>19.1013916500994</v>
       </c>
       <c r="C46" t="n">
-        <v>4.91304347826087</v>
+        <v>30.2915766738661</v>
       </c>
       <c r="D46" t="n">
-        <v>1.02732240437158</v>
+        <v>4.27142857142857</v>
       </c>
       <c r="E46" t="n">
-        <v>0.87298707189839</v>
+        <v>6.18956452165962</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45899</v>
+        <v>45976</v>
       </c>
       <c r="B47" t="n">
-        <v>10.1368421052632</v>
+        <v>17.756862745098</v>
       </c>
       <c r="C47" t="n">
-        <v>5.20689655172414</v>
+        <v>26.2012578616352</v>
       </c>
       <c r="D47" t="n">
-        <v>1.09831460674157</v>
+        <v>3.97701149425287</v>
       </c>
       <c r="E47" t="n">
-        <v>0.922981805334746</v>
+        <v>5.51793540009739</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45906</v>
+        <v>45983</v>
       </c>
       <c r="B48" t="n">
-        <v>10.4680073126143</v>
+        <v>15.7677165354331</v>
       </c>
       <c r="C48" t="n">
-        <v>5.42647058823529</v>
+        <v>20.8428874734607</v>
       </c>
       <c r="D48" t="n">
-        <v>1.16857142857143</v>
+        <v>3.20113314447592</v>
       </c>
       <c r="E48" t="n">
-        <v>0.992122592159518</v>
+        <v>4.30862408116782</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45913</v>
+        <v>45990</v>
       </c>
       <c r="B49" t="n">
-        <v>11.8780991735537</v>
+        <v>13.2061657032755</v>
       </c>
       <c r="C49" t="n">
-        <v>5.36533957845433</v>
+        <v>13.092555331992</v>
       </c>
       <c r="D49" t="n">
-        <v>1.18181818181818</v>
+        <v>2.40277777777778</v>
       </c>
       <c r="E49" t="n">
-        <v>1.03644461171748</v>
+        <v>2.72733809500983</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
       <c r="B50" t="n">
-        <v>11.0818713450292</v>
+        <v>11.2030947775629</v>
       </c>
       <c r="C50" t="n">
-        <v>5.86018957345972</v>
+        <v>7.28286852589641</v>
       </c>
       <c r="D50" t="n">
-        <v>1.13186813186813</v>
+        <v>1.87362637362637</v>
       </c>
       <c r="E50" t="n">
-        <v>1.0727952356817</v>
+        <v>1.60066871498283</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45927</v>
+        <v>46004</v>
       </c>
       <c r="B51" t="n">
-        <v>11.0773694390716</v>
+        <v>10.8740310077519</v>
       </c>
       <c r="C51" t="n">
-        <v>6.11954022988506</v>
+        <v>6.2808764940239</v>
       </c>
       <c r="D51" t="n">
-        <v>1.09090909090909</v>
+        <v>1.73841961852861</v>
       </c>
       <c r="E51" t="n">
-        <v>1.11399029065002</v>
+        <v>1.24107067466014</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45934</v>
+        <v>46011</v>
       </c>
       <c r="B52" t="n">
-        <v>10.8235294117647</v>
+        <v>10.7864077669903</v>
       </c>
       <c r="C52" t="n">
-        <v>6.7780269058296</v>
+        <v>6.07676767676768</v>
       </c>
       <c r="D52" t="n">
-        <v>0.997422680412371</v>
+        <v>1.78082191780822</v>
       </c>
       <c r="E52" t="n">
-        <v>1.24014700291471</v>
+        <v>1.1148095909732</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45941</v>
+        <v>46018</v>
       </c>
       <c r="B53" t="n">
-        <v>11.3193430656934</v>
+        <v>10.7619047619048</v>
       </c>
       <c r="C53" t="n">
-        <v>9.54054054054054</v>
+        <v>6.07594936708861</v>
       </c>
       <c r="D53" t="n">
-        <v>1.13098236775819</v>
+        <v>1.82596685082873</v>
       </c>
       <c r="E53" t="n">
-        <v>1.6523208365213</v>
+        <v>1.03258971101937</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45948</v>
+        <v>46025</v>
       </c>
       <c r="B54" t="n">
-        <v>13.344894026975</v>
+        <v>10.3684210526316</v>
       </c>
       <c r="C54" t="n">
-        <v>13.5646551724138</v>
+        <v>5.71690427698574</v>
       </c>
       <c r="D54" t="n">
-        <v>1.72750642673522</v>
+        <v>1.76486486486486</v>
       </c>
       <c r="E54" t="n">
-        <v>2.59003123207343</v>
+        <v>0.971747068998655</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45955</v>
+        <v>46032</v>
       </c>
       <c r="B55" t="n">
-        <v>14.7901701323251</v>
+        <v>9.7296786389414</v>
       </c>
       <c r="C55" t="n">
-        <v>18.91875</v>
+        <v>5.70347648261759</v>
       </c>
       <c r="D55" t="n">
-        <v>2.61930294906166</v>
+        <v>1.74210526315789</v>
       </c>
       <c r="E55" t="n">
-        <v>3.89172810196176</v>
+        <v>0.911667101681644</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45962</v>
+        <v>46039</v>
       </c>
       <c r="B56" t="n">
-        <v>17.7967806841046</v>
+        <v>9.31725417439703</v>
       </c>
       <c r="C56" t="n">
-        <v>26.3354838709677</v>
+        <v>5.39845261121857</v>
       </c>
       <c r="D56" t="n">
-        <v>3.63888888888889</v>
+        <v>1.81395348837209</v>
       </c>
       <c r="E56" t="n">
-        <v>5.44023796646836</v>
+        <v>0.894441798263291</v>
       </c>
     </row>
   </sheetData>
